--- a/fruit_data.xlsx
+++ b/fruit_data.xlsx
@@ -24675,10 +24675,10 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>0</v>
+        <v>111.76855</v>
       </c>
       <c r="G240" t="n">
-        <v>0</v>
+        <v>30.42612</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -24713,10 +24713,10 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>0</v>
+        <v>111.20105</v>
       </c>
       <c r="G241" t="n">
-        <v>0</v>
+        <v>30.47052</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -24756,10 +24756,10 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>0</v>
+        <v>113.91667</v>
       </c>
       <c r="G242" t="n">
-        <v>0</v>
+        <v>30.91667</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -24799,10 +24799,10 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>0</v>
+        <v>112.42468</v>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
+        <v>30.04174</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -24837,10 +24837,10 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>0</v>
+        <v>112.23242</v>
       </c>
       <c r="G244" t="n">
-        <v>0</v>
+        <v>30.05902</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -24875,10 +24875,10 @@
         </is>
       </c>
       <c r="F245" t="n">
-        <v>0</v>
+        <v>113.90039</v>
       </c>
       <c r="G245" t="n">
-        <v>0</v>
+        <v>29.72454</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -24913,10 +24913,10 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>0</v>
+        <v>109.7182</v>
       </c>
       <c r="G246" t="n">
-        <v>0</v>
+        <v>30.60173</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -24956,10 +24956,10 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>0</v>
+        <v>109.7182</v>
       </c>
       <c r="G247" t="n">
-        <v>0</v>
+        <v>30.60173</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -24994,10 +24994,10 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>0</v>
+        <v>111.45025</v>
       </c>
       <c r="G248" t="n">
-        <v>0</v>
+        <v>30.37807</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -25032,10 +25032,10 @@
         </is>
       </c>
       <c r="F249" t="n">
-        <v>0</v>
+        <v>115.39056</v>
       </c>
       <c r="G249" t="n">
-        <v>0</v>
+        <v>30.785</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -25070,10 +25070,10 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>0</v>
+        <v>110.73333</v>
       </c>
       <c r="G250" t="n">
-        <v>0</v>
+        <v>32.05</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -25108,10 +25108,10 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>0</v>
+        <v>111.66944</v>
       </c>
       <c r="G251" t="n">
-        <v>0</v>
+        <v>32.385</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -25146,10 +25146,10 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>0</v>
+        <v>111.66944</v>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>32.385</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -25184,10 +25184,10 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>0</v>
+        <v>110.74951</v>
       </c>
       <c r="G253" t="n">
-        <v>0</v>
+        <v>31.34686</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -25222,10 +25222,10 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="G254" t="n">
-        <v>0</v>
+        <v>40.53333</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -25260,10 +25260,10 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>0</v>
+        <v>119.33333</v>
       </c>
       <c r="G255" t="n">
-        <v>0</v>
+        <v>41.6</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -25293,10 +25293,10 @@
         </is>
       </c>
       <c r="F256" t="n">
-        <v>0</v>
+        <v>106.8</v>
       </c>
       <c r="G256" t="n">
-        <v>0</v>
+        <v>39.65</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -25331,10 +25331,10 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>0</v>
+        <v>129.5</v>
       </c>
       <c r="G257" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -25364,10 +25364,10 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>0</v>
+        <v>126.41667</v>
       </c>
       <c r="G258" t="n">
-        <v>0</v>
+        <v>41.93333</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -25402,10 +25402,10 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>0</v>
+        <v>125.74475</v>
       </c>
       <c r="G259" t="n">
-        <v>0</v>
+        <v>42.28468</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -25440,10 +25440,10 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>0</v>
+        <v>125.75936</v>
       </c>
       <c r="G260" t="n">
-        <v>0</v>
+        <v>41.67928</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -25473,10 +25473,10 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>0</v>
+        <v>124.11667</v>
       </c>
       <c r="G261" t="n">
-        <v>0</v>
+        <v>50.41667</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -25511,10 +25511,10 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>0</v>
+        <v>127.96194</v>
       </c>
       <c r="G262" t="n">
-        <v>0</v>
+        <v>45.21167</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -25549,10 +25549,10 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>0</v>
+        <v>130.56806</v>
       </c>
       <c r="G263" t="n">
-        <v>0</v>
+        <v>45.75056</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -25587,10 +25587,10 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>0</v>
+        <v>130.51667</v>
       </c>
       <c r="G264" t="n">
-        <v>0</v>
+        <v>44.91667</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -25620,10 +25620,10 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>0</v>
+        <v>128.84056</v>
       </c>
       <c r="G265" t="n">
-        <v>0</v>
+        <v>47.7275</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -25653,10 +25653,10 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>0</v>
+        <v>97.36667</v>
       </c>
       <c r="G266" t="n">
-        <v>0</v>
+        <v>37.36667</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -25691,10 +25691,10 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>0</v>
+        <v>102.4</v>
       </c>
       <c r="G267" t="n">
-        <v>0</v>
+        <v>36.48333</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -25729,10 +25729,10 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>0</v>
+        <v>102.4</v>
       </c>
       <c r="G268" t="n">
-        <v>0</v>
+        <v>36.48333</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -25767,10 +25767,10 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>0</v>
+        <v>94.36667</v>
       </c>
       <c r="G269" t="n">
-        <v>0</v>
+        <v>29.63333</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -25805,10 +25805,10 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="G270" t="n">
-        <v>0</v>
+        <v>29.68333</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -25843,10 +25843,10 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>0</v>
+        <v>93.06667</v>
       </c>
       <c r="G271" t="n">
-        <v>0</v>
+        <v>29.05</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -25886,10 +25886,10 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>91.13333</v>
       </c>
       <c r="G272" t="n">
-        <v>0</v>
+        <v>29.65</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -25924,10 +25924,10 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>111.47917</v>
       </c>
       <c r="G273" t="n">
-        <v>0</v>
+        <v>33.29778</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -25962,10 +25962,10 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>116.46</v>
       </c>
       <c r="G274" t="n">
-        <v>0</v>
+        <v>36.14</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -26000,10 +26000,10 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>117.12</v>
       </c>
       <c r="G275" t="n">
-        <v>0</v>
+        <v>37.44</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -26038,10 +26038,10 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>102.25</v>
       </c>
       <c r="G276" t="n">
-        <v>0</v>
+        <v>26.65</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -26076,10 +26076,10 @@
         </is>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>104.66667</v>
       </c>
       <c r="G277" t="n">
-        <v>0</v>
+        <v>29.51667</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -26114,10 +26114,10 @@
         </is>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>113.76667</v>
       </c>
       <c r="G278" t="n">
-        <v>0</v>
+        <v>26.48333</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -26152,10 +26152,10 @@
         </is>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>110.93333</v>
       </c>
       <c r="G279" t="n">
-        <v>0</v>
+        <v>36.68333</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -26185,10 +26185,10 @@
         </is>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>108.63333</v>
       </c>
       <c r="G280" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -26223,10 +26223,10 @@
         </is>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>106.33333</v>
       </c>
       <c r="G281" t="n">
-        <v>0</v>
+        <v>38.1</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -26261,10 +26261,10 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>0</v>
+        <v>126.18829</v>
       </c>
       <c r="G282" t="n">
-        <v>0</v>
+        <v>41.12268</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -26299,10 +26299,10 @@
         </is>
       </c>
       <c r="F283" t="n">
-        <v>0</v>
+        <v>124.15</v>
       </c>
       <c r="G283" t="n">
-        <v>0</v>
+        <v>39.88333</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -26332,10 +26332,10 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>0</v>
+        <v>117.01667</v>
       </c>
       <c r="G284" t="n">
-        <v>0</v>
+        <v>25.08333</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -26370,10 +26370,10 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>0</v>
+        <v>118.46667</v>
       </c>
       <c r="G285" t="n">
-        <v>0</v>
+        <v>36.68333</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -26403,10 +26403,10 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>0</v>
+        <v>122.11667</v>
       </c>
       <c r="G286" t="n">
-        <v>0</v>
+        <v>37.51667</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>

--- a/fruit_data.xlsx
+++ b/fruit_data.xlsx
@@ -589,6 +589,7 @@
       <c r="K2" t="n">
         <v>2</v>
       </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>国家地理标志产品，中国特色农产品优势区。果大形正、橙红鲜艳，肉质脆嫩化渣，风味浓甜芳香，年产超百万吨。</t>
@@ -643,6 +644,7 @@
       <c r="K3" t="n">
         <v>3</v>
       </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>中国特色农产品优势区，中欧地理标志互认。生长于三峡河谷地带，果皮薄、果肉细嫩化渣、汁多味甜。</t>
@@ -697,6 +699,7 @@
       <c r="K4" t="n">
         <v>3</v>
       </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>国家地理标志产品，一年四季有鲜橙。种植于长江三峡河谷，皮薄色鲜、肉脆汁多、香味浓郁。</t>
@@ -751,6 +754,7 @@
       <c r="K5" t="n">
         <v>1</v>
       </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>首批中国特色农产品优势区，中欧地理标志互认。中国驰名中外的优良柑橘品种，果小皮薄、少核汁多、甜酸适口。</t>
@@ -805,6 +809,7 @@
       <c r="K6" t="n">
         <v>11</v>
       </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>中国特色农产品优势区，中欧地理标志互认。果形扁圆、皮薄易剥、肉质细嫩、酸甜适口。</t>
@@ -859,6 +864,7 @@
       <c r="K7" t="n">
         <v>11</v>
       </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>第四批中国特色农产品优势区。丹江口库区优质气候，果面光滑、色泽橙红、风味浓郁。</t>
@@ -913,6 +919,7 @@
       <c r="K8" t="n">
         <v>3</v>
       </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>第四批中国特色农产品优势区。中国沃柑之乡，果肉橙红、细嫩化渣、甜度高，晚熟柑橘代表。</t>
@@ -967,6 +974,7 @@
       <c r="K9" t="n">
         <v>2</v>
       </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>第四批中国特色农产品优势区。果小皮薄、清甜化渣，春节前后上市的热销柑橘。</t>
@@ -1021,6 +1029,7 @@
       <c r="K10" t="n">
         <v>2</v>
       </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>中国特色农产品优势区，中欧地理标志互认。果皮金黄、油胞细密、皮脆肉甜，可连皮食用。</t>
@@ -1075,6 +1084,7 @@
       <c r="K11" t="n">
         <v>12</v>
       </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>中国特色农产品优势区，中欧地理标志互认。果大皮薄、瓤肉无籽、汁多味甜，中国柚类第一品牌。</t>
@@ -1129,6 +1139,7 @@
       <c r="K12" t="n">
         <v>1</v>
       </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>第四批中国特色农产品优势区。井冈山革命老区特色产业，果肉脆嫩、甜酸适口、耐贮藏。</t>
@@ -1183,6 +1194,7 @@
       <c r="K13" t="n">
         <v>1</v>
       </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>第二批中国特色农产品优势区。果形端正、皮薄光滑、果肉粉红、酸甜适度。</t>
@@ -1237,6 +1249,7 @@
       <c r="K14" t="n">
         <v>1</v>
       </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>中欧地理标志互认。沙田柚优良品种，果大形正、皮薄肉厚、清甜爽口。</t>
@@ -1291,6 +1304,7 @@
       <c r="K15" t="n">
         <v>1</v>
       </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>中国特色农产品优势区。历史上列为皇家贡品，果形美观、皮薄易剥、肉脆化渣。</t>
@@ -1345,6 +1359,7 @@
       <c r="K16" t="n">
         <v>1</v>
       </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>第四批中国特色农产品优势区。袁隆平院士推荐，肉质脆嫩、味甜如冰糖。</t>
@@ -1399,6 +1414,7 @@
       <c r="K17" t="n">
         <v>1</v>
       </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>国家地理标志产品。果形端正、色泽鲜艳、皮薄少核、汁多味甜。</t>
@@ -1453,6 +1469,7 @@
       <c r="K18" t="n">
         <v>3</v>
       </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>第二批中国特色农产品优势区。果肉呈玫瑰红或紫红色，富含花青素，酸甜适口。</t>
@@ -1507,6 +1524,7 @@
       <c r="K19" t="n">
         <v>11</v>
       </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>中欧地理标志互认，中国柠檬之都。全国80%以上柠檬产自安岳，果皮金黄、酸度适中、香气浓郁。</t>
@@ -1561,6 +1579,7 @@
       <c r="K20" t="n">
         <v>2</v>
       </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>第二批中国特色农产品优势区。干热河谷气候，早熟优势明显，果形美观、酸甜适口。</t>
@@ -1615,6 +1634,7 @@
       <c r="K21" t="n">
         <v>3</v>
       </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>第二批中国特色农产品优势区。北纬30度柑橘黄金带，晚熟柑橘错峰上市，果肉细嫩、甜度高。</t>
@@ -1669,6 +1689,7 @@
       <c r="K22" t="n">
         <v>2</v>
       </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>首批中国特色农产品优势区，中欧地理标志互认。色泽艳红、果形端正、肉质细脆、酸甜适口，中国苹果第一县。</t>
@@ -1723,6 +1744,7 @@
       <c r="K23" t="n">
         <v>2</v>
       </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>中欧地理标志互认，中国苹果之都。个大形正、色泽艳红、质脆多汁、酸甜适口，极耐贮藏。</t>
@@ -1777,6 +1799,7 @@
       <c r="K24" t="n">
         <v>12</v>
       </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>第四批中国特色农产品优势区，世界三大苹果品牌之一。与美国蛇果、日本富士齐名，果形端正、色泽浓红、香气浓郁。</t>
@@ -1831,6 +1854,7 @@
       <c r="K25" t="n">
         <v>1</v>
       </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>中欧地理标志互认。天山雪水灌溉，光照充足，果面光滑细腻、色泽光亮、糖度高，冰糖心独特。</t>
@@ -1885,6 +1909,7 @@
       <c r="K26" t="n">
         <v>3</v>
       </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>第二批中国特色农产品优势区，中欧地理标志互认。色泽鲜艳、个大形正、质细汁多、酸甜适度。</t>
@@ -1939,6 +1964,7 @@
       <c r="K27" t="n">
         <v>11</v>
       </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>首批中国特色农产品优势区，中欧地理标志互认。亚洲最佳苹果适生区之一，色艳味浓、耐贮藏。</t>
@@ -1993,6 +2019,7 @@
       <c r="K28" t="n">
         <v>2</v>
       </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>第二批中国特色农产品优势区。沂蒙山区生态优势，果形端正、色泽艳丽、肉质细脆、汁多味甜。</t>
@@ -2047,6 +2074,7 @@
       <c r="K29" t="n">
         <v>1</v>
       </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>第二批中国特色农产品优势区，中欧地理标志互认。黄土高原优生区，色泽浓红、果形端庄、脆甜多汁。</t>
@@ -2101,6 +2129,7 @@
       <c r="K30" t="n">
         <v>1</v>
       </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>第二批中国特色农产品优势区。太行山深处生态种植，果形端正、果面光洁、肉质细脆、酸甜适口。</t>
@@ -2155,6 +2184,7 @@
       <c r="K31" t="n">
         <v>10</v>
       </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>国家地理标志产品。中国南方最大苹果产区，高海拔强日照，早熟优势突出，色泽艳丽、酸甜适口。</t>
@@ -2209,6 +2239,7 @@
       <c r="K32" t="n">
         <v>12</v>
       </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>首批中国特色农产品优势区，中欧地理标志互认。皮薄肉细、汁多味甜、香气浓郁，有梨中皇后美誉。</t>
@@ -2322,6 +2353,7 @@
       <c r="K34" t="n">
         <v>12</v>
       </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>第二批中国特色农产品优势区，中欧地理标志互认。果形端正似鸭头，皮薄肉细、脆嫩多汁、清香爽口。</t>
@@ -2376,6 +2408,7 @@
       <c r="K35" t="n">
         <v>10</v>
       </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>第四批中国特色农产品优势区。果心小、果肉洁白、肉质细腻、松脆多汁，早中熟品种。</t>
@@ -2430,6 +2463,7 @@
       <c r="K36" t="n">
         <v>10</v>
       </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>中国四大名梨之一，国家地理标志产品。果肉细嫩清脆、汁多味甜，明清时期即为贡品。</t>
@@ -2484,6 +2518,7 @@
       <c r="K37" t="n">
         <v>10</v>
       </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>第四批中国特色农产品优势区。果皮金黄、肉质酥脆、汁多味甜，国家地理标志产品。</t>
@@ -2538,6 +2573,7 @@
       <c r="K38" t="n">
         <v>10</v>
       </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>第二批中国特色农产品优势区。果实色泽鲜艳、果肉细腻、汁多味甜，有梨中之王美誉。</t>
@@ -2592,6 +2628,7 @@
       <c r="K39" t="n">
         <v>9</v>
       </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>第二批中国特色农产品优势区，中欧地理标志互认。皮薄肉脆、汁多味甜，含糖量高达24%，中国最甜葡萄。</t>
@@ -2646,6 +2683,7 @@
       <c r="K40" t="n">
         <v>9</v>
       </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>首批中国特色农产品优势区。果穗整齐、果粒均匀、色泽深紫、酸甜适口。</t>
@@ -2700,6 +2738,7 @@
       <c r="K41" t="n">
         <v>9</v>
       </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>第四批中国特色农产品优势区。北纬39度葡萄黄金带，果粒饱满、色泽艳丽、风味浓郁。</t>
@@ -2754,6 +2793,7 @@
       <c r="K42" t="n">
         <v>9</v>
       </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>中欧地理标志互认。果实紫黑、皮薄肉厚、玫瑰香气浓郁，鲜食加工兼优。</t>
@@ -2808,6 +2848,7 @@
       <c r="K43" t="n">
         <v>8</v>
       </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>第四批中国特色农产品优势区。南方葡萄精品产区，果穗大、果粒均匀、色泽紫黑、甜度高。</t>
@@ -2862,6 +2903,7 @@
       <c r="K44" t="n">
         <v>8</v>
       </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>国家地理标志产品。云南高原特色水果，早熟优势明显，果粒饱满、色泽深紫、香气浓郁。</t>
@@ -2916,6 +2958,7 @@
       <c r="K45" t="n">
         <v>11</v>
       </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>中欧地理标志互认，中国猕猴桃之乡。果形端正、果肉翠绿，VC含量极高，酸甜清爽，产量全国第一。</t>
@@ -2970,6 +3013,7 @@
       <c r="K46" t="n">
         <v>11</v>
       </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>中欧地理标志互认。秦岭北麓优越生态，果肉细腻、酸甜适口、耐贮藏。</t>
@@ -3024,6 +3068,7 @@
       <c r="K47" t="n">
         <v>9</v>
       </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>首批中国特色农产品优势区，中欧地理标志互认。果心红色放射状，果肉细嫩、香甜清爽。</t>
@@ -3078,6 +3123,7 @@
       <c r="K48" t="n">
         <v>9</v>
       </c>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>第四批中国特色农产品优势区，中欧地理标志互认。贵州喀斯特高原特色，果心红色、肉质细腻、香甜多汁。</t>
@@ -3132,6 +3178,7 @@
       <c r="K49" t="n">
         <v>10</v>
       </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>中欧地理标志互认。全国品质最优猕猴桃产区之一，果肉翠绿、细嫩多汁、酸甜适口。</t>
@@ -3186,6 +3233,7 @@
       <c r="K50" t="n">
         <v>3</v>
       </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>国家地理标志产品。北纬40度黄金草莓带，果实圆锥形、色泽鲜红、香味浓郁，中国草莓第一县。</t>
@@ -3240,6 +3288,7 @@
       <c r="K51" t="n">
         <v>3</v>
       </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>国家地理标志产品。中国草莓十大主产区之一，果大形正、色泽鲜红、甜酸适口。</t>
@@ -3294,6 +3343,7 @@
       <c r="K52" t="n">
         <v>2</v>
       </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>国家地理标志产品。浙江草莓名镇，果实鲜红、肉质细腻、甜度高、香气浓郁。</t>
@@ -3348,6 +3398,7 @@
       <c r="K53" t="n">
         <v>7</v>
       </c>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>国家地理标志产品。果大核小、色紫黑发亮、甜酸适口，有果中玛瑙之称。</t>
@@ -3402,6 +3453,7 @@
       <c r="K54" t="n">
         <v>7</v>
       </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>国家地理标志产品。浙江杨梅主产区，果色紫红、肉柱丰满、甜酸适口。</t>
@@ -3456,6 +3508,7 @@
       <c r="K55" t="n">
         <v>7</v>
       </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>国家地理标志产品。江南第一杨梅，果大色艳、肉厚汁多、甜酸适度。</t>
@@ -3510,6 +3563,7 @@
       <c r="K56" t="n">
         <v>3</v>
       </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>冬季上市蓝莓代表产区。云南高原冷凉气候，果粉厚、甜度高、风味浓郁，错峰供应全国市场。</t>
@@ -3564,6 +3618,7 @@
       <c r="K57" t="n">
         <v>7</v>
       </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>国家地理标志产品。中国蓝莓之乡，果粒饱满、果粉厚、花青素含量高，有机种植。</t>
@@ -3618,6 +3673,7 @@
       <c r="K58" t="n">
         <v>7</v>
       </c>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
           <t>国家地理标志产品。沿海蓝莓产区，果粒大、甜度高、果实硬度好耐贮运。</t>
@@ -3672,6 +3728,7 @@
       <c r="K59" t="n">
         <v>7</v>
       </c>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>岭南佳果之首。果肉晶莹剔透如凝脂，清甜爽口，挂绿品种举世闻名，国家地理标志产品。</t>
@@ -3726,6 +3783,7 @@
       <c r="K60" t="n">
         <v>6</v>
       </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>中国荔枝之乡，国家地理标志产品。果大肉厚、核小味甜，成熟期比广东早，全国最早上市。</t>
@@ -3780,6 +3838,7 @@
       <c r="K61" t="n">
         <v>7</v>
       </c>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>晚熟荔枝代表，国家地理标志产品。中国最北缘荔枝产区，口感清甜、果大核小、耐贮运。</t>
@@ -3834,6 +3893,7 @@
       <c r="K62" t="n">
         <v>8</v>
       </c>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>国家地理标志产品。世界储良龙眼发源地，果大肉厚、晶莹剔透、清甜爽口。</t>
@@ -3888,6 +3948,7 @@
       <c r="K63" t="n">
         <v>8</v>
       </c>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
           <t>国家地理标志产品。肉厚核小、汁多味甜、肉质脆爽，石硖龙眼中的极品。</t>
@@ -3942,6 +4003,7 @@
       <c r="K64" t="n">
         <v>7</v>
       </c>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
           <t>首批中国特色农产品优势区。中国芒果之乡，南亚热带季风气候，果肉金黄、纤维少、甜度高。</t>
@@ -3996,6 +4058,7 @@
       <c r="K65" t="n">
         <v>9</v>
       </c>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
           <t>国家地理标志产品。纬度最北的热带芒果产区，果肉金黄细腻、纤维极少、甜度高、香气浓郁。</t>
@@ -4050,6 +4113,7 @@
       <c r="K66" t="n">
         <v>4</v>
       </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>国家地理标志产品。中国最早上市芒果产区，1月起可采收，果形美观、肉质细嫩、甜度高。</t>
@@ -4104,6 +4168,7 @@
       <c r="K67" t="n">
         <v>8</v>
       </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>首批中国特色农产品优势区，中欧地理标志互认。中国桃乡，果大色艳、肉质细密、甜而多汁。</t>
@@ -4158,6 +4223,7 @@
       <c r="K68" t="n">
         <v>7</v>
       </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
           <t>国家地理标志产品。中国最好吃的水蜜桃，果大皮薄、柔软多汁、味甜如蜜，可吸食。</t>
@@ -4212,6 +4278,7 @@
       <c r="K69" t="n">
         <v>8</v>
       </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
           <t>国家地理标志产品。浙江名桃，果形美观、肉质细软、汁多味甜、香气浓郁。</t>
@@ -4266,6 +4333,7 @@
       <c r="K70" t="n">
         <v>7</v>
       </c>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
           <t>国家地理标志产品。中国水蜜桃三大基地之一，白里透红、皮薄肉厚、鲜甜多汁。</t>
@@ -4320,6 +4388,7 @@
       <c r="K71" t="n">
         <v>6</v>
       </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>国家地理标志产品。中国大樱桃之乡，个大色艳、肉脆味甜，成熟早于全国多数产区。</t>
@@ -4374,6 +4443,7 @@
       <c r="K72" t="n">
         <v>6</v>
       </c>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>国家地理标志产品。高山峡谷气候，果大色艳、肉厚汁多、酸甜适口。</t>
@@ -4487,6 +4557,7 @@
       <c r="K74" t="n">
         <v>8</v>
       </c>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
           <t>首批中国特色农产品优势区，中欧地理标志互认。瓜肉色如晶玉、甘美肥厚、含糖量高达15%，瓜中之王。</t>
@@ -4541,6 +4612,7 @@
       <c r="K75" t="n">
         <v>9</v>
       </c>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
           <t>国家地理标志产品。南疆特色哈密瓜，肉厚质细、清香甘甜、极耐贮藏。</t>
@@ -4595,6 +4667,7 @@
       <c r="K76" t="n">
         <v>8</v>
       </c>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
           <t>国家地理标志产品。压砂地种植，个大皮厚、耐贮运，沙甜可口，富硒健康。</t>
@@ -4649,6 +4722,7 @@
       <c r="K77" t="n">
         <v>1</v>
       </c>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
           <t>第四批中国特色农产品优势区。中国红江橙发源地，果肉橙红、肉质柔嫩、酸甜适口。</t>
@@ -4703,6 +4777,7 @@
       <c r="K78" t="n">
         <v>10</v>
       </c>
+      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
           <t>国家地理标志产品。中国香蕉之乡，果形美观、皮薄肉滑、香甜可口。</t>
@@ -4757,6 +4832,7 @@
       <c r="K79" t="n">
         <v>3</v>
       </c>
+      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
           <t>海南冬春特色水果。果小形美、色泽鲜红、皮薄肉厚、酸甜可口，冬季供应全国。</t>
@@ -4811,6 +4887,7 @@
       <c r="K80" t="n">
         <v>2</v>
       </c>
+      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
           <t>全国苹果产量最大的县之一。黄土高原优生区，果形端正、色泽艳红、脆甜多汁。</t>
@@ -4865,6 +4942,7 @@
       <c r="K81" t="n">
         <v>10</v>
       </c>
+      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
           <t>国家地理标志产品。中国冬枣之乡，皮薄肉脆、细嫩多汁、甜如冰糖。</t>
@@ -4919,6 +4997,7 @@
       <c r="K82" t="n">
         <v>10</v>
       </c>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
           <t>第二批中国特色农产品优势区。中国冬枣原产地，皮薄肉脆、甘甜清香，VC含量极高。</t>
@@ -4973,6 +5052,7 @@
       <c r="K83" t="n">
         <v>8</v>
       </c>
+      <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
           <t>中国国家地理标志产品，驰名古今，核心产区在开封、商丘、周口。瓜瓤鲜红、汁多味甜，河南西瓜产量全国第一，占全国1/5以上。</t>
@@ -5027,6 +5107,7 @@
       <c r="K84" t="n">
         <v>8</v>
       </c>
+      <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
           <t>国务院首批命名的"中国西瓜之乡"，全国最大县级商品西瓜基地，种植面积约35万亩，总产量120万吨。瓜大皮薄、瓤脆汁甜。</t>
@@ -5081,6 +5162,7 @@
       <c r="K85" t="n">
         <v>7</v>
       </c>
+      <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
           <t>全国最大设施西瓜生产基地，种植面积30万亩，产量100万吨。代表品种"甘美一号"，糖酸比均衡，安全性高。</t>
@@ -5135,6 +5217,7 @@
       <c r="K86" t="n">
         <v>7</v>
       </c>
+      <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
           <t>火山岩土壤孕育的富硒西瓜，硒含量0.021mg/kg，糖度12.8-13.4Brix。麒麟瓜代表产区，早熟上市，5月上旬即可采收。</t>
@@ -5189,6 +5272,7 @@
       <c r="K87" t="n">
         <v>8</v>
       </c>
+      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
           <t>昼夜温差大造就超高糖度，中心糖度达13.6Brix，番茄红素含量全国之最(4.3mg/100g)。单果均重4-6kg。</t>
@@ -5243,6 +5327,7 @@
       <c r="K88" t="n">
         <v>7</v>
       </c>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
           <t>300余年种植史，国家地理标志保护产品。西北重要西瓜产区，品种以西农八号、京欣系列为主，沙瓤多汁。</t>
@@ -5297,6 +5382,7 @@
       <c r="K89" t="n">
         <v>7</v>
       </c>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
           <t>闻名全国的精品西瓜，设施栽培技术领先。代表品种有京欣系列、L600等，皮薄瓤红、甜脆适口。</t>
@@ -5351,6 +5437,7 @@
       <c r="K90" t="n">
         <v>4</v>
       </c>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
           <t>全国最大的菠萝生产基地，产量占全国约38%-40%。种植面积约35万亩，年产量约70-80万吨。主栽品种"巴厘"，果大汁多、肉脆味甜。</t>
@@ -5405,6 +5492,7 @@
       <c r="K91" t="n">
         <v>10</v>
       </c>
+      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
           <t>金钻凤梨(MD-2)代表产区，果肉金黄色、细腻无纤维、清甜爽口，含糖量高达16.8%，几乎无需泡盐水即可食用。全年可多批次采收。</t>
@@ -5459,6 +5547,7 @@
       <c r="K92" t="n">
         <v>8</v>
       </c>
+      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
           <t>香水菠萝含天然酯类芳香物质，开果即香溢满室。可溶性固形物含量高达17.1%，果眼浅平、削皮易净，品质居全国前列。</t>
@@ -5513,6 +5602,7 @@
       <c r="K93" t="n">
         <v>6</v>
       </c>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
           <t>国家地理标志认证，种植面积达5万亩，年产超6万吨。黄土高原气候，干燥光照强，甜度可达20%以上，风味浓郁。</t>
@@ -5567,6 +5657,7 @@
       <c r="K94" t="n">
         <v>6</v>
       </c>
+      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
           <t>高海拔低纬度产区，全国最早熟樱桃产区之一(4月底即可上市)。糖度15%-21%，果面光洁、果香浓郁。</t>
@@ -5621,6 +5712,7 @@
       <c r="K95" t="n">
         <v>6</v>
       </c>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
           <t>"金州大樱桃"获地理标志认证，东北最大樱桃产区。品种丰富(美早、萨米脱、佳红等)，果大色艳、硬度高耐运输。</t>
@@ -5675,6 +5767,7 @@
       <c r="K96" t="n">
         <v>11</v>
       </c>
+      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
           <t>中国国家地理标志产品，种植面积约23.86万亩，产量达87万吨。个大形圆、肉厚质软、无核脆甜，可鲜食可加工柿饼。</t>
@@ -5729,6 +5822,7 @@
       <c r="K97" t="n">
         <v>11</v>
       </c>
+      <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
           <t>国家地理标志保护产品，种植面积36万亩，年产鲜柿28万吨。个大皮薄、肉多汁甜，柿饼以"个大、霜白、底亮、质润、味香甜"著称。</t>
@@ -5783,6 +5877,7 @@
       <c r="K98" t="n">
         <v>11</v>
       </c>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
           <t>被誉为"中国磨盘柿之乡"，栽培面积3万多亩。果形如磨盘、个大皮薄、汁浓味甜，单果可达半斤以上，有"色胜金依，甘逾玉液"美誉。</t>
@@ -5837,6 +5932,7 @@
       <c r="K99" t="n">
         <v>7</v>
       </c>
+      <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
           <t>中国最名贵荔枝品种之一，母树仅存一株。果肉晶莹剔透、爽脆微香，品质极上。广东"增城挂绿"为荔枝中的极品，历史文化价值极高。</t>
@@ -5891,6 +5987,7 @@
       <c r="K100" t="n">
         <v>7</v>
       </c>
+      <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
           <t>广西灵山特产，中国荔枝之乡。灵山荔枝种植历史可追溯至唐朝，果大核小、肉厚汁多、香甜味美，以"香荔"品种最为驰名。</t>
@@ -5945,6 +6042,7 @@
       <c r="K101" t="n">
         <v>8</v>
       </c>
+      <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
           <t>桂七芒(桂热82号)为百色独有品种，中国芒果之乡核心代表。果形S形，表皮始终青绿，甜度高达26%，香气复合(果香+木香+花香+奶香)，核薄如纸。</t>
@@ -5999,6 +6097,7 @@
       <c r="K102" t="n">
         <v>5</v>
       </c>
+      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
           <t>中国最早上市芒果产区代表。贵妃芒皮薄核小、汁多纤维少、甜度高，色彩艳丽如彩虹。4月至5月中旬为黄金品尝期。</t>
@@ -6053,6 +6152,7 @@
       <c r="K103" t="n">
         <v>10</v>
       </c>
+      <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
           <t>"中国火龙果之乡"，种植面积3.42万亩。采用夜间补光技术延长产期，品种紫红龙，果肉紫红、甜度20度以上，富含花青素。</t>
@@ -6107,6 +6207,7 @@
       <c r="K104" t="n">
         <v>10</v>
       </c>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
           <t>广西火龙果产量全国第一，南宁为核心产区。采用排架密植和夜间补光技术，一年长达8个月采摘期，单果均重600克以上。</t>
@@ -6144,6 +6245,7 @@
           <t>丹棱县</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>11</v>
       </c>
@@ -6198,6 +6300,7 @@
           <t>丹棱县</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>10</v>
       </c>
@@ -6252,11 +6355,12 @@
           <t>安岳县</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>11</v>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
         <v>11</v>
@@ -6264,6 +6368,7 @@
       <c r="K107" t="n">
         <v>12</v>
       </c>
+      <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
           <t>深加工需求庞大（果汁、香料），可对接工厂渠道。</t>
@@ -6301,6 +6406,7 @@
           <t>苍溪县</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>8</v>
       </c>
@@ -6313,6 +6419,7 @@
       <c r="K108" t="n">
         <v>10</v>
       </c>
+      <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
           <t>果大、肉脆、汁多，适合中秋礼品市场。</t>
@@ -6350,6 +6457,7 @@
           <t>金川县</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>8</v>
       </c>
@@ -6362,6 +6470,7 @@
       <c r="K109" t="n">
         <v>10</v>
       </c>
+      <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
           <t>生长于高原，无污染，可打“生态牌”。</t>
@@ -6399,6 +6508,7 @@
           <t>龙泉驿区</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>4</v>
       </c>
@@ -6453,6 +6563,7 @@
           <t>攀枝花市</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>6.5</v>
       </c>
@@ -6507,6 +6618,7 @@
           <t>仁和区</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>7</v>
       </c>
@@ -6519,6 +6631,7 @@
       <c r="K112" t="n">
         <v>10</v>
       </c>
+      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
           <t>国内芒果晚熟产区，可对接北方秋冬市场。</t>
@@ -6556,6 +6669,7 @@
           <t>会理市</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>7.7</v>
       </c>
@@ -6610,6 +6724,7 @@
           <t>双流区</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>12</v>
       </c>
@@ -6622,6 +6737,7 @@
       <c r="K114" t="n">
         <v>5</v>
       </c>
+      <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
           <t>高价值、高损耗单品。</t>
@@ -6659,6 +6775,7 @@
           <t>新平县</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>1</v>
       </c>
@@ -6671,6 +6788,7 @@
       <c r="K115" t="n">
         <v>4</v>
       </c>
+      <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
           <t>云南沃柑上市期覆盖冬春，是广西沃柑的接力品。宾川、新平品质最佳，糖酸比优秀。注意：产区分散，山路运输成本高，需提前规划集货路线。</t>
@@ -6708,11 +6826,12 @@
           <t>新平县</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>10</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J116" t="n">
         <v>10</v>
@@ -6720,6 +6839,7 @@
       <c r="K116" t="n">
         <v>12</v>
       </c>
+      <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
           <t>褚橙品牌效应极强，但产地采购门槛高、价格透明。可关注周边品质相近的“高原冰糖橙”，避开品牌溢价，主打“同一片山水”的性价比。防霜冻是冬季发货首要任务。</t>
@@ -6757,6 +6877,7 @@
           <t>建水县</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>5</v>
       </c>
@@ -6769,6 +6890,7 @@
       <c r="K117" t="n">
         <v>8</v>
       </c>
+      <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
           <t>建水是全国最早的阳光玫瑰产区之一，4月底即可上市，价格高但需抢早。注意果锈、果型和香味，采购必须测底糖（16°以上）。冷链运输是强制要求，否则掉粒烂果。</t>
@@ -6806,6 +6928,7 @@
           <t>建水县</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>4</v>
       </c>
@@ -6818,6 +6941,7 @@
       <c r="K118" t="n">
         <v>6</v>
       </c>
+      <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
           <t>露天栽培为主，早熟优势明显。核心风险是果实变软和掉粒，必须要求产地分级包装，轴硬不落粒为佳。</t>
@@ -6855,6 +6979,7 @@
           <t>弥勒市</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>12</v>
       </c>
@@ -6909,6 +7034,7 @@
           <t>宾川县</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>8</v>
       </c>
@@ -6921,6 +7047,7 @@
       <c r="K120" t="n">
         <v>10</v>
       </c>
+      <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
           <t>宾川石榴果面漂亮，籽粒深红。注意：成熟度不足时籽粒色浅、味酸，需把控采摘时间。软籽石榴客单价高，适合作为你秋季的利润品。</t>
@@ -6958,6 +7085,7 @@
           <t>华坪县</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>6</v>
       </c>
@@ -6970,6 +7098,7 @@
       <c r="K121" t="n">
         <v>9</v>
       </c>
+      <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
           <t>华坪是全国纬度最高的芒果产区，晚熟凯特芒果8-11月上市，可对接四川攀枝花产区做联合集货。注意：凯特芒果丝多、易生水泡病，采购要验果肉纤维。</t>
@@ -7007,6 +7136,7 @@
           <t>丘北县</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>6</v>
       </c>
@@ -7019,6 +7149,7 @@
       <c r="K122" t="n">
         <v>7</v>
       </c>
+      <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
           <t>果期极短，仅20天左右，必须精准卡位。采购时紧盯成熟度，七八成熟采摘，过硬无味、过软运输必烂。适合作为短平快的高价引流品。</t>
@@ -7056,6 +7187,7 @@
           <t>昭阳区</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
         <v>7</v>
       </c>
@@ -7068,6 +7200,7 @@
       <c r="K123" t="n">
         <v>9</v>
       </c>
+      <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
           <t>昭通苹果是西南地区唯一的大面积早熟苹果产区，比北方早一个月。但果锈、果面粗糙是常见问题，采购标准必须明确果面洁净度和着色率。</t>
@@ -7105,6 +7238,7 @@
           <t>高州市</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
         <v>5</v>
       </c>
@@ -7117,6 +7251,7 @@
       <c r="K124" t="n">
         <v>6</v>
       </c>
+      <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
           <t>全球最大连片荔枝产区，上市最早。但这完全是时间与速度的游戏：“一日色变，二日香变”。你必须提前在产地立好预冷和分拣场地，要求采摘后2小时内进冰水预冷，全程冷链，零秒延迟。没有稳定冷链合作方，绝不要碰。</t>
@@ -7154,6 +7289,7 @@
           <t>增城区</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>6</v>
       </c>
@@ -7166,6 +7302,7 @@
       <c r="K125" t="n">
         <v>7</v>
       </c>
+      <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
           <t>广东顶级荔枝，价格高，但大小年极其严重，桂味在2022-2023年几乎绝收。采购前必须实地看花看果，不接盲单。糯米糍皮薄易爆，运输损耗率天然高达15-20%，报价必须计入。</t>
@@ -7203,6 +7340,7 @@
           <t>高州市</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>7</v>
       </c>
@@ -7215,6 +7353,7 @@
       <c r="K126" t="n">
         <v>8</v>
       </c>
+      <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
           <t>储良个大肉厚，石硖小个甜脆。龙眼比荔枝稍耐储，但仍需全程冷链。注意产区规律：龙眼季恰逢台风季，一旦台风登录，货源中断、价格暴涨是常有的事，要预留备选产区。</t>
@@ -7252,6 +7391,7 @@
           <t>四会市</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>12</v>
       </c>
@@ -7264,6 +7404,7 @@
       <c r="K127" t="n">
         <v>2</v>
       </c>
+      <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
           <t>广东本地人高度认可是“正宗砂糖橘”。但现在面临广西砂糖橘的强烈冲击，价格倒挂。你若是从广东采购发往外地，必须计算清楚物流成本，否则拼不过广西货。可主打“原产地理标志”卖给有执念的客群。</t>
@@ -7301,6 +7442,7 @@
           <t>梅县区</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>9</v>
       </c>
@@ -7313,6 +7455,7 @@
       <c r="K128" t="n">
         <v>1</v>
       </c>
+      <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
           <t>金柚（沙田柚）是耐储品，采购后可以静放后熟返糖。注意区分：蜜柚9月上市，要现卖；沙田柚11月后上市，越放越甜，可操作窗口期很长，是冬季拼车的理想填充品。</t>
@@ -7350,11 +7493,12 @@
           <t>高州市</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>11</v>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>11</v>
@@ -7362,6 +7506,7 @@
       <c r="K129" t="n">
         <v>12</v>
       </c>
+      <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
           <t>广东香蕉种植散，规模化不如广西，但粉蕉品质好。香蕉是乙烯敏感品，储运必须做保鲜处理和轻放，催熟工艺掌握不好会导致大量投诉，建议找本地分选包装厂一件代发。</t>
@@ -7399,6 +7544,7 @@
           <t>荔浦市</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>12</v>
       </c>
@@ -7411,6 +7557,7 @@
       <c r="K130" t="n">
         <v>3</v>
       </c>
+      <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
           <t>这曾是全国的“发财果”，但现在产能严重过剩，地头价常跌破成本。你的机会不在统货，而在高标准的精选果：挑55以上规格、无花皮的高品质果，才能做出利润。否则就是跟万千小贩拼烂价。</t>
@@ -7448,6 +7595,7 @@
           <t>武鸣区</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>1</v>
       </c>
@@ -7460,6 +7608,7 @@
       <c r="K131" t="n">
         <v>4</v>
       </c>
+      <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
           <t>武鸣沃柑统治了中国晚熟柑橘半壁江山。你的采购策略：避开1-2月出园高峰期，那时大车排队，价格混乱，果品不稳定。可在3-4月入库后的精品中挑选，那时货权集中，品质一眼能看明。</t>
@@ -7497,6 +7646,7 @@
           <t>田东县</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>6</v>
       </c>
@@ -7509,6 +7659,7 @@
       <c r="K132" t="n">
         <v>8</v>
       </c>
+      <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
           <t>桂七芒果是广西独有的顶级单品，香气独特，不可错过。但桂七果期短（7月中至8月初），且青皮熟，顾客不懂识别会投诉不熟。你必须在销售时附上“熟了是青的，捏软才吃”的提示卡。</t>
@@ -7546,18 +7697,20 @@
           <t>隆安县</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>5</v>
       </c>
       <c r="I133" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J133" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K133" t="n">
-        <v>1</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
           <t>隆安是全国最大的火龙果产区，夜里万灯齐明补光，能全年产果。注意：补光果与自然光果甜度无大差异，但鳞片易干枯，卖相不佳。采购时要明确鳞片新鲜度标准。</t>
@@ -7595,6 +7748,7 @@
           <t>北流市</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
         <v>7</v>
       </c>
@@ -7607,6 +7761,7 @@
       <c r="K134" t="n">
         <v>10</v>
       </c>
+      <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
           <t>黄金百香果“钦蜜9号”是近年爆品，纯甜不酸，彻底颠覆认知。但苗源混乱，必须追认正宗钦蜜9号种苗的果园。紫皮百香果酸度大，主要走加工，生鲜你只做黄金。注意果面、皱缩度。</t>
@@ -7644,11 +7799,12 @@
           <t>恭城瑶族自治县</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>10</v>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J135" t="n">
         <v>10</v>
@@ -7656,6 +7812,7 @@
       <c r="K135" t="n">
         <v>12</v>
       </c>
+      <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
           <t>恭城月柿闻名全国，但大部分加工为柿饼。你可操作甜脆柿，采摘后直接可食，不用脱涩。它的核心卖点是“脆甜得像苹果”，测试甜度要在15°以上。注意包装要防挤压。</t>
@@ -7693,6 +7850,7 @@
           <t>八步区</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>5</v>
       </c>
@@ -7705,6 +7863,7 @@
       <c r="K136" t="n">
         <v>7</v>
       </c>
+      <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
           <t>广西李子消费独特，配以辣椒盐蘸食。你发往外地要同时附带这种吃法说明，创造体验感。注意三华李成熟期梅雨季节，裂果、落果严重，需把控采购天气。</t>
@@ -7801,6 +7960,7 @@
           <t>修文县</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>10</v>
       </c>
@@ -7813,6 +7973,7 @@
       <c r="K138" t="n">
         <v>3</v>
       </c>
+      <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr">
         <is>
           <t>属于中华系长果形猕猴桃，维C高。核心痛点在后熟：来货不能硬，也不能全软。必须教会你的下游小店如何催熟（与苹果香蕉密封放置），否则顾客买回家就像啃石头，复购归零。</t>
@@ -7850,6 +8011,7 @@
           <t>麻江县</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>6</v>
       </c>
@@ -7862,6 +8024,7 @@
       <c r="K139" t="n">
         <v>8</v>
       </c>
+      <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr">
         <is>
           <t>中国蓝莓之乡，规模大，但上市集中在夏季，与云南冬春蓝莓错峰。注意：夏季蓝莓果粉易磨损，要求采摘后直接进预冷间，否则果粉丢失、卖相变差。适合发周边市场。</t>
@@ -7899,6 +8062,7 @@
           <t>罗甸县</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>11</v>
       </c>
@@ -7911,6 +8075,7 @@
       <c r="K140" t="n">
         <v>2</v>
       </c>
+      <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr">
         <is>
           <t>贵州最有名的甜橙，橙味浓郁。产区为干热河谷，品质较稳定。可与四川爱媛、春见搭配，作为冬季柑橘拼车里的补充单品，丰富产品线。</t>
@@ -7948,6 +8113,7 @@
           <t>纳雍县</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
         <v>4</v>
       </c>
@@ -7960,6 +8126,7 @@
       <c r="K141" t="n">
         <v>6</v>
       </c>
+      <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
           <t>是中国樱桃（非车厘子）中的优良品种，比北方甜樱桃早，但皮极薄、肉极软，储运极其困难。你若要碰，只能做航空直达或极短途4.2米车当日达，否则一地红水。新手慎碰。</t>
@@ -7997,6 +8164,7 @@
           <t>罗甸县</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
         <v>7</v>
       </c>
@@ -8009,6 +8177,7 @@
       <c r="K142" t="n">
         <v>10</v>
       </c>
+      <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
           <t>北盘江干热河谷带，因昼夜温差大，火龙果甜度比两广更高。注意：贵州火龙果总体上鳞片偏软，不耐长途反复装卸，适合发往省内或周边市场。</t>
@@ -8046,6 +8215,7 @@
           <t>乐东黎族自治县</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
         <v>1</v>
       </c>
@@ -8058,6 +8228,7 @@
       <c r="K143" t="n">
         <v>4</v>
       </c>
+      <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
           <t>海南芒果是最早上市的芒果产区，1月开始就有台农供应。这是你春节前最抢眼的高价品。核心风险是跨海轮渡，一旦遭遇大雾或台风封航，车辆滞留在码头，你整车的损毁和延误将是致命的。必须有应急预案。</t>
@@ -8095,6 +8266,7 @@
           <t>乐东县</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>9</v>
       </c>
@@ -8107,6 +8279,7 @@
       <c r="K144" t="n">
         <v>10</v>
       </c>
+      <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
           <t>皇帝蕉体小味甜，是高价值品种。运输中极度怕压、怕风、怕冷，包装必须要用泡膜隔垫，码垛不能超过一定高度。</t>
@@ -8144,6 +8317,7 @@
           <t>万宁市</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>2</v>
       </c>
@@ -8156,6 +8330,7 @@
       <c r="K145" t="n">
         <v>4</v>
       </c>
+      <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
           <t>“海南菠萝”常被用于低价旅游引流品，但金钻凤梨品质极佳。你务必打“凤梨”概念，不打“菠萝”，强调免泡盐水、不剌嘴的卖点。凤梨采收标准是果眼平滑、果柄处无腐烂。</t>
@@ -8193,6 +8368,7 @@
           <t>澄迈县</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>4</v>
       </c>
@@ -8205,6 +8381,7 @@
       <c r="K146" t="n">
         <v>5</v>
       </c>
+      <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
           <t>全国最早上市的荔枝，比广东早半个月以上，价格奇高。采购和广东荔枝同样原则：冰水预冷、全程冷链。第一次做建议小批量测试，感受跨海时效。</t>
@@ -8242,18 +8419,20 @@
           <t>乐东黎族自治县</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I147" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J147" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K147" t="n">
-        <v>1</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
           <t>与广西形成上市互补，尤其1-4月，广西货少时海南货有能力供货。主要挑战仍是出岛物流，成本高于陆运。</t>
@@ -8291,18 +8470,20 @@
           <t>琼山区</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I148" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J148" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K148" t="n">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr">
         <is>
           <t>海南莲雾中的精品，黑金刚清甜脆爽，是高利润品。但此物极难保存，碰伤即烂，果体极脆。要求采摘时戴手套，单果套网套，定做托盘。只能发对高品质有要求、能接受高价格的高端客户。</t>
@@ -8340,6 +8521,7 @@
           <t>乐东县</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>1</v>
       </c>
@@ -8352,6 +8534,7 @@
       <c r="K149" t="n">
         <v>4</v>
       </c>
+      <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
           <t>乐东蜜瓜甜度高，品相好。冬季供应全国，但价格不菲。采购时要测中心糖度，16度以上达标。哈密瓜类较耐运，是你从海南发货相对最稳妥的品类。</t>
@@ -8406,6 +8589,7 @@
       <c r="K150" t="n">
         <v>5</v>
       </c>
+      <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。浙江省杭州市余杭区特产，中国枇杷之乡。果形饱满、色泽金黄、果肉细腻、汁多味甜，栽培历史超千年。以"软条白沙""大红袍"品种最为著名。</t>
@@ -8452,7 +8636,7 @@
         <v>3</v>
       </c>
       <c r="I151" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J151" t="n">
         <v>3</v>
@@ -8460,6 +8644,7 @@
       <c r="K151" t="n">
         <v>4</v>
       </c>
+      <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。福建省漳州市云霄县特产，早熟优质枇杷产区。果实橙黄色、果肉细嫩、汁多味甜，三月中旬即可上市，比国内其他产区早15-30天。</t>
@@ -8506,7 +8691,7 @@
         <v>9</v>
       </c>
       <c r="I152" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J152" t="n">
         <v>9</v>
@@ -8514,6 +8699,7 @@
       <c r="K152" t="n">
         <v>10</v>
       </c>
+      <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。陕西省西安市临潼区特产，中国石榴之乡。以色泽艳丽、果大皮薄、汁多味甜、籽粒饱满著称，栽培历史超2000年。代表品种"净皮甜""三白甜"。</t>
@@ -8568,6 +8754,7 @@
       <c r="K153" t="n">
         <v>9</v>
       </c>
+      <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。云南省红河州蒙自市特产，中国石榴之乡。果形端正、色泽艳丽、籽粒晶莹、汁多味甜，全国上市最早的石榴产区之一。</t>
@@ -8614,7 +8801,7 @@
         <v>10</v>
       </c>
       <c r="I154" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J154" t="n">
         <v>10</v>
@@ -8622,6 +8809,7 @@
       <c r="K154" t="n">
         <v>11</v>
       </c>
+      <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。新疆和田地区特产，以皮薄、粒大、汁多、味甜闻名。独特的昼夜温差和充足的日照造就了极高的含糖量。</t>
@@ -8668,7 +8856,7 @@
         <v>10</v>
       </c>
       <c r="I155" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J155" t="n">
         <v>10</v>
@@ -8676,6 +8864,7 @@
       <c r="K155" t="n">
         <v>11</v>
       </c>
+      <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。新疆巴音郭楞州若羌县特产，中国红枣之乡。果形饱满、色泽紫红、皮薄肉厚、核小味甜，富含多种维生素和矿物质，自然风干后品质极佳。</t>
@@ -8722,7 +8911,7 @@
         <v>9</v>
       </c>
       <c r="I156" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J156" t="n">
         <v>9</v>
@@ -8730,6 +8919,7 @@
       <c r="K156" t="n">
         <v>10</v>
       </c>
+      <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。河北省沧州市特产，中国红枣之乡。果实小巧玲珑、皮薄肉厚、核小味甜，掰开可见金色糖丝，故名"金丝小枣"。</t>
@@ -8776,7 +8966,7 @@
         <v>9</v>
       </c>
       <c r="I157" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J157" t="n">
         <v>9</v>
@@ -8784,6 +8974,7 @@
       <c r="K157" t="n">
         <v>10</v>
       </c>
+      <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。山西省运城市稷山县特产，中国十大名枣之一。呈板圆形、色泽深红、皮薄肉厚、核小味甜，为历代贡品。</t>
@@ -8830,7 +9021,7 @@
         <v>6</v>
       </c>
       <c r="I158" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J158" t="n">
         <v>6</v>
@@ -8838,6 +9029,7 @@
       <c r="K158" t="n">
         <v>7</v>
       </c>
+      <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。新疆巴音郭楞州轮台县特产，中国白杏之乡。果肉细腻、汁多味甜、香气浓郁，可鲜食亦可加工，杏仁味美。</t>
@@ -8881,17 +9073,18 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I159" t="n">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="J159" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="K159" t="n">
-        <v>7</v>
-      </c>
+        <v>7.5</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。甘肃省兰州市特产，中国优质杏产区。果大肉厚、色泽金黄、汁多味甜、香气浓郁，为西北地区著名杏品种。</t>
@@ -8938,7 +9131,7 @@
         <v>7</v>
       </c>
       <c r="I160" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J160" t="n">
         <v>7</v>
@@ -8946,6 +9139,7 @@
       <c r="K160" t="n">
         <v>8</v>
       </c>
+      <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。河北张家口特产，以杏肉厚实、甜酸适口、杏仁饱满著称。</t>
@@ -8992,7 +9186,7 @@
         <v>9</v>
       </c>
       <c r="I161" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J161" t="n">
         <v>9</v>
@@ -9000,6 +9194,7 @@
       <c r="K161" t="n">
         <v>10</v>
       </c>
+      <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。河北省承德市兴隆县特产，中国山楂之乡。果实个大色红、肉厚味酸、营养丰富，为加工果丹皮、山楂糕的优质原料。</t>
@@ -9054,6 +9249,7 @@
       <c r="K162" t="n">
         <v>11</v>
       </c>
+      <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。山东省临沂市平邑县特产，以果大色红、肉厚酸适著称。</t>
@@ -9100,7 +9296,7 @@
         <v>9</v>
       </c>
       <c r="I163" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J163" t="n">
         <v>9</v>
@@ -9108,6 +9304,7 @@
       <c r="K163" t="n">
         <v>10</v>
       </c>
+      <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。河北省石家庄赵县特产，中国雪花梨之乡。果肉洁白如玉、汁多味甜、有清香，为传统出口果品。</t>
@@ -9162,6 +9359,7 @@
       <c r="K164" t="n">
         <v>11</v>
       </c>
+      <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。甘肃省兰州市特产，中国百合之乡。</t>
@@ -9216,6 +9414,7 @@
       <c r="K165" t="n">
         <v>4</v>
       </c>
+      <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。江苏省镇江市句容市特产，中国草莓之乡。果形端正、色泽鲜艳、甜酸适口，为南方设施草莓的代表产区。</t>
@@ -9262,7 +9461,7 @@
         <v>7</v>
       </c>
       <c r="I166" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J166" t="n">
         <v>7</v>
@@ -9270,6 +9469,7 @@
       <c r="K166" t="n">
         <v>8</v>
       </c>
+      <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。福建省福州市永泰县特产，中国李果之乡。果实扁圆形、色泽紫红、肉厚核小、酸甜适口，为加工蜜饯的优质原料。</t>
@@ -9324,6 +9524,7 @@
       <c r="K167" t="n">
         <v>7</v>
       </c>
+      <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。广东省韶关市翁源县特产，中国三华李之乡。果大肉厚、核小味甜、爽脆可口。</t>
@@ -9370,7 +9571,7 @@
         <v>7</v>
       </c>
       <c r="I168" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J168" t="n">
         <v>7</v>
@@ -9378,6 +9579,7 @@
       <c r="K168" t="n">
         <v>8</v>
       </c>
+      <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。上海市浦东新区（原南汇区）特产。果形圆整、色泽粉红、皮薄肉厚、汁多味甜，有"上海特产"之称。</t>
@@ -9432,6 +9634,7 @@
       <c r="K169" t="n">
         <v>9</v>
       </c>
+      <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr">
         <is>
           <t>国家地理标志保护产品。甘肃省天水市秦安县特产，中国桃之乡。果大色艳、汁多味甜，为西北地区优质桃产区。</t>
@@ -9545,6 +9748,7 @@
       <c r="K171" t="n">
         <v>3</v>
       </c>
+      <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr">
         <is>
           <t>海南省三亚市特产，高端热带水果。果实色泽红艳、清甜爽脆、水分充足，有"树上矿泉水"之称。</t>
@@ -9599,6 +9803,7 @@
       <c r="K172" t="n">
         <v>10</v>
       </c>
+      <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr">
         <is>
           <t>海南省特产，世界最大水果。果肉金黄、香甜浓郁，可鲜食或加工。</t>
@@ -9653,6 +9858,7 @@
       <c r="K173" t="n">
         <v>11</v>
       </c>
+      <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr">
         <is>
           <t>广西玉林北流特产，中国百香果之乡。果实香气浓郁、酸甜可口，维生素C含量丰富。</t>
@@ -9749,6 +9955,7 @@
           <t>长阳土家族自治县</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
         <v>11</v>
       </c>
@@ -9921,6 +10128,7 @@
           <t>公安县</t>
         </is>
       </c>
+      <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
         <v>7</v>
       </c>
@@ -9975,6 +10183,7 @@
           <t>赤壁市</t>
         </is>
       </c>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
         <v>8</v>
       </c>
@@ -10029,6 +10238,7 @@
           <t>建始县</t>
         </is>
       </c>
+      <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
         <v>9</v>
       </c>
@@ -10142,11 +10352,12 @@
           <t>宜都市</t>
         </is>
       </c>
+      <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
         <v>10</v>
       </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J182" t="n">
         <v>10</v>
@@ -10196,6 +10407,7 @@
           <t>罗田县</t>
         </is>
       </c>
+      <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
         <v>8</v>
       </c>
@@ -10250,6 +10462,7 @@
           <t>房县</t>
         </is>
       </c>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
         <v>4</v>
       </c>
@@ -10304,6 +10517,7 @@
           <t>老河口市</t>
         </is>
       </c>
+      <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
         <v>6</v>
       </c>
@@ -10358,6 +10572,7 @@
           <t>老河口市</t>
         </is>
       </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
         <v>7</v>
       </c>
@@ -10412,6 +10627,7 @@
           <t>兴山县</t>
         </is>
       </c>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
         <v>11</v>
       </c>
@@ -10466,6 +10682,7 @@
           <t>凉城县</t>
         </is>
       </c>
+      <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
         <v>8</v>
       </c>
@@ -10520,6 +10737,7 @@
           <t>宁城县</t>
         </is>
       </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
         <v>9</v>
       </c>
@@ -10569,6 +10787,8 @@
           <t>乌海市</t>
         </is>
       </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
         <v>7</v>
       </c>
@@ -10623,6 +10843,7 @@
           <t>延吉市</t>
         </is>
       </c>
+      <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
         <v>9</v>
       </c>
@@ -10672,6 +10893,8 @@
           <t>白山市</t>
         </is>
       </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
         <v>7</v>
       </c>
@@ -10726,6 +10949,7 @@
           <t>柳河县</t>
         </is>
       </c>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
         <v>8</v>
       </c>
@@ -10780,6 +11004,7 @@
           <t>通化县</t>
         </is>
       </c>
+      <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
         <v>7</v>
       </c>
@@ -10829,6 +11054,8 @@
           <t>大兴安岭地区</t>
         </is>
       </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
         <v>7</v>
       </c>
@@ -10883,6 +11110,7 @@
           <t>尚志市</t>
         </is>
       </c>
+      <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
         <v>7</v>
       </c>
@@ -10937,6 +11165,7 @@
           <t>勃利县</t>
         </is>
       </c>
+      <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
         <v>6</v>
       </c>
@@ -10991,6 +11220,7 @@
           <t>穆棱市</t>
         </is>
       </c>
+      <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
         <v>9</v>
       </c>
@@ -11040,6 +11270,8 @@
           <t>伊春市</t>
         </is>
       </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
         <v>7</v>
       </c>
@@ -11089,6 +11321,8 @@
           <t>海西蒙古族藏族自治州</t>
         </is>
       </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
         <v>7</v>
       </c>
@@ -11143,6 +11377,7 @@
           <t>乐都区</t>
         </is>
       </c>
+      <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
         <v>8</v>
       </c>
@@ -11197,6 +11432,7 @@
           <t>乐都区</t>
         </is>
       </c>
+      <c r="G202" t="inlineStr"/>
       <c r="H202" t="n">
         <v>6</v>
       </c>
@@ -11251,6 +11487,7 @@
           <t>巴宜区</t>
         </is>
       </c>
+      <c r="G203" t="inlineStr"/>
       <c r="H203" t="n">
         <v>9</v>
       </c>
@@ -11305,6 +11542,7 @@
           <t>芒康县</t>
         </is>
       </c>
+      <c r="G204" t="inlineStr"/>
       <c r="H204" t="n">
         <v>8</v>
       </c>
@@ -11359,6 +11597,7 @@
           <t>朗县</t>
         </is>
       </c>
+      <c r="G205" t="inlineStr"/>
       <c r="H205" t="n">
         <v>9</v>
       </c>
@@ -11472,6 +11711,7 @@
           <t>西峡县</t>
         </is>
       </c>
+      <c r="G207" t="inlineStr"/>
       <c r="H207" t="n">
         <v>8</v>
       </c>
@@ -11526,6 +11766,7 @@
           <t>肥城市</t>
         </is>
       </c>
+      <c r="G208" t="inlineStr"/>
       <c r="H208" t="n">
         <v>8</v>
       </c>
@@ -11580,6 +11821,7 @@
           <t>乐陵市</t>
         </is>
       </c>
+      <c r="G209" t="inlineStr"/>
       <c r="H209" t="n">
         <v>9</v>
       </c>
@@ -11634,6 +11876,7 @@
           <t>会理市</t>
         </is>
       </c>
+      <c r="G210" t="inlineStr"/>
       <c r="H210" t="n">
         <v>8</v>
       </c>
@@ -11688,6 +11931,7 @@
           <t>威远县</t>
         </is>
       </c>
+      <c r="G211" t="inlineStr"/>
       <c r="H211" t="n">
         <v>7</v>
       </c>
@@ -11742,6 +11986,7 @@
           <t>炎陵县</t>
         </is>
       </c>
+      <c r="G212" t="inlineStr"/>
       <c r="H212" t="n">
         <v>7</v>
       </c>
@@ -11796,6 +12041,7 @@
           <t>隰县</t>
         </is>
       </c>
+      <c r="G213" t="inlineStr"/>
       <c r="H213" t="n">
         <v>9</v>
       </c>
@@ -11845,6 +12091,8 @@
           <t>东方市</t>
         </is>
       </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
       <c r="H214" t="n">
         <v>5</v>
       </c>
@@ -11899,6 +12147,7 @@
           <t>灵武市</t>
         </is>
       </c>
+      <c r="G215" t="inlineStr"/>
       <c r="H215" t="n">
         <v>9</v>
       </c>
@@ -11953,6 +12202,7 @@
           <t>集安市</t>
         </is>
       </c>
+      <c r="G216" t="inlineStr"/>
       <c r="H216" t="n">
         <v>8</v>
       </c>
@@ -12007,6 +12257,7 @@
           <t>东港市</t>
         </is>
       </c>
+      <c r="G217" t="inlineStr"/>
       <c r="H217" t="n">
         <v>12</v>
       </c>
@@ -12056,6 +12307,8 @@
           <t>龙岩市</t>
         </is>
       </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
       <c r="H218" t="n">
         <v>7</v>
       </c>
@@ -12110,6 +12363,7 @@
           <t>青州市</t>
         </is>
       </c>
+      <c r="G219" t="inlineStr"/>
       <c r="H219" t="n">
         <v>9</v>
       </c>
@@ -12159,6 +12413,8 @@
           <t>威海市</t>
         </is>
       </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
       <c r="H220" t="n">
         <v>7</v>
       </c>
@@ -12230,6 +12486,7 @@
       <c r="K221" t="n">
         <v>9</v>
       </c>
+      <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
           <t>中国国家地理标志产品，马陆镇种植葡萄已有40余年历史</t>
@@ -12284,6 +12541,7 @@
       <c r="K222" t="n">
         <v>8.5</v>
       </c>
+      <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr">
         <is>
           <t>中国国家地理标志产品，奉贤黄桃果大味甜</t>
@@ -12321,6 +12579,7 @@
           <t>巴宜区</t>
         </is>
       </c>
+      <c r="G223" t="inlineStr"/>
       <c r="H223" t="n">
         <v>9</v>
       </c>
@@ -12333,6 +12592,7 @@
       <c r="K223" t="n">
         <v>11</v>
       </c>
+      <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr">
         <is>
           <t>西藏林芝高海拔苹果，日照充足糖分高，地理标志产品</t>
@@ -12370,6 +12630,7 @@
           <t>察隅县</t>
         </is>
       </c>
+      <c r="G224" t="inlineStr"/>
       <c r="H224" t="n">
         <v>9</v>
       </c>
@@ -12382,6 +12643,7 @@
       <c r="K224" t="n">
         <v>10.5</v>
       </c>
+      <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr">
         <is>
           <t>西藏察隅高海拔野生猕猴桃改良品种，地理标志产品</t>
@@ -12419,6 +12681,7 @@
           <t>中宁县</t>
         </is>
       </c>
+      <c r="G225" t="inlineStr"/>
       <c r="H225" t="n">
         <v>6</v>
       </c>
@@ -12431,6 +12694,7 @@
       <c r="K225" t="n">
         <v>9</v>
       </c>
+      <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr">
         <is>
           <t>宁夏枸杞甲天下，中宁枸杞是国家地理标志保护产品</t>
@@ -12468,6 +12732,7 @@
           <t>海原县</t>
         </is>
       </c>
+      <c r="G226" t="inlineStr"/>
       <c r="H226" t="n">
         <v>9</v>
       </c>
@@ -12480,6 +12745,7 @@
       <c r="K226" t="n">
         <v>10.5</v>
       </c>
+      <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr">
         <is>
           <t>海原香水梨为宁夏地方名优特产</t>
@@ -12534,6 +12800,7 @@
       <c r="K227" t="n">
         <v>9.5</v>
       </c>
+      <c r="L227" t="inlineStr"/>
       <c r="M227" t="inlineStr">
         <is>
           <t>中国国家地理标志产品，茶淀葡萄久负盛名</t>
@@ -12588,6 +12855,7 @@
       <c r="K228" t="n">
         <v>7.5</v>
       </c>
+      <c r="L228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
           <t>蓟州桑梓西瓜为天津地理标志农产品</t>
@@ -12625,6 +12893,7 @@
           <t>怀远县</t>
         </is>
       </c>
+      <c r="G229" t="inlineStr"/>
       <c r="H229" t="n">
         <v>9</v>
       </c>
@@ -12637,6 +12906,7 @@
       <c r="K229" t="n">
         <v>10.5</v>
       </c>
+      <c r="L229" t="inlineStr"/>
       <c r="M229" t="inlineStr">
         <is>
           <t>中国国家地理标志产品，怀远石榴历史悠久</t>
@@ -12674,6 +12944,7 @@
           <t>萧县</t>
         </is>
       </c>
+      <c r="G230" t="inlineStr"/>
       <c r="H230" t="n">
         <v>7</v>
       </c>
@@ -12686,6 +12957,7 @@
       <c r="K230" t="n">
         <v>8.5</v>
       </c>
+      <c r="L230" t="inlineStr"/>
       <c r="M230" t="inlineStr">
         <is>
           <t>中国国家地理标志产品，萧县葡萄栽培历史超千年</t>
@@ -12723,6 +12995,7 @@
           <t>广丰区</t>
         </is>
       </c>
+      <c r="G231" t="inlineStr"/>
       <c r="H231" t="n">
         <v>11</v>
       </c>
@@ -12735,6 +13008,7 @@
       <c r="K231" t="n">
         <v>2</v>
       </c>
+      <c r="L231" t="inlineStr"/>
       <c r="M231" t="inlineStr">
         <is>
           <t>中国国家地理标志产品，广丰马家柚果肉红嫩汁多味甜</t>
@@ -12772,6 +13046,7 @@
           <t>吉州区</t>
         </is>
       </c>
+      <c r="G232" t="inlineStr"/>
       <c r="H232" t="n">
         <v>10</v>
       </c>
@@ -12784,6 +13059,7 @@
       <c r="K232" t="n">
         <v>1</v>
       </c>
+      <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr">
         <is>
           <t>江西井冈山革命老区特色产业，蜜柚品牌</t>
@@ -12821,6 +13097,7 @@
           <t>梁平区</t>
         </is>
       </c>
+      <c r="G233" t="inlineStr"/>
       <c r="H233" t="n">
         <v>10</v>
       </c>
@@ -12833,6 +13110,7 @@
       <c r="K233" t="n">
         <v>1</v>
       </c>
+      <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr">
         <is>
           <t>中国国家地理标志产品，与广西沙田柚、福建文旦柚齐名</t>
@@ -12870,6 +13148,7 @@
           <t>潼南区</t>
         </is>
       </c>
+      <c r="G234" t="inlineStr"/>
       <c r="H234" t="n">
         <v>9</v>
       </c>
@@ -12882,6 +13161,7 @@
       <c r="K234" t="n">
         <v>11</v>
       </c>
+      <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr">
         <is>
           <t>重庆潼南为中国柠檬之都，全国最大柠檬生产基地</t>
@@ -12919,6 +13199,7 @@
           <t>磴口县</t>
         </is>
       </c>
+      <c r="G235" t="inlineStr"/>
       <c r="H235" t="n">
         <v>7</v>
       </c>
@@ -12931,6 +13212,7 @@
       <c r="K235" t="n">
         <v>8.5</v>
       </c>
+      <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr">
         <is>
           <t>河套平原特产蜜瓜，地理标志农产品</t>
@@ -12968,6 +13250,7 @@
           <t>鄂伦春自治旗</t>
         </is>
       </c>
+      <c r="G236" t="inlineStr"/>
       <c r="H236" t="n">
         <v>7</v>
       </c>
@@ -12980,6 +13263,7 @@
       <c r="K236" t="n">
         <v>8.5</v>
       </c>
+      <c r="L236" t="inlineStr"/>
       <c r="M236" t="inlineStr">
         <is>
           <t>大兴安岭野生蓝莓，鄂伦春自治旗地理标志产品</t>
@@ -13017,6 +13301,7 @@
           <t>民和回族土族自治县</t>
         </is>
       </c>
+      <c r="G237" t="inlineStr"/>
       <c r="H237" t="n">
         <v>7</v>
       </c>
@@ -13029,6 +13314,7 @@
       <c r="K237" t="n">
         <v>8.5</v>
       </c>
+      <c r="L237" t="inlineStr"/>
       <c r="M237" t="inlineStr">
         <is>
           <t>青海民和旱砂西瓜地理标志农产品</t>
@@ -13066,6 +13352,7 @@
           <t>尚志市</t>
         </is>
       </c>
+      <c r="G238" t="inlineStr"/>
       <c r="H238" t="n">
         <v>7</v>
       </c>
@@ -13078,6 +13365,7 @@
       <c r="K238" t="n">
         <v>8.5</v>
       </c>
+      <c r="L238" t="inlineStr"/>
       <c r="M238" t="inlineStr">
         <is>
           <t>中国红树莓之乡——尚志，国家地理标志保护产品</t>
@@ -13115,6 +13403,7 @@
           <t>友好区</t>
         </is>
       </c>
+      <c r="G239" t="inlineStr"/>
       <c r="H239" t="n">
         <v>7</v>
       </c>
@@ -13127,6 +13416,7 @@
       <c r="K239" t="n">
         <v>8.5</v>
       </c>
+      <c r="L239" t="inlineStr"/>
       <c r="M239" t="inlineStr">
         <is>
           <t>小兴安岭野生蓝莓核心产区，地理标志产品</t>
@@ -13164,6 +13454,7 @@
           <t>天涯区</t>
         </is>
       </c>
+      <c r="G240" t="inlineStr"/>
       <c r="H240" t="n">
         <v>1</v>
       </c>
@@ -13176,6 +13467,7 @@
       <c r="K240" t="n">
         <v>5</v>
       </c>
+      <c r="L240" t="inlineStr"/>
       <c r="M240" t="inlineStr">
         <is>
           <t>中国国家地理标志产品，三亚热带芒果品质优异</t>
@@ -13208,6 +13500,8 @@
           <t>琼中黎族苗族自治县</t>
         </is>
       </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
       <c r="H241" t="n">
         <v>10</v>
       </c>
@@ -13220,6 +13514,7 @@
       <c r="K241" t="n">
         <v>12</v>
       </c>
+      <c r="L241" t="inlineStr"/>
       <c r="M241" t="inlineStr">
         <is>
           <t>中国国家地理标志产品，海南琼中绿橙皮薄汁多</t>
@@ -13252,6 +13547,7 @@
           <t>文昌市</t>
         </is>
       </c>
+      <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr">
         <is>
           <t>东郊镇</t>
@@ -13269,6 +13565,7 @@
       <c r="K242" t="n">
         <v>9</v>
       </c>
+      <c r="L242" t="inlineStr"/>
       <c r="M242" t="inlineStr">
         <is>
           <t>海南文昌椰子之乡，全国最大椰子产地，地理标志产品</t>
@@ -13306,6 +13603,7 @@
           <t>民勤县</t>
         </is>
       </c>
+      <c r="G243" t="inlineStr"/>
       <c r="H243" t="n">
         <v>7</v>
       </c>
@@ -13318,6 +13616,7 @@
       <c r="K243" t="n">
         <v>8.5</v>
       </c>
+      <c r="L243" t="inlineStr"/>
       <c r="M243" t="inlineStr">
         <is>
           <t>中国国家地理标志产品，民勤沙漠蜜瓜品质上乘</t>
@@ -13355,6 +13654,7 @@
           <t>西峰区</t>
         </is>
       </c>
+      <c r="G244" t="inlineStr"/>
       <c r="H244" t="n">
         <v>9</v>
       </c>
@@ -13367,6 +13667,7 @@
       <c r="K244" t="n">
         <v>11</v>
       </c>
+      <c r="L244" t="inlineStr"/>
       <c r="M244" t="inlineStr">
         <is>
           <t>中国国家地理标志产品，庆阳苹果品牌价值超百亿</t>
@@ -13438,7 +13739,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>F245</t>
+          <t>F335</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -13483,6 +13784,7 @@
       <c r="K246" t="n">
         <v>9.5</v>
       </c>
+      <c r="L246" t="inlineStr"/>
       <c r="M246" t="inlineStr">
         <is>
           <t>国家地理标志产品。中国蜜桔之乡寻乌县特产，皮薄色鲜、质脆化渣、清香无核，特早熟品种农历七月即可上市。</t>
@@ -13492,7 +13794,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>F246</t>
+          <t>F336</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -13537,6 +13839,7 @@
       <c r="K247" t="n">
         <v>1</v>
       </c>
+      <c r="L247" t="inlineStr"/>
       <c r="M247" t="inlineStr">
         <is>
           <t>国家地理标志产品（2016年获批）。中国桔柚之乡会昌特产，桔与柚杂交品种，果肉细嫩化渣、汁多清甜，耐贮藏可至次年5月。</t>
@@ -13546,7 +13849,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>F247</t>
+          <t>F337</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -13583,14 +13886,15 @@
         <v>6</v>
       </c>
       <c r="I248" t="n">
-        <v>6</v>
+        <v>7.9</v>
       </c>
       <c r="J248" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="K248" t="n">
-        <v>6</v>
-      </c>
+        <v>7.5</v>
+      </c>
+      <c r="L248" t="inlineStr"/>
       <c r="M248" t="inlineStr">
         <is>
           <t>国家地理标志产品。上饶县铁山乡特产，果大核小、色泽紫红、肉厚汁多，种植历史超200年，每年6月中上旬采收。</t>
@@ -13600,7 +13904,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>F248</t>
+          <t>F338</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -13645,6 +13949,7 @@
       <c r="K249" t="n">
         <v>11.5</v>
       </c>
+      <c r="L249" t="inlineStr"/>
       <c r="M249" t="inlineStr">
         <is>
           <t>国家地理标志产品。新干县三湖镇传统红桔品种，果皮朱红色、光滑易剥离、汁多味香、酸甜适度、较耐储藏。</t>
@@ -13654,7 +13959,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>F249</t>
+          <t>F339</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -13699,6 +14004,7 @@
       <c r="K250" t="n">
         <v>12</v>
       </c>
+      <c r="L250" t="inlineStr"/>
       <c r="M250" t="inlineStr">
         <is>
           <t>国家地理标志产品。中国金桔之乡遂川特产，千年贡果，宋代欧阳修誉之为珍果。果大皮薄、味甜微酸，10月中下旬成熟上市。</t>
@@ -13708,7 +14014,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>F250</t>
+          <t>F340</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -13753,6 +14059,7 @@
       <c r="K251" t="n">
         <v>10</v>
       </c>
+      <c r="L251" t="inlineStr"/>
       <c r="M251" t="inlineStr">
         <is>
           <t>国家地理标志产品（三重保护）。奉新县赤岸镇为核心产区，含红心、黄心、绿心多品种，8月下旬至10月下旬为盛产期，风味浓郁。</t>
@@ -13762,7 +14069,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>F251</t>
+          <t>F341</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13807,6 +14114,7 @@
       <c r="K252" t="n">
         <v>10.5</v>
       </c>
+      <c r="L252" t="inlineStr"/>
       <c r="M252" t="inlineStr">
         <is>
           <t>国家地理标志产品（2002年获批）。新郑灰枣、鸡心枣为代表，核小肉厚、味甜营养丰富。9月下旬至10月中旬集中采收，可供应至次年5月。</t>
@@ -13816,7 +14124,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>F252</t>
+          <t>F342</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13861,6 +14169,7 @@
       <c r="K253" t="n">
         <v>10</v>
       </c>
+      <c r="L253" t="inlineStr"/>
       <c r="M253" t="inlineStr">
         <is>
           <t>国家地理标志产品（2007年获批）。中州名果，产于荥阳邙岭，籽粒大、色紫红、味甘甜、无核软渣，秋分前后成熟。</t>
@@ -13870,7 +14179,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>F253</t>
+          <t>F343</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13915,6 +14224,7 @@
       <c r="K254" t="n">
         <v>5</v>
       </c>
+      <c r="L254" t="inlineStr"/>
       <c r="M254" t="inlineStr">
         <is>
           <t>国家地理标志产品暨农产品地理标志。中国露地早熟樱桃第一县，同品种比山东陕西早熟10天以上，5月盛产，色泽红艳、肉厚汁多。</t>
@@ -13969,6 +14279,7 @@
       <c r="K255" t="n">
         <v>9</v>
       </c>
+      <c r="L255" t="inlineStr"/>
       <c r="M255" t="inlineStr">
         <is>
           <t>国家地理标志产品暨农产品地理标志（2017年获批）。缑氏镇为核心产区，品种含夏黑、巨峰、阳光玫瑰等，7月至9月梯次成熟。</t>
@@ -14023,6 +14334,7 @@
       <c r="K256" t="n">
         <v>10</v>
       </c>
+      <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr">
         <is>
           <t>国家地理标志产品暨农产品地理标志。全国五大山楂产地之一，太行山深山区种植，果实鲜红、总糖含量10.58%，兼具食药价值。</t>
@@ -14077,6 +14389,7 @@
       <c r="K257" t="n">
         <v>6</v>
       </c>
+      <c r="L257" t="inlineStr"/>
       <c r="M257" t="inlineStr">
         <is>
           <t>国家地理标志产品（2011年获批）。渑池县果园乡李家村为核心产区，因果形似鸡蛋又称鸡蛋杏，核肉分离摇晃有声，栽培历史超2000年。</t>
@@ -14131,6 +14444,7 @@
       <c r="K258" t="n">
         <v>11</v>
       </c>
+      <c r="L258" t="inlineStr"/>
       <c r="M258" t="inlineStr">
         <is>
           <t>国家地理标志证明商标。中华名果，全县44万亩种植面积。山地气候使成熟期比同纬度产区提早约10天，9月中下旬至10月中下旬集中上市。</t>
@@ -14185,6 +14499,7 @@
       <c r="K259" t="n">
         <v>10</v>
       </c>
+      <c r="L259" t="inlineStr"/>
       <c r="M259" t="inlineStr">
         <is>
           <t>国家地理标志产品（2007年获批）。周恩来总理亲自审定命名，洞口县为中国雪峰蜜桔之乡。色泽鲜艳、皮薄汁多、甜味浓郁有蜂蜜香醇。</t>
@@ -14239,6 +14554,7 @@
       <c r="K260" t="n">
         <v>12.5</v>
       </c>
+      <c r="L260" t="inlineStr"/>
       <c r="M260" t="inlineStr">
         <is>
           <t>国家地理标志产品。中国冰糖橙之都，种植面积28.5万亩全国第一，土壤富含硒元素。糖酸比高达41.1:1，浓甜清香、肉质细嫩。</t>
@@ -14293,6 +14609,7 @@
       <c r="K261" t="n">
         <v>1</v>
       </c>
+      <c r="L261" t="inlineStr"/>
       <c r="M261" t="inlineStr">
         <is>
           <t>国家地理标志产品（2018年获批）。湘西山区特产，皮薄易剥、肉质脆嫩、耐贮藏，11月下旬成熟，可贮至次年3-4月风味不变。</t>
@@ -14347,6 +14664,7 @@
       <c r="K262" t="n">
         <v>12.5</v>
       </c>
+      <c r="L262" t="inlineStr"/>
       <c r="M262" t="inlineStr">
         <is>
           <t>国家地理标志产品（2008年获批，全国首批）。桃川镇为中国香柚之乡核心产区，果形似葫芦，底部有金钱花印环，富硒清香，耐贮4-5个月。</t>
@@ -14401,6 +14719,7 @@
       <c r="K263" t="n">
         <v>8.5</v>
       </c>
+      <c r="L263" t="inlineStr"/>
       <c r="M263" t="inlineStr">
         <is>
           <t>国家地理标志产品暨农产品地理标志。湖南首个国家级农产品地理标志示范样板。翠冠、圆黄、黄金三品种梯次上市，肉质乳白细嫩无渣。</t>
@@ -14455,6 +14774,7 @@
       <c r="K264" t="n">
         <v>11</v>
       </c>
+      <c r="L264" t="inlineStr"/>
       <c r="M264" t="inlineStr">
         <is>
           <t>国家农产品地理标志。浏阳沿溪镇等3乡镇保护面积1000公顷。果皮甜脆、果肉厚、味略酸，大棚覆盖可延迟至元月中下旬上市。</t>
@@ -14509,6 +14829,7 @@
       <c r="K265" t="n">
         <v>9</v>
       </c>
+      <c r="L265" t="inlineStr"/>
       <c r="M265" t="inlineStr">
         <is>
           <t>国家地理标志产品暨农产品地理标志。湘西凤凰县9.8万亩种植面积，红阳、东红等红心品种为主，8月下旬至9月上旬成熟，果心红色放射状、甜度高。</t>
@@ -14563,6 +14884,7 @@
       <c r="K266" t="n">
         <v>6</v>
       </c>
+      <c r="L266" t="inlineStr"/>
       <c r="M266" t="inlineStr">
         <is>
           <t>国家地理标志产品（三重保护）。产于新安江畔漳潭、绵潭、瀹潭三村，800余年栽培史。皮薄肉厚、鲜美多汁，5月中下旬至6月上旬集中上市。</t>
@@ -14617,6 +14939,7 @@
       <c r="K267" t="n">
         <v>6</v>
       </c>
+      <c r="L267" t="inlineStr"/>
       <c r="M267" t="inlineStr">
         <is>
           <t>国家地理标志产品暨农产品地理标志。淮北市首个农业地标产品。形似倒置笆斗，皮薄肉厚、酸甜适口。5月下旬至7月上旬采收。</t>
@@ -14671,6 +14994,7 @@
       <c r="K268" t="n">
         <v>7</v>
       </c>
+      <c r="L268" t="inlineStr"/>
       <c r="M268" t="inlineStr">
         <is>
           <t>国家地理标志产品暨农产品地理标志。砀山黄油桃果面全红或橙红、果肉浓黄色，可溶性固形物14.5%-16.8%，6月下旬至7月中旬主要上市。</t>
@@ -14717,14 +15041,15 @@
         <v>7</v>
       </c>
       <c r="I269" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J269" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="K269" t="n">
-        <v>7</v>
-      </c>
+        <v>8.5</v>
+      </c>
+      <c r="L269" t="inlineStr"/>
       <c r="M269" t="inlineStr">
         <is>
           <t>国家地理标志产品（2016年获批）。安徽四大名果之一，曾为皇家贡果。形似小苹果，皮薄汁多渣少、酸甜爽口，7月中下旬成熟。</t>
@@ -14779,6 +15104,7 @@
       <c r="K270" t="n">
         <v>5</v>
       </c>
+      <c r="L270" t="inlineStr"/>
       <c r="M270" t="inlineStr">
         <is>
           <t>中国四大著名樱桃品种之一，唐宋时期即为贡品，被誉为春果第一枝。沙颍河两岸种植，4月下旬成熟，比一般樱桃早熟10天以上。</t>
@@ -14816,6 +15142,7 @@
           <t>白水县</t>
         </is>
       </c>
+      <c r="G271" t="inlineStr"/>
       <c r="H271" t="n">
         <v>9</v>
       </c>
@@ -14828,6 +15155,7 @@
       <c r="K271" t="n">
         <v>12</v>
       </c>
+      <c r="L271" t="inlineStr"/>
       <c r="M271" t="inlineStr">
         <is>
           <t>国家地理标志产品。白水县是苹果优生区，果形端正、色泽鲜艳、酸甜适口，年产超百万吨。</t>
@@ -14865,6 +15193,7 @@
           <t>清涧县</t>
         </is>
       </c>
+      <c r="G272" t="inlineStr"/>
       <c r="H272" t="n">
         <v>9</v>
       </c>
@@ -14877,6 +15206,7 @@
       <c r="K272" t="n">
         <v>10</v>
       </c>
+      <c r="L272" t="inlineStr"/>
       <c r="M272" t="inlineStr">
         <is>
           <t>国家地理标志产品。皮薄肉厚、油分大、糖分高，陕北黄土高原独特气候孕育。</t>
@@ -14914,6 +15244,7 @@
           <t>城固县</t>
         </is>
       </c>
+      <c r="G273" t="inlineStr"/>
       <c r="H273" t="n">
         <v>10</v>
       </c>
@@ -14926,6 +15257,7 @@
       <c r="K273" t="n">
         <v>1</v>
       </c>
+      <c r="L273" t="inlineStr"/>
       <c r="M273" t="inlineStr">
         <is>
           <t>国家地理标志产品。中国最北缘柑橘产区，果形整齐、色泽艳丽、酸甜适口。</t>
@@ -14963,6 +15295,7 @@
           <t>彬州市</t>
         </is>
       </c>
+      <c r="G274" t="inlineStr"/>
       <c r="H274" t="n">
         <v>9</v>
       </c>
@@ -14975,6 +15308,7 @@
       <c r="K274" t="n">
         <v>10</v>
       </c>
+      <c r="L274" t="inlineStr"/>
       <c r="M274" t="inlineStr">
         <is>
           <t>国家地理标志产品。皮薄核小、汁多酥脆、甜酸适口，黄土高原沟壑区独特品质。</t>
@@ -15007,6 +15341,8 @@
           <t>延安市</t>
         </is>
       </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
       <c r="H275" t="n">
         <v>10</v>
       </c>
@@ -15019,6 +15355,7 @@
       <c r="K275" t="n">
         <v>3</v>
       </c>
+      <c r="L275" t="inlineStr"/>
       <c r="M275" t="inlineStr">
         <is>
           <t>陕北黄土高原优生区，海拔800-1300米，所产红富士苹果色泽鲜红、糖度高、耐储存。</t>
@@ -15051,6 +15388,8 @@
           <t>西安市</t>
         </is>
       </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
       <c r="H276" t="n">
         <v>12</v>
       </c>
@@ -15063,6 +15402,7 @@
       <c r="K276" t="n">
         <v>4</v>
       </c>
+      <c r="L276" t="inlineStr"/>
       <c r="M276" t="inlineStr">
         <is>
           <t>秦岭北麓无公害草莓产区，采用温室促成栽培，果大味甜，上市期跨越冬春两季。</t>
@@ -15100,6 +15440,7 @@
           <t>永春县</t>
         </is>
       </c>
+      <c r="G277" t="inlineStr"/>
       <c r="H277" t="n">
         <v>11</v>
       </c>
@@ -15112,6 +15453,7 @@
       <c r="K277" t="n">
         <v>2</v>
       </c>
+      <c r="L277" t="inlineStr"/>
       <c r="M277" t="inlineStr">
         <is>
           <t>国家地理标志产品。果实扁圆、色泽橙黄、汁多化渣、风味浓郁，素有'东方佳果'美誉。</t>
@@ -15144,6 +15486,8 @@
           <t>莆田市</t>
         </is>
       </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr"/>
       <c r="H278" t="n">
         <v>3</v>
       </c>
@@ -15156,6 +15500,7 @@
       <c r="K278" t="n">
         <v>5</v>
       </c>
+      <c r="L278" t="inlineStr"/>
       <c r="M278" t="inlineStr">
         <is>
           <t>国家地理标志产品，中国枇杷之乡。果大肉厚、汁多味甜、可食率高，早熟品种领先全国。</t>
@@ -15193,6 +15538,7 @@
           <t>闽侯县</t>
         </is>
       </c>
+      <c r="G279" t="inlineStr"/>
       <c r="H279" t="n">
         <v>7</v>
       </c>
@@ -15205,6 +15551,7 @@
       <c r="K279" t="n">
         <v>10</v>
       </c>
+      <c r="L279" t="inlineStr"/>
       <c r="M279" t="inlineStr">
         <is>
           <t>国家地理标志产品。福州特色水果，肉质脆嫩、回甘悠长，加工品种多样。</t>
@@ -15242,6 +15589,7 @@
           <t>诏安县</t>
         </is>
       </c>
+      <c r="G280" t="inlineStr"/>
       <c r="H280" t="n">
         <v>4</v>
       </c>
@@ -15254,6 +15602,7 @@
       <c r="K280" t="n">
         <v>5</v>
       </c>
+      <c r="L280" t="inlineStr"/>
       <c r="M280" t="inlineStr">
         <is>
           <t>国家地理标志产品。中国青梅之乡，果大肉厚核小、酸度高，是蜜饯和青梅酒的优质原料。</t>
@@ -15291,6 +15640,7 @@
           <t>建瓯市</t>
         </is>
       </c>
+      <c r="G281" t="inlineStr"/>
       <c r="H281" t="n">
         <v>9</v>
       </c>
@@ -15303,6 +15653,7 @@
       <c r="K281" t="n">
         <v>10</v>
       </c>
+      <c r="L281" t="inlineStr"/>
       <c r="M281" t="inlineStr">
         <is>
           <t>国家地理标志产品。中国锥栗之乡，果粒大、种仁饱满、糯性强、香甜可口。</t>
@@ -15340,6 +15691,7 @@
           <t>福鼎市</t>
         </is>
       </c>
+      <c r="G282" t="inlineStr"/>
       <c r="H282" t="n">
         <v>10</v>
       </c>
@@ -15352,6 +15704,7 @@
       <c r="K282" t="n">
         <v>1</v>
       </c>
+      <c r="L282" t="inlineStr"/>
       <c r="M282" t="inlineStr">
         <is>
           <t>国家地理标志产品。一年四季开花结果，果大皮薄、汁多味甜、清香爽口。</t>
@@ -15389,6 +15742,7 @@
           <t>长泰区</t>
         </is>
       </c>
+      <c r="G283" t="inlineStr"/>
       <c r="H283" t="n">
         <v>11</v>
       </c>
@@ -15401,6 +15755,7 @@
       <c r="K283" t="n">
         <v>2</v>
       </c>
+      <c r="L283" t="inlineStr"/>
       <c r="M283" t="inlineStr">
         <is>
           <t>国家地理标志产品。果大色艳、质脆化渣、汁多味甜，长泰县气候土壤适宜。</t>
@@ -15438,6 +15793,7 @@
           <t>闽侯县</t>
         </is>
       </c>
+      <c r="G284" t="inlineStr"/>
       <c r="H284" t="n">
         <v>6</v>
       </c>
@@ -15450,6 +15806,7 @@
       <c r="K284" t="n">
         <v>7</v>
       </c>
+      <c r="L284" t="inlineStr"/>
       <c r="M284" t="inlineStr">
         <is>
           <t>福州荔枝主产县，品种有元红、兰竹等，果肉厚、汁多味甜、香气浓郁。</t>
@@ -15504,6 +15861,7 @@
       <c r="K285" t="n">
         <v>1</v>
       </c>
+      <c r="L285" t="inlineStr"/>
       <c r="M285" t="inlineStr">
         <is>
           <t>国家地理标志产品。'涌泉蜜桔'闻名全国，果皮薄、肉质细嫩、无核化渣、甜度极高。</t>
@@ -15541,6 +15899,7 @@
           <t>黄岩区</t>
         </is>
       </c>
+      <c r="G286" t="inlineStr"/>
       <c r="H286" t="n">
         <v>10</v>
       </c>
@@ -15553,6 +15912,7 @@
       <c r="K286" t="n">
         <v>1</v>
       </c>
+      <c r="L286" t="inlineStr"/>
       <c r="M286" t="inlineStr">
         <is>
           <t>国家地理标志产品。中国蜜桔之乡，有1700多年种植历史，果皮薄韧、汁多味甜。</t>
@@ -15590,6 +15950,7 @@
           <t>象山县</t>
         </is>
       </c>
+      <c r="G287" t="inlineStr"/>
       <c r="H287" t="n">
         <v>11</v>
       </c>
@@ -15602,6 +15963,7 @@
       <c r="K287" t="n">
         <v>1</v>
       </c>
+      <c r="L287" t="inlineStr"/>
       <c r="M287" t="inlineStr">
         <is>
           <t>国家地理标志产品。品种为'爱媛28号'，果皮极薄、肉质极细嫩化渣、甜度14°以上。</t>
@@ -15639,11 +16001,12 @@
           <t>余姚市</t>
         </is>
       </c>
+      <c r="G288" t="inlineStr"/>
       <c r="H288" t="n">
         <v>6</v>
       </c>
       <c r="I288" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J288" t="n">
         <v>6</v>
@@ -15651,6 +16014,7 @@
       <c r="K288" t="n">
         <v>7</v>
       </c>
+      <c r="L288" t="inlineStr"/>
       <c r="M288" t="inlineStr">
         <is>
           <t>国家地理标志产品。栽培历史千年以上，品种以荸荠种为主，果色深紫、酸甜适口。</t>
@@ -15683,6 +16047,8 @@
           <t>衢州市</t>
         </is>
       </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr"/>
       <c r="H289" t="n">
         <v>11</v>
       </c>
@@ -15695,6 +16061,7 @@
       <c r="K289" t="n">
         <v>2</v>
       </c>
+      <c r="L289" t="inlineStr"/>
       <c r="M289" t="inlineStr">
         <is>
           <t>国家地理标志产品。果形端正、色泽橙黄、皮松易剥、囊瓣肥大、汁多味甜。</t>
@@ -15732,6 +16099,7 @@
           <t>常山县</t>
         </is>
       </c>
+      <c r="G290" t="inlineStr"/>
       <c r="H290" t="n">
         <v>11</v>
       </c>
@@ -15744,6 +16112,7 @@
       <c r="K290" t="n">
         <v>2</v>
       </c>
+      <c r="L290" t="inlineStr"/>
       <c r="M290" t="inlineStr">
         <is>
           <t>国家地理标志产品。橘柚天然杂交品种，果肉脆嫩、酸甜微苦、清火明目、耐贮藏。</t>
@@ -15781,11 +16150,12 @@
           <t>桐乡市</t>
         </is>
       </c>
+      <c r="G291" t="inlineStr"/>
       <c r="H291" t="n">
         <v>6</v>
       </c>
       <c r="I291" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J291" t="n">
         <v>6</v>
@@ -15793,6 +16163,7 @@
       <c r="K291" t="n">
         <v>7</v>
       </c>
+      <c r="L291" t="inlineStr"/>
       <c r="M291" t="inlineStr">
         <is>
           <t>国家地理标志产品。中国最古老名李之一，果大色艳、肉质细嫩、汁液极多、甜中微酸。</t>
@@ -15825,6 +16196,8 @@
           <t>大连市</t>
         </is>
       </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr"/>
       <c r="H292" t="n">
         <v>5</v>
       </c>
@@ -15837,6 +16210,7 @@
       <c r="K292" t="n">
         <v>7</v>
       </c>
+      <c r="L292" t="inlineStr"/>
       <c r="M292" t="inlineStr">
         <is>
           <t>国家地理标志产品。大连温室樱桃全国最早上市，果大色艳、肉硬味甜，设施+露地结合拉长供应期。</t>
@@ -15869,6 +16243,8 @@
           <t>丹东市</t>
         </is>
       </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr"/>
       <c r="H293" t="n">
         <v>12</v>
       </c>
@@ -15881,6 +16257,7 @@
       <c r="K293" t="n">
         <v>4</v>
       </c>
+      <c r="L293" t="inlineStr"/>
       <c r="M293" t="inlineStr">
         <is>
           <t>国家地理标志产品。中国草莓第一市，主栽品种'红颜'(九九草莓)，果大味浓、色泽鲜红，温室促成栽培。</t>
@@ -15918,6 +16295,7 @@
           <t>盖州市</t>
         </is>
       </c>
+      <c r="G294" t="inlineStr"/>
       <c r="H294" t="n">
         <v>8</v>
       </c>
@@ -15930,6 +16308,7 @@
       <c r="K294" t="n">
         <v>10</v>
       </c>
+      <c r="L294" t="inlineStr"/>
       <c r="M294" t="inlineStr">
         <is>
           <t>国家地理标志产品。辽南葡萄主产县，品种以巨峰为主，果粒大、色泽深紫、甜酸适口。</t>
@@ -15967,6 +16346,7 @@
           <t>绥中县</t>
         </is>
       </c>
+      <c r="G295" t="inlineStr"/>
       <c r="H295" t="n">
         <v>9</v>
       </c>
@@ -15979,6 +16359,7 @@
       <c r="K295" t="n">
         <v>10</v>
       </c>
+      <c r="L295" t="inlineStr"/>
       <c r="M295" t="inlineStr">
         <is>
           <t>国家地理标志产品。果皮金黄、果肉白色、脆嫩多汁、酸甜适口，是中国优质白梨代表。</t>
@@ -16016,6 +16397,7 @@
           <t>辽中区</t>
         </is>
       </c>
+      <c r="G296" t="inlineStr"/>
       <c r="H296" t="n">
         <v>10</v>
       </c>
@@ -16028,6 +16410,7 @@
       <c r="K296" t="n">
         <v>3</v>
       </c>
+      <c r="L296" t="inlineStr"/>
       <c r="M296" t="inlineStr">
         <is>
           <t>国家地理标志产品。耐寒苹果品种，适合东北气候，果个大、色泽红、酸甜适口。</t>
@@ -16065,6 +16448,7 @@
           <t>庄河市</t>
         </is>
       </c>
+      <c r="G297" t="inlineStr"/>
       <c r="H297" t="n">
         <v>6</v>
       </c>
@@ -16077,6 +16461,7 @@
       <c r="K297" t="n">
         <v>8</v>
       </c>
+      <c r="L297" t="inlineStr"/>
       <c r="M297" t="inlineStr">
         <is>
           <t>国家地理标志产品。庄河市土壤偏酸、气候凉爽，所产蓝莓果粉厚、甜酸适口、花青素含量高。</t>
@@ -16109,11 +16494,13 @@
           <t>朝阳市</t>
         </is>
       </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr"/>
       <c r="H298" t="n">
         <v>9</v>
       </c>
       <c r="I298" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J298" t="n">
         <v>9</v>
@@ -16121,6 +16508,7 @@
       <c r="K298" t="n">
         <v>10</v>
       </c>
+      <c r="L298" t="inlineStr"/>
       <c r="M298" t="inlineStr">
         <is>
           <t>辽西干旱地区优质大枣，皮薄肉厚、核小糖高，朝阳小枣（平顶枣）品种独特。</t>
@@ -16153,6 +16541,8 @@
           <t>苏州市</t>
         </is>
       </c>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr"/>
       <c r="H299" t="n">
         <v>6</v>
       </c>
@@ -16165,6 +16555,7 @@
       <c r="K299" t="n">
         <v>8</v>
       </c>
+      <c r="L299" t="inlineStr"/>
       <c r="M299" t="inlineStr">
         <is>
           <t>苏州东山、西山产区，与碧螺春茶园套种，果味清香独特。实际产品为洞庭枇杷、杨梅等套种水果。</t>
@@ -16202,6 +16593,7 @@
           <t>句容市</t>
         </is>
       </c>
+      <c r="G300" t="inlineStr"/>
       <c r="H300" t="n">
         <v>7</v>
       </c>
@@ -16214,6 +16606,7 @@
       <c r="K300" t="n">
         <v>9</v>
       </c>
+      <c r="L300" t="inlineStr"/>
       <c r="M300" t="inlineStr">
         <is>
           <t>国家地理标志产品。江苏最大鲜食葡萄产区，以巨峰、夏黑为主，果粒大、色泽深、甜度高。</t>
@@ -16268,6 +16661,7 @@
       <c r="K301" t="n">
         <v>7</v>
       </c>
+      <c r="L301" t="inlineStr"/>
       <c r="M301" t="inlineStr">
         <is>
           <t>国家地理标志产品阳山水蜜桃，中国最著名水蜜桃品牌。果大皮薄、汁多味甜、入口即化。</t>
@@ -16305,11 +16699,12 @@
           <t>吴中区</t>
         </is>
       </c>
+      <c r="G302" t="inlineStr"/>
       <c r="H302" t="n">
         <v>5</v>
       </c>
       <c r="I302" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J302" t="n">
         <v>5</v>
@@ -16317,6 +16712,7 @@
       <c r="K302" t="n">
         <v>6</v>
       </c>
+      <c r="L302" t="inlineStr"/>
       <c r="M302" t="inlineStr">
         <is>
           <t>国家地理标志产品东山白沙枇杷。果肉洁白、细嫩多汁、甜中微酸，太湖东山独特小气候。</t>
@@ -16354,6 +16750,7 @@
           <t>丰县</t>
         </is>
       </c>
+      <c r="G303" t="inlineStr"/>
       <c r="H303" t="n">
         <v>9</v>
       </c>
@@ -16366,6 +16763,7 @@
       <c r="K303" t="n">
         <v>12</v>
       </c>
+      <c r="L303" t="inlineStr"/>
       <c r="M303" t="inlineStr">
         <is>
           <t>国家地理标志产品。江苏最大苹果产区，黄淮平原优生区，果个大、色泽艳、甜酸适口。</t>
@@ -16403,6 +16801,7 @@
           <t>溧水区</t>
         </is>
       </c>
+      <c r="G304" t="inlineStr"/>
       <c r="H304" t="n">
         <v>12</v>
       </c>
@@ -16415,6 +16814,7 @@
       <c r="K304" t="n">
         <v>3</v>
       </c>
+      <c r="L304" t="inlineStr"/>
       <c r="M304" t="inlineStr">
         <is>
           <t>国家地理标志产品。长江流域冬季草莓优势区，温室促成栽培，果大味甜、色泽鲜红。</t>
@@ -16452,6 +16852,7 @@
           <t>江都区</t>
         </is>
       </c>
+      <c r="G305" t="inlineStr"/>
       <c r="H305" t="n">
         <v>9</v>
       </c>
@@ -16464,6 +16865,7 @@
       <c r="K305" t="n">
         <v>11</v>
       </c>
+      <c r="L305" t="inlineStr"/>
       <c r="M305" t="inlineStr">
         <is>
           <t>苏中地区特色猕猴桃产区，依托里下河平原优质土壤，果肉细嫩、甜酸适口。</t>
@@ -16501,6 +16903,7 @@
           <t>句容市</t>
         </is>
       </c>
+      <c r="G306" t="inlineStr"/>
       <c r="H306" t="n">
         <v>7</v>
       </c>
@@ -16513,6 +16916,7 @@
       <c r="K306" t="n">
         <v>9</v>
       </c>
+      <c r="L306" t="inlineStr"/>
       <c r="M306" t="inlineStr">
         <is>
           <t>茅山丘陵地区优质葡萄产区，以巨峰、夏黑、阳光玫瑰为主，果粒大、甜度高。</t>
@@ -16550,6 +16954,7 @@
           <t>秦州区</t>
         </is>
       </c>
+      <c r="G307" t="inlineStr"/>
       <c r="H307" t="n">
         <v>9</v>
       </c>
@@ -16562,6 +16967,7 @@
       <c r="K307" t="n">
         <v>10</v>
       </c>
+      <c r="L307" t="inlineStr"/>
       <c r="M307" t="inlineStr">
         <is>
           <t>国家地理标志产品。元帅系苹果优生区，形色味俱佳，果形高粱、五棱突起、肉质细脆、香甜多汁。</t>
@@ -16594,6 +17000,8 @@
           <t>兰州市</t>
         </is>
       </c>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr"/>
       <c r="H308" t="n">
         <v>9</v>
       </c>
@@ -16606,6 +17014,7 @@
       <c r="K308" t="n">
         <v>2</v>
       </c>
+      <c r="L308" t="inlineStr"/>
       <c r="M308" t="inlineStr">
         <is>
           <t>国家地理标志产品。兰州特有品种，果大皮薄、肉质细脆、汁多味甜，耐贮藏至次年春天。</t>
@@ -16643,11 +17052,12 @@
           <t>漠河市</t>
         </is>
       </c>
+      <c r="G309" t="inlineStr"/>
       <c r="H309" t="n">
         <v>7</v>
       </c>
       <c r="I309" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J309" t="n">
         <v>7</v>
@@ -16655,6 +17065,7 @@
       <c r="K309" t="n">
         <v>8</v>
       </c>
+      <c r="L309" t="inlineStr"/>
       <c r="M309" t="inlineStr">
         <is>
           <t>国家地理标志产品。中国最北野生蓝莓产区，果实小但花青素极高、风味浓郁独特。</t>
@@ -16687,6 +17098,8 @@
           <t>牡丹江市</t>
         </is>
       </c>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr"/>
       <c r="H310" t="n">
         <v>9</v>
       </c>
@@ -16699,6 +17112,7 @@
       <c r="K310" t="n">
         <v>10</v>
       </c>
+      <c r="L310" t="inlineStr"/>
       <c r="M310" t="inlineStr">
         <is>
           <t>中国最大的沙棘种植基地之一，耐寒品种，果实橙黄、维生素C含量极高、酸甜适口。</t>
@@ -16736,6 +17150,7 @@
           <t>延吉市</t>
         </is>
       </c>
+      <c r="G311" t="inlineStr"/>
       <c r="H311" t="n">
         <v>9</v>
       </c>
@@ -16748,6 +17163,7 @@
       <c r="K311" t="n">
         <v>10</v>
       </c>
+      <c r="L311" t="inlineStr"/>
       <c r="M311" t="inlineStr">
         <is>
           <t>国家地理标志产品延边苹果梨。苹果与梨的天然杂交，果大形正、肉质细脆、酸甜可口、耐贮藏。</t>
@@ -16780,11 +17196,13 @@
           <t>白山市</t>
         </is>
       </c>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr"/>
       <c r="H312" t="n">
         <v>7</v>
       </c>
       <c r="I312" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J312" t="n">
         <v>7</v>
@@ -16792,6 +17210,7 @@
       <c r="K312" t="n">
         <v>8</v>
       </c>
+      <c r="L312" t="inlineStr"/>
       <c r="M312" t="inlineStr">
         <is>
           <t>国家地理标志产品。长白山区野生蓝莓，高海拔冷凉气候，果实花青素含量极高，风味浓郁。</t>
@@ -16824,11 +17243,13 @@
           <t>通化市</t>
         </is>
       </c>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr"/>
       <c r="H313" t="n">
         <v>9</v>
       </c>
       <c r="I313" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J313" t="n">
         <v>9</v>
@@ -16836,6 +17257,7 @@
       <c r="K313" t="n">
         <v>10</v>
       </c>
+      <c r="L313" t="inlineStr"/>
       <c r="M313" t="inlineStr">
         <is>
           <t>国家地理标志产品。长白山区野生山葡萄，抗寒力极强，果实小而色深，是酿制冰葡萄酒的优质原料。</t>
@@ -16868,11 +17290,13 @@
           <t>四平市</t>
         </is>
       </c>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr"/>
       <c r="H314" t="n">
         <v>9</v>
       </c>
       <c r="I314" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J314" t="n">
         <v>9</v>
@@ -16880,6 +17304,7 @@
       <c r="K314" t="n">
         <v>10</v>
       </c>
+      <c r="L314" t="inlineStr"/>
       <c r="M314" t="inlineStr">
         <is>
           <t>东北地区优质山楂产区，果实大、色泽红、酸度高，适合加工和鲜食。</t>
@@ -16917,6 +17342,7 @@
           <t>临猗县</t>
         </is>
       </c>
+      <c r="G315" t="inlineStr"/>
       <c r="H315" t="n">
         <v>10</v>
       </c>
@@ -16929,6 +17355,7 @@
       <c r="K315" t="n">
         <v>3</v>
       </c>
+      <c r="L315" t="inlineStr"/>
       <c r="M315" t="inlineStr">
         <is>
           <t>国家地理标志产品。山西最大苹果产区，黄土高原优生区，果个大、色泽红、糖度高、耐贮存。</t>
@@ -16961,6 +17388,8 @@
           <t>吕梁市</t>
         </is>
       </c>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr"/>
       <c r="H316" t="n">
         <v>9</v>
       </c>
@@ -16973,6 +17402,7 @@
       <c r="K316" t="n">
         <v>10</v>
       </c>
+      <c r="L316" t="inlineStr"/>
       <c r="M316" t="inlineStr">
         <is>
           <t>国家地理标志产品。黄河沿岸红枣优生区，皮薄肉厚、含糖量高、营养丰富，木枣品种闻名。</t>
@@ -17005,6 +17435,8 @@
           <t>晋中市</t>
         </is>
       </c>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr"/>
       <c r="H317" t="n">
         <v>8</v>
       </c>
@@ -17017,6 +17449,7 @@
       <c r="K317" t="n">
         <v>10</v>
       </c>
+      <c r="L317" t="inlineStr"/>
       <c r="M317" t="inlineStr">
         <is>
           <t>晋中盆地优质葡萄产区，以巨峰、无核白等品种为主，甜度高、品质佳。</t>
@@ -17049,11 +17482,13 @@
           <t>晋城市</t>
         </is>
       </c>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr"/>
       <c r="H318" t="n">
         <v>9</v>
       </c>
       <c r="I318" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J318" t="n">
         <v>9</v>
@@ -17061,6 +17496,7 @@
       <c r="K318" t="n">
         <v>10</v>
       </c>
+      <c r="L318" t="inlineStr"/>
       <c r="M318" t="inlineStr">
         <is>
           <t>太行山区优质山楂产区，果实大、色泽红艳、酸味纯正。</t>
@@ -17098,6 +17534,7 @@
           <t>万州区</t>
         </is>
       </c>
+      <c r="G319" t="inlineStr"/>
       <c r="H319" t="n">
         <v>10</v>
       </c>
@@ -17110,6 +17547,7 @@
       <c r="K319" t="n">
         <v>2</v>
       </c>
+      <c r="L319" t="inlineStr"/>
       <c r="M319" t="inlineStr">
         <is>
           <t>国家地理标志产品。三峡库区特有气候，果大皮薄、汁多味酸、香气浓郁。</t>
@@ -17147,6 +17585,7 @@
           <t>长寿区</t>
         </is>
       </c>
+      <c r="G320" t="inlineStr"/>
       <c r="H320" t="n">
         <v>11</v>
       </c>
@@ -17159,6 +17598,7 @@
       <c r="K320" t="n">
         <v>1</v>
       </c>
+      <c r="L320" t="inlineStr"/>
       <c r="M320" t="inlineStr">
         <is>
           <t>国家地理标志产品。果形端正、果皮金黄、果肉脆嫩、汁多味甜微酸。</t>
@@ -17196,6 +17636,7 @@
           <t>江津区</t>
         </is>
       </c>
+      <c r="G321" t="inlineStr"/>
       <c r="H321" t="n">
         <v>10</v>
       </c>
@@ -17208,6 +17649,7 @@
       <c r="K321" t="n">
         <v>2</v>
       </c>
+      <c r="L321" t="inlineStr"/>
       <c r="M321" t="inlineStr">
         <is>
           <t>重庆最大柑橘产区，长江沿岸优质甜橙、锦橙基地，汁多味甜。</t>
@@ -17245,6 +17687,7 @@
           <t>永川区</t>
         </is>
       </c>
+      <c r="G322" t="inlineStr"/>
       <c r="H322" t="n">
         <v>8</v>
       </c>
@@ -17257,6 +17700,7 @@
       <c r="K322" t="n">
         <v>9</v>
       </c>
+      <c r="L322" t="inlineStr"/>
       <c r="M322" t="inlineStr">
         <is>
           <t>渝西优质梨产区，果皮薄、肉质细脆、汁多味甜。</t>
@@ -17294,6 +17738,7 @@
           <t>忠县</t>
         </is>
       </c>
+      <c r="G323" t="inlineStr"/>
       <c r="H323" t="n">
         <v>10</v>
       </c>
@@ -17306,6 +17751,7 @@
       <c r="K323" t="n">
         <v>2</v>
       </c>
+      <c r="L323" t="inlineStr"/>
       <c r="M323" t="inlineStr">
         <is>
           <t>三峡库区柑橘产业带核心县，哈姆林甜橙、夏橙等优质品种。</t>
@@ -17338,6 +17784,8 @@
           <t>吴忠市</t>
         </is>
       </c>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr"/>
       <c r="H324" t="n">
         <v>8</v>
       </c>
@@ -17350,6 +17798,7 @@
       <c r="K324" t="n">
         <v>10</v>
       </c>
+      <c r="L324" t="inlineStr"/>
       <c r="M324" t="inlineStr">
         <is>
           <t>国家地理标志产品贺兰山东麓葡萄酒产区，鲜食葡萄品质同样出众，果粒大、糖度高。</t>
@@ -17382,6 +17831,8 @@
           <t>海东市</t>
         </is>
       </c>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr"/>
       <c r="H325" t="n">
         <v>6</v>
       </c>
@@ -17394,6 +17845,7 @@
       <c r="K325" t="n">
         <v>7</v>
       </c>
+      <c r="L325" t="inlineStr"/>
       <c r="M325" t="inlineStr">
         <is>
           <t>青海东部河谷地区优质大樱桃产区，高海拔冷凉气候，果大色艳、甜度高。</t>
@@ -17426,6 +17878,8 @@
           <t>海南藏族自治州</t>
         </is>
       </c>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr"/>
       <c r="H326" t="n">
         <v>9</v>
       </c>
@@ -17438,6 +17892,7 @@
       <c r="K326" t="n">
         <v>10</v>
       </c>
+      <c r="L326" t="inlineStr"/>
       <c r="M326" t="inlineStr">
         <is>
           <t>黄河河谷独特品种，果皮薄、果肉软、汁多酸甜，冷冻后风味更佳。</t>
@@ -17475,6 +17930,7 @@
           <t>磴口县</t>
         </is>
       </c>
+      <c r="G327" t="inlineStr"/>
       <c r="H327" t="n">
         <v>7</v>
       </c>
@@ -17487,6 +17943,7 @@
       <c r="K327" t="n">
         <v>8</v>
       </c>
+      <c r="L327" t="inlineStr"/>
       <c r="M327" t="inlineStr">
         <is>
           <t>国家地理标志产品。河套地区特有的甜瓜品种，果皮金黄、果肉翠绿、汁多味甜、香气浓郁。</t>
@@ -17519,6 +17976,8 @@
           <t>赤峰市</t>
         </is>
       </c>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr"/>
       <c r="H328" t="n">
         <v>9</v>
       </c>
@@ -17531,6 +17990,7 @@
       <c r="K328" t="n">
         <v>10</v>
       </c>
+      <c r="L328" t="inlineStr"/>
       <c r="M328" t="inlineStr">
         <is>
           <t>内蒙古东部沙棘优势产区，果实橙红、维生素含量极高、酸甜适口。</t>
@@ -17568,6 +18028,7 @@
           <t>昌平区</t>
         </is>
       </c>
+      <c r="G329" t="inlineStr"/>
       <c r="H329" t="n">
         <v>12</v>
       </c>
@@ -17580,6 +18041,7 @@
       <c r="K329" t="n">
         <v>4</v>
       </c>
+      <c r="L329" t="inlineStr"/>
       <c r="M329" t="inlineStr">
         <is>
           <t>国家地理标志产品。北京冬季草莓主产区，温室促成栽培，果大味甜、品质佳。</t>
@@ -17617,6 +18079,7 @@
           <t>密云区</t>
         </is>
       </c>
+      <c r="G330" t="inlineStr"/>
       <c r="H330" t="n">
         <v>5</v>
       </c>
@@ -17629,6 +18092,7 @@
       <c r="K330" t="n">
         <v>7</v>
       </c>
+      <c r="L330" t="inlineStr"/>
       <c r="M330" t="inlineStr">
         <is>
           <t>北京优质樱桃产区，密云水库周边独特小气候，果大色艳、甜酸适口。</t>
@@ -17666,6 +18130,7 @@
           <t>蓟州区</t>
         </is>
       </c>
+      <c r="G331" t="inlineStr"/>
       <c r="H331" t="n">
         <v>10</v>
       </c>
@@ -17678,6 +18143,7 @@
       <c r="K331" t="n">
         <v>11</v>
       </c>
+      <c r="L331" t="inlineStr"/>
       <c r="M331" t="inlineStr">
         <is>
           <t>国家地理标志产品。盘山磨盘柿，果个大、皮薄汁多、味甜无核，可鲜食可制饼。</t>
@@ -17715,6 +18181,7 @@
           <t>滨海新区</t>
         </is>
       </c>
+      <c r="G332" t="inlineStr"/>
       <c r="H332" t="n">
         <v>8</v>
       </c>
@@ -17727,6 +18194,7 @@
       <c r="K332" t="n">
         <v>10</v>
       </c>
+      <c r="L332" t="inlineStr"/>
       <c r="M332" t="inlineStr">
         <is>
           <t>天津滨海盐碱地改良葡萄产区，以茶淀玫瑰香葡萄闻名，果粒小但香气浓郁、甜度高。</t>
@@ -17764,6 +18232,7 @@
           <t>武清区</t>
         </is>
       </c>
+      <c r="G333" t="inlineStr"/>
       <c r="H333" t="n">
         <v>6</v>
       </c>
@@ -17776,6 +18245,7 @@
       <c r="K333" t="n">
         <v>7</v>
       </c>
+      <c r="L333" t="inlineStr"/>
       <c r="M333" t="inlineStr">
         <is>
           <t>天津传统西瓜产区，沙质土壤、光照充足，瓜大皮薄、沙甜多汁。</t>
@@ -17813,6 +18283,7 @@
           <t>崇明区</t>
         </is>
       </c>
+      <c r="G334" t="inlineStr"/>
       <c r="H334" t="n">
         <v>10</v>
       </c>
@@ -17825,6 +18296,7 @@
       <c r="K334" t="n">
         <v>1</v>
       </c>
+      <c r="L334" t="inlineStr"/>
       <c r="M334" t="inlineStr">
         <is>
           <t>上海最大柑橘产区，长江口冲积岛独特沙性土壤，果皮薄、汁多味甜。</t>
@@ -17862,6 +18334,7 @@
           <t>嘉定区</t>
         </is>
       </c>
+      <c r="G335" t="inlineStr"/>
       <c r="H335" t="n">
         <v>7</v>
       </c>
@@ -17874,6 +18347,7 @@
       <c r="K335" t="n">
         <v>9</v>
       </c>
+      <c r="L335" t="inlineStr"/>
       <c r="M335" t="inlineStr">
         <is>
           <t>国家地理标志产品马陆葡萄。上海精品葡萄代表，以巨峰为主，果粒大、色泽深、甜度高。</t>
@@ -22748,6 +23222,7 @@
           <t>丹棱县</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="n">
         <v>103.53</v>
       </c>
@@ -22786,6 +23261,7 @@
           <t>东坡区</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="n">
         <v>103.83</v>
       </c>
@@ -22824,6 +23300,7 @@
           <t>蒲江县</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="n">
         <v>103.51</v>
       </c>
@@ -22862,6 +23339,7 @@
           <t>金堂县</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="n">
         <v>104.41</v>
       </c>
@@ -22900,6 +23378,7 @@
           <t>丹棱县</t>
         </is>
       </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
         <v>103.53</v>
       </c>
@@ -22938,6 +23417,7 @@
           <t>蒲江县</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
         <v>103.51</v>
       </c>
@@ -22976,6 +23456,7 @@
           <t>名山区</t>
         </is>
       </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
         <v>103.11</v>
       </c>
@@ -23014,6 +23495,7 @@
           <t>安岳县</t>
         </is>
       </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
         <v>105.34</v>
       </c>
@@ -23052,6 +23534,7 @@
           <t>苍溪县</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
         <v>105.93</v>
       </c>
@@ -23090,6 +23573,7 @@
           <t>金川县</t>
         </is>
       </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
         <v>102.06</v>
       </c>
@@ -23128,6 +23612,7 @@
           <t>龙泉驿区</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
         <v>104.27</v>
       </c>
@@ -23166,6 +23651,7 @@
           <t>双流区</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
         <v>103.92</v>
       </c>
@@ -23204,6 +23690,7 @@
           <t>攀枝花市</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="n">
         <v>102.26</v>
       </c>
@@ -23242,6 +23729,7 @@
           <t>攀枝花市</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
         <v>101.72</v>
       </c>
@@ -23280,6 +23768,7 @@
           <t>仁和区</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
         <v>101.74</v>
       </c>
@@ -23318,6 +23807,7 @@
           <t>米易县</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="n">
         <v>102.11</v>
       </c>
@@ -23356,6 +23846,7 @@
           <t>会理市</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="n">
         <v>102.25</v>
       </c>
@@ -23394,6 +23885,7 @@
           <t>双流区</t>
         </is>
       </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="n">
         <v>103.92</v>
       </c>
@@ -23432,6 +23924,7 @@
           <t>新平县</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="n">
         <v>101.99</v>
       </c>
@@ -23470,6 +23963,7 @@
           <t>宾川县</t>
         </is>
       </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="n">
         <v>100.58</v>
       </c>
@@ -23508,6 +24002,7 @@
           <t>建水县</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="n">
         <v>102.83</v>
       </c>
@@ -23546,6 +24041,7 @@
           <t>新平县</t>
         </is>
       </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="n">
         <v>101.99</v>
       </c>
@@ -23584,6 +24080,7 @@
           <t>华宁县</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="n">
         <v>102.93</v>
       </c>
@@ -23622,6 +24119,7 @@
           <t>建水县</t>
         </is>
       </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="n">
         <v>102.83</v>
       </c>
@@ -23660,6 +24158,7 @@
           <t>宾川县</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="n">
         <v>100.58</v>
       </c>
@@ -23698,6 +24197,7 @@
           <t>元谋县</t>
         </is>
       </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="n">
         <v>101.87</v>
       </c>
@@ -23736,6 +24236,7 @@
           <t>建水县</t>
         </is>
       </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="n">
         <v>102.83</v>
       </c>
@@ -23774,6 +24275,7 @@
           <t>元谋县</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="n">
         <v>101.87</v>
       </c>
@@ -23812,6 +24314,7 @@
           <t>弥勒市</t>
         </is>
       </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="n">
         <v>103.41</v>
       </c>
@@ -23850,6 +24353,7 @@
           <t>沾益区</t>
         </is>
       </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
         <v>103.82</v>
       </c>
@@ -23888,6 +24392,7 @@
           <t>澄江市</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
         <v>102.91</v>
       </c>
@@ -23926,6 +24431,7 @@
           <t>大理州</t>
         </is>
       </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
         <v>100.23</v>
       </c>
@@ -23964,6 +24470,7 @@
           <t>宾川县</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
         <v>100.58</v>
       </c>
@@ -24002,6 +24509,7 @@
           <t>蒙自市</t>
         </is>
       </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
         <v>103.36</v>
       </c>
@@ -24040,6 +24548,7 @@
           <t>永仁县</t>
         </is>
       </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="n">
         <v>101.67</v>
       </c>
@@ -24078,6 +24587,7 @@
           <t>华坪县</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="n">
         <v>101.27</v>
       </c>
@@ -24116,6 +24626,7 @@
           <t>元阳县</t>
         </is>
       </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="n">
         <v>102.83</v>
       </c>
@@ -24154,6 +24665,7 @@
           <t>永德县</t>
         </is>
       </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="n">
         <v>99.26000000000001</v>
       </c>
@@ -24192,6 +24704,7 @@
           <t>丘北县</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="n">
         <v>104.19</v>
       </c>
@@ -24230,6 +24743,7 @@
           <t>开远市</t>
         </is>
       </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="n">
         <v>103.27</v>
       </c>
@@ -24268,6 +24782,7 @@
           <t>富民县</t>
         </is>
       </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="n">
         <v>102.5</v>
       </c>
@@ -24306,6 +24821,7 @@
           <t>昭阳区</t>
         </is>
       </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="n">
         <v>103.71</v>
       </c>
@@ -24344,6 +24860,7 @@
           <t>高州市</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="n">
         <v>110.85</v>
       </c>
@@ -24382,6 +24899,7 @@
           <t>增城区</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
         <v>113.81</v>
       </c>
@@ -24420,6 +24938,7 @@
           <t>高州市</t>
         </is>
       </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
         <v>110.85</v>
       </c>
@@ -24458,6 +24977,7 @@
           <t>阳东区</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>112.01</v>
       </c>
@@ -24496,6 +25016,7 @@
           <t>四会市</t>
         </is>
       </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
         <v>112.73</v>
       </c>
@@ -24534,6 +25055,7 @@
           <t>清远市</t>
         </is>
       </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
         <v>113.06</v>
       </c>
@@ -24572,6 +25094,7 @@
           <t>梅县区</t>
         </is>
       </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
         <v>116.1</v>
       </c>
@@ -24610,6 +25133,7 @@
           <t>高州市</t>
         </is>
       </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
         <v>110.85</v>
       </c>
@@ -24648,6 +25172,7 @@
           <t>徐闻县</t>
         </is>
       </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>110.18</v>
       </c>
@@ -24686,6 +25211,7 @@
           <t>荔浦市</t>
         </is>
       </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
         <v>110.39</v>
       </c>
@@ -24724,6 +25250,7 @@
           <t>蒙山县</t>
         </is>
       </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="n">
         <v>110.52</v>
       </c>
@@ -24762,6 +25289,7 @@
           <t>象州县</t>
         </is>
       </c>
+      <c r="E166" t="inlineStr"/>
       <c r="F166" t="n">
         <v>109.68</v>
       </c>
@@ -24800,6 +25328,7 @@
           <t>武鸣区</t>
         </is>
       </c>
+      <c r="E167" t="inlineStr"/>
       <c r="F167" t="n">
         <v>108.28</v>
       </c>
@@ -24838,6 +25367,7 @@
           <t>田东县</t>
         </is>
       </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="n">
         <v>107.12</v>
       </c>
@@ -24876,6 +25406,7 @@
           <t>隆安县</t>
         </is>
       </c>
+      <c r="E169" t="inlineStr"/>
       <c r="F169" t="n">
         <v>107.7</v>
       </c>
@@ -24914,6 +25445,7 @@
           <t>扶绥县</t>
         </is>
       </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="n">
         <v>107.9</v>
       </c>
@@ -24952,6 +25484,7 @@
           <t>北流市</t>
         </is>
       </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
         <v>110.35</v>
       </c>
@@ -24990,6 +25523,7 @@
           <t>钦州市</t>
         </is>
       </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
         <v>108.65</v>
       </c>
@@ -25028,6 +25562,7 @@
           <t>崇左市</t>
         </is>
       </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="n">
         <v>107.35</v>
       </c>
@@ -25066,6 +25601,7 @@
           <t>恭城瑶族自治县</t>
         </is>
       </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
         <v>110.83</v>
       </c>
@@ -25104,6 +25640,7 @@
           <t>八步区</t>
         </is>
       </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
         <v>111.55</v>
       </c>
@@ -25142,6 +25679,7 @@
           <t>浦北县</t>
         </is>
       </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
         <v>109.56</v>
       </c>
@@ -25180,6 +25718,7 @@
           <t>天峨县</t>
         </is>
       </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>107.17</v>
       </c>
@@ -25261,6 +25800,7 @@
           <t>紫云县</t>
         </is>
       </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
         <v>106.08</v>
       </c>
@@ -25299,6 +25839,7 @@
           <t>修文县</t>
         </is>
       </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
         <v>106.59</v>
       </c>
@@ -25337,6 +25878,7 @@
           <t>麻江县</t>
         </is>
       </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
         <v>107.59</v>
       </c>
@@ -25375,6 +25917,7 @@
           <t>龙里县</t>
         </is>
       </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="n">
         <v>106.98</v>
       </c>
@@ -25413,6 +25956,7 @@
           <t>罗甸县</t>
         </is>
       </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="n">
         <v>106.75</v>
       </c>
@@ -25451,6 +25995,7 @@
           <t>纳雍县</t>
         </is>
       </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="n">
         <v>105.38</v>
       </c>
@@ -25489,6 +26034,7 @@
           <t>六盘水市</t>
         </is>
       </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="n">
         <v>104.83</v>
       </c>
@@ -25527,6 +26073,7 @@
           <t>罗甸县</t>
         </is>
       </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
         <v>106.75</v>
       </c>
@@ -25565,6 +26112,7 @@
           <t>贞丰县</t>
         </is>
       </c>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="n">
         <v>105.65</v>
       </c>
@@ -25603,6 +26151,7 @@
           <t>三亚市</t>
         </is>
       </c>
+      <c r="E188" t="inlineStr"/>
       <c r="F188" t="n">
         <v>109.51</v>
       </c>
@@ -25641,6 +26190,7 @@
           <t>乐东县</t>
         </is>
       </c>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="n">
         <v>109.17</v>
       </c>
@@ -25679,6 +26229,7 @@
           <t>陵水县</t>
         </is>
       </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="n">
         <v>110.04</v>
       </c>
@@ -25717,6 +26268,7 @@
           <t>东方市</t>
         </is>
       </c>
+      <c r="E191" t="inlineStr"/>
       <c r="F191" t="n">
         <v>108.65</v>
       </c>
@@ -25755,6 +26307,7 @@
           <t>乐东县</t>
         </is>
       </c>
+      <c r="E192" t="inlineStr"/>
       <c r="F192" t="n">
         <v>109.17</v>
       </c>
@@ -25793,6 +26346,7 @@
           <t>东方市</t>
         </is>
       </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="n">
         <v>108.65</v>
       </c>
@@ -25831,6 +26385,7 @@
           <t>澄迈县</t>
         </is>
       </c>
+      <c r="E194" t="inlineStr"/>
       <c r="F194" t="n">
         <v>110</v>
       </c>
@@ -25869,6 +26424,7 @@
           <t>琼海市</t>
         </is>
       </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="n">
         <v>110.47</v>
       </c>
@@ -25907,6 +26463,7 @@
           <t>万宁市</t>
         </is>
       </c>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="n">
         <v>110.39</v>
       </c>
@@ -25945,6 +26502,7 @@
           <t>澄迈县</t>
         </is>
       </c>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="n">
         <v>110</v>
       </c>
@@ -25983,6 +26541,7 @@
           <t>海口市</t>
         </is>
       </c>
+      <c r="E198" t="inlineStr"/>
       <c r="F198" t="n">
         <v>110.2</v>
       </c>
@@ -26021,6 +26580,7 @@
           <t>陵水县</t>
         </is>
       </c>
+      <c r="E199" t="inlineStr"/>
       <c r="F199" t="n">
         <v>110.04</v>
       </c>
@@ -26059,6 +26619,7 @@
           <t>万宁市</t>
         </is>
       </c>
+      <c r="E200" t="inlineStr"/>
       <c r="F200" t="n">
         <v>110.39</v>
       </c>
@@ -26097,6 +26658,7 @@
           <t>东方市</t>
         </is>
       </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="n">
         <v>108.65</v>
       </c>
@@ -26135,6 +26697,7 @@
           <t>乐东县</t>
         </is>
       </c>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="n">
         <v>109.17</v>
       </c>
@@ -26173,6 +26736,7 @@
           <t>琼山区</t>
         </is>
       </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="n">
         <v>110.35</v>
       </c>
@@ -26211,6 +26775,7 @@
           <t>文昌市</t>
         </is>
       </c>
+      <c r="E204" t="inlineStr"/>
       <c r="F204" t="n">
         <v>110.8</v>
       </c>
@@ -26249,6 +26814,7 @@
           <t>三亚市</t>
         </is>
       </c>
+      <c r="E205" t="inlineStr"/>
       <c r="F205" t="n">
         <v>109.51</v>
       </c>
@@ -26287,6 +26853,7 @@
           <t>乐东县</t>
         </is>
       </c>
+      <c r="E206" t="inlineStr"/>
       <c r="F206" t="n">
         <v>109.17</v>
       </c>
@@ -26325,6 +26892,7 @@
           <t>三亚市</t>
         </is>
       </c>
+      <c r="E207" t="inlineStr"/>
       <c r="F207" t="n">
         <v>109.51</v>
       </c>
@@ -26363,6 +26931,7 @@
           <t>石棉县</t>
         </is>
       </c>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="n">
         <v>102.36</v>
       </c>
@@ -27519,6 +28088,7 @@
           <t>长阳土家族自治县</t>
         </is>
       </c>
+      <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>111.20105</v>
       </c>
@@ -27643,6 +28213,7 @@
           <t>公安县</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
         <v>112.23242</v>
       </c>
@@ -27681,6 +28252,7 @@
           <t>赤壁市</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
         <v>113.90039</v>
       </c>
@@ -27719,6 +28291,7 @@
           <t>建始县</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
         <v>109.7182</v>
       </c>
@@ -27800,6 +28373,7 @@
           <t>宜都市</t>
         </is>
       </c>
+      <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
         <v>111.45025</v>
       </c>
@@ -27838,6 +28412,7 @@
           <t>罗田县</t>
         </is>
       </c>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
         <v>115.39056</v>
       </c>
@@ -27876,6 +28451,7 @@
           <t>房县</t>
         </is>
       </c>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
         <v>110.73333</v>
       </c>
@@ -27914,6 +28490,7 @@
           <t>老河口市</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr"/>
       <c r="F245" t="n">
         <v>111.66944</v>
       </c>
@@ -27952,6 +28529,7 @@
           <t>老河口市</t>
         </is>
       </c>
+      <c r="E246" t="inlineStr"/>
       <c r="F246" t="n">
         <v>111.66944</v>
       </c>
@@ -27990,6 +28568,7 @@
           <t>兴山县</t>
         </is>
       </c>
+      <c r="E247" t="inlineStr"/>
       <c r="F247" t="n">
         <v>110.74951</v>
       </c>
@@ -28028,6 +28607,7 @@
           <t>凉城县</t>
         </is>
       </c>
+      <c r="E248" t="inlineStr"/>
       <c r="F248" t="n">
         <v>112.5</v>
       </c>
@@ -28066,6 +28646,7 @@
           <t>宁城县</t>
         </is>
       </c>
+      <c r="E249" t="inlineStr"/>
       <c r="F249" t="n">
         <v>119.33333</v>
       </c>
@@ -28099,6 +28680,8 @@
           <t>乌海市</t>
         </is>
       </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr"/>
       <c r="F250" t="n">
         <v>106.8</v>
       </c>
@@ -28137,6 +28720,7 @@
           <t>延吉市</t>
         </is>
       </c>
+      <c r="E251" t="inlineStr"/>
       <c r="F251" t="n">
         <v>129.5</v>
       </c>
@@ -28170,6 +28754,8 @@
           <t>白山市</t>
         </is>
       </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="n">
         <v>126.41667</v>
       </c>
@@ -28208,6 +28794,7 @@
           <t>柳河县</t>
         </is>
       </c>
+      <c r="E253" t="inlineStr"/>
       <c r="F253" t="n">
         <v>125.74475</v>
       </c>
@@ -28246,6 +28833,7 @@
           <t>通化县</t>
         </is>
       </c>
+      <c r="E254" t="inlineStr"/>
       <c r="F254" t="n">
         <v>125.75936</v>
       </c>
@@ -28279,6 +28867,8 @@
           <t>大兴安岭地区</t>
         </is>
       </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr"/>
       <c r="F255" t="n">
         <v>124.11667</v>
       </c>
@@ -28317,6 +28907,7 @@
           <t>尚志市</t>
         </is>
       </c>
+      <c r="E256" t="inlineStr"/>
       <c r="F256" t="n">
         <v>127.96194</v>
       </c>
@@ -28355,6 +28946,7 @@
           <t>勃利县</t>
         </is>
       </c>
+      <c r="E257" t="inlineStr"/>
       <c r="F257" t="n">
         <v>130.56806</v>
       </c>
@@ -28393,6 +28985,7 @@
           <t>穆棱市</t>
         </is>
       </c>
+      <c r="E258" t="inlineStr"/>
       <c r="F258" t="n">
         <v>130.51667</v>
       </c>
@@ -28426,6 +29019,8 @@
           <t>伊春市</t>
         </is>
       </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr"/>
       <c r="F259" t="n">
         <v>128.84056</v>
       </c>
@@ -28459,6 +29054,8 @@
           <t>海西蒙古族藏族自治州</t>
         </is>
       </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr"/>
       <c r="F260" t="n">
         <v>97.36667</v>
       </c>
@@ -28497,6 +29094,7 @@
           <t>乐都区</t>
         </is>
       </c>
+      <c r="E261" t="inlineStr"/>
       <c r="F261" t="n">
         <v>102.4</v>
       </c>
@@ -28535,6 +29133,7 @@
           <t>乐都区</t>
         </is>
       </c>
+      <c r="E262" t="inlineStr"/>
       <c r="F262" t="n">
         <v>102.4</v>
       </c>
@@ -28573,6 +29172,7 @@
           <t>巴宜区</t>
         </is>
       </c>
+      <c r="E263" t="inlineStr"/>
       <c r="F263" t="n">
         <v>94.36667</v>
       </c>
@@ -28611,6 +29211,7 @@
           <t>芒康县</t>
         </is>
       </c>
+      <c r="E264" t="inlineStr"/>
       <c r="F264" t="n">
         <v>98.59999999999999</v>
       </c>
@@ -28649,6 +29250,7 @@
           <t>朗县</t>
         </is>
       </c>
+      <c r="E265" t="inlineStr"/>
       <c r="F265" t="n">
         <v>93.06667</v>
       </c>
@@ -28730,6 +29332,7 @@
           <t>西峡县</t>
         </is>
       </c>
+      <c r="E267" t="inlineStr"/>
       <c r="F267" t="n">
         <v>111.47917</v>
       </c>
@@ -28768,6 +29371,7 @@
           <t>肥城市</t>
         </is>
       </c>
+      <c r="E268" t="inlineStr"/>
       <c r="F268" t="n">
         <v>116.46</v>
       </c>
@@ -28806,6 +29410,7 @@
           <t>乐陵市</t>
         </is>
       </c>
+      <c r="E269" t="inlineStr"/>
       <c r="F269" t="n">
         <v>117.12</v>
       </c>
@@ -28844,6 +29449,7 @@
           <t>会理市</t>
         </is>
       </c>
+      <c r="E270" t="inlineStr"/>
       <c r="F270" t="n">
         <v>102.25</v>
       </c>
@@ -28882,6 +29488,7 @@
           <t>威远县</t>
         </is>
       </c>
+      <c r="E271" t="inlineStr"/>
       <c r="F271" t="n">
         <v>104.66667</v>
       </c>
@@ -28920,6 +29527,7 @@
           <t>炎陵县</t>
         </is>
       </c>
+      <c r="E272" t="inlineStr"/>
       <c r="F272" t="n">
         <v>113.76667</v>
       </c>
@@ -28958,6 +29566,7 @@
           <t>隰县</t>
         </is>
       </c>
+      <c r="E273" t="inlineStr"/>
       <c r="F273" t="n">
         <v>110.93333</v>
       </c>
@@ -28991,6 +29600,8 @@
           <t>东方市</t>
         </is>
       </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr"/>
       <c r="F274" t="n">
         <v>108.63333</v>
       </c>
@@ -29029,6 +29640,7 @@
           <t>灵武市</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr"/>
       <c r="F275" t="n">
         <v>106.33333</v>
       </c>
@@ -29067,6 +29679,7 @@
           <t>集安市</t>
         </is>
       </c>
+      <c r="E276" t="inlineStr"/>
       <c r="F276" t="n">
         <v>126.18829</v>
       </c>
@@ -29105,6 +29718,7 @@
           <t>东港市</t>
         </is>
       </c>
+      <c r="E277" t="inlineStr"/>
       <c r="F277" t="n">
         <v>124.15</v>
       </c>
@@ -29138,6 +29752,8 @@
           <t>龙岩市</t>
         </is>
       </c>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr"/>
       <c r="F278" t="n">
         <v>117.01667</v>
       </c>
@@ -29176,6 +29792,7 @@
           <t>青州市</t>
         </is>
       </c>
+      <c r="E279" t="inlineStr"/>
       <c r="F279" t="n">
         <v>118.46667</v>
       </c>
@@ -29209,6 +29826,8 @@
           <t>威海市</t>
         </is>
       </c>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr"/>
       <c r="F280" t="n">
         <v>122.11667</v>
       </c>
@@ -29333,6 +29952,7 @@
           <t>巴宜区</t>
         </is>
       </c>
+      <c r="E283" t="inlineStr"/>
       <c r="F283" t="n">
         <v>94.361</v>
       </c>
@@ -29371,6 +29991,7 @@
           <t>察隅县</t>
         </is>
       </c>
+      <c r="E284" t="inlineStr"/>
       <c r="F284" t="n">
         <v>97.465</v>
       </c>
@@ -29409,6 +30030,7 @@
           <t>中宁县</t>
         </is>
       </c>
+      <c r="E285" t="inlineStr"/>
       <c r="F285" t="n">
         <v>105.685</v>
       </c>
@@ -29447,6 +30069,7 @@
           <t>海原县</t>
         </is>
       </c>
+      <c r="E286" t="inlineStr"/>
       <c r="F286" t="n">
         <v>105.643</v>
       </c>
@@ -29571,6 +30194,7 @@
           <t>怀远县</t>
         </is>
       </c>
+      <c r="E289" t="inlineStr"/>
       <c r="F289" t="n">
         <v>117.205</v>
       </c>
@@ -29609,6 +30233,7 @@
           <t>萧县</t>
         </is>
       </c>
+      <c r="E290" t="inlineStr"/>
       <c r="F290" t="n">
         <v>116.947</v>
       </c>
@@ -29647,6 +30272,7 @@
           <t>广丰区</t>
         </is>
       </c>
+      <c r="E291" t="inlineStr"/>
       <c r="F291" t="n">
         <v>118.191</v>
       </c>
@@ -29685,6 +30311,7 @@
           <t>吉州区</t>
         </is>
       </c>
+      <c r="E292" t="inlineStr"/>
       <c r="F292" t="n">
         <v>114.994</v>
       </c>
@@ -29723,6 +30350,7 @@
           <t>梁平区</t>
         </is>
       </c>
+      <c r="E293" t="inlineStr"/>
       <c r="F293" t="n">
         <v>107.802</v>
       </c>
@@ -29761,6 +30389,7 @@
           <t>潼南区</t>
         </is>
       </c>
+      <c r="E294" t="inlineStr"/>
       <c r="F294" t="n">
         <v>105.84</v>
       </c>
@@ -29799,6 +30428,7 @@
           <t>磴口县</t>
         </is>
       </c>
+      <c r="E295" t="inlineStr"/>
       <c r="F295" t="n">
         <v>107.008</v>
       </c>
@@ -29837,6 +30467,7 @@
           <t>鄂伦春自治旗</t>
         </is>
       </c>
+      <c r="E296" t="inlineStr"/>
       <c r="F296" t="n">
         <v>123.726</v>
       </c>
@@ -29875,6 +30506,7 @@
           <t>民和回族土族自治县</t>
         </is>
       </c>
+      <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
         <v>102.83</v>
       </c>
@@ -29883,7 +30515,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>F245</t>
+          <t>F335</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -29913,6 +30545,7 @@
           <t>尚志市</t>
         </is>
       </c>
+      <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
         <v>127.961</v>
       </c>
@@ -29921,7 +30554,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>F246</t>
+          <t>F336</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -29951,6 +30584,7 @@
           <t>友好区</t>
         </is>
       </c>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
         <v>128.841</v>
       </c>
@@ -29959,7 +30593,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>F247</t>
+          <t>F337</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -29989,6 +30623,7 @@
           <t>天涯区</t>
         </is>
       </c>
+      <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>109.506</v>
       </c>
@@ -29997,7 +30632,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>F248</t>
+          <t>F338</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -30022,6 +30657,8 @@
           <t>琼中黎族苗族自治县</t>
         </is>
       </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
         <v>109.838</v>
       </c>
@@ -30030,7 +30667,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>F249</t>
+          <t>F339</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -30055,6 +30692,7 @@
           <t>文昌市</t>
         </is>
       </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr">
         <is>
           <t>东郊镇</t>
@@ -30068,7 +30706,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>F250</t>
+          <t>F340</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -30098,6 +30736,7 @@
           <t>民勤县</t>
         </is>
       </c>
+      <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
         <v>103.094</v>
       </c>
@@ -30106,7 +30745,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>F251</t>
+          <t>F341</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -30136,6 +30775,7 @@
           <t>西峰区</t>
         </is>
       </c>
+      <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
         <v>107.651</v>
       </c>
@@ -30144,7 +30784,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>F252</t>
+          <t>F342</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -30187,7 +30827,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>F253</t>
+          <t>F343</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -30230,7 +30870,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>F245</t>
+          <t>F335</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -30273,7 +30913,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>F246</t>
+          <t>F336</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -30316,7 +30956,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>F247</t>
+          <t>F337</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -30359,7 +30999,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>F248</t>
+          <t>F338</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -30402,7 +31042,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>F249</t>
+          <t>F339</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -30445,7 +31085,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>F250</t>
+          <t>F340</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -30488,7 +31128,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>F251</t>
+          <t>F341</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -30531,7 +31171,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>F252</t>
+          <t>F342</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -30574,7 +31214,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>F253</t>
+          <t>F343</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -31292,6 +31932,7 @@
           <t>白水县</t>
         </is>
       </c>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="n">
         <v>109.59</v>
       </c>
@@ -31330,6 +31971,7 @@
           <t>清涧县</t>
         </is>
       </c>
+      <c r="E332" t="inlineStr"/>
       <c r="F332" t="n">
         <v>110.12</v>
       </c>
@@ -31368,6 +32010,7 @@
           <t>城固县</t>
         </is>
       </c>
+      <c r="E333" t="inlineStr"/>
       <c r="F333" t="n">
         <v>107.33</v>
       </c>
@@ -31406,6 +32049,7 @@
           <t>彬州市</t>
         </is>
       </c>
+      <c r="E334" t="inlineStr"/>
       <c r="F334" t="n">
         <v>108.08</v>
       </c>
@@ -31439,6 +32083,8 @@
           <t>延安市</t>
         </is>
       </c>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr"/>
       <c r="F335" t="n">
         <v>109.49</v>
       </c>
@@ -31472,6 +32118,8 @@
           <t>西安市</t>
         </is>
       </c>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr"/>
       <c r="F336" t="n">
         <v>108.94</v>
       </c>
@@ -31510,6 +32158,7 @@
           <t>永春县</t>
         </is>
       </c>
+      <c r="E337" t="inlineStr"/>
       <c r="F337" t="n">
         <v>118.29</v>
       </c>
@@ -31543,6 +32192,8 @@
           <t>莆田市</t>
         </is>
       </c>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>119.01</v>
       </c>
@@ -31581,6 +32232,7 @@
           <t>闽侯县</t>
         </is>
       </c>
+      <c r="E339" t="inlineStr"/>
       <c r="F339" t="n">
         <v>119.13</v>
       </c>
@@ -31619,6 +32271,7 @@
           <t>诏安县</t>
         </is>
       </c>
+      <c r="E340" t="inlineStr"/>
       <c r="F340" t="n">
         <v>117.18</v>
       </c>
@@ -31657,6 +32310,7 @@
           <t>建瓯市</t>
         </is>
       </c>
+      <c r="E341" t="inlineStr"/>
       <c r="F341" t="n">
         <v>118.3</v>
       </c>
@@ -31695,6 +32349,7 @@
           <t>福鼎市</t>
         </is>
       </c>
+      <c r="E342" t="inlineStr"/>
       <c r="F342" t="n">
         <v>120.22</v>
       </c>
@@ -31733,6 +32388,7 @@
           <t>长泰区</t>
         </is>
       </c>
+      <c r="E343" t="inlineStr"/>
       <c r="F343" t="n">
         <v>117.76</v>
       </c>
@@ -31771,6 +32427,7 @@
           <t>闽侯县</t>
         </is>
       </c>
+      <c r="E344" t="inlineStr"/>
       <c r="F344" t="n">
         <v>119.13</v>
       </c>
@@ -31852,6 +32509,7 @@
           <t>黄岩区</t>
         </is>
       </c>
+      <c r="E346" t="inlineStr"/>
       <c r="F346" t="n">
         <v>121.26</v>
       </c>
@@ -31890,6 +32548,7 @@
           <t>象山县</t>
         </is>
       </c>
+      <c r="E347" t="inlineStr"/>
       <c r="F347" t="n">
         <v>121.87</v>
       </c>
@@ -31928,6 +32587,7 @@
           <t>余姚市</t>
         </is>
       </c>
+      <c r="E348" t="inlineStr"/>
       <c r="F348" t="n">
         <v>121.16</v>
       </c>
@@ -31961,6 +32621,8 @@
           <t>衢州市</t>
         </is>
       </c>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr"/>
       <c r="F349" t="n">
         <v>118.87</v>
       </c>
@@ -31999,6 +32661,7 @@
           <t>常山县</t>
         </is>
       </c>
+      <c r="E350" t="inlineStr"/>
       <c r="F350" t="n">
         <v>118.51</v>
       </c>
@@ -32037,6 +32700,7 @@
           <t>桐乡市</t>
         </is>
       </c>
+      <c r="E351" t="inlineStr"/>
       <c r="F351" t="n">
         <v>120.56</v>
       </c>
@@ -32070,6 +32734,8 @@
           <t>大连市</t>
         </is>
       </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr"/>
       <c r="F352" t="n">
         <v>121.61</v>
       </c>
@@ -32103,6 +32769,8 @@
           <t>丹东市</t>
         </is>
       </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr"/>
       <c r="F353" t="n">
         <v>124.35</v>
       </c>
@@ -32141,6 +32809,7 @@
           <t>盖州市</t>
         </is>
       </c>
+      <c r="E354" t="inlineStr"/>
       <c r="F354" t="n">
         <v>122.35</v>
       </c>
@@ -32179,6 +32848,7 @@
           <t>绥中县</t>
         </is>
       </c>
+      <c r="E355" t="inlineStr"/>
       <c r="F355" t="n">
         <v>120.34</v>
       </c>
@@ -32217,6 +32887,7 @@
           <t>辽中区</t>
         </is>
       </c>
+      <c r="E356" t="inlineStr"/>
       <c r="F356" t="n">
         <v>122.73</v>
       </c>
@@ -32255,6 +32926,7 @@
           <t>庄河市</t>
         </is>
       </c>
+      <c r="E357" t="inlineStr"/>
       <c r="F357" t="n">
         <v>122.98</v>
       </c>
@@ -32288,6 +32960,8 @@
           <t>朝阳市</t>
         </is>
       </c>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="inlineStr"/>
       <c r="F358" t="n">
         <v>120.45</v>
       </c>
@@ -32321,6 +32995,8 @@
           <t>苏州市</t>
         </is>
       </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr"/>
       <c r="F359" t="n">
         <v>120.63</v>
       </c>
@@ -32359,6 +33035,7 @@
           <t>句容市</t>
         </is>
       </c>
+      <c r="E360" t="inlineStr"/>
       <c r="F360" t="n">
         <v>119.16</v>
       </c>
@@ -32440,6 +33117,7 @@
           <t>吴中区</t>
         </is>
       </c>
+      <c r="E362" t="inlineStr"/>
       <c r="F362" t="n">
         <v>120.63</v>
       </c>
@@ -32478,6 +33156,7 @@
           <t>丰县</t>
         </is>
       </c>
+      <c r="E363" t="inlineStr"/>
       <c r="F363" t="n">
         <v>116.6</v>
       </c>
@@ -32516,6 +33195,7 @@
           <t>溧水区</t>
         </is>
       </c>
+      <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
         <v>119.02</v>
       </c>
@@ -32554,6 +33234,7 @@
           <t>江都区</t>
         </is>
       </c>
+      <c r="E365" t="inlineStr"/>
       <c r="F365" t="n">
         <v>119.57</v>
       </c>
@@ -32592,6 +33273,7 @@
           <t>句容市</t>
         </is>
       </c>
+      <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
         <v>119.16</v>
       </c>
@@ -32630,6 +33312,7 @@
           <t>秦州区</t>
         </is>
       </c>
+      <c r="E367" t="inlineStr"/>
       <c r="F367" t="n">
         <v>105.72</v>
       </c>
@@ -32663,6 +33346,8 @@
           <t>兰州市</t>
         </is>
       </c>
+      <c r="D368" t="inlineStr"/>
+      <c r="E368" t="inlineStr"/>
       <c r="F368" t="n">
         <v>103.83</v>
       </c>
@@ -32701,6 +33386,7 @@
           <t>漠河市</t>
         </is>
       </c>
+      <c r="E369" t="inlineStr"/>
       <c r="F369" t="n">
         <v>122.54</v>
       </c>
@@ -32734,6 +33420,8 @@
           <t>牡丹江市</t>
         </is>
       </c>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="n">
         <v>129.63</v>
       </c>
@@ -32772,6 +33460,7 @@
           <t>延吉市</t>
         </is>
       </c>
+      <c r="E371" t="inlineStr"/>
       <c r="F371" t="n">
         <v>129.51</v>
       </c>
@@ -32805,6 +33494,8 @@
           <t>白山市</t>
         </is>
       </c>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="n">
         <v>126.41</v>
       </c>
@@ -32838,6 +33529,8 @@
           <t>通化市</t>
         </is>
       </c>
+      <c r="D373" t="inlineStr"/>
+      <c r="E373" t="inlineStr"/>
       <c r="F373" t="n">
         <v>125.94</v>
       </c>
@@ -32871,6 +33564,8 @@
           <t>四平市</t>
         </is>
       </c>
+      <c r="D374" t="inlineStr"/>
+      <c r="E374" t="inlineStr"/>
       <c r="F374" t="n">
         <v>124.37</v>
       </c>
@@ -32909,6 +33604,7 @@
           <t>临猗县</t>
         </is>
       </c>
+      <c r="E375" t="inlineStr"/>
       <c r="F375" t="n">
         <v>110.77</v>
       </c>
@@ -32942,6 +33638,8 @@
           <t>吕梁市</t>
         </is>
       </c>
+      <c r="D376" t="inlineStr"/>
+      <c r="E376" t="inlineStr"/>
       <c r="F376" t="n">
         <v>111.14</v>
       </c>
@@ -32975,6 +33673,8 @@
           <t>晋中市</t>
         </is>
       </c>
+      <c r="D377" t="inlineStr"/>
+      <c r="E377" t="inlineStr"/>
       <c r="F377" t="n">
         <v>112.75</v>
       </c>
@@ -33008,6 +33708,8 @@
           <t>晋城市</t>
         </is>
       </c>
+      <c r="D378" t="inlineStr"/>
+      <c r="E378" t="inlineStr"/>
       <c r="F378" t="n">
         <v>0</v>
       </c>
@@ -33046,6 +33748,7 @@
           <t>万州区</t>
         </is>
       </c>
+      <c r="E379" t="inlineStr"/>
       <c r="F379" t="n">
         <v>108.41</v>
       </c>
@@ -33084,6 +33787,7 @@
           <t>长寿区</t>
         </is>
       </c>
+      <c r="E380" t="inlineStr"/>
       <c r="F380" t="n">
         <v>107.08</v>
       </c>
@@ -33122,6 +33826,7 @@
           <t>江津区</t>
         </is>
       </c>
+      <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
         <v>106.26</v>
       </c>
@@ -33160,6 +33865,7 @@
           <t>永川区</t>
         </is>
       </c>
+      <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
         <v>105.89</v>
       </c>
@@ -33198,6 +33904,7 @@
           <t>忠县</t>
         </is>
       </c>
+      <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
         <v>108.02</v>
       </c>
@@ -33231,6 +33938,8 @@
           <t>吴忠市</t>
         </is>
       </c>
+      <c r="D384" t="inlineStr"/>
+      <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
         <v>106.2</v>
       </c>
@@ -33264,6 +33973,8 @@
           <t>海东市</t>
         </is>
       </c>
+      <c r="D385" t="inlineStr"/>
+      <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>102.1</v>
       </c>
@@ -33297,6 +34008,8 @@
           <t>海南藏族自治州</t>
         </is>
       </c>
+      <c r="D386" t="inlineStr"/>
+      <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
         <v>100.62</v>
       </c>
@@ -33335,6 +34048,7 @@
           <t>磴口县</t>
         </is>
       </c>
+      <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
         <v>107.01</v>
       </c>
@@ -33368,6 +34082,8 @@
           <t>赤峰市</t>
         </is>
       </c>
+      <c r="D388" t="inlineStr"/>
+      <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
         <v>118.89</v>
       </c>
@@ -33406,6 +34122,7 @@
           <t>昌平区</t>
         </is>
       </c>
+      <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>116.23</v>
       </c>
@@ -33444,6 +34161,7 @@
           <t>密云区</t>
         </is>
       </c>
+      <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
         <v>116.84</v>
       </c>
@@ -33482,6 +34200,7 @@
           <t>蓟州区</t>
         </is>
       </c>
+      <c r="E391" t="inlineStr"/>
       <c r="F391" t="n">
         <v>117.41</v>
       </c>
@@ -33520,6 +34239,7 @@
           <t>滨海新区</t>
         </is>
       </c>
+      <c r="E392" t="inlineStr"/>
       <c r="F392" t="n">
         <v>117.65</v>
       </c>
@@ -33558,6 +34278,7 @@
           <t>武清区</t>
         </is>
       </c>
+      <c r="E393" t="inlineStr"/>
       <c r="F393" t="n">
         <v>117.04</v>
       </c>
@@ -33596,6 +34317,7 @@
           <t>崇明区</t>
         </is>
       </c>
+      <c r="E394" t="inlineStr"/>
       <c r="F394" t="n">
         <v>121.4</v>
       </c>
@@ -33634,6 +34356,7 @@
           <t>嘉定区</t>
         </is>
       </c>
+      <c r="E395" t="inlineStr"/>
       <c r="F395" t="n">
         <v>121.27</v>
       </c>

--- a/fruit_data.xlsx
+++ b/fruit_data.xlsx
@@ -5540,10 +5540,10 @@
         <v>11</v>
       </c>
       <c r="J86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -7544,10 +7544,10 @@
         <v>11</v>
       </c>
       <c r="J122" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K122" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>巴东国家地理标志产品。三峡库区晚熟柑橘，果大皮薄、肉脆汁多、甜酸适口，四季有鲜橙。</t>
+          <t>巴东国家地理标志产品。三峡库区晚熟柑橘品种，果大皮薄、肉脆汁多、甜酸适口，11月至次年2月为最佳品赏期。巴东通过多品种搭配(伦晚、夏橙、九月红、椪柑、纽荷尔)实现四季有鲜橙。</t>
         </is>
       </c>
     </row>
@@ -21299,16 +21299,16 @@
         </is>
       </c>
       <c r="H369" t="n">
-        <v>102.18</v>
+        <v>3.5</v>
       </c>
       <c r="I369" t="n">
-        <v>27.4</v>
+        <v>4.5</v>
       </c>
       <c r="J369" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K369" t="n">
         <v>4</v>
-      </c>
-      <c r="K369" t="n">
-        <v>5</v>
       </c>
       <c r="L369" t="inlineStr">
         <is>

--- a/fruit_data.xlsx
+++ b/fruit_data.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M432"/>
+  <dimension ref="A1:M441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9745,7 +9745,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>广西百香果</t>
+          <t>百香果</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -24720,6 +24720,447 @@
       <c r="M432" t="inlineStr">
         <is>
           <t>国家地理标志产品。法兰西西梅新疆产区，果肉金黄、甘甜如蜜、营养丰富。</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>F469</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>徐闻菠萝</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>热带水果</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>湛江市</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>徐闻县</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr"/>
+      <c r="J433" t="n">
+        <v>2</v>
+      </c>
+      <c r="K433" t="n">
+        <v>5</v>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>春季集中型</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>国家地理标志产品（愚公楼菠萝），全国最大菠萝生产基地，被称为"菠萝的海"。果大汁多、肉脆味甜、香气浓烈，2-5月为核心盛产期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>F470</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>澄迈福橙</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>柑橘类</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>海南省</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>澄迈县</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>福山镇</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr"/>
+      <c r="J434" t="n">
+        <v>10</v>
+      </c>
+      <c r="K434" t="n">
+        <v>2</v>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>冬季巅峰型</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>国家地理标志产品+农产品地理标志（AGI01859），"中国十大名橙"之一。得益于火山岩红土壤，皮薄汁多、肉红可口、味清香蜜。10月至次年2月挂果上市，春节期间为最佳品赏期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>F471</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>元江芒果</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>热带水果</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>云南省</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>玉溪市</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>元江哈尼族彝族傣族自治县</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr"/>
+      <c r="J435" t="n">
+        <v>5</v>
+      </c>
+      <c r="K435" t="n">
+        <v>9</v>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>夏季集中型</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>国家地理标志证明商标，全国名特优新农产品。24万亩种植面积，早中晚熟品种搭配（台农、金凤凰、帕拉英达、金煌等），5-9月错峰上市。</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>F472</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>崀山脐橙</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>柑橘类</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>邵阳市</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>新宁县</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr"/>
+      <c r="J436" t="n">
+        <v>11</v>
+      </c>
+      <c r="K436" t="n">
+        <v>12</v>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>秋季巅峰型</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>国家地理标志产品（2007年登记），"中国脐橙第一县"。50万亩种植面积，年产70万吨。纽荷尔、崀丰等品种，11月中下旬成熟采收，耐贮藏至次年4月。</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>F473</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>东山白玉枇杷</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>仁果类</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>江苏省</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>苏州市</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>吴中区</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr"/>
+      <c r="J437" t="n">
+        <v>5</v>
+      </c>
+      <c r="K437" t="n">
+        <v>6</v>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>早春集中型</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>农产品地理标志+地理标志证明商标，全国名特优新农产品。太湖小气候孕育，果肉洁白晶莹、甘甜微酸，5月中旬至6月初盛产。</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>F474</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>宾川红提葡萄</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>浆果类</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>云南省</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>大理白族自治州</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>宾川县</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr"/>
+      <c r="J438" t="n">
+        <v>6</v>
+      </c>
+      <c r="K438" t="n">
+        <v>9</v>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>夏秋持续型</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>国家地理标志证明商标，全国县级最大早熟鲜食葡萄基地（18万亩）。干热河谷气候，较全国主产区早熟40-50天，5-12月鲜果供应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>F475</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>莆田荔枝</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>热带水果</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>福建省</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>莆田市</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>荔城区</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr"/>
+      <c r="J439" t="n">
+        <v>7</v>
+      </c>
+      <c r="K439" t="n">
+        <v>7</v>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>夏季集中型</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>国家地理标志产品（2014年批准），千年荔枝之乡（古荔树近1300年）。陈紫、状元红等品种，7月中下旬（小暑至大暑）成熟，"离枝即食"，盛产期仅约两周。</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>F476</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>敖汉沙棘</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>浆果类</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>内蒙古自治区</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>赤峰市</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>敖汉旗</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr"/>
+      <c r="J440" t="n">
+        <v>8</v>
+      </c>
+      <c r="K440" t="n">
+        <v>9</v>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>秋季巅峰型</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>地理标志证明商标（敖汉沙棘），全国名特优新农产品（阿尔山寒地沙棘）。维C之王，16万亩沙棘林，8-9月成熟采收。</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>F477</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>扎兰屯沙果</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>仁果类</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>内蒙古自治区</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>呼伦贝尔市</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>扎兰屯市</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr"/>
+      <c r="J441" t="n">
+        <v>8</v>
+      </c>
+      <c r="K441" t="n">
+        <v>9</v>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>秋季巅峰型</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>国家地理标志产品，内蒙古东部传统水果。果小酸甜、香气浓郁，可鲜食亦可制果干果脯，8-9月成熟。</t>
         </is>
       </c>
     </row>
@@ -24736,7 +25177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I420"/>
+  <dimension ref="A1:I429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="13.7265625" customWidth="1" min="1" max="1"/>
@@ -41576,6 +42017,303 @@
       <c r="I420" t="inlineStr">
         <is>
           <t>核心产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>970000071</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>湛江市</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>徐闻县</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr"/>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>F469</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>一般产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>970000072</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>海南省</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>澄迈县</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>福山镇</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr"/>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>F470</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>一般产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>970000073</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>云南省</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>玉溪市</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>元江哈尼族彝族傣族自治县</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr"/>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>F471</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>一般产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>970000074</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>邵阳市</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>新宁县</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr"/>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>F472</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>一般产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>970000075</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>江苏省</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>苏州市</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>吴中区</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr"/>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>F473</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>一般产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>970000076</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>云南省</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>大理白族自治州</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>宾川县</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr"/>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>F474</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>一般产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>970000077</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>福建省</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>莆田市</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>荔城区</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr"/>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>F475</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>一般产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>970000078</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>内蒙古自治区</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>赤峰市</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>敖汉旗</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr"/>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>F476</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>一般产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>970000079</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>内蒙古自治区</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>呼伦贝尔市</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>扎兰屯市</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr"/>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>F477</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>一般产区</t>
         </is>
       </c>
     </row>

--- a/fruit_data.xlsx
+++ b/fruit_data.xlsx
@@ -6177,6 +6177,7 @@
           <t>丹棱县</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>11</v>
       </c>
@@ -6231,6 +6232,7 @@
           <t>丹棱县</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>10</v>
       </c>
@@ -6285,6 +6287,7 @@
           <t>苍溪县</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>8</v>
       </c>
@@ -6339,6 +6342,7 @@
           <t>金川县</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>8</v>
       </c>
@@ -6393,6 +6397,7 @@
           <t>龙泉驿区</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>4</v>
       </c>
@@ -6506,6 +6511,7 @@
           <t>会理市</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>7.9</v>
       </c>
@@ -6560,6 +6566,7 @@
           <t>双流区</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>12</v>
       </c>
@@ -6614,6 +6621,7 @@
           <t>新平县</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>1</v>
       </c>
@@ -6668,6 +6676,7 @@
           <t>新平县</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>10</v>
       </c>
@@ -6722,6 +6731,7 @@
           <t>弥勒市</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>12</v>
       </c>
@@ -6776,6 +6786,7 @@
           <t>宾川县</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>8</v>
       </c>
@@ -6830,6 +6841,7 @@
           <t>华坪县</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>6</v>
       </c>
@@ -6884,6 +6896,7 @@
           <t>丘北县</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>6</v>
       </c>
@@ -6938,6 +6951,7 @@
           <t>昭阳区</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>7</v>
       </c>
@@ -6992,6 +7006,7 @@
           <t>高州市</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>5</v>
       </c>
@@ -7046,6 +7061,7 @@
           <t>增城区</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>6</v>
       </c>
@@ -7100,6 +7116,7 @@
           <t>高州市</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>7</v>
       </c>
@@ -7154,6 +7171,7 @@
           <t>四会市</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>12</v>
       </c>
@@ -7267,6 +7285,7 @@
           <t>高州市</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>11</v>
       </c>
@@ -7321,6 +7340,7 @@
           <t>荔浦市</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>12</v>
       </c>
@@ -7375,6 +7395,7 @@
           <t>田东县</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>6</v>
       </c>
@@ -7429,6 +7450,7 @@
           <t>隆安县</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>5</v>
       </c>
@@ -7483,6 +7505,7 @@
           <t>北流市</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>7</v>
       </c>
@@ -7537,6 +7560,7 @@
           <t>八步区</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>5</v>
       </c>
@@ -7709,6 +7733,7 @@
           <t>麻江县</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>6</v>
       </c>
@@ -7763,6 +7788,7 @@
           <t>罗甸县</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>11</v>
       </c>
@@ -7817,6 +7843,7 @@
           <t>纳雍县</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>4</v>
       </c>
@@ -7871,6 +7898,7 @@
           <t>罗甸县</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>7</v>
       </c>
@@ -7925,6 +7953,7 @@
           <t>乐东黎族自治县</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>1</v>
       </c>
@@ -7979,6 +8008,7 @@
           <t>乐东县</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>9</v>
       </c>
@@ -8033,6 +8063,7 @@
           <t>万宁市</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>2</v>
       </c>
@@ -8087,6 +8118,7 @@
           <t>澄迈县</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>4</v>
       </c>
@@ -8141,6 +8173,7 @@
           <t>乐东黎族自治县</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>3</v>
       </c>
@@ -8195,6 +8228,7 @@
           <t>琼山区</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
         <v>12</v>
       </c>
@@ -8249,6 +8283,7 @@
           <t>乐东县</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>1</v>
       </c>
@@ -9778,6 +9813,7 @@
           <t>长阳土家族自治县</t>
         </is>
       </c>
+      <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
         <v>11</v>
       </c>
@@ -9950,6 +9986,7 @@
           <t>公安县</t>
         </is>
       </c>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
         <v>7</v>
       </c>
@@ -10004,6 +10041,7 @@
           <t>赤壁市</t>
         </is>
       </c>
+      <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
         <v>8</v>
       </c>
@@ -10058,6 +10096,7 @@
           <t>建始县</t>
         </is>
       </c>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
         <v>9</v>
       </c>
@@ -10171,6 +10210,7 @@
           <t>宜都市</t>
         </is>
       </c>
+      <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
         <v>10</v>
       </c>
@@ -10225,6 +10265,7 @@
           <t>罗田县</t>
         </is>
       </c>
+      <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
         <v>8</v>
       </c>
@@ -10279,6 +10320,7 @@
           <t>房县</t>
         </is>
       </c>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
         <v>4</v>
       </c>
@@ -10333,6 +10375,7 @@
           <t>老河口市</t>
         </is>
       </c>
+      <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
         <v>6</v>
       </c>
@@ -10387,6 +10430,7 @@
           <t>老河口市</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
         <v>7</v>
       </c>
@@ -10441,6 +10485,7 @@
           <t>兴山县</t>
         </is>
       </c>
+      <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
         <v>11</v>
       </c>
@@ -10495,6 +10540,7 @@
           <t>凉城县</t>
         </is>
       </c>
+      <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
         <v>8</v>
       </c>
@@ -10549,6 +10595,7 @@
           <t>宁城县</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
         <v>9</v>
       </c>
@@ -10598,6 +10645,8 @@
           <t>乌海市</t>
         </is>
       </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
       <c r="H176" t="n">
         <v>7</v>
       </c>
@@ -10706,6 +10755,8 @@
           <t>白山市</t>
         </is>
       </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
         <v>7</v>
       </c>
@@ -10760,6 +10811,7 @@
           <t>柳河县</t>
         </is>
       </c>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
         <v>8</v>
       </c>
@@ -10814,6 +10866,7 @@
           <t>通化县</t>
         </is>
       </c>
+      <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
         <v>7</v>
       </c>
@@ -10863,6 +10916,8 @@
           <t>大兴安岭地区</t>
         </is>
       </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
         <v>7</v>
       </c>
@@ -10917,6 +10972,7 @@
           <t>尚志市</t>
         </is>
       </c>
+      <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
         <v>7</v>
       </c>
@@ -10971,6 +11027,7 @@
           <t>勃利县</t>
         </is>
       </c>
+      <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
         <v>6</v>
       </c>
@@ -11025,6 +11082,7 @@
           <t>穆棱市</t>
         </is>
       </c>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
         <v>9</v>
       </c>
@@ -11079,6 +11137,7 @@
           <t>友好区</t>
         </is>
       </c>
+      <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
         <v>7</v>
       </c>
@@ -11128,6 +11187,8 @@
           <t>海西蒙古族藏族自治州</t>
         </is>
       </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
         <v>7</v>
       </c>
@@ -11182,6 +11243,7 @@
           <t>乐都区</t>
         </is>
       </c>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
         <v>8</v>
       </c>
@@ -11236,6 +11298,7 @@
           <t>乐都区</t>
         </is>
       </c>
+      <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
         <v>6</v>
       </c>
@@ -11290,6 +11353,7 @@
           <t>巴宜区</t>
         </is>
       </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
         <v>9</v>
       </c>
@@ -11344,6 +11408,7 @@
           <t>芒康县</t>
         </is>
       </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
         <v>8</v>
       </c>
@@ -11398,6 +11463,7 @@
           <t>朗县</t>
         </is>
       </c>
+      <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
         <v>9</v>
       </c>
@@ -11511,6 +11577,7 @@
           <t>西峡县</t>
         </is>
       </c>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
         <v>8</v>
       </c>
@@ -11565,6 +11632,7 @@
           <t>肥城市</t>
         </is>
       </c>
+      <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
         <v>8</v>
       </c>
@@ -11619,6 +11687,7 @@
           <t>乐陵市</t>
         </is>
       </c>
+      <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
         <v>9</v>
       </c>
@@ -11673,6 +11742,7 @@
           <t>威远县</t>
         </is>
       </c>
+      <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
         <v>7</v>
       </c>
@@ -11727,6 +11797,7 @@
           <t>炎陵县</t>
         </is>
       </c>
+      <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
         <v>7</v>
       </c>
@@ -11781,6 +11852,7 @@
           <t>隰县</t>
         </is>
       </c>
+      <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
         <v>9</v>
       </c>
@@ -11830,6 +11902,8 @@
           <t>东方市</t>
         </is>
       </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
         <v>5</v>
       </c>
@@ -11884,6 +11958,7 @@
           <t>灵武市</t>
         </is>
       </c>
+      <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
         <v>9</v>
       </c>
@@ -11938,6 +12013,7 @@
           <t>集安市</t>
         </is>
       </c>
+      <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
         <v>8</v>
       </c>
@@ -11987,6 +12063,8 @@
           <t>龙岩市</t>
         </is>
       </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
       <c r="H202" t="n">
         <v>7</v>
       </c>
@@ -12041,6 +12119,7 @@
           <t>青州市</t>
         </is>
       </c>
+      <c r="G203" t="inlineStr"/>
       <c r="H203" t="n">
         <v>9</v>
       </c>
@@ -12090,6 +12169,8 @@
           <t>威海市</t>
         </is>
       </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
       <c r="H204" t="n">
         <v>7</v>
       </c>
@@ -12262,6 +12343,7 @@
           <t>察隅县</t>
         </is>
       </c>
+      <c r="G207" t="inlineStr"/>
       <c r="H207" t="n">
         <v>9</v>
       </c>
@@ -12316,6 +12398,7 @@
           <t>中宁县</t>
         </is>
       </c>
+      <c r="G208" t="inlineStr"/>
       <c r="H208" t="n">
         <v>6</v>
       </c>
@@ -12370,6 +12453,7 @@
           <t>海原县</t>
         </is>
       </c>
+      <c r="G209" t="inlineStr"/>
       <c r="H209" t="n">
         <v>9</v>
       </c>
@@ -12483,6 +12567,7 @@
           <t>怀远县</t>
         </is>
       </c>
+      <c r="G211" t="inlineStr"/>
       <c r="H211" t="n">
         <v>9</v>
       </c>
@@ -12537,6 +12622,7 @@
           <t>萧县</t>
         </is>
       </c>
+      <c r="G212" t="inlineStr"/>
       <c r="H212" t="n">
         <v>7</v>
       </c>
@@ -12591,6 +12677,7 @@
           <t>广丰区</t>
         </is>
       </c>
+      <c r="G213" t="inlineStr"/>
       <c r="H213" t="n">
         <v>11</v>
       </c>
@@ -12645,6 +12732,7 @@
           <t>梁平区</t>
         </is>
       </c>
+      <c r="G214" t="inlineStr"/>
       <c r="H214" t="n">
         <v>10</v>
       </c>
@@ -12699,6 +12787,7 @@
           <t>潼南区</t>
         </is>
       </c>
+      <c r="G215" t="inlineStr"/>
       <c r="H215" t="n">
         <v>9</v>
       </c>
@@ -12753,6 +12842,7 @@
           <t>磴口县</t>
         </is>
       </c>
+      <c r="G216" t="inlineStr"/>
       <c r="H216" t="n">
         <v>7</v>
       </c>
@@ -12807,6 +12897,7 @@
           <t>鄂伦春自治旗</t>
         </is>
       </c>
+      <c r="G217" t="inlineStr"/>
       <c r="H217" t="n">
         <v>7</v>
       </c>
@@ -12861,6 +12952,7 @@
           <t>民和回族土族自治县</t>
         </is>
       </c>
+      <c r="G218" t="inlineStr"/>
       <c r="H218" t="n">
         <v>7</v>
       </c>
@@ -12910,6 +13002,8 @@
           <t>琼中黎族苗族自治县</t>
         </is>
       </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
       <c r="H219" t="n">
         <v>10</v>
       </c>
@@ -12959,6 +13053,7 @@
           <t>文昌市</t>
         </is>
       </c>
+      <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
           <t>东郊镇</t>
@@ -13018,6 +13113,7 @@
           <t>民勤县</t>
         </is>
       </c>
+      <c r="G221" t="inlineStr"/>
       <c r="H221" t="n">
         <v>7</v>
       </c>
@@ -13072,6 +13168,7 @@
           <t>西峰区</t>
         </is>
       </c>
+      <c r="G222" t="inlineStr"/>
       <c r="H222" t="n">
         <v>9</v>
       </c>
@@ -14604,6 +14701,7 @@
           <t>白水县</t>
         </is>
       </c>
+      <c r="G248" t="inlineStr"/>
       <c r="H248" t="n">
         <v>9</v>
       </c>
@@ -14658,6 +14756,7 @@
           <t>清涧县</t>
         </is>
       </c>
+      <c r="G249" t="inlineStr"/>
       <c r="H249" t="n">
         <v>9</v>
       </c>
@@ -14712,6 +14811,7 @@
           <t>城固县</t>
         </is>
       </c>
+      <c r="G250" t="inlineStr"/>
       <c r="H250" t="n">
         <v>10</v>
       </c>
@@ -14766,6 +14866,7 @@
           <t>彬州市</t>
         </is>
       </c>
+      <c r="G251" t="inlineStr"/>
       <c r="H251" t="n">
         <v>9</v>
       </c>
@@ -14815,6 +14916,8 @@
           <t>延安市</t>
         </is>
       </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr"/>
       <c r="H252" t="n">
         <v>10</v>
       </c>
@@ -14864,6 +14967,8 @@
           <t>西安市</t>
         </is>
       </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr"/>
       <c r="H253" t="n">
         <v>12</v>
       </c>
@@ -14918,6 +15023,7 @@
           <t>永春县</t>
         </is>
       </c>
+      <c r="G254" t="inlineStr"/>
       <c r="H254" t="n">
         <v>11</v>
       </c>
@@ -14967,6 +15073,8 @@
           <t>莆田市</t>
         </is>
       </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr"/>
       <c r="H255" t="n">
         <v>3</v>
       </c>
@@ -15021,6 +15129,7 @@
           <t>闽侯县</t>
         </is>
       </c>
+      <c r="G256" t="inlineStr"/>
       <c r="H256" t="n">
         <v>7</v>
       </c>
@@ -15075,6 +15184,7 @@
           <t>诏安县</t>
         </is>
       </c>
+      <c r="G257" t="inlineStr"/>
       <c r="H257" t="n">
         <v>4</v>
       </c>
@@ -15129,6 +15239,7 @@
           <t>建瓯市</t>
         </is>
       </c>
+      <c r="G258" t="inlineStr"/>
       <c r="H258" t="n">
         <v>9</v>
       </c>
@@ -15183,6 +15294,7 @@
           <t>福鼎市</t>
         </is>
       </c>
+      <c r="G259" t="inlineStr"/>
       <c r="H259" t="n">
         <v>10</v>
       </c>
@@ -15237,6 +15349,7 @@
           <t>长泰区</t>
         </is>
       </c>
+      <c r="G260" t="inlineStr"/>
       <c r="H260" t="n">
         <v>11</v>
       </c>
@@ -15291,6 +15404,7 @@
           <t>闽侯县</t>
         </is>
       </c>
+      <c r="G261" t="inlineStr"/>
       <c r="H261" t="n">
         <v>6</v>
       </c>
@@ -15404,6 +15518,7 @@
           <t>黄岩区</t>
         </is>
       </c>
+      <c r="G263" t="inlineStr"/>
       <c r="H263" t="n">
         <v>10</v>
       </c>
@@ -15458,6 +15573,7 @@
           <t>象山县</t>
         </is>
       </c>
+      <c r="G264" t="inlineStr"/>
       <c r="H264" t="n">
         <v>11</v>
       </c>
@@ -15512,6 +15628,7 @@
           <t>余姚市</t>
         </is>
       </c>
+      <c r="G265" t="inlineStr"/>
       <c r="H265" t="n">
         <v>6</v>
       </c>
@@ -15561,6 +15678,8 @@
           <t>衢州市</t>
         </is>
       </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
       <c r="H266" t="n">
         <v>11</v>
       </c>
@@ -15615,6 +15734,7 @@
           <t>常山县</t>
         </is>
       </c>
+      <c r="G267" t="inlineStr"/>
       <c r="H267" t="n">
         <v>11</v>
       </c>
@@ -15669,6 +15789,7 @@
           <t>桐乡市</t>
         </is>
       </c>
+      <c r="G268" t="inlineStr"/>
       <c r="H268" t="n">
         <v>6</v>
       </c>
@@ -15718,6 +15839,8 @@
           <t>大连市</t>
         </is>
       </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr"/>
       <c r="H269" t="n">
         <v>5</v>
       </c>
@@ -15767,6 +15890,8 @@
           <t>丹东市</t>
         </is>
       </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
       <c r="H270" t="n">
         <v>12</v>
       </c>
@@ -15821,6 +15946,7 @@
           <t>盖州市</t>
         </is>
       </c>
+      <c r="G271" t="inlineStr"/>
       <c r="H271" t="n">
         <v>8</v>
       </c>
@@ -15875,6 +16001,7 @@
           <t>绥中县</t>
         </is>
       </c>
+      <c r="G272" t="inlineStr"/>
       <c r="H272" t="n">
         <v>9</v>
       </c>
@@ -15929,6 +16056,7 @@
           <t>辽中区</t>
         </is>
       </c>
+      <c r="G273" t="inlineStr"/>
       <c r="H273" t="n">
         <v>10</v>
       </c>
@@ -15983,6 +16111,7 @@
           <t>庄河市</t>
         </is>
       </c>
+      <c r="G274" t="inlineStr"/>
       <c r="H274" t="n">
         <v>6</v>
       </c>
@@ -16032,6 +16161,8 @@
           <t>朝阳市</t>
         </is>
       </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
       <c r="H275" t="n">
         <v>9</v>
       </c>
@@ -16081,6 +16212,8 @@
           <t>苏州市</t>
         </is>
       </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
       <c r="H276" t="n">
         <v>6</v>
       </c>
@@ -16135,6 +16268,7 @@
           <t>句容市</t>
         </is>
       </c>
+      <c r="G277" t="inlineStr"/>
       <c r="H277" t="n">
         <v>7</v>
       </c>
@@ -16189,6 +16323,7 @@
           <t>吴中区</t>
         </is>
       </c>
+      <c r="G278" t="inlineStr"/>
       <c r="H278" t="n">
         <v>5</v>
       </c>
@@ -16243,6 +16378,7 @@
           <t>丰县</t>
         </is>
       </c>
+      <c r="G279" t="inlineStr"/>
       <c r="H279" t="n">
         <v>9</v>
       </c>
@@ -16297,6 +16433,7 @@
           <t>溧水区</t>
         </is>
       </c>
+      <c r="G280" t="inlineStr"/>
       <c r="H280" t="n">
         <v>12</v>
       </c>
@@ -16351,6 +16488,7 @@
           <t>江都区</t>
         </is>
       </c>
+      <c r="G281" t="inlineStr"/>
       <c r="H281" t="n">
         <v>9</v>
       </c>
@@ -16405,6 +16543,7 @@
           <t>句容市</t>
         </is>
       </c>
+      <c r="G282" t="inlineStr"/>
       <c r="H282" t="n">
         <v>7</v>
       </c>
@@ -16459,6 +16598,7 @@
           <t>秦州区</t>
         </is>
       </c>
+      <c r="G283" t="inlineStr"/>
       <c r="H283" t="n">
         <v>9</v>
       </c>
@@ -16508,6 +16648,8 @@
           <t>兰州市</t>
         </is>
       </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr"/>
       <c r="H284" t="n">
         <v>9</v>
       </c>
@@ -16562,6 +16704,7 @@
           <t>牡丹江市</t>
         </is>
       </c>
+      <c r="G285" t="inlineStr"/>
       <c r="H285" t="n">
         <v>9</v>
       </c>
@@ -16611,6 +16754,8 @@
           <t>通化市</t>
         </is>
       </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr"/>
       <c r="H286" t="n">
         <v>9</v>
       </c>
@@ -16660,6 +16805,8 @@
           <t>四平市</t>
         </is>
       </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr"/>
       <c r="H287" t="n">
         <v>9</v>
       </c>
@@ -16714,6 +16861,7 @@
           <t>临猗县</t>
         </is>
       </c>
+      <c r="G288" t="inlineStr"/>
       <c r="H288" t="n">
         <v>10</v>
       </c>
@@ -16763,6 +16911,8 @@
           <t>吕梁市</t>
         </is>
       </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr"/>
       <c r="H289" t="n">
         <v>9</v>
       </c>
@@ -16812,6 +16962,8 @@
           <t>晋中市</t>
         </is>
       </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr"/>
       <c r="H290" t="n">
         <v>8</v>
       </c>
@@ -16861,6 +17013,8 @@
           <t>晋城市</t>
         </is>
       </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr"/>
       <c r="H291" t="n">
         <v>9</v>
       </c>
@@ -16915,6 +17069,7 @@
           <t>万州区</t>
         </is>
       </c>
+      <c r="G292" t="inlineStr"/>
       <c r="H292" t="n">
         <v>10</v>
       </c>
@@ -16969,6 +17124,7 @@
           <t>长寿区</t>
         </is>
       </c>
+      <c r="G293" t="inlineStr"/>
       <c r="H293" t="n">
         <v>11</v>
       </c>
@@ -17023,6 +17179,7 @@
           <t>江津区</t>
         </is>
       </c>
+      <c r="G294" t="inlineStr"/>
       <c r="H294" t="n">
         <v>10</v>
       </c>
@@ -17077,6 +17234,7 @@
           <t>永川区</t>
         </is>
       </c>
+      <c r="G295" t="inlineStr"/>
       <c r="H295" t="n">
         <v>8</v>
       </c>
@@ -17131,6 +17289,7 @@
           <t>忠县</t>
         </is>
       </c>
+      <c r="G296" t="inlineStr"/>
       <c r="H296" t="n">
         <v>10</v>
       </c>
@@ -17180,6 +17339,8 @@
           <t>吴忠市</t>
         </is>
       </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr"/>
       <c r="H297" t="n">
         <v>8</v>
       </c>
@@ -17229,6 +17390,8 @@
           <t>海东市</t>
         </is>
       </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr"/>
       <c r="H298" t="n">
         <v>6</v>
       </c>
@@ -17278,6 +17441,8 @@
           <t>海南藏族自治州</t>
         </is>
       </c>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr"/>
       <c r="H299" t="n">
         <v>9</v>
       </c>
@@ -17332,6 +17497,7 @@
           <t>磴口县</t>
         </is>
       </c>
+      <c r="G300" t="inlineStr"/>
       <c r="H300" t="n">
         <v>7</v>
       </c>
@@ -17381,6 +17547,8 @@
           <t>赤峰市</t>
         </is>
       </c>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr"/>
       <c r="H301" t="n">
         <v>9</v>
       </c>
@@ -17435,6 +17603,7 @@
           <t>昌平区</t>
         </is>
       </c>
+      <c r="G302" t="inlineStr"/>
       <c r="H302" t="n">
         <v>12</v>
       </c>
@@ -17489,6 +17658,7 @@
           <t>密云区</t>
         </is>
       </c>
+      <c r="G303" t="inlineStr"/>
       <c r="H303" t="n">
         <v>5</v>
       </c>
@@ -17543,6 +17713,7 @@
           <t>蓟州区</t>
         </is>
       </c>
+      <c r="G304" t="inlineStr"/>
       <c r="H304" t="n">
         <v>10</v>
       </c>
@@ -17597,6 +17768,7 @@
           <t>滨海新区</t>
         </is>
       </c>
+      <c r="G305" t="inlineStr"/>
       <c r="H305" t="n">
         <v>8</v>
       </c>
@@ -17651,6 +17823,7 @@
           <t>武清区</t>
         </is>
       </c>
+      <c r="G306" t="inlineStr"/>
       <c r="H306" t="n">
         <v>6</v>
       </c>
@@ -17705,6 +17878,7 @@
           <t>崇明区</t>
         </is>
       </c>
+      <c r="G307" t="inlineStr"/>
       <c r="H307" t="n">
         <v>10</v>
       </c>
@@ -17759,6 +17933,7 @@
           <t>嘉定区</t>
         </is>
       </c>
+      <c r="G308" t="inlineStr"/>
       <c r="H308" t="n">
         <v>7</v>
       </c>
@@ -20704,6 +20879,7 @@
           <t>雷波县</t>
         </is>
       </c>
+      <c r="G358" t="inlineStr"/>
       <c r="H358" t="n">
         <v>10.9</v>
       </c>
@@ -20758,6 +20934,7 @@
           <t>盐源县</t>
         </is>
       </c>
+      <c r="G359" t="inlineStr"/>
       <c r="H359" t="n">
         <v>7.9</v>
       </c>
@@ -20812,6 +20989,7 @@
           <t>蒲江县</t>
         </is>
       </c>
+      <c r="G360" t="inlineStr"/>
       <c r="H360" t="n">
         <v>8.9</v>
       </c>
@@ -20866,6 +21044,7 @@
           <t>都江堰市</t>
         </is>
       </c>
+      <c r="G361" t="inlineStr"/>
       <c r="H361" t="n">
         <v>103.62</v>
       </c>
@@ -20920,6 +21099,7 @@
           <t>米易县</t>
         </is>
       </c>
+      <c r="G362" t="inlineStr"/>
       <c r="H362" t="n">
         <v>12</v>
       </c>
@@ -20974,6 +21154,7 @@
           <t>邻水县</t>
         </is>
       </c>
+      <c r="G363" t="inlineStr"/>
       <c r="H363" t="n">
         <v>106.93</v>
       </c>
@@ -21028,6 +21209,7 @@
           <t>石棉县</t>
         </is>
       </c>
+      <c r="G364" t="inlineStr"/>
       <c r="H364" t="n">
         <v>1</v>
       </c>
@@ -21082,6 +21264,7 @@
           <t>德昌县</t>
         </is>
       </c>
+      <c r="G365" t="inlineStr"/>
       <c r="H365" t="n">
         <v>3.5</v>
       </c>
@@ -21136,6 +21319,7 @@
           <t>江阳区</t>
         </is>
       </c>
+      <c r="G366" t="inlineStr"/>
       <c r="H366" t="n">
         <v>8</v>
       </c>
@@ -21190,6 +21374,7 @@
           <t>大邑县</t>
         </is>
       </c>
+      <c r="G367" t="inlineStr"/>
       <c r="H367" t="n">
         <v>4.5</v>
       </c>
@@ -21244,6 +21429,7 @@
           <t>从江县</t>
         </is>
       </c>
+      <c r="G368" t="inlineStr"/>
       <c r="H368" t="n">
         <v>108.9</v>
       </c>
@@ -21298,6 +21484,7 @@
           <t>水城区</t>
         </is>
       </c>
+      <c r="G369" t="inlineStr"/>
       <c r="H369" t="n">
         <v>104.82</v>
       </c>
@@ -21352,6 +21539,7 @@
           <t>威宁彝族回族苗族自治县</t>
         </is>
       </c>
+      <c r="G370" t="inlineStr"/>
       <c r="H370" t="n">
         <v>104.28</v>
       </c>
@@ -21406,6 +21594,7 @@
           <t>开阳县</t>
         </is>
       </c>
+      <c r="G371" t="inlineStr"/>
       <c r="H371" t="n">
         <v>106.97</v>
       </c>
@@ -21460,6 +21649,7 @@
           <t>荔波县</t>
         </is>
       </c>
+      <c r="G372" t="inlineStr"/>
       <c r="H372" t="n">
         <v>107.88</v>
       </c>
@@ -21514,6 +21704,7 @@
           <t>沿河土家族自治县</t>
         </is>
       </c>
+      <c r="G373" t="inlineStr"/>
       <c r="H373" t="n">
         <v>108.5</v>
       </c>
@@ -21568,6 +21759,7 @@
           <t>敦煌市</t>
         </is>
       </c>
+      <c r="G374" t="inlineStr"/>
       <c r="H374" t="n">
         <v>8</v>
       </c>
@@ -21622,6 +21814,7 @@
           <t>皋兰县</t>
         </is>
       </c>
+      <c r="G375" t="inlineStr"/>
       <c r="H375" t="n">
         <v>1</v>
       </c>
@@ -21676,6 +21869,7 @@
           <t>临泽县</t>
         </is>
       </c>
+      <c r="G376" t="inlineStr"/>
       <c r="H376" t="n">
         <v>8.9</v>
       </c>
@@ -21730,6 +21924,7 @@
           <t>秦安县</t>
         </is>
       </c>
+      <c r="G377" t="inlineStr"/>
       <c r="H377" t="n">
         <v>105.67</v>
       </c>
@@ -21784,6 +21979,7 @@
           <t>金寨县</t>
         </is>
       </c>
+      <c r="G378" t="inlineStr"/>
       <c r="H378" t="n">
         <v>115.93</v>
       </c>
@@ -21838,6 +22034,7 @@
           <t>徽州区</t>
         </is>
       </c>
+      <c r="G379" t="inlineStr"/>
       <c r="H379" t="n">
         <v>118.34</v>
       </c>
@@ -21892,6 +22089,7 @@
           <t>黟县</t>
         </is>
       </c>
+      <c r="G380" t="inlineStr"/>
       <c r="H380" t="n">
         <v>117.94</v>
       </c>
@@ -21946,6 +22144,7 @@
           <t>万州区</t>
         </is>
       </c>
+      <c r="G381" t="inlineStr"/>
       <c r="H381" t="n">
         <v>108.41</v>
       </c>
@@ -22000,6 +22199,7 @@
           <t>万州区</t>
         </is>
       </c>
+      <c r="G382" t="inlineStr"/>
       <c r="H382" t="n">
         <v>108.41</v>
       </c>
@@ -22054,6 +22254,7 @@
           <t>开州区</t>
         </is>
       </c>
+      <c r="G383" t="inlineStr"/>
       <c r="H383" t="n">
         <v>108.42</v>
       </c>
@@ -22108,6 +22309,7 @@
           <t>黔江区</t>
         </is>
       </c>
+      <c r="G384" t="inlineStr"/>
       <c r="H384" t="n">
         <v>108.77</v>
       </c>
@@ -22162,6 +22364,7 @@
           <t>璧山区</t>
         </is>
       </c>
+      <c r="G385" t="inlineStr"/>
       <c r="H385" t="n">
         <v>106.23</v>
       </c>
@@ -22216,6 +22419,7 @@
           <t>集安市</t>
         </is>
       </c>
+      <c r="G386" t="inlineStr"/>
       <c r="H386" t="n">
         <v>126.18</v>
       </c>
@@ -22270,6 +22474,7 @@
           <t>洮南市</t>
         </is>
       </c>
+      <c r="G387" t="inlineStr"/>
       <c r="H387" t="n">
         <v>122.78</v>
       </c>
@@ -22324,6 +22529,7 @@
           <t>勃利县</t>
         </is>
       </c>
+      <c r="G388" t="inlineStr"/>
       <c r="H388" t="n">
         <v>130.57</v>
       </c>
@@ -22378,6 +22584,7 @@
           <t>孙吴县</t>
         </is>
       </c>
+      <c r="G389" t="inlineStr"/>
       <c r="H389" t="n">
         <v>127.33</v>
       </c>
@@ -22432,6 +22639,7 @@
           <t>宁陵县</t>
         </is>
       </c>
+      <c r="G390" t="inlineStr"/>
       <c r="H390" t="n">
         <v>115.32</v>
       </c>
@@ -22486,6 +22694,7 @@
           <t>荥阳市</t>
         </is>
       </c>
+      <c r="G391" t="inlineStr"/>
       <c r="H391" t="n">
         <v>113.38</v>
       </c>
@@ -22540,6 +22749,7 @@
           <t>深州市</t>
         </is>
       </c>
+      <c r="G392" t="inlineStr"/>
       <c r="H392" t="n">
         <v>115.56</v>
       </c>
@@ -22594,6 +22804,7 @@
           <t>怀来县</t>
         </is>
       </c>
+      <c r="G393" t="inlineStr"/>
       <c r="H393" t="n">
         <v>115.52</v>
       </c>
@@ -22648,6 +22859,7 @@
           <t>黄骅市</t>
         </is>
       </c>
+      <c r="G394" t="inlineStr"/>
       <c r="H394" t="n">
         <v>117.35</v>
       </c>
@@ -22702,6 +22914,7 @@
           <t>赵县</t>
         </is>
       </c>
+      <c r="G395" t="inlineStr"/>
       <c r="H395" t="n">
         <v>114.78</v>
       </c>
@@ -22756,6 +22969,7 @@
           <t>襄汾县</t>
         </is>
       </c>
+      <c r="G396" t="inlineStr"/>
       <c r="H396" t="n">
         <v>111.44</v>
       </c>
@@ -22810,6 +23024,7 @@
           <t>平陆县</t>
         </is>
       </c>
+      <c r="G397" t="inlineStr"/>
       <c r="H397" t="n">
         <v>111.22</v>
       </c>
@@ -22864,6 +23079,7 @@
           <t>清徐县</t>
         </is>
       </c>
+      <c r="G398" t="inlineStr"/>
       <c r="H398" t="n">
         <v>112.35</v>
       </c>
@@ -22918,6 +23134,7 @@
           <t>惠山区</t>
         </is>
       </c>
+      <c r="G399" t="inlineStr"/>
       <c r="H399" t="n">
         <v>120.3</v>
       </c>
@@ -22972,6 +23189,7 @@
           <t>句容市</t>
         </is>
       </c>
+      <c r="G400" t="inlineStr"/>
       <c r="H400" t="n">
         <v>119.16</v>
       </c>
@@ -23026,6 +23244,7 @@
           <t>吴中区</t>
         </is>
       </c>
+      <c r="G401" t="inlineStr"/>
       <c r="H401" t="n">
         <v>120.4</v>
       </c>
@@ -23080,6 +23299,7 @@
           <t>丰县</t>
         </is>
       </c>
+      <c r="G402" t="inlineStr"/>
       <c r="H402" t="n">
         <v>116.6</v>
       </c>
@@ -23134,6 +23354,7 @@
           <t>凤凰县</t>
         </is>
       </c>
+      <c r="G403" t="inlineStr"/>
       <c r="H403" t="n">
         <v>109.6</v>
       </c>
@@ -23188,6 +23409,7 @@
           <t>道县</t>
         </is>
       </c>
+      <c r="G404" t="inlineStr"/>
       <c r="H404" t="n">
         <v>111.6</v>
       </c>
@@ -23242,6 +23464,7 @@
           <t>枣阳市</t>
         </is>
       </c>
+      <c r="G405" t="inlineStr"/>
       <c r="H405" t="n">
         <v>112.77</v>
       </c>
@@ -23296,6 +23519,7 @@
           <t>麻城市</t>
         </is>
       </c>
+      <c r="G406" t="inlineStr"/>
       <c r="H406" t="n">
         <v>115.03</v>
       </c>
@@ -23350,6 +23574,7 @@
           <t>蒙阴县</t>
         </is>
       </c>
+      <c r="G407" t="inlineStr"/>
       <c r="H407" t="n">
         <v>117.93</v>
       </c>
@@ -23404,6 +23629,7 @@
           <t>博山区</t>
         </is>
       </c>
+      <c r="G408" t="inlineStr"/>
       <c r="H408" t="n">
         <v>117.86</v>
       </c>
@@ -23458,6 +23684,7 @@
           <t>黄陵县</t>
         </is>
       </c>
+      <c r="G409" t="inlineStr"/>
       <c r="H409" t="n">
         <v>9</v>
       </c>
@@ -23512,6 +23739,7 @@
           <t>郁南县</t>
         </is>
       </c>
+      <c r="G410" t="inlineStr"/>
       <c r="H410" t="n">
         <v>111.54</v>
       </c>
@@ -23566,6 +23794,7 @@
           <t>德庆县</t>
         </is>
       </c>
+      <c r="G411" t="inlineStr"/>
       <c r="H411" t="n">
         <v>111.77</v>
       </c>
@@ -23620,6 +23849,7 @@
           <t>梅县区</t>
         </is>
       </c>
+      <c r="G412" t="inlineStr"/>
       <c r="H412" t="n">
         <v>116.1</v>
       </c>
@@ -23674,6 +23904,7 @@
           <t>连州市</t>
         </is>
       </c>
+      <c r="G413" t="inlineStr"/>
       <c r="H413" t="n">
         <v>112.38</v>
       </c>
@@ -23728,6 +23959,7 @@
           <t>容县</t>
         </is>
       </c>
+      <c r="G414" t="inlineStr"/>
       <c r="H414" t="n">
         <v>110.55</v>
       </c>
@@ -23782,6 +24014,7 @@
           <t>富川瑶族自治县</t>
         </is>
       </c>
+      <c r="G415" t="inlineStr"/>
       <c r="H415" t="n">
         <v>10.9</v>
       </c>
@@ -23836,6 +24069,7 @@
           <t>保城镇</t>
         </is>
       </c>
+      <c r="G416" t="inlineStr"/>
       <c r="H416" t="n">
         <v>109.7</v>
       </c>
@@ -23890,6 +24124,7 @@
           <t>天涯区</t>
         </is>
       </c>
+      <c r="G417" t="inlineStr"/>
       <c r="H417" t="n">
         <v>109.51</v>
       </c>
@@ -23944,6 +24179,7 @@
           <t>佛罗镇</t>
         </is>
       </c>
+      <c r="G418" t="inlineStr"/>
       <c r="H418" t="n">
         <v>108.98</v>
       </c>
@@ -23998,6 +24234,7 @@
           <t>龙海区</t>
         </is>
       </c>
+      <c r="G419" t="inlineStr"/>
       <c r="H419" t="n">
         <v>117.8</v>
       </c>
@@ -24052,6 +24289,7 @@
           <t>仙游县</t>
         </is>
       </c>
+      <c r="G420" t="inlineStr"/>
       <c r="H420" t="n">
         <v>118.69</v>
       </c>
@@ -24106,6 +24344,7 @@
           <t>顺昌县</t>
         </is>
       </c>
+      <c r="G421" t="inlineStr"/>
       <c r="H421" t="n">
         <v>117.81</v>
       </c>
@@ -24160,6 +24399,7 @@
           <t>浦江县</t>
         </is>
       </c>
+      <c r="G422" t="inlineStr"/>
       <c r="H422" t="n">
         <v>119.89</v>
       </c>
@@ -24214,6 +24454,7 @@
           <t>玉环市</t>
         </is>
       </c>
+      <c r="G423" t="inlineStr"/>
       <c r="H423" t="n">
         <v>121.23</v>
       </c>
@@ -24268,6 +24509,7 @@
           <t>孟连傣族拉祜族佤族自治县</t>
         </is>
       </c>
+      <c r="G424" t="inlineStr"/>
       <c r="H424" t="n">
         <v>99.58</v>
       </c>
@@ -24322,6 +24564,7 @@
           <t>华宁县</t>
         </is>
       </c>
+      <c r="G425" t="inlineStr"/>
       <c r="H425" t="n">
         <v>102.93</v>
       </c>
@@ -24376,6 +24619,7 @@
           <t>高昌区</t>
         </is>
       </c>
+      <c r="G426" t="inlineStr"/>
       <c r="H426" t="n">
         <v>89.19</v>
       </c>
@@ -24430,6 +24674,7 @@
           <t>伊州区</t>
         </is>
       </c>
+      <c r="G427" t="inlineStr"/>
       <c r="H427" t="n">
         <v>6</v>
       </c>
@@ -24484,6 +24729,7 @@
           <t>伽师县</t>
         </is>
       </c>
+      <c r="G428" t="inlineStr"/>
       <c r="H428" t="n">
         <v>8</v>
       </c>
@@ -24538,6 +24784,7 @@
           <t>徐闻县</t>
         </is>
       </c>
+      <c r="G429" t="inlineStr"/>
       <c r="H429" t="n">
         <v>1</v>
       </c>
@@ -24592,6 +24839,7 @@
           <t>福山镇</t>
         </is>
       </c>
+      <c r="G430" t="inlineStr"/>
       <c r="H430" t="n">
         <v>1</v>
       </c>
@@ -24646,6 +24894,7 @@
           <t>元江哈尼族彝族傣族自治县</t>
         </is>
       </c>
+      <c r="G431" t="inlineStr"/>
       <c r="H431" t="n">
         <v>1</v>
       </c>
@@ -24700,6 +24949,7 @@
           <t>新宁县</t>
         </is>
       </c>
+      <c r="G432" t="inlineStr"/>
       <c r="H432" t="n">
         <v>1</v>
       </c>
@@ -24754,6 +25004,7 @@
           <t>吴中区</t>
         </is>
       </c>
+      <c r="G433" t="inlineStr"/>
       <c r="H433" t="n">
         <v>1</v>
       </c>
@@ -24808,6 +25059,7 @@
           <t>宾川县</t>
         </is>
       </c>
+      <c r="G434" t="inlineStr"/>
       <c r="H434" t="n">
         <v>1</v>
       </c>
@@ -24862,6 +25114,7 @@
           <t>荔城区</t>
         </is>
       </c>
+      <c r="G435" t="inlineStr"/>
       <c r="H435" t="n">
         <v>1</v>
       </c>
@@ -24916,6 +25169,7 @@
           <t>敖汉旗</t>
         </is>
       </c>
+      <c r="G436" t="inlineStr"/>
       <c r="H436" t="n">
         <v>1</v>
       </c>
@@ -24970,6 +25224,7 @@
           <t>扎兰屯市</t>
         </is>
       </c>
+      <c r="G437" t="inlineStr"/>
       <c r="H437" t="n">
         <v>1</v>
       </c>
@@ -25024,6 +25279,7 @@
           <t>攀枝花市</t>
         </is>
       </c>
+      <c r="G438" t="inlineStr"/>
       <c r="H438" t="n">
         <v>6.5</v>
       </c>
@@ -25041,6 +25297,7 @@
           <t>冬季巅峰型</t>
         </is>
       </c>
+      <c r="M438" t="inlineStr"/>
     </row>
     <row r="439" hidden="1">
       <c r="A439" t="inlineStr">
@@ -30049,6 +30306,7 @@
           <t>丹棱县</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="n">
         <v>103.53</v>
       </c>
@@ -30087,6 +30345,7 @@
           <t>东坡区</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="n">
         <v>103.83</v>
       </c>
@@ -30125,6 +30384,7 @@
           <t>蒲江县</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="n">
         <v>103.51</v>
       </c>
@@ -30163,6 +30423,7 @@
           <t>金堂县</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="n">
         <v>104.41</v>
       </c>
@@ -30201,6 +30462,7 @@
           <t>名山区</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="n">
         <v>103.11</v>
       </c>
@@ -30239,6 +30501,7 @@
           <t>苍溪县</t>
         </is>
       </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="n">
         <v>105.93</v>
       </c>
@@ -30277,6 +30540,7 @@
           <t>金川县</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="n">
         <v>102.06</v>
       </c>
@@ -30315,6 +30579,7 @@
           <t>龙泉驿区</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="n">
         <v>104.27</v>
       </c>
@@ -30353,6 +30618,7 @@
           <t>双流区</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
         <v>103.92</v>
       </c>
@@ -30434,6 +30700,7 @@
           <t>会理市</t>
         </is>
       </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="n">
         <v>102.25</v>
       </c>
@@ -30472,6 +30739,7 @@
           <t>新平县</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="n">
         <v>101.99</v>
       </c>
@@ -30510,6 +30778,7 @@
           <t>华宁县</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="n">
         <v>102.93</v>
       </c>
@@ -30548,6 +30817,7 @@
           <t>弥勒市</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="n">
         <v>103.41</v>
       </c>
@@ -30586,6 +30856,7 @@
           <t>沾益区</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="n">
         <v>103.82</v>
       </c>
@@ -30624,6 +30895,7 @@
           <t>澄江市</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="n">
         <v>102.91</v>
       </c>
@@ -30662,6 +30934,7 @@
           <t>大理州</t>
         </is>
       </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
         <v>100.23</v>
       </c>
@@ -30700,6 +30973,7 @@
           <t>蒙自市</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
         <v>103.36</v>
       </c>
@@ -30738,6 +31012,7 @@
           <t>永仁县</t>
         </is>
       </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
         <v>101.67</v>
       </c>
@@ -30776,6 +31051,7 @@
           <t>华坪县</t>
         </is>
       </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
         <v>101.27</v>
       </c>
@@ -30814,6 +31090,7 @@
           <t>元阳县</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
         <v>102.83</v>
       </c>
@@ -30852,6 +31129,7 @@
           <t>永德县</t>
         </is>
       </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
         <v>99.26000000000001</v>
       </c>
@@ -30890,6 +31168,7 @@
           <t>丘北县</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
         <v>104.19</v>
       </c>
@@ -30928,6 +31207,7 @@
           <t>开远市</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
         <v>103.27</v>
       </c>
@@ -30966,6 +31246,7 @@
           <t>富民县</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="n">
         <v>102.5</v>
       </c>
@@ -31004,6 +31285,7 @@
           <t>昭阳区</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
         <v>103.71</v>
       </c>
@@ -31042,6 +31324,7 @@
           <t>高州市</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
         <v>110.85</v>
       </c>
@@ -31080,6 +31363,7 @@
           <t>增城区</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="n">
         <v>113.81</v>
       </c>
@@ -31118,6 +31402,7 @@
           <t>阳东区</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="n">
         <v>112.01</v>
       </c>
@@ -31156,6 +31441,7 @@
           <t>四会市</t>
         </is>
       </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="n">
         <v>112.73</v>
       </c>
@@ -31194,6 +31480,7 @@
           <t>清远市</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="n">
         <v>113.06</v>
       </c>
@@ -31232,6 +31519,7 @@
           <t>徐闻县</t>
         </is>
       </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="n">
         <v>110.18</v>
       </c>
@@ -31270,6 +31558,7 @@
           <t>荔浦市</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="n">
         <v>110.39</v>
       </c>
@@ -31308,6 +31597,7 @@
           <t>蒙山县</t>
         </is>
       </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="n">
         <v>110.52</v>
       </c>
@@ -31346,6 +31636,7 @@
           <t>象州县</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="n">
         <v>109.68</v>
       </c>
@@ -31384,6 +31675,7 @@
           <t>田东县</t>
         </is>
       </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="n">
         <v>107.12</v>
       </c>
@@ -31422,6 +31714,7 @@
           <t>隆安县</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="n">
         <v>107.7</v>
       </c>
@@ -31460,6 +31753,7 @@
           <t>扶绥县</t>
         </is>
       </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="n">
         <v>107.9</v>
       </c>
@@ -31498,6 +31792,7 @@
           <t>北流市</t>
         </is>
       </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="n">
         <v>110.35</v>
       </c>
@@ -31536,6 +31831,7 @@
           <t>钦州市</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="n">
         <v>108.65</v>
       </c>
@@ -31574,6 +31870,7 @@
           <t>崇左市</t>
         </is>
       </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="n">
         <v>107.35</v>
       </c>
@@ -31612,6 +31909,7 @@
           <t>八步区</t>
         </is>
       </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
         <v>111.55</v>
       </c>
@@ -31650,6 +31948,7 @@
           <t>浦北县</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
         <v>109.56</v>
       </c>
@@ -31688,6 +31987,7 @@
           <t>天峨县</t>
         </is>
       </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
         <v>107.17</v>
       </c>
@@ -31726,6 +32026,7 @@
           <t>紫云县</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
         <v>106.08</v>
       </c>
@@ -31764,6 +32065,7 @@
           <t>麻江县</t>
         </is>
       </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
         <v>107.59</v>
       </c>
@@ -31802,6 +32104,7 @@
           <t>龙里县</t>
         </is>
       </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="n">
         <v>106.98</v>
       </c>
@@ -31840,6 +32143,7 @@
           <t>罗甸县</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="n">
         <v>106.75</v>
       </c>
@@ -31878,6 +32182,7 @@
           <t>纳雍县</t>
         </is>
       </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="n">
         <v>105.38</v>
       </c>
@@ -31916,6 +32221,7 @@
           <t>六盘水市</t>
         </is>
       </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="n">
         <v>104.83</v>
       </c>
@@ -31954,6 +32260,7 @@
           <t>贞丰县</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="n">
         <v>105.65</v>
       </c>
@@ -31992,6 +32299,7 @@
           <t>三亚市</t>
         </is>
       </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="n">
         <v>109.51</v>
       </c>
@@ -32030,6 +32338,7 @@
           <t>乐东县</t>
         </is>
       </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="n">
         <v>109.17</v>
       </c>
@@ -32068,6 +32377,7 @@
           <t>陵水县</t>
         </is>
       </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="n">
         <v>110.04</v>
       </c>
@@ -32106,6 +32416,7 @@
           <t>东方市</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="n">
         <v>108.65</v>
       </c>
@@ -32144,6 +32455,7 @@
           <t>澄迈县</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
         <v>110</v>
       </c>
@@ -32182,6 +32494,7 @@
           <t>琼海市</t>
         </is>
       </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
         <v>110.47</v>
       </c>
@@ -32220,6 +32533,7 @@
           <t>万宁市</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>110.39</v>
       </c>
@@ -32258,6 +32572,7 @@
           <t>海口市</t>
         </is>
       </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
         <v>110.2</v>
       </c>
@@ -32296,6 +32611,7 @@
           <t>琼山区</t>
         </is>
       </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
         <v>110.35</v>
       </c>
@@ -32334,6 +32650,7 @@
           <t>文昌市</t>
         </is>
       </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
         <v>110.8</v>
       </c>
@@ -32372,6 +32689,7 @@
           <t>石棉县</t>
         </is>
       </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
         <v>102.36</v>
       </c>
@@ -33485,6 +33803,7 @@
           <t>长阳土家族自治县</t>
         </is>
       </c>
+      <c r="E188" t="inlineStr"/>
       <c r="F188" t="n">
         <v>111.20105</v>
       </c>
@@ -33609,6 +33928,7 @@
           <t>公安县</t>
         </is>
       </c>
+      <c r="E191" t="inlineStr"/>
       <c r="F191" t="n">
         <v>112.23242</v>
       </c>
@@ -33647,6 +33967,7 @@
           <t>赤壁市</t>
         </is>
       </c>
+      <c r="E192" t="inlineStr"/>
       <c r="F192" t="n">
         <v>113.90039</v>
       </c>
@@ -33685,6 +34006,7 @@
           <t>建始县</t>
         </is>
       </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="n">
         <v>109.7182</v>
       </c>
@@ -33766,6 +34088,7 @@
           <t>宜都市</t>
         </is>
       </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="n">
         <v>111.45025</v>
       </c>
@@ -33804,6 +34127,7 @@
           <t>罗田县</t>
         </is>
       </c>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="n">
         <v>115.39056</v>
       </c>
@@ -33842,6 +34166,7 @@
           <t>房县</t>
         </is>
       </c>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="n">
         <v>110.73333</v>
       </c>
@@ -33880,6 +34205,7 @@
           <t>老河口市</t>
         </is>
       </c>
+      <c r="E198" t="inlineStr"/>
       <c r="F198" t="n">
         <v>111.66944</v>
       </c>
@@ -33918,6 +34244,7 @@
           <t>老河口市</t>
         </is>
       </c>
+      <c r="E199" t="inlineStr"/>
       <c r="F199" t="n">
         <v>111.66944</v>
       </c>
@@ -33956,6 +34283,7 @@
           <t>兴山县</t>
         </is>
       </c>
+      <c r="E200" t="inlineStr"/>
       <c r="F200" t="n">
         <v>110.74951</v>
       </c>
@@ -33994,6 +34322,7 @@
           <t>凉城县</t>
         </is>
       </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="n">
         <v>112.5</v>
       </c>
@@ -34032,6 +34361,7 @@
           <t>宁城县</t>
         </is>
       </c>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="n">
         <v>119.33333</v>
       </c>
@@ -34065,6 +34395,8 @@
           <t>乌海市</t>
         </is>
       </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="n">
         <v>106.8</v>
       </c>
@@ -34103,6 +34435,7 @@
           <t>延吉市</t>
         </is>
       </c>
+      <c r="E204" t="inlineStr"/>
       <c r="F204" t="n">
         <v>129.5</v>
       </c>
@@ -34136,6 +34469,8 @@
           <t>白山市</t>
         </is>
       </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
       <c r="F205" t="n">
         <v>126.41667</v>
       </c>
@@ -34174,6 +34509,7 @@
           <t>柳河县</t>
         </is>
       </c>
+      <c r="E206" t="inlineStr"/>
       <c r="F206" t="n">
         <v>125.74475</v>
       </c>
@@ -34212,6 +34548,7 @@
           <t>通化县</t>
         </is>
       </c>
+      <c r="E207" t="inlineStr"/>
       <c r="F207" t="n">
         <v>125.75936</v>
       </c>
@@ -34245,6 +34582,8 @@
           <t>大兴安岭地区</t>
         </is>
       </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="n">
         <v>124.11667</v>
       </c>
@@ -34283,6 +34622,7 @@
           <t>尚志市</t>
         </is>
       </c>
+      <c r="E209" t="inlineStr"/>
       <c r="F209" t="n">
         <v>127.96194</v>
       </c>
@@ -34321,6 +34661,7 @@
           <t>勃利县</t>
         </is>
       </c>
+      <c r="E210" t="inlineStr"/>
       <c r="F210" t="n">
         <v>130.56806</v>
       </c>
@@ -34359,6 +34700,7 @@
           <t>穆棱市</t>
         </is>
       </c>
+      <c r="E211" t="inlineStr"/>
       <c r="F211" t="n">
         <v>130.51667</v>
       </c>
@@ -34392,6 +34734,8 @@
           <t>伊春市</t>
         </is>
       </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
       <c r="F212" t="n">
         <v>128.84056</v>
       </c>
@@ -34425,6 +34769,8 @@
           <t>海西蒙古族藏族自治州</t>
         </is>
       </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
       <c r="F213" t="n">
         <v>97.36667</v>
       </c>
@@ -34463,6 +34809,7 @@
           <t>乐都区</t>
         </is>
       </c>
+      <c r="E214" t="inlineStr"/>
       <c r="F214" t="n">
         <v>102.4</v>
       </c>
@@ -34501,6 +34848,7 @@
           <t>乐都区</t>
         </is>
       </c>
+      <c r="E215" t="inlineStr"/>
       <c r="F215" t="n">
         <v>102.4</v>
       </c>
@@ -34539,6 +34887,7 @@
           <t>芒康县</t>
         </is>
       </c>
+      <c r="E216" t="inlineStr"/>
       <c r="F216" t="n">
         <v>98.59999999999999</v>
       </c>
@@ -34577,6 +34926,7 @@
           <t>朗县</t>
         </is>
       </c>
+      <c r="E217" t="inlineStr"/>
       <c r="F217" t="n">
         <v>93.06667</v>
       </c>
@@ -34658,6 +35008,7 @@
           <t>西峡县</t>
         </is>
       </c>
+      <c r="E219" t="inlineStr"/>
       <c r="F219" t="n">
         <v>111.47917</v>
       </c>
@@ -34696,6 +35047,7 @@
           <t>肥城市</t>
         </is>
       </c>
+      <c r="E220" t="inlineStr"/>
       <c r="F220" t="n">
         <v>116.46</v>
       </c>
@@ -34734,6 +35086,7 @@
           <t>乐陵市</t>
         </is>
       </c>
+      <c r="E221" t="inlineStr"/>
       <c r="F221" t="n">
         <v>117.12</v>
       </c>
@@ -34772,6 +35125,7 @@
           <t>威远县</t>
         </is>
       </c>
+      <c r="E222" t="inlineStr"/>
       <c r="F222" t="n">
         <v>104.66667</v>
       </c>
@@ -34810,6 +35164,7 @@
           <t>炎陵县</t>
         </is>
       </c>
+      <c r="E223" t="inlineStr"/>
       <c r="F223" t="n">
         <v>113.76667</v>
       </c>
@@ -34848,6 +35203,7 @@
           <t>隰县</t>
         </is>
       </c>
+      <c r="E224" t="inlineStr"/>
       <c r="F224" t="n">
         <v>110.93333</v>
       </c>
@@ -34881,6 +35237,8 @@
           <t>东方市</t>
         </is>
       </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
       <c r="F225" t="n">
         <v>108.63333</v>
       </c>
@@ -34919,6 +35277,7 @@
           <t>灵武市</t>
         </is>
       </c>
+      <c r="E226" t="inlineStr"/>
       <c r="F226" t="n">
         <v>106.33333</v>
       </c>
@@ -34957,6 +35316,7 @@
           <t>集安市</t>
         </is>
       </c>
+      <c r="E227" t="inlineStr"/>
       <c r="F227" t="n">
         <v>126.18829</v>
       </c>
@@ -34990,6 +35350,8 @@
           <t>龙岩市</t>
         </is>
       </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
       <c r="F228" t="n">
         <v>117.01667</v>
       </c>
@@ -35028,6 +35390,7 @@
           <t>青州市</t>
         </is>
       </c>
+      <c r="E229" t="inlineStr"/>
       <c r="F229" t="n">
         <v>118.46667</v>
       </c>
@@ -35061,6 +35424,8 @@
           <t>威海市</t>
         </is>
       </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
       <c r="F230" t="n">
         <v>122.11667</v>
       </c>
@@ -35185,6 +35550,7 @@
           <t>巴宜区</t>
         </is>
       </c>
+      <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
         <v>94.361</v>
       </c>
@@ -35223,6 +35589,7 @@
           <t>察隅县</t>
         </is>
       </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
         <v>97.465</v>
       </c>
@@ -35261,6 +35628,7 @@
           <t>中宁县</t>
         </is>
       </c>
+      <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>105.685</v>
       </c>
@@ -35299,6 +35667,7 @@
           <t>海原县</t>
         </is>
       </c>
+      <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
         <v>105.643</v>
       </c>
@@ -35380,6 +35749,7 @@
           <t>怀远县</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
         <v>117.205</v>
       </c>
@@ -35418,6 +35788,7 @@
           <t>萧县</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
         <v>116.947</v>
       </c>
@@ -35456,6 +35827,7 @@
           <t>广丰区</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
         <v>118.191</v>
       </c>
@@ -35494,6 +35866,7 @@
           <t>梁平区</t>
         </is>
       </c>
+      <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>107.802</v>
       </c>
@@ -35532,6 +35905,7 @@
           <t>潼南区</t>
         </is>
       </c>
+      <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
         <v>105.84</v>
       </c>
@@ -35570,6 +35944,7 @@
           <t>磴口县</t>
         </is>
       </c>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
         <v>107.008</v>
       </c>
@@ -35608,6 +35983,7 @@
           <t>鄂伦春自治旗</t>
         </is>
       </c>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
         <v>123.726</v>
       </c>
@@ -35646,6 +36022,7 @@
           <t>民和回族土族自治县</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr"/>
       <c r="F245" t="n">
         <v>102.83</v>
       </c>
@@ -35684,6 +36061,7 @@
           <t>尚志市</t>
         </is>
       </c>
+      <c r="E246" t="inlineStr"/>
       <c r="F246" t="n">
         <v>127.961</v>
       </c>
@@ -35722,6 +36100,7 @@
           <t>友好区</t>
         </is>
       </c>
+      <c r="E247" t="inlineStr"/>
       <c r="F247" t="n">
         <v>128.841</v>
       </c>
@@ -35760,6 +36139,7 @@
           <t>天涯区</t>
         </is>
       </c>
+      <c r="E248" t="inlineStr"/>
       <c r="F248" t="n">
         <v>109.506</v>
       </c>
@@ -35793,6 +36173,8 @@
           <t>琼中黎族苗族自治县</t>
         </is>
       </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr"/>
       <c r="F249" t="n">
         <v>109.838</v>
       </c>
@@ -35826,6 +36208,7 @@
           <t>文昌市</t>
         </is>
       </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
           <t>东郊镇</t>
@@ -35869,6 +36252,7 @@
           <t>西峰区</t>
         </is>
       </c>
+      <c r="E251" t="inlineStr"/>
       <c r="F251" t="n">
         <v>107.651</v>
       </c>
@@ -36939,6 +37323,7 @@
           <t>白水县</t>
         </is>
       </c>
+      <c r="E276" t="inlineStr"/>
       <c r="F276" t="n">
         <v>109.59</v>
       </c>
@@ -36977,6 +37362,7 @@
           <t>彬州市</t>
         </is>
       </c>
+      <c r="E277" t="inlineStr"/>
       <c r="F277" t="n">
         <v>108.08</v>
       </c>
@@ -37015,6 +37401,7 @@
           <t>永春县</t>
         </is>
       </c>
+      <c r="E278" t="inlineStr"/>
       <c r="F278" t="n">
         <v>118.29</v>
       </c>
@@ -37053,6 +37440,7 @@
           <t>诏安县</t>
         </is>
       </c>
+      <c r="E279" t="inlineStr"/>
       <c r="F279" t="n">
         <v>117.18</v>
       </c>
@@ -37134,6 +37522,7 @@
           <t>黄岩区</t>
         </is>
       </c>
+      <c r="E281" t="inlineStr"/>
       <c r="F281" t="n">
         <v>121.26</v>
       </c>
@@ -37172,6 +37561,7 @@
           <t>余姚市</t>
         </is>
       </c>
+      <c r="E282" t="inlineStr"/>
       <c r="F282" t="n">
         <v>121.16</v>
       </c>
@@ -37210,6 +37600,7 @@
           <t>常山县</t>
         </is>
       </c>
+      <c r="E283" t="inlineStr"/>
       <c r="F283" t="n">
         <v>118.51</v>
       </c>
@@ -37243,6 +37634,8 @@
           <t>大连市</t>
         </is>
       </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr"/>
       <c r="F284" t="n">
         <v>121.61</v>
       </c>
@@ -37281,6 +37674,7 @@
           <t>盖州市</t>
         </is>
       </c>
+      <c r="E285" t="inlineStr"/>
       <c r="F285" t="n">
         <v>122.35</v>
       </c>
@@ -37319,6 +37713,7 @@
           <t>辽中区</t>
         </is>
       </c>
+      <c r="E286" t="inlineStr"/>
       <c r="F286" t="n">
         <v>122.73</v>
       </c>
@@ -37352,6 +37747,8 @@
           <t>苏州市</t>
         </is>
       </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr"/>
       <c r="F287" t="n">
         <v>120.63</v>
       </c>
@@ -37390,6 +37787,7 @@
           <t>句容市</t>
         </is>
       </c>
+      <c r="E288" t="inlineStr"/>
       <c r="F288" t="n">
         <v>119.16</v>
       </c>
@@ -37428,6 +37826,7 @@
           <t>吴中区</t>
         </is>
       </c>
+      <c r="E289" t="inlineStr"/>
       <c r="F289" t="n">
         <v>120.63</v>
       </c>
@@ -37466,6 +37865,7 @@
           <t>江都区</t>
         </is>
       </c>
+      <c r="E290" t="inlineStr"/>
       <c r="F290" t="n">
         <v>119.57</v>
       </c>
@@ -37504,6 +37904,7 @@
           <t>牡丹江市</t>
         </is>
       </c>
+      <c r="E291" t="inlineStr"/>
       <c r="F291" t="n">
         <v>129.63</v>
       </c>
@@ -37537,6 +37938,8 @@
           <t>通化市</t>
         </is>
       </c>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr"/>
       <c r="F292" t="n">
         <v>125.94</v>
       </c>
@@ -37575,6 +37978,7 @@
           <t>临猗县</t>
         </is>
       </c>
+      <c r="E293" t="inlineStr"/>
       <c r="F293" t="n">
         <v>110.77</v>
       </c>
@@ -37608,6 +38012,8 @@
           <t>晋城市</t>
         </is>
       </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr"/>
       <c r="F294" t="n">
         <v>0</v>
       </c>
@@ -37646,6 +38052,7 @@
           <t>长寿区</t>
         </is>
       </c>
+      <c r="E295" t="inlineStr"/>
       <c r="F295" t="n">
         <v>107.08</v>
       </c>
@@ -37684,6 +38091,7 @@
           <t>永川区</t>
         </is>
       </c>
+      <c r="E296" t="inlineStr"/>
       <c r="F296" t="n">
         <v>105.89</v>
       </c>
@@ -37717,6 +38125,8 @@
           <t>吴忠市</t>
         </is>
       </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
         <v>106.2</v>
       </c>
@@ -37750,6 +38160,8 @@
           <t>海东市</t>
         </is>
       </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
         <v>102.1</v>
       </c>
@@ -37788,6 +38200,7 @@
           <t>磴口县</t>
         </is>
       </c>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
         <v>107.01</v>
       </c>
@@ -37821,6 +38234,8 @@
           <t>赤峰市</t>
         </is>
       </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>118.89</v>
       </c>
@@ -37859,6 +38274,7 @@
           <t>密云区</t>
         </is>
       </c>
+      <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
         <v>116.84</v>
       </c>
@@ -37897,6 +38313,7 @@
           <t>滨海新区</t>
         </is>
       </c>
+      <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>117.65</v>
       </c>
@@ -37935,6 +38352,7 @@
           <t>嘉定区</t>
         </is>
       </c>
+      <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
         <v>121.27</v>
       </c>
@@ -37973,6 +38391,7 @@
           <t>民和回族土族自治县</t>
         </is>
       </c>
+      <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
         <v>0</v>
       </c>
@@ -38011,6 +38430,7 @@
           <t>友好区</t>
         </is>
       </c>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
         <v>0</v>
       </c>
@@ -38044,6 +38464,8 @@
           <t>琼中黎族苗族自治县</t>
         </is>
       </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
         <v>0</v>
       </c>
@@ -38077,6 +38499,7 @@
           <t>文昌市</t>
         </is>
       </c>
+      <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
           <t>东郊镇</t>
@@ -38120,11 +38543,12 @@
           <t>民勤县</t>
         </is>
       </c>
+      <c r="E308" t="inlineStr"/>
       <c r="F308" t="n">
-        <v>0</v>
+        <v>103.1</v>
       </c>
       <c r="G308" t="n">
-        <v>0</v>
+        <v>38.63</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
@@ -38133,7 +38557,7 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>一般产区</t>
+          <t>重要产区</t>
         </is>
       </c>
     </row>
@@ -38158,6 +38582,7 @@
           <t>西峰区</t>
         </is>
       </c>
+      <c r="E309" t="inlineStr"/>
       <c r="F309" t="n">
         <v>0</v>
       </c>
@@ -39572,6 +39997,7 @@
           <t>雷波县</t>
         </is>
       </c>
+      <c r="E342" t="inlineStr"/>
       <c r="F342" t="n">
         <v>103.57</v>
       </c>
@@ -39610,6 +40036,7 @@
           <t>盐源县</t>
         </is>
       </c>
+      <c r="E343" t="inlineStr"/>
       <c r="F343" t="n">
         <v>101.51</v>
       </c>
@@ -39648,6 +40075,7 @@
           <t>蒲江县</t>
         </is>
       </c>
+      <c r="E344" t="inlineStr"/>
       <c r="F344" t="n">
         <v>103.54</v>
       </c>
@@ -39686,6 +40114,7 @@
           <t>都江堰市</t>
         </is>
       </c>
+      <c r="E345" t="inlineStr"/>
       <c r="F345" t="n">
         <v>103.62</v>
       </c>
@@ -39724,6 +40153,7 @@
           <t>米易县</t>
         </is>
       </c>
+      <c r="E346" t="inlineStr"/>
       <c r="F346" t="n">
         <v>102.11</v>
       </c>
@@ -39762,6 +40192,7 @@
           <t>邻水县</t>
         </is>
       </c>
+      <c r="E347" t="inlineStr"/>
       <c r="F347" t="n">
         <v>106.93</v>
       </c>
@@ -39800,6 +40231,7 @@
           <t>石棉县</t>
         </is>
       </c>
+      <c r="E348" t="inlineStr"/>
       <c r="F348" t="n">
         <v>102.36</v>
       </c>
@@ -39838,6 +40270,7 @@
           <t>德昌县</t>
         </is>
       </c>
+      <c r="E349" t="inlineStr"/>
       <c r="F349" t="n">
         <v>102.18</v>
       </c>
@@ -39876,6 +40309,7 @@
           <t>江阳区</t>
         </is>
       </c>
+      <c r="E350" t="inlineStr"/>
       <c r="F350" t="n">
         <v>105.44</v>
       </c>
@@ -39914,6 +40348,7 @@
           <t>大邑县</t>
         </is>
       </c>
+      <c r="E351" t="inlineStr"/>
       <c r="F351" t="n">
         <v>103.52</v>
       </c>
@@ -39952,6 +40387,7 @@
           <t>从江县</t>
         </is>
       </c>
+      <c r="E352" t="inlineStr"/>
       <c r="F352" t="n">
         <v>108.9</v>
       </c>
@@ -39990,6 +40426,7 @@
           <t>水城区</t>
         </is>
       </c>
+      <c r="E353" t="inlineStr"/>
       <c r="F353" t="n">
         <v>104.82</v>
       </c>
@@ -40028,6 +40465,7 @@
           <t>威宁彝族回族苗族自治县</t>
         </is>
       </c>
+      <c r="E354" t="inlineStr"/>
       <c r="F354" t="n">
         <v>104.28</v>
       </c>
@@ -40066,6 +40504,7 @@
           <t>开阳县</t>
         </is>
       </c>
+      <c r="E355" t="inlineStr"/>
       <c r="F355" t="n">
         <v>106.97</v>
       </c>
@@ -40104,6 +40543,7 @@
           <t>荔波县</t>
         </is>
       </c>
+      <c r="E356" t="inlineStr"/>
       <c r="F356" t="n">
         <v>107.88</v>
       </c>
@@ -40142,6 +40582,7 @@
           <t>沿河土家族自治县</t>
         </is>
       </c>
+      <c r="E357" t="inlineStr"/>
       <c r="F357" t="n">
         <v>108.5</v>
       </c>
@@ -40180,6 +40621,7 @@
           <t>敦煌市</t>
         </is>
       </c>
+      <c r="E358" t="inlineStr"/>
       <c r="F358" t="n">
         <v>94.66</v>
       </c>
@@ -40218,6 +40660,7 @@
           <t>皋兰县</t>
         </is>
       </c>
+      <c r="E359" t="inlineStr"/>
       <c r="F359" t="n">
         <v>103.95</v>
       </c>
@@ -40256,6 +40699,7 @@
           <t>临泽县</t>
         </is>
       </c>
+      <c r="E360" t="inlineStr"/>
       <c r="F360" t="n">
         <v>100.16</v>
       </c>
@@ -40294,6 +40738,7 @@
           <t>秦安县</t>
         </is>
       </c>
+      <c r="E361" t="inlineStr"/>
       <c r="F361" t="n">
         <v>105.67</v>
       </c>
@@ -40332,6 +40777,7 @@
           <t>金寨县</t>
         </is>
       </c>
+      <c r="E362" t="inlineStr"/>
       <c r="F362" t="n">
         <v>115.93</v>
       </c>
@@ -40370,6 +40816,7 @@
           <t>徽州区</t>
         </is>
       </c>
+      <c r="E363" t="inlineStr"/>
       <c r="F363" t="n">
         <v>118.34</v>
       </c>
@@ -40408,6 +40855,7 @@
           <t>黟县</t>
         </is>
       </c>
+      <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
         <v>117.94</v>
       </c>
@@ -40446,6 +40894,7 @@
           <t>万州区</t>
         </is>
       </c>
+      <c r="E365" t="inlineStr"/>
       <c r="F365" t="n">
         <v>108.41</v>
       </c>
@@ -40484,6 +40933,7 @@
           <t>万州区</t>
         </is>
       </c>
+      <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
         <v>108.41</v>
       </c>
@@ -40522,6 +40972,7 @@
           <t>开州区</t>
         </is>
       </c>
+      <c r="E367" t="inlineStr"/>
       <c r="F367" t="n">
         <v>108.42</v>
       </c>
@@ -40560,6 +41011,7 @@
           <t>黔江区</t>
         </is>
       </c>
+      <c r="E368" t="inlineStr"/>
       <c r="F368" t="n">
         <v>108.77</v>
       </c>
@@ -40598,6 +41050,7 @@
           <t>璧山区</t>
         </is>
       </c>
+      <c r="E369" t="inlineStr"/>
       <c r="F369" t="n">
         <v>106.23</v>
       </c>
@@ -40636,6 +41089,7 @@
           <t>集安市</t>
         </is>
       </c>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="n">
         <v>126.18</v>
       </c>
@@ -40674,6 +41128,7 @@
           <t>洮南市</t>
         </is>
       </c>
+      <c r="E371" t="inlineStr"/>
       <c r="F371" t="n">
         <v>122.78</v>
       </c>
@@ -40712,6 +41167,7 @@
           <t>勃利县</t>
         </is>
       </c>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="n">
         <v>130.57</v>
       </c>
@@ -40750,6 +41206,7 @@
           <t>孙吴县</t>
         </is>
       </c>
+      <c r="E373" t="inlineStr"/>
       <c r="F373" t="n">
         <v>127.33</v>
       </c>
@@ -40788,6 +41245,7 @@
           <t>宁陵县</t>
         </is>
       </c>
+      <c r="E374" t="inlineStr"/>
       <c r="F374" t="n">
         <v>115.32</v>
       </c>
@@ -40826,6 +41284,7 @@
           <t>荥阳市</t>
         </is>
       </c>
+      <c r="E375" t="inlineStr"/>
       <c r="F375" t="n">
         <v>113.38</v>
       </c>
@@ -40864,6 +41323,7 @@
           <t>深州市</t>
         </is>
       </c>
+      <c r="E376" t="inlineStr"/>
       <c r="F376" t="n">
         <v>115.56</v>
       </c>
@@ -40902,6 +41362,7 @@
           <t>怀来县</t>
         </is>
       </c>
+      <c r="E377" t="inlineStr"/>
       <c r="F377" t="n">
         <v>115.52</v>
       </c>
@@ -40940,6 +41401,7 @@
           <t>黄骅市</t>
         </is>
       </c>
+      <c r="E378" t="inlineStr"/>
       <c r="F378" t="n">
         <v>117.35</v>
       </c>
@@ -40978,6 +41440,7 @@
           <t>赵县</t>
         </is>
       </c>
+      <c r="E379" t="inlineStr"/>
       <c r="F379" t="n">
         <v>114.78</v>
       </c>
@@ -41016,6 +41479,7 @@
           <t>襄汾县</t>
         </is>
       </c>
+      <c r="E380" t="inlineStr"/>
       <c r="F380" t="n">
         <v>111.44</v>
       </c>
@@ -41054,6 +41518,7 @@
           <t>平陆县</t>
         </is>
       </c>
+      <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
         <v>111.22</v>
       </c>
@@ -41092,6 +41557,7 @@
           <t>清徐县</t>
         </is>
       </c>
+      <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
         <v>112.35</v>
       </c>
@@ -41130,6 +41596,7 @@
           <t>惠山区</t>
         </is>
       </c>
+      <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
         <v>120.3</v>
       </c>
@@ -41168,6 +41635,7 @@
           <t>句容市</t>
         </is>
       </c>
+      <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
         <v>119.16</v>
       </c>
@@ -41206,6 +41674,7 @@
           <t>吴中区</t>
         </is>
       </c>
+      <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>120.4</v>
       </c>
@@ -41244,6 +41713,7 @@
           <t>丰县</t>
         </is>
       </c>
+      <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
         <v>116.6</v>
       </c>
@@ -41282,6 +41752,7 @@
           <t>凤凰县</t>
         </is>
       </c>
+      <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
         <v>109.6</v>
       </c>
@@ -41320,6 +41791,7 @@
           <t>道县</t>
         </is>
       </c>
+      <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
         <v>111.6</v>
       </c>
@@ -41358,6 +41830,7 @@
           <t>枣阳市</t>
         </is>
       </c>
+      <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>112.77</v>
       </c>
@@ -41396,6 +41869,7 @@
           <t>麻城市</t>
         </is>
       </c>
+      <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
         <v>115.03</v>
       </c>
@@ -41434,6 +41908,7 @@
           <t>蒙阴县</t>
         </is>
       </c>
+      <c r="E391" t="inlineStr"/>
       <c r="F391" t="n">
         <v>117.93</v>
       </c>
@@ -41472,6 +41947,7 @@
           <t>博山区</t>
         </is>
       </c>
+      <c r="E392" t="inlineStr"/>
       <c r="F392" t="n">
         <v>117.86</v>
       </c>
@@ -41510,6 +41986,7 @@
           <t>黄陵县</t>
         </is>
       </c>
+      <c r="E393" t="inlineStr"/>
       <c r="F393" t="n">
         <v>109.26</v>
       </c>
@@ -41548,6 +42025,7 @@
           <t>郁南县</t>
         </is>
       </c>
+      <c r="E394" t="inlineStr"/>
       <c r="F394" t="n">
         <v>111.54</v>
       </c>
@@ -41586,6 +42064,7 @@
           <t>德庆县</t>
         </is>
       </c>
+      <c r="E395" t="inlineStr"/>
       <c r="F395" t="n">
         <v>111.77</v>
       </c>
@@ -41624,6 +42103,7 @@
           <t>梅县区</t>
         </is>
       </c>
+      <c r="E396" t="inlineStr"/>
       <c r="F396" t="n">
         <v>116.1</v>
       </c>
@@ -41662,6 +42142,7 @@
           <t>连州市</t>
         </is>
       </c>
+      <c r="E397" t="inlineStr"/>
       <c r="F397" t="n">
         <v>112.38</v>
       </c>
@@ -41700,6 +42181,7 @@
           <t>容县</t>
         </is>
       </c>
+      <c r="E398" t="inlineStr"/>
       <c r="F398" t="n">
         <v>110.55</v>
       </c>
@@ -41738,6 +42220,7 @@
           <t>富川瑶族自治县</t>
         </is>
       </c>
+      <c r="E399" t="inlineStr"/>
       <c r="F399" t="n">
         <v>111.28</v>
       </c>
@@ -41776,6 +42259,7 @@
           <t>保城镇</t>
         </is>
       </c>
+      <c r="E400" t="inlineStr"/>
       <c r="F400" t="n">
         <v>109.7</v>
       </c>
@@ -41814,6 +42298,7 @@
           <t>天涯区</t>
         </is>
       </c>
+      <c r="E401" t="inlineStr"/>
       <c r="F401" t="n">
         <v>109.51</v>
       </c>
@@ -41852,6 +42337,7 @@
           <t>佛罗镇</t>
         </is>
       </c>
+      <c r="E402" t="inlineStr"/>
       <c r="F402" t="n">
         <v>108.98</v>
       </c>
@@ -41890,6 +42376,7 @@
           <t>龙海区</t>
         </is>
       </c>
+      <c r="E403" t="inlineStr"/>
       <c r="F403" t="n">
         <v>117.8</v>
       </c>
@@ -41928,6 +42415,7 @@
           <t>仙游县</t>
         </is>
       </c>
+      <c r="E404" t="inlineStr"/>
       <c r="F404" t="n">
         <v>118.69</v>
       </c>
@@ -41966,6 +42454,7 @@
           <t>顺昌县</t>
         </is>
       </c>
+      <c r="E405" t="inlineStr"/>
       <c r="F405" t="n">
         <v>117.81</v>
       </c>
@@ -42004,6 +42493,7 @@
           <t>浦江县</t>
         </is>
       </c>
+      <c r="E406" t="inlineStr"/>
       <c r="F406" t="n">
         <v>119.89</v>
       </c>
@@ -42042,6 +42532,7 @@
           <t>玉环市</t>
         </is>
       </c>
+      <c r="E407" t="inlineStr"/>
       <c r="F407" t="n">
         <v>121.23</v>
       </c>
@@ -42080,6 +42571,7 @@
           <t>孟连傣族拉祜族佤族自治县</t>
         </is>
       </c>
+      <c r="E408" t="inlineStr"/>
       <c r="F408" t="n">
         <v>99.58</v>
       </c>
@@ -42118,6 +42610,7 @@
           <t>华宁县</t>
         </is>
       </c>
+      <c r="E409" t="inlineStr"/>
       <c r="F409" t="n">
         <v>102.93</v>
       </c>
@@ -42156,6 +42649,7 @@
           <t>高昌区</t>
         </is>
       </c>
+      <c r="E410" t="inlineStr"/>
       <c r="F410" t="n">
         <v>89.19</v>
       </c>
@@ -42194,6 +42688,7 @@
           <t>伊州区</t>
         </is>
       </c>
+      <c r="E411" t="inlineStr"/>
       <c r="F411" t="n">
         <v>93.51000000000001</v>
       </c>
@@ -42232,6 +42727,7 @@
           <t>伽师县</t>
         </is>
       </c>
+      <c r="E412" t="inlineStr"/>
       <c r="F412" t="n">
         <v>76.73</v>
       </c>
@@ -42270,6 +42766,7 @@
           <t>徐闻县</t>
         </is>
       </c>
+      <c r="E413" t="inlineStr"/>
       <c r="F413" t="n">
         <v>0</v>
       </c>
@@ -42308,6 +42805,7 @@
           <t>福山镇</t>
         </is>
       </c>
+      <c r="E414" t="inlineStr"/>
       <c r="F414" t="n">
         <v>0</v>
       </c>
@@ -42346,6 +42844,7 @@
           <t>元江哈尼族彝族傣族自治县</t>
         </is>
       </c>
+      <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
         <v>0</v>
       </c>
@@ -42384,6 +42883,7 @@
           <t>新宁县</t>
         </is>
       </c>
+      <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
         <v>0</v>
       </c>
@@ -42422,6 +42922,7 @@
           <t>吴中区</t>
         </is>
       </c>
+      <c r="E417" t="inlineStr"/>
       <c r="F417" t="n">
         <v>0</v>
       </c>
@@ -42460,6 +42961,7 @@
           <t>宾川县</t>
         </is>
       </c>
+      <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
         <v>0</v>
       </c>
@@ -42498,6 +43000,7 @@
           <t>荔城区</t>
         </is>
       </c>
+      <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
         <v>0</v>
       </c>
@@ -42536,6 +43039,7 @@
           <t>敖汉旗</t>
         </is>
       </c>
+      <c r="E420" t="inlineStr"/>
       <c r="F420" t="n">
         <v>0</v>
       </c>
@@ -42574,6 +43078,7 @@
           <t>扎兰屯市</t>
         </is>
       </c>
+      <c r="E421" t="inlineStr"/>
       <c r="F421" t="n">
         <v>0</v>
       </c>
@@ -42612,6 +43117,7 @@
           <t>攀枝花市</t>
         </is>
       </c>
+      <c r="E422" t="inlineStr"/>
       <c r="F422" t="n">
         <v>101.72</v>
       </c>

--- a/fruit_data.xlsx
+++ b/fruit_data.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M449"/>
+  <dimension ref="A1:M454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6177,7 +6177,6 @@
           <t>丹棱县</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>11</v>
       </c>
@@ -6232,7 +6231,6 @@
           <t>丹棱县</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>10</v>
       </c>
@@ -6287,7 +6285,6 @@
           <t>苍溪县</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>8</v>
       </c>
@@ -6342,7 +6339,6 @@
           <t>金川县</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>8</v>
       </c>
@@ -6397,7 +6393,6 @@
           <t>龙泉驿区</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>4</v>
       </c>
@@ -6429,7 +6424,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>巨峰、夏黑</t>
+          <t>巨峰</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6511,7 +6506,6 @@
           <t>会理市</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>7.9</v>
       </c>
@@ -6566,7 +6560,6 @@
           <t>双流区</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>12</v>
       </c>
@@ -6621,7 +6614,6 @@
           <t>新平县</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>1</v>
       </c>
@@ -6676,7 +6668,6 @@
           <t>新平县</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>10</v>
       </c>
@@ -6731,7 +6722,6 @@
           <t>弥勒市</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>12</v>
       </c>
@@ -6786,7 +6776,6 @@
           <t>宾川县</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>8</v>
       </c>
@@ -6841,7 +6830,6 @@
           <t>华坪县</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>6</v>
       </c>
@@ -6896,7 +6884,6 @@
           <t>丘北县</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>6</v>
       </c>
@@ -6951,7 +6938,6 @@
           <t>昭阳区</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>7</v>
       </c>
@@ -7006,7 +6992,6 @@
           <t>高州市</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>5</v>
       </c>
@@ -7061,7 +7046,6 @@
           <t>增城区</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>6</v>
       </c>
@@ -7116,7 +7100,6 @@
           <t>高州市</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>7</v>
       </c>
@@ -7171,7 +7154,6 @@
           <t>四会市</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>12</v>
       </c>
@@ -7285,7 +7267,6 @@
           <t>高州市</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>11</v>
       </c>
@@ -7340,7 +7321,6 @@
           <t>荔浦市</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>12</v>
       </c>
@@ -7395,7 +7375,6 @@
           <t>田东县</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>6</v>
       </c>
@@ -7450,7 +7429,6 @@
           <t>隆安县</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>5</v>
       </c>
@@ -7505,7 +7483,6 @@
           <t>北流市</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>7</v>
       </c>
@@ -7560,7 +7537,6 @@
           <t>八步区</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>5</v>
       </c>
@@ -7733,7 +7709,6 @@
           <t>麻江县</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>6</v>
       </c>
@@ -7788,7 +7763,6 @@
           <t>罗甸县</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>11</v>
       </c>
@@ -7843,7 +7817,6 @@
           <t>纳雍县</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>4</v>
       </c>
@@ -7898,7 +7871,6 @@
           <t>罗甸县</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>7</v>
       </c>
@@ -7953,7 +7925,6 @@
           <t>乐东黎族自治县</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>1</v>
       </c>
@@ -8008,7 +7979,6 @@
           <t>乐东县</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>9</v>
       </c>
@@ -8063,7 +8033,6 @@
           <t>万宁市</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>2</v>
       </c>
@@ -8118,7 +8087,6 @@
           <t>澄迈县</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>4</v>
       </c>
@@ -8173,7 +8141,6 @@
           <t>乐东黎族自治县</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>3</v>
       </c>
@@ -8228,7 +8195,6 @@
           <t>琼山区</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
         <v>12</v>
       </c>
@@ -8283,7 +8249,6 @@
           <t>乐东县</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>1</v>
       </c>
@@ -9813,7 +9778,6 @@
           <t>长阳土家族自治县</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
         <v>11</v>
       </c>
@@ -9986,7 +9950,6 @@
           <t>公安县</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
         <v>7</v>
       </c>
@@ -10041,7 +10004,6 @@
           <t>赤壁市</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
         <v>8</v>
       </c>
@@ -10096,7 +10058,6 @@
           <t>建始县</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
         <v>9</v>
       </c>
@@ -10210,7 +10171,6 @@
           <t>宜都市</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
         <v>10</v>
       </c>
@@ -10265,7 +10225,6 @@
           <t>罗田县</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
         <v>8</v>
       </c>
@@ -10320,7 +10279,6 @@
           <t>房县</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
         <v>4</v>
       </c>
@@ -10375,7 +10333,6 @@
           <t>老河口市</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
         <v>6</v>
       </c>
@@ -10430,7 +10387,6 @@
           <t>老河口市</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
         <v>7</v>
       </c>
@@ -10485,7 +10441,6 @@
           <t>兴山县</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
         <v>11</v>
       </c>
@@ -10540,7 +10495,6 @@
           <t>凉城县</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
         <v>8</v>
       </c>
@@ -10595,7 +10549,6 @@
           <t>宁城县</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
         <v>9</v>
       </c>
@@ -10645,8 +10598,6 @@
           <t>乌海市</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
       <c r="H176" t="n">
         <v>7</v>
       </c>
@@ -10755,8 +10706,6 @@
           <t>白山市</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
         <v>7</v>
       </c>
@@ -10811,7 +10760,6 @@
           <t>柳河县</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
         <v>8</v>
       </c>
@@ -10866,7 +10814,6 @@
           <t>通化县</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
         <v>7</v>
       </c>
@@ -10916,8 +10863,6 @@
           <t>大兴安岭地区</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
         <v>7</v>
       </c>
@@ -10972,7 +10917,6 @@
           <t>尚志市</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
         <v>7</v>
       </c>
@@ -11027,7 +10971,6 @@
           <t>勃利县</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
         <v>6</v>
       </c>
@@ -11082,7 +11025,6 @@
           <t>穆棱市</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
         <v>9</v>
       </c>
@@ -11137,7 +11079,6 @@
           <t>友好区</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
         <v>7</v>
       </c>
@@ -11187,8 +11128,6 @@
           <t>海西蒙古族藏族自治州</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
         <v>7</v>
       </c>
@@ -11243,7 +11182,6 @@
           <t>乐都区</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
         <v>8</v>
       </c>
@@ -11298,7 +11236,6 @@
           <t>乐都区</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
         <v>6</v>
       </c>
@@ -11353,7 +11290,6 @@
           <t>巴宜区</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
         <v>9</v>
       </c>
@@ -11408,7 +11344,6 @@
           <t>芒康县</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
         <v>8</v>
       </c>
@@ -11463,7 +11398,6 @@
           <t>朗县</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
         <v>9</v>
       </c>
@@ -11577,7 +11511,6 @@
           <t>西峡县</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
         <v>8</v>
       </c>
@@ -11632,7 +11565,6 @@
           <t>肥城市</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
         <v>8</v>
       </c>
@@ -11687,7 +11619,6 @@
           <t>乐陵市</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
         <v>9</v>
       </c>
@@ -11742,7 +11673,6 @@
           <t>威远县</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
         <v>7</v>
       </c>
@@ -11797,7 +11727,6 @@
           <t>炎陵县</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
         <v>7</v>
       </c>
@@ -11852,7 +11781,6 @@
           <t>隰县</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
         <v>9</v>
       </c>
@@ -11902,8 +11830,6 @@
           <t>东方市</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
         <v>5</v>
       </c>
@@ -11958,7 +11884,6 @@
           <t>灵武市</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
         <v>9</v>
       </c>
@@ -12013,7 +11938,6 @@
           <t>集安市</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
         <v>8</v>
       </c>
@@ -12063,8 +11987,6 @@
           <t>龙岩市</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
       <c r="H202" t="n">
         <v>7</v>
       </c>
@@ -12119,7 +12041,6 @@
           <t>青州市</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr"/>
       <c r="H203" t="n">
         <v>9</v>
       </c>
@@ -12169,8 +12090,6 @@
           <t>威海市</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
       <c r="H204" t="n">
         <v>7</v>
       </c>
@@ -12343,7 +12262,6 @@
           <t>察隅县</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr"/>
       <c r="H207" t="n">
         <v>9</v>
       </c>
@@ -12398,7 +12316,6 @@
           <t>中宁县</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr"/>
       <c r="H208" t="n">
         <v>6</v>
       </c>
@@ -12453,7 +12370,6 @@
           <t>海原县</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr"/>
       <c r="H209" t="n">
         <v>9</v>
       </c>
@@ -12567,7 +12483,6 @@
           <t>怀远县</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr"/>
       <c r="H211" t="n">
         <v>9</v>
       </c>
@@ -12622,7 +12537,6 @@
           <t>萧县</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr"/>
       <c r="H212" t="n">
         <v>7</v>
       </c>
@@ -12677,7 +12591,6 @@
           <t>广丰区</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
       <c r="H213" t="n">
         <v>11</v>
       </c>
@@ -12732,7 +12645,6 @@
           <t>梁平区</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
       <c r="H214" t="n">
         <v>10</v>
       </c>
@@ -12787,7 +12699,6 @@
           <t>潼南区</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr"/>
       <c r="H215" t="n">
         <v>9</v>
       </c>
@@ -12842,7 +12753,6 @@
           <t>磴口县</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
       <c r="H216" t="n">
         <v>7</v>
       </c>
@@ -12897,7 +12807,6 @@
           <t>鄂伦春自治旗</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
       <c r="H217" t="n">
         <v>7</v>
       </c>
@@ -12952,7 +12861,6 @@
           <t>民和回族土族自治县</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr"/>
       <c r="H218" t="n">
         <v>7</v>
       </c>
@@ -13002,8 +12910,6 @@
           <t>琼中黎族苗族自治县</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
       <c r="H219" t="n">
         <v>10</v>
       </c>
@@ -13053,7 +12959,6 @@
           <t>文昌市</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
           <t>东郊镇</t>
@@ -13113,7 +13018,6 @@
           <t>民勤县</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr"/>
       <c r="H221" t="n">
         <v>7</v>
       </c>
@@ -13168,7 +13072,6 @@
           <t>西峰区</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr"/>
       <c r="H222" t="n">
         <v>9</v>
       </c>
@@ -14701,7 +14604,6 @@
           <t>白水县</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr"/>
       <c r="H248" t="n">
         <v>9</v>
       </c>
@@ -14756,7 +14658,6 @@
           <t>清涧县</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr"/>
       <c r="H249" t="n">
         <v>9</v>
       </c>
@@ -14811,7 +14712,6 @@
           <t>城固县</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr"/>
       <c r="H250" t="n">
         <v>10</v>
       </c>
@@ -14866,7 +14766,6 @@
           <t>彬州市</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr"/>
       <c r="H251" t="n">
         <v>9</v>
       </c>
@@ -14916,8 +14815,6 @@
           <t>延安市</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
       <c r="H252" t="n">
         <v>10</v>
       </c>
@@ -14967,8 +14864,6 @@
           <t>西安市</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr"/>
-      <c r="G253" t="inlineStr"/>
       <c r="H253" t="n">
         <v>12</v>
       </c>
@@ -15023,7 +14918,6 @@
           <t>永春县</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr"/>
       <c r="H254" t="n">
         <v>11</v>
       </c>
@@ -15073,8 +14967,6 @@
           <t>莆田市</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr"/>
-      <c r="G255" t="inlineStr"/>
       <c r="H255" t="n">
         <v>3</v>
       </c>
@@ -15129,7 +15021,6 @@
           <t>闽侯县</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr"/>
       <c r="H256" t="n">
         <v>7</v>
       </c>
@@ -15184,7 +15075,6 @@
           <t>诏安县</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr"/>
       <c r="H257" t="n">
         <v>4</v>
       </c>
@@ -15239,7 +15129,6 @@
           <t>建瓯市</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr"/>
       <c r="H258" t="n">
         <v>9</v>
       </c>
@@ -15294,7 +15183,6 @@
           <t>福鼎市</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr"/>
       <c r="H259" t="n">
         <v>10</v>
       </c>
@@ -15349,7 +15237,6 @@
           <t>长泰区</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr"/>
       <c r="H260" t="n">
         <v>11</v>
       </c>
@@ -15404,7 +15291,6 @@
           <t>闽侯县</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr"/>
       <c r="H261" t="n">
         <v>6</v>
       </c>
@@ -15518,7 +15404,6 @@
           <t>黄岩区</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr"/>
       <c r="H263" t="n">
         <v>10</v>
       </c>
@@ -15573,7 +15458,6 @@
           <t>象山县</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr"/>
       <c r="H264" t="n">
         <v>11</v>
       </c>
@@ -15628,7 +15512,6 @@
           <t>余姚市</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr"/>
       <c r="H265" t="n">
         <v>6</v>
       </c>
@@ -15678,8 +15561,6 @@
           <t>衢州市</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr"/>
       <c r="H266" t="n">
         <v>11</v>
       </c>
@@ -15734,7 +15615,6 @@
           <t>常山县</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr"/>
       <c r="H267" t="n">
         <v>11</v>
       </c>
@@ -15789,7 +15669,6 @@
           <t>桐乡市</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr"/>
       <c r="H268" t="n">
         <v>6</v>
       </c>
@@ -15839,8 +15718,6 @@
           <t>大连市</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr"/>
-      <c r="G269" t="inlineStr"/>
       <c r="H269" t="n">
         <v>5</v>
       </c>
@@ -15890,8 +15767,6 @@
           <t>丹东市</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr"/>
       <c r="H270" t="n">
         <v>12</v>
       </c>
@@ -15946,7 +15821,6 @@
           <t>盖州市</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr"/>
       <c r="H271" t="n">
         <v>8</v>
       </c>
@@ -16001,7 +15875,6 @@
           <t>绥中县</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr"/>
       <c r="H272" t="n">
         <v>9</v>
       </c>
@@ -16056,7 +15929,6 @@
           <t>辽中区</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr"/>
       <c r="H273" t="n">
         <v>10</v>
       </c>
@@ -16111,7 +15983,6 @@
           <t>庄河市</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr"/>
       <c r="H274" t="n">
         <v>6</v>
       </c>
@@ -16161,8 +16032,6 @@
           <t>朝阳市</t>
         </is>
       </c>
-      <c r="F275" t="inlineStr"/>
-      <c r="G275" t="inlineStr"/>
       <c r="H275" t="n">
         <v>9</v>
       </c>
@@ -16212,8 +16081,6 @@
           <t>苏州市</t>
         </is>
       </c>
-      <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr"/>
       <c r="H276" t="n">
         <v>6</v>
       </c>
@@ -16268,7 +16135,6 @@
           <t>句容市</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr"/>
       <c r="H277" t="n">
         <v>7</v>
       </c>
@@ -16323,7 +16189,6 @@
           <t>吴中区</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr"/>
       <c r="H278" t="n">
         <v>5</v>
       </c>
@@ -16378,7 +16243,6 @@
           <t>丰县</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr"/>
       <c r="H279" t="n">
         <v>9</v>
       </c>
@@ -16433,7 +16297,6 @@
           <t>溧水区</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr"/>
       <c r="H280" t="n">
         <v>12</v>
       </c>
@@ -16488,7 +16351,6 @@
           <t>江都区</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr"/>
       <c r="H281" t="n">
         <v>9</v>
       </c>
@@ -16543,7 +16405,6 @@
           <t>句容市</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr"/>
       <c r="H282" t="n">
         <v>7</v>
       </c>
@@ -16598,7 +16459,6 @@
           <t>秦州区</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr"/>
       <c r="H283" t="n">
         <v>9</v>
       </c>
@@ -16648,8 +16508,6 @@
           <t>兰州市</t>
         </is>
       </c>
-      <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr"/>
       <c r="H284" t="n">
         <v>9</v>
       </c>
@@ -16704,7 +16562,6 @@
           <t>牡丹江市</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr"/>
       <c r="H285" t="n">
         <v>9</v>
       </c>
@@ -16754,8 +16611,6 @@
           <t>通化市</t>
         </is>
       </c>
-      <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr"/>
       <c r="H286" t="n">
         <v>9</v>
       </c>
@@ -16805,8 +16660,6 @@
           <t>四平市</t>
         </is>
       </c>
-      <c r="F287" t="inlineStr"/>
-      <c r="G287" t="inlineStr"/>
       <c r="H287" t="n">
         <v>9</v>
       </c>
@@ -16861,7 +16714,6 @@
           <t>临猗县</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr"/>
       <c r="H288" t="n">
         <v>10</v>
       </c>
@@ -16911,8 +16763,6 @@
           <t>吕梁市</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr"/>
-      <c r="G289" t="inlineStr"/>
       <c r="H289" t="n">
         <v>9</v>
       </c>
@@ -16962,8 +16812,6 @@
           <t>晋中市</t>
         </is>
       </c>
-      <c r="F290" t="inlineStr"/>
-      <c r="G290" t="inlineStr"/>
       <c r="H290" t="n">
         <v>8</v>
       </c>
@@ -17013,8 +16861,6 @@
           <t>晋城市</t>
         </is>
       </c>
-      <c r="F291" t="inlineStr"/>
-      <c r="G291" t="inlineStr"/>
       <c r="H291" t="n">
         <v>9</v>
       </c>
@@ -17069,7 +16915,6 @@
           <t>万州区</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr"/>
       <c r="H292" t="n">
         <v>10</v>
       </c>
@@ -17124,7 +16969,6 @@
           <t>长寿区</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr"/>
       <c r="H293" t="n">
         <v>11</v>
       </c>
@@ -17179,7 +17023,6 @@
           <t>江津区</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr"/>
       <c r="H294" t="n">
         <v>10</v>
       </c>
@@ -17234,7 +17077,6 @@
           <t>永川区</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr"/>
       <c r="H295" t="n">
         <v>8</v>
       </c>
@@ -17289,7 +17131,6 @@
           <t>忠县</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr"/>
       <c r="H296" t="n">
         <v>10</v>
       </c>
@@ -17339,8 +17180,6 @@
           <t>吴忠市</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr"/>
-      <c r="G297" t="inlineStr"/>
       <c r="H297" t="n">
         <v>8</v>
       </c>
@@ -17390,8 +17229,6 @@
           <t>海东市</t>
         </is>
       </c>
-      <c r="F298" t="inlineStr"/>
-      <c r="G298" t="inlineStr"/>
       <c r="H298" t="n">
         <v>6</v>
       </c>
@@ -17441,8 +17278,6 @@
           <t>海南藏族自治州</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr"/>
-      <c r="G299" t="inlineStr"/>
       <c r="H299" t="n">
         <v>9</v>
       </c>
@@ -17497,7 +17332,6 @@
           <t>磴口县</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr"/>
       <c r="H300" t="n">
         <v>7</v>
       </c>
@@ -17547,8 +17381,6 @@
           <t>赤峰市</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr"/>
-      <c r="G301" t="inlineStr"/>
       <c r="H301" t="n">
         <v>9</v>
       </c>
@@ -17603,7 +17435,6 @@
           <t>昌平区</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr"/>
       <c r="H302" t="n">
         <v>12</v>
       </c>
@@ -17658,7 +17489,6 @@
           <t>密云区</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr"/>
       <c r="H303" t="n">
         <v>5</v>
       </c>
@@ -17713,7 +17543,6 @@
           <t>蓟州区</t>
         </is>
       </c>
-      <c r="G304" t="inlineStr"/>
       <c r="H304" t="n">
         <v>10</v>
       </c>
@@ -17768,7 +17597,6 @@
           <t>滨海新区</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr"/>
       <c r="H305" t="n">
         <v>8</v>
       </c>
@@ -17823,7 +17651,6 @@
           <t>武清区</t>
         </is>
       </c>
-      <c r="G306" t="inlineStr"/>
       <c r="H306" t="n">
         <v>6</v>
       </c>
@@ -17878,7 +17705,6 @@
           <t>崇明区</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr"/>
       <c r="H307" t="n">
         <v>10</v>
       </c>
@@ -17933,7 +17759,6 @@
           <t>嘉定区</t>
         </is>
       </c>
-      <c r="G308" t="inlineStr"/>
       <c r="H308" t="n">
         <v>7</v>
       </c>
@@ -20879,7 +20704,6 @@
           <t>雷波县</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr"/>
       <c r="H358" t="n">
         <v>10.9</v>
       </c>
@@ -20934,7 +20758,6 @@
           <t>盐源县</t>
         </is>
       </c>
-      <c r="G359" t="inlineStr"/>
       <c r="H359" t="n">
         <v>7.9</v>
       </c>
@@ -20989,7 +20812,6 @@
           <t>蒲江县</t>
         </is>
       </c>
-      <c r="G360" t="inlineStr"/>
       <c r="H360" t="n">
         <v>8.9</v>
       </c>
@@ -21044,7 +20866,6 @@
           <t>都江堰市</t>
         </is>
       </c>
-      <c r="G361" t="inlineStr"/>
       <c r="H361" t="n">
         <v>103.62</v>
       </c>
@@ -21099,7 +20920,6 @@
           <t>米易县</t>
         </is>
       </c>
-      <c r="G362" t="inlineStr"/>
       <c r="H362" t="n">
         <v>12</v>
       </c>
@@ -21154,7 +20974,6 @@
           <t>邻水县</t>
         </is>
       </c>
-      <c r="G363" t="inlineStr"/>
       <c r="H363" t="n">
         <v>106.93</v>
       </c>
@@ -21209,7 +21028,6 @@
           <t>石棉县</t>
         </is>
       </c>
-      <c r="G364" t="inlineStr"/>
       <c r="H364" t="n">
         <v>1</v>
       </c>
@@ -21264,7 +21082,6 @@
           <t>德昌县</t>
         </is>
       </c>
-      <c r="G365" t="inlineStr"/>
       <c r="H365" t="n">
         <v>3.5</v>
       </c>
@@ -21319,7 +21136,6 @@
           <t>江阳区</t>
         </is>
       </c>
-      <c r="G366" t="inlineStr"/>
       <c r="H366" t="n">
         <v>8</v>
       </c>
@@ -21374,7 +21190,6 @@
           <t>大邑县</t>
         </is>
       </c>
-      <c r="G367" t="inlineStr"/>
       <c r="H367" t="n">
         <v>4.5</v>
       </c>
@@ -21429,7 +21244,6 @@
           <t>从江县</t>
         </is>
       </c>
-      <c r="G368" t="inlineStr"/>
       <c r="H368" t="n">
         <v>108.9</v>
       </c>
@@ -21484,7 +21298,6 @@
           <t>水城区</t>
         </is>
       </c>
-      <c r="G369" t="inlineStr"/>
       <c r="H369" t="n">
         <v>104.82</v>
       </c>
@@ -21539,7 +21352,6 @@
           <t>威宁彝族回族苗族自治县</t>
         </is>
       </c>
-      <c r="G370" t="inlineStr"/>
       <c r="H370" t="n">
         <v>104.28</v>
       </c>
@@ -21594,7 +21406,6 @@
           <t>开阳县</t>
         </is>
       </c>
-      <c r="G371" t="inlineStr"/>
       <c r="H371" t="n">
         <v>106.97</v>
       </c>
@@ -21649,7 +21460,6 @@
           <t>荔波县</t>
         </is>
       </c>
-      <c r="G372" t="inlineStr"/>
       <c r="H372" t="n">
         <v>107.88</v>
       </c>
@@ -21704,7 +21514,6 @@
           <t>沿河土家族自治县</t>
         </is>
       </c>
-      <c r="G373" t="inlineStr"/>
       <c r="H373" t="n">
         <v>108.5</v>
       </c>
@@ -21759,7 +21568,6 @@
           <t>敦煌市</t>
         </is>
       </c>
-      <c r="G374" t="inlineStr"/>
       <c r="H374" t="n">
         <v>8</v>
       </c>
@@ -21814,7 +21622,6 @@
           <t>皋兰县</t>
         </is>
       </c>
-      <c r="G375" t="inlineStr"/>
       <c r="H375" t="n">
         <v>1</v>
       </c>
@@ -21869,7 +21676,6 @@
           <t>临泽县</t>
         </is>
       </c>
-      <c r="G376" t="inlineStr"/>
       <c r="H376" t="n">
         <v>8.9</v>
       </c>
@@ -21924,7 +21730,6 @@
           <t>秦安县</t>
         </is>
       </c>
-      <c r="G377" t="inlineStr"/>
       <c r="H377" t="n">
         <v>105.67</v>
       </c>
@@ -21979,7 +21784,6 @@
           <t>金寨县</t>
         </is>
       </c>
-      <c r="G378" t="inlineStr"/>
       <c r="H378" t="n">
         <v>115.93</v>
       </c>
@@ -22034,7 +21838,6 @@
           <t>徽州区</t>
         </is>
       </c>
-      <c r="G379" t="inlineStr"/>
       <c r="H379" t="n">
         <v>118.34</v>
       </c>
@@ -22089,7 +21892,6 @@
           <t>黟县</t>
         </is>
       </c>
-      <c r="G380" t="inlineStr"/>
       <c r="H380" t="n">
         <v>117.94</v>
       </c>
@@ -22144,7 +21946,6 @@
           <t>万州区</t>
         </is>
       </c>
-      <c r="G381" t="inlineStr"/>
       <c r="H381" t="n">
         <v>108.41</v>
       </c>
@@ -22199,7 +22000,6 @@
           <t>万州区</t>
         </is>
       </c>
-      <c r="G382" t="inlineStr"/>
       <c r="H382" t="n">
         <v>108.41</v>
       </c>
@@ -22254,7 +22054,6 @@
           <t>开州区</t>
         </is>
       </c>
-      <c r="G383" t="inlineStr"/>
       <c r="H383" t="n">
         <v>108.42</v>
       </c>
@@ -22309,7 +22108,6 @@
           <t>黔江区</t>
         </is>
       </c>
-      <c r="G384" t="inlineStr"/>
       <c r="H384" t="n">
         <v>108.77</v>
       </c>
@@ -22364,7 +22162,6 @@
           <t>璧山区</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr"/>
       <c r="H385" t="n">
         <v>106.23</v>
       </c>
@@ -22419,7 +22216,6 @@
           <t>集安市</t>
         </is>
       </c>
-      <c r="G386" t="inlineStr"/>
       <c r="H386" t="n">
         <v>126.18</v>
       </c>
@@ -22474,7 +22270,6 @@
           <t>洮南市</t>
         </is>
       </c>
-      <c r="G387" t="inlineStr"/>
       <c r="H387" t="n">
         <v>122.78</v>
       </c>
@@ -22529,7 +22324,6 @@
           <t>勃利县</t>
         </is>
       </c>
-      <c r="G388" t="inlineStr"/>
       <c r="H388" t="n">
         <v>130.57</v>
       </c>
@@ -22584,7 +22378,6 @@
           <t>孙吴县</t>
         </is>
       </c>
-      <c r="G389" t="inlineStr"/>
       <c r="H389" t="n">
         <v>127.33</v>
       </c>
@@ -22639,7 +22432,6 @@
           <t>宁陵县</t>
         </is>
       </c>
-      <c r="G390" t="inlineStr"/>
       <c r="H390" t="n">
         <v>115.32</v>
       </c>
@@ -22694,7 +22486,6 @@
           <t>荥阳市</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr"/>
       <c r="H391" t="n">
         <v>113.38</v>
       </c>
@@ -22749,7 +22540,6 @@
           <t>深州市</t>
         </is>
       </c>
-      <c r="G392" t="inlineStr"/>
       <c r="H392" t="n">
         <v>115.56</v>
       </c>
@@ -22804,7 +22594,6 @@
           <t>怀来县</t>
         </is>
       </c>
-      <c r="G393" t="inlineStr"/>
       <c r="H393" t="n">
         <v>115.52</v>
       </c>
@@ -22859,7 +22648,6 @@
           <t>黄骅市</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr"/>
       <c r="H394" t="n">
         <v>117.35</v>
       </c>
@@ -22914,7 +22702,6 @@
           <t>赵县</t>
         </is>
       </c>
-      <c r="G395" t="inlineStr"/>
       <c r="H395" t="n">
         <v>114.78</v>
       </c>
@@ -22969,7 +22756,6 @@
           <t>襄汾县</t>
         </is>
       </c>
-      <c r="G396" t="inlineStr"/>
       <c r="H396" t="n">
         <v>111.44</v>
       </c>
@@ -23024,7 +22810,6 @@
           <t>平陆县</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr"/>
       <c r="H397" t="n">
         <v>111.22</v>
       </c>
@@ -23079,12 +22864,11 @@
           <t>清徐县</t>
         </is>
       </c>
-      <c r="G398" t="inlineStr"/>
       <c r="H398" t="n">
-        <v>112.35</v>
+        <v>7.5</v>
       </c>
       <c r="I398" t="n">
-        <v>37.61</v>
+        <v>10.9</v>
       </c>
       <c r="J398" t="n">
         <v>8</v>
@@ -23099,7 +22883,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>国家地理标志产品。山西葡萄之乡，千年种植历史，粒大饱满、风味浓郁。</t>
+          <t>国家地理标志产品。山西葡萄之乡，千年种植历史，粒大饱满、风味浓郁。月下旬至8月是葡萄采摘黄金期，夏黑、巨峰、玫瑰香等采摘期可延续到10月，卡拉斯玫瑰等晚熟鲜食葡萄</t>
         </is>
       </c>
     </row>
@@ -23134,7 +22918,6 @@
           <t>惠山区</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr"/>
       <c r="H399" t="n">
         <v>120.3</v>
       </c>
@@ -23189,7 +22972,6 @@
           <t>句容市</t>
         </is>
       </c>
-      <c r="G400" t="inlineStr"/>
       <c r="H400" t="n">
         <v>119.16</v>
       </c>
@@ -23244,7 +23026,6 @@
           <t>吴中区</t>
         </is>
       </c>
-      <c r="G401" t="inlineStr"/>
       <c r="H401" t="n">
         <v>120.4</v>
       </c>
@@ -23299,7 +23080,6 @@
           <t>丰县</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr"/>
       <c r="H402" t="n">
         <v>116.6</v>
       </c>
@@ -23354,7 +23134,6 @@
           <t>凤凰县</t>
         </is>
       </c>
-      <c r="G403" t="inlineStr"/>
       <c r="H403" t="n">
         <v>109.6</v>
       </c>
@@ -23409,7 +23188,6 @@
           <t>道县</t>
         </is>
       </c>
-      <c r="G404" t="inlineStr"/>
       <c r="H404" t="n">
         <v>111.6</v>
       </c>
@@ -23464,7 +23242,6 @@
           <t>枣阳市</t>
         </is>
       </c>
-      <c r="G405" t="inlineStr"/>
       <c r="H405" t="n">
         <v>112.77</v>
       </c>
@@ -23519,7 +23296,6 @@
           <t>麻城市</t>
         </is>
       </c>
-      <c r="G406" t="inlineStr"/>
       <c r="H406" t="n">
         <v>115.03</v>
       </c>
@@ -23574,7 +23350,6 @@
           <t>蒙阴县</t>
         </is>
       </c>
-      <c r="G407" t="inlineStr"/>
       <c r="H407" t="n">
         <v>117.93</v>
       </c>
@@ -23629,7 +23404,6 @@
           <t>博山区</t>
         </is>
       </c>
-      <c r="G408" t="inlineStr"/>
       <c r="H408" t="n">
         <v>117.86</v>
       </c>
@@ -23684,7 +23458,6 @@
           <t>黄陵县</t>
         </is>
       </c>
-      <c r="G409" t="inlineStr"/>
       <c r="H409" t="n">
         <v>9</v>
       </c>
@@ -23739,7 +23512,6 @@
           <t>郁南县</t>
         </is>
       </c>
-      <c r="G410" t="inlineStr"/>
       <c r="H410" t="n">
         <v>111.54</v>
       </c>
@@ -23794,7 +23566,6 @@
           <t>德庆县</t>
         </is>
       </c>
-      <c r="G411" t="inlineStr"/>
       <c r="H411" t="n">
         <v>111.77</v>
       </c>
@@ -23849,7 +23620,6 @@
           <t>梅县区</t>
         </is>
       </c>
-      <c r="G412" t="inlineStr"/>
       <c r="H412" t="n">
         <v>116.1</v>
       </c>
@@ -23904,7 +23674,6 @@
           <t>连州市</t>
         </is>
       </c>
-      <c r="G413" t="inlineStr"/>
       <c r="H413" t="n">
         <v>112.38</v>
       </c>
@@ -23959,7 +23728,6 @@
           <t>容县</t>
         </is>
       </c>
-      <c r="G414" t="inlineStr"/>
       <c r="H414" t="n">
         <v>110.55</v>
       </c>
@@ -24014,7 +23782,6 @@
           <t>富川瑶族自治县</t>
         </is>
       </c>
-      <c r="G415" t="inlineStr"/>
       <c r="H415" t="n">
         <v>10.9</v>
       </c>
@@ -24069,7 +23836,6 @@
           <t>保城镇</t>
         </is>
       </c>
-      <c r="G416" t="inlineStr"/>
       <c r="H416" t="n">
         <v>109.7</v>
       </c>
@@ -24124,7 +23890,6 @@
           <t>天涯区</t>
         </is>
       </c>
-      <c r="G417" t="inlineStr"/>
       <c r="H417" t="n">
         <v>109.51</v>
       </c>
@@ -24179,7 +23944,6 @@
           <t>佛罗镇</t>
         </is>
       </c>
-      <c r="G418" t="inlineStr"/>
       <c r="H418" t="n">
         <v>108.98</v>
       </c>
@@ -24234,7 +23998,6 @@
           <t>龙海区</t>
         </is>
       </c>
-      <c r="G419" t="inlineStr"/>
       <c r="H419" t="n">
         <v>117.8</v>
       </c>
@@ -24289,7 +24052,6 @@
           <t>仙游县</t>
         </is>
       </c>
-      <c r="G420" t="inlineStr"/>
       <c r="H420" t="n">
         <v>118.69</v>
       </c>
@@ -24344,7 +24106,6 @@
           <t>顺昌县</t>
         </is>
       </c>
-      <c r="G421" t="inlineStr"/>
       <c r="H421" t="n">
         <v>117.81</v>
       </c>
@@ -24399,7 +24160,6 @@
           <t>浦江县</t>
         </is>
       </c>
-      <c r="G422" t="inlineStr"/>
       <c r="H422" t="n">
         <v>119.89</v>
       </c>
@@ -24454,7 +24214,6 @@
           <t>玉环市</t>
         </is>
       </c>
-      <c r="G423" t="inlineStr"/>
       <c r="H423" t="n">
         <v>121.23</v>
       </c>
@@ -24509,7 +24268,6 @@
           <t>孟连傣族拉祜族佤族自治县</t>
         </is>
       </c>
-      <c r="G424" t="inlineStr"/>
       <c r="H424" t="n">
         <v>99.58</v>
       </c>
@@ -24564,7 +24322,6 @@
           <t>华宁县</t>
         </is>
       </c>
-      <c r="G425" t="inlineStr"/>
       <c r="H425" t="n">
         <v>102.93</v>
       </c>
@@ -24619,7 +24376,6 @@
           <t>高昌区</t>
         </is>
       </c>
-      <c r="G426" t="inlineStr"/>
       <c r="H426" t="n">
         <v>89.19</v>
       </c>
@@ -24674,7 +24430,6 @@
           <t>伊州区</t>
         </is>
       </c>
-      <c r="G427" t="inlineStr"/>
       <c r="H427" t="n">
         <v>6</v>
       </c>
@@ -24729,7 +24484,6 @@
           <t>伽师县</t>
         </is>
       </c>
-      <c r="G428" t="inlineStr"/>
       <c r="H428" t="n">
         <v>8</v>
       </c>
@@ -24784,7 +24538,6 @@
           <t>徐闻县</t>
         </is>
       </c>
-      <c r="G429" t="inlineStr"/>
       <c r="H429" t="n">
         <v>1</v>
       </c>
@@ -24839,7 +24592,6 @@
           <t>福山镇</t>
         </is>
       </c>
-      <c r="G430" t="inlineStr"/>
       <c r="H430" t="n">
         <v>1</v>
       </c>
@@ -24894,7 +24646,6 @@
           <t>元江哈尼族彝族傣族自治县</t>
         </is>
       </c>
-      <c r="G431" t="inlineStr"/>
       <c r="H431" t="n">
         <v>1</v>
       </c>
@@ -24949,7 +24700,6 @@
           <t>新宁县</t>
         </is>
       </c>
-      <c r="G432" t="inlineStr"/>
       <c r="H432" t="n">
         <v>1</v>
       </c>
@@ -25004,7 +24754,6 @@
           <t>吴中区</t>
         </is>
       </c>
-      <c r="G433" t="inlineStr"/>
       <c r="H433" t="n">
         <v>1</v>
       </c>
@@ -25059,7 +24808,6 @@
           <t>宾川县</t>
         </is>
       </c>
-      <c r="G434" t="inlineStr"/>
       <c r="H434" t="n">
         <v>1</v>
       </c>
@@ -25114,7 +24862,6 @@
           <t>荔城区</t>
         </is>
       </c>
-      <c r="G435" t="inlineStr"/>
       <c r="H435" t="n">
         <v>1</v>
       </c>
@@ -25169,7 +24916,6 @@
           <t>敖汉旗</t>
         </is>
       </c>
-      <c r="G436" t="inlineStr"/>
       <c r="H436" t="n">
         <v>1</v>
       </c>
@@ -25224,7 +24970,6 @@
           <t>扎兰屯市</t>
         </is>
       </c>
-      <c r="G437" t="inlineStr"/>
       <c r="H437" t="n">
         <v>1</v>
       </c>
@@ -25279,7 +25024,6 @@
           <t>攀枝花市</t>
         </is>
       </c>
-      <c r="G438" t="inlineStr"/>
       <c r="H438" t="n">
         <v>6.5</v>
       </c>
@@ -25297,7 +25041,6 @@
           <t>冬季巅峰型</t>
         </is>
       </c>
-      <c r="M438" t="inlineStr"/>
     </row>
     <row r="439" hidden="1">
       <c r="A439" t="inlineStr">
@@ -25945,6 +25688,276 @@
       <c r="M449" t="inlineStr">
         <is>
           <t>国家地理标志产品，2002年入选。新郑红枣、灰枣为优良品种，皮薄肉厚、味甜、营养丰富。9月中旬至10月中旬采收，可供应至次年5月。</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>F489</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>吊干杏</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>仁果类</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>新疆维吾尔自治区</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>阿克苏地区</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>阿克苏市</t>
+        </is>
+      </c>
+      <c r="H450" t="n">
+        <v>7</v>
+      </c>
+      <c r="I450" t="n">
+        <v>9</v>
+      </c>
+      <c r="J450" t="n">
+        <v>7</v>
+      </c>
+      <c r="K450" t="n">
+        <v>8</v>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>夏季集中型</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>新疆阿克苏特产，树上自然吊干，糖度高，肉质厚实，口感香甜，为中国著名的杏干原料。国家地理标志产品。</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>F490</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>福建百香果</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>热带水果</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>福建省</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>龙岩市</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>新罗区</t>
+        </is>
+      </c>
+      <c r="H451" t="n">
+        <v>7</v>
+      </c>
+      <c r="I451" t="n">
+        <v>12</v>
+      </c>
+      <c r="J451" t="n">
+        <v>8</v>
+      </c>
+      <c r="K451" t="n">
+        <v>10</v>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>全年供应型</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>福建龙岩百香果产区，气候温暖湿润，果香浓郁，酸甜适口，全国百香果重要集散地。</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>F491</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>广东百香果</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>热带水果</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>河源市</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>源城区</t>
+        </is>
+      </c>
+      <c r="H452" t="n">
+        <v>6</v>
+      </c>
+      <c r="I452" t="n">
+        <v>12</v>
+      </c>
+      <c r="J452" t="n">
+        <v>7</v>
+      </c>
+      <c r="K452" t="n">
+        <v>10</v>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>全年供应型</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>广东河源百香果，粤北山区气候适宜，果实饱满、酸甜平衡，华南重要百香果产区。</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>F492</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>海南百香果</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>热带水果</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>海南省</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>海口市</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>琼山区</t>
+        </is>
+      </c>
+      <c r="H453" t="n">
+        <v>5</v>
+      </c>
+      <c r="I453" t="n">
+        <v>11</v>
+      </c>
+      <c r="J453" t="n">
+        <v>6</v>
+      </c>
+      <c r="K453" t="n">
+        <v>9</v>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>全年供应型</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>海南热带百香果，光热资源丰富，上市早、周期长，冬季仍可供应鲜果。</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>F493</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>贵州百香果</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>热带水果</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>贵州省</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>黔南布依族苗族自治州</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>都匀市</t>
+        </is>
+      </c>
+      <c r="H454" t="n">
+        <v>7</v>
+      </c>
+      <c r="I454" t="n">
+        <v>11</v>
+      </c>
+      <c r="J454" t="n">
+        <v>8</v>
+      </c>
+      <c r="K454" t="n">
+        <v>10</v>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>秋季巅峰型</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>贵州黔南百香果，高原山地种植，昼夜温差大，果香浓郁，品质优良。</t>
         </is>
       </c>
     </row>
@@ -25967,7 +25980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I433"/>
+  <dimension ref="A1:I438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="13.7265625" customWidth="1" min="1" max="1"/>
@@ -30306,7 +30319,6 @@
           <t>丹棱县</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="n">
         <v>103.53</v>
       </c>
@@ -30345,7 +30357,6 @@
           <t>东坡区</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="n">
         <v>103.83</v>
       </c>
@@ -30384,7 +30395,6 @@
           <t>蒲江县</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="n">
         <v>103.51</v>
       </c>
@@ -30423,7 +30433,6 @@
           <t>金堂县</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="n">
         <v>104.41</v>
       </c>
@@ -30462,7 +30471,6 @@
           <t>名山区</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="n">
         <v>103.11</v>
       </c>
@@ -30501,7 +30509,6 @@
           <t>苍溪县</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="n">
         <v>105.93</v>
       </c>
@@ -30540,7 +30547,6 @@
           <t>金川县</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="n">
         <v>102.06</v>
       </c>
@@ -30579,7 +30585,6 @@
           <t>龙泉驿区</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="n">
         <v>104.27</v>
       </c>
@@ -30618,7 +30623,6 @@
           <t>双流区</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
         <v>103.92</v>
       </c>
@@ -30700,7 +30704,6 @@
           <t>会理市</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="n">
         <v>102.25</v>
       </c>
@@ -30739,7 +30742,6 @@
           <t>新平县</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
       <c r="F112" t="n">
         <v>101.99</v>
       </c>
@@ -30778,7 +30780,6 @@
           <t>华宁县</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="n">
         <v>102.93</v>
       </c>
@@ -30817,7 +30818,6 @@
           <t>弥勒市</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="n">
         <v>103.41</v>
       </c>
@@ -30856,7 +30856,6 @@
           <t>沾益区</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="n">
         <v>103.82</v>
       </c>
@@ -30895,7 +30894,6 @@
           <t>澄江市</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="n">
         <v>102.91</v>
       </c>
@@ -30934,7 +30932,6 @@
           <t>大理州</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
         <v>100.23</v>
       </c>
@@ -30973,7 +30970,6 @@
           <t>蒙自市</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
         <v>103.36</v>
       </c>
@@ -31012,7 +31008,6 @@
           <t>永仁县</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
         <v>101.67</v>
       </c>
@@ -31051,7 +31046,6 @@
           <t>华坪县</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
         <v>101.27</v>
       </c>
@@ -31090,7 +31084,6 @@
           <t>元阳县</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
         <v>102.83</v>
       </c>
@@ -31129,7 +31122,6 @@
           <t>永德县</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
         <v>99.26000000000001</v>
       </c>
@@ -31168,7 +31160,6 @@
           <t>丘北县</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
         <v>104.19</v>
       </c>
@@ -31207,7 +31198,6 @@
           <t>开远市</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
         <v>103.27</v>
       </c>
@@ -31246,7 +31236,6 @@
           <t>富民县</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="n">
         <v>102.5</v>
       </c>
@@ -31285,7 +31274,6 @@
           <t>昭阳区</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
         <v>103.71</v>
       </c>
@@ -31324,7 +31312,6 @@
           <t>高州市</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
         <v>110.85</v>
       </c>
@@ -31363,7 +31350,6 @@
           <t>增城区</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="n">
         <v>113.81</v>
       </c>
@@ -31402,7 +31388,6 @@
           <t>阳东区</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="n">
         <v>112.01</v>
       </c>
@@ -31441,7 +31426,6 @@
           <t>四会市</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
       <c r="F130" t="n">
         <v>112.73</v>
       </c>
@@ -31480,7 +31464,6 @@
           <t>清远市</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
       <c r="F131" t="n">
         <v>113.06</v>
       </c>
@@ -31519,7 +31502,6 @@
           <t>徐闻县</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
       <c r="F132" t="n">
         <v>110.18</v>
       </c>
@@ -31558,7 +31540,6 @@
           <t>荔浦市</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="n">
         <v>110.39</v>
       </c>
@@ -31597,7 +31578,6 @@
           <t>蒙山县</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="n">
         <v>110.52</v>
       </c>
@@ -31636,7 +31616,6 @@
           <t>象州县</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="n">
         <v>109.68</v>
       </c>
@@ -31675,7 +31654,6 @@
           <t>田东县</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
       <c r="F136" t="n">
         <v>107.12</v>
       </c>
@@ -31714,7 +31692,6 @@
           <t>隆安县</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
       <c r="F137" t="n">
         <v>107.7</v>
       </c>
@@ -31753,7 +31730,6 @@
           <t>扶绥县</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
       <c r="F138" t="n">
         <v>107.9</v>
       </c>
@@ -31792,7 +31768,6 @@
           <t>北流市</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" t="n">
         <v>110.35</v>
       </c>
@@ -31831,7 +31806,6 @@
           <t>钦州市</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
       <c r="F140" t="n">
         <v>108.65</v>
       </c>
@@ -31870,7 +31844,6 @@
           <t>崇左市</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
       <c r="F141" t="n">
         <v>107.35</v>
       </c>
@@ -31909,7 +31882,6 @@
           <t>八步区</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
         <v>111.55</v>
       </c>
@@ -31948,7 +31920,6 @@
           <t>浦北县</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
         <v>109.56</v>
       </c>
@@ -31987,7 +31958,6 @@
           <t>天峨县</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
         <v>107.17</v>
       </c>
@@ -32026,7 +31996,6 @@
           <t>紫云县</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
         <v>106.08</v>
       </c>
@@ -32065,7 +32034,6 @@
           <t>麻江县</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
         <v>107.59</v>
       </c>
@@ -32104,7 +32072,6 @@
           <t>龙里县</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
       <c r="F147" t="n">
         <v>106.98</v>
       </c>
@@ -32143,7 +32110,6 @@
           <t>罗甸县</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
       <c r="F148" t="n">
         <v>106.75</v>
       </c>
@@ -32182,7 +32148,6 @@
           <t>纳雍县</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
       <c r="F149" t="n">
         <v>105.38</v>
       </c>
@@ -32221,7 +32186,6 @@
           <t>六盘水市</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
       <c r="F150" t="n">
         <v>104.83</v>
       </c>
@@ -32260,7 +32224,6 @@
           <t>贞丰县</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
       <c r="F151" t="n">
         <v>105.65</v>
       </c>
@@ -32299,7 +32262,6 @@
           <t>三亚市</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
       <c r="F152" t="n">
         <v>109.51</v>
       </c>
@@ -32338,7 +32300,6 @@
           <t>乐东县</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
       <c r="F153" t="n">
         <v>109.17</v>
       </c>
@@ -32377,7 +32338,6 @@
           <t>陵水县</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
       <c r="F154" t="n">
         <v>110.04</v>
       </c>
@@ -32416,7 +32376,6 @@
           <t>东方市</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr"/>
       <c r="F155" t="n">
         <v>108.65</v>
       </c>
@@ -32455,7 +32414,6 @@
           <t>澄迈县</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
         <v>110</v>
       </c>
@@ -32494,7 +32452,6 @@
           <t>琼海市</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
         <v>110.47</v>
       </c>
@@ -32533,7 +32490,6 @@
           <t>万宁市</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>110.39</v>
       </c>
@@ -32572,7 +32528,6 @@
           <t>海口市</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
         <v>110.2</v>
       </c>
@@ -32611,7 +32566,6 @@
           <t>琼山区</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
         <v>110.35</v>
       </c>
@@ -32650,7 +32604,6 @@
           <t>文昌市</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
         <v>110.8</v>
       </c>
@@ -32689,7 +32642,6 @@
           <t>石棉县</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
         <v>102.36</v>
       </c>
@@ -33803,7 +33755,6 @@
           <t>长阳土家族自治县</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
       <c r="F188" t="n">
         <v>111.20105</v>
       </c>
@@ -33928,7 +33879,6 @@
           <t>公安县</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr"/>
       <c r="F191" t="n">
         <v>112.23242</v>
       </c>
@@ -33967,7 +33917,6 @@
           <t>赤壁市</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
       <c r="F192" t="n">
         <v>113.90039</v>
       </c>
@@ -34006,7 +33955,6 @@
           <t>建始县</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr"/>
       <c r="F193" t="n">
         <v>109.7182</v>
       </c>
@@ -34088,7 +34036,6 @@
           <t>宜都市</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr"/>
       <c r="F195" t="n">
         <v>111.45025</v>
       </c>
@@ -34127,7 +34074,6 @@
           <t>罗田县</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
       <c r="F196" t="n">
         <v>115.39056</v>
       </c>
@@ -34166,7 +34112,6 @@
           <t>房县</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr"/>
       <c r="F197" t="n">
         <v>110.73333</v>
       </c>
@@ -34205,7 +34150,6 @@
           <t>老河口市</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr"/>
       <c r="F198" t="n">
         <v>111.66944</v>
       </c>
@@ -34244,7 +34188,6 @@
           <t>老河口市</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr"/>
       <c r="F199" t="n">
         <v>111.66944</v>
       </c>
@@ -34283,7 +34226,6 @@
           <t>兴山县</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr"/>
       <c r="F200" t="n">
         <v>110.74951</v>
       </c>
@@ -34322,7 +34264,6 @@
           <t>凉城县</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr"/>
       <c r="F201" t="n">
         <v>112.5</v>
       </c>
@@ -34361,7 +34302,6 @@
           <t>宁城县</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr"/>
       <c r="F202" t="n">
         <v>119.33333</v>
       </c>
@@ -34395,8 +34335,6 @@
           <t>乌海市</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr"/>
       <c r="F203" t="n">
         <v>106.8</v>
       </c>
@@ -34435,7 +34373,6 @@
           <t>延吉市</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr"/>
       <c r="F204" t="n">
         <v>129.5</v>
       </c>
@@ -34469,8 +34406,6 @@
           <t>白山市</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr"/>
       <c r="F205" t="n">
         <v>126.41667</v>
       </c>
@@ -34509,7 +34444,6 @@
           <t>柳河县</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr"/>
       <c r="F206" t="n">
         <v>125.74475</v>
       </c>
@@ -34548,7 +34482,6 @@
           <t>通化县</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr"/>
       <c r="F207" t="n">
         <v>125.75936</v>
       </c>
@@ -34582,8 +34515,6 @@
           <t>大兴安岭地区</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
       <c r="F208" t="n">
         <v>124.11667</v>
       </c>
@@ -34622,7 +34553,6 @@
           <t>尚志市</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr"/>
       <c r="F209" t="n">
         <v>127.96194</v>
       </c>
@@ -34661,7 +34591,6 @@
           <t>勃利县</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr"/>
       <c r="F210" t="n">
         <v>130.56806</v>
       </c>
@@ -34700,7 +34629,6 @@
           <t>穆棱市</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr"/>
       <c r="F211" t="n">
         <v>130.51667</v>
       </c>
@@ -34734,8 +34662,6 @@
           <t>伊春市</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
       <c r="F212" t="n">
         <v>128.84056</v>
       </c>
@@ -34769,8 +34695,6 @@
           <t>海西蒙古族藏族自治州</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
       <c r="F213" t="n">
         <v>97.36667</v>
       </c>
@@ -34809,7 +34733,6 @@
           <t>乐都区</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr"/>
       <c r="F214" t="n">
         <v>102.4</v>
       </c>
@@ -34848,7 +34771,6 @@
           <t>乐都区</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr"/>
       <c r="F215" t="n">
         <v>102.4</v>
       </c>
@@ -34887,7 +34809,6 @@
           <t>芒康县</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr"/>
       <c r="F216" t="n">
         <v>98.59999999999999</v>
       </c>
@@ -34926,7 +34847,6 @@
           <t>朗县</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr"/>
       <c r="F217" t="n">
         <v>93.06667</v>
       </c>
@@ -35008,7 +34928,6 @@
           <t>西峡县</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr"/>
       <c r="F219" t="n">
         <v>111.47917</v>
       </c>
@@ -35047,12 +34966,11 @@
           <t>肥城市</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
       <c r="F220" t="n">
-        <v>116.46</v>
+        <v>116.65</v>
       </c>
       <c r="G220" t="n">
-        <v>36.14</v>
+        <v>36.15</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -35086,7 +35004,6 @@
           <t>乐陵市</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr"/>
       <c r="F221" t="n">
         <v>117.12</v>
       </c>
@@ -35125,7 +35042,6 @@
           <t>威远县</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr"/>
       <c r="F222" t="n">
         <v>104.66667</v>
       </c>
@@ -35164,7 +35080,6 @@
           <t>炎陵县</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr"/>
       <c r="F223" t="n">
         <v>113.76667</v>
       </c>
@@ -35203,7 +35118,6 @@
           <t>隰县</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr"/>
       <c r="F224" t="n">
         <v>110.93333</v>
       </c>
@@ -35237,8 +35151,6 @@
           <t>东方市</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr"/>
       <c r="F225" t="n">
         <v>108.63333</v>
       </c>
@@ -35277,7 +35189,6 @@
           <t>灵武市</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr"/>
       <c r="F226" t="n">
         <v>106.33333</v>
       </c>
@@ -35316,7 +35227,6 @@
           <t>集安市</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr"/>
       <c r="F227" t="n">
         <v>126.18829</v>
       </c>
@@ -35350,8 +35260,6 @@
           <t>龙岩市</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr"/>
       <c r="F228" t="n">
         <v>117.01667</v>
       </c>
@@ -35390,7 +35298,6 @@
           <t>青州市</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr"/>
       <c r="F229" t="n">
         <v>118.46667</v>
       </c>
@@ -35424,8 +35331,6 @@
           <t>威海市</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr"/>
       <c r="F230" t="n">
         <v>122.11667</v>
       </c>
@@ -35550,7 +35455,6 @@
           <t>巴宜区</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
         <v>94.361</v>
       </c>
@@ -35589,7 +35493,6 @@
           <t>察隅县</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
         <v>97.465</v>
       </c>
@@ -35628,7 +35531,6 @@
           <t>中宁县</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>105.685</v>
       </c>
@@ -35667,7 +35569,6 @@
           <t>海原县</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
         <v>105.643</v>
       </c>
@@ -35749,7 +35650,6 @@
           <t>怀远县</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
         <v>117.205</v>
       </c>
@@ -35788,7 +35688,6 @@
           <t>萧县</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
         <v>116.947</v>
       </c>
@@ -35827,7 +35726,6 @@
           <t>广丰区</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
         <v>118.191</v>
       </c>
@@ -35866,7 +35764,6 @@
           <t>梁平区</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>107.802</v>
       </c>
@@ -35905,7 +35802,6 @@
           <t>潼南区</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
         <v>105.84</v>
       </c>
@@ -35944,7 +35840,6 @@
           <t>磴口县</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
         <v>107.008</v>
       </c>
@@ -35983,7 +35878,6 @@
           <t>鄂伦春自治旗</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
         <v>123.726</v>
       </c>
@@ -36022,7 +35916,6 @@
           <t>民和回族土族自治县</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr"/>
       <c r="F245" t="n">
         <v>102.83</v>
       </c>
@@ -36061,7 +35954,6 @@
           <t>尚志市</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr"/>
       <c r="F246" t="n">
         <v>127.961</v>
       </c>
@@ -36100,7 +35992,6 @@
           <t>友好区</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr"/>
       <c r="F247" t="n">
         <v>128.841</v>
       </c>
@@ -36139,7 +36030,6 @@
           <t>天涯区</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr"/>
       <c r="F248" t="n">
         <v>109.506</v>
       </c>
@@ -36173,8 +36063,6 @@
           <t>琼中黎族苗族自治县</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr"/>
       <c r="F249" t="n">
         <v>109.838</v>
       </c>
@@ -36208,7 +36096,6 @@
           <t>文昌市</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
           <t>东郊镇</t>
@@ -36252,7 +36139,6 @@
           <t>西峰区</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr"/>
       <c r="F251" t="n">
         <v>107.651</v>
       </c>
@@ -37323,7 +37209,6 @@
           <t>白水县</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr"/>
       <c r="F276" t="n">
         <v>109.59</v>
       </c>
@@ -37362,7 +37247,6 @@
           <t>彬州市</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr"/>
       <c r="F277" t="n">
         <v>108.08</v>
       </c>
@@ -37401,7 +37285,6 @@
           <t>永春县</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr"/>
       <c r="F278" t="n">
         <v>118.29</v>
       </c>
@@ -37440,7 +37323,6 @@
           <t>诏安县</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr"/>
       <c r="F279" t="n">
         <v>117.18</v>
       </c>
@@ -37522,7 +37404,6 @@
           <t>黄岩区</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr"/>
       <c r="F281" t="n">
         <v>121.26</v>
       </c>
@@ -37561,7 +37442,6 @@
           <t>余姚市</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr"/>
       <c r="F282" t="n">
         <v>121.16</v>
       </c>
@@ -37600,7 +37480,6 @@
           <t>常山县</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr"/>
       <c r="F283" t="n">
         <v>118.51</v>
       </c>
@@ -37634,8 +37513,6 @@
           <t>大连市</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
-      <c r="E284" t="inlineStr"/>
       <c r="F284" t="n">
         <v>121.61</v>
       </c>
@@ -37674,7 +37551,6 @@
           <t>盖州市</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr"/>
       <c r="F285" t="n">
         <v>122.35</v>
       </c>
@@ -37713,7 +37589,6 @@
           <t>辽中区</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr"/>
       <c r="F286" t="n">
         <v>122.73</v>
       </c>
@@ -37747,8 +37622,6 @@
           <t>苏州市</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
-      <c r="E287" t="inlineStr"/>
       <c r="F287" t="n">
         <v>120.63</v>
       </c>
@@ -37787,7 +37660,6 @@
           <t>句容市</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr"/>
       <c r="F288" t="n">
         <v>119.16</v>
       </c>
@@ -37826,7 +37698,6 @@
           <t>吴中区</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr"/>
       <c r="F289" t="n">
         <v>120.63</v>
       </c>
@@ -37865,7 +37736,6 @@
           <t>江都区</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr"/>
       <c r="F290" t="n">
         <v>119.57</v>
       </c>
@@ -37904,7 +37774,6 @@
           <t>牡丹江市</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr"/>
       <c r="F291" t="n">
         <v>129.63</v>
       </c>
@@ -37938,8 +37807,6 @@
           <t>通化市</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr"/>
       <c r="F292" t="n">
         <v>125.94</v>
       </c>
@@ -37978,7 +37845,6 @@
           <t>临猗县</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr"/>
       <c r="F293" t="n">
         <v>110.77</v>
       </c>
@@ -38012,8 +37878,6 @@
           <t>晋城市</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr"/>
       <c r="F294" t="n">
         <v>0</v>
       </c>
@@ -38052,7 +37916,6 @@
           <t>长寿区</t>
         </is>
       </c>
-      <c r="E295" t="inlineStr"/>
       <c r="F295" t="n">
         <v>107.08</v>
       </c>
@@ -38091,7 +37954,6 @@
           <t>永川区</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr"/>
       <c r="F296" t="n">
         <v>105.89</v>
       </c>
@@ -38125,8 +37987,6 @@
           <t>吴忠市</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
-      <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
         <v>106.2</v>
       </c>
@@ -38160,8 +38020,6 @@
           <t>海东市</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
-      <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
         <v>102.1</v>
       </c>
@@ -38200,7 +38058,6 @@
           <t>磴口县</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
         <v>107.01</v>
       </c>
@@ -38234,8 +38091,6 @@
           <t>赤峰市</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
-      <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>118.89</v>
       </c>
@@ -38274,7 +38129,6 @@
           <t>密云区</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
         <v>116.84</v>
       </c>
@@ -38313,7 +38167,6 @@
           <t>滨海新区</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>117.65</v>
       </c>
@@ -38352,7 +38205,6 @@
           <t>嘉定区</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
         <v>121.27</v>
       </c>
@@ -38391,7 +38243,6 @@
           <t>民和回族土族自治县</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
         <v>0</v>
       </c>
@@ -38430,7 +38281,6 @@
           <t>友好区</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
         <v>0</v>
       </c>
@@ -38464,8 +38314,6 @@
           <t>琼中黎族苗族自治县</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
-      <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
         <v>0</v>
       </c>
@@ -38499,7 +38347,6 @@
           <t>文昌市</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
           <t>东郊镇</t>
@@ -38543,7 +38390,6 @@
           <t>民勤县</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr"/>
       <c r="F308" t="n">
         <v>103.1</v>
       </c>
@@ -38582,7 +38428,6 @@
           <t>西峰区</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr"/>
       <c r="F309" t="n">
         <v>0</v>
       </c>
@@ -39444,10 +39289,10 @@
         </is>
       </c>
       <c r="F329" t="n">
-        <v>0</v>
+        <v>106.77</v>
       </c>
       <c r="G329" t="n">
-        <v>0</v>
+        <v>22.09</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
@@ -39456,7 +39301,7 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>一级产区</t>
+          <t>重要产区</t>
         </is>
       </c>
     </row>
@@ -39487,10 +39332,10 @@
         </is>
       </c>
       <c r="F330" t="n">
-        <v>0</v>
+        <v>107.91</v>
       </c>
       <c r="G330" t="n">
-        <v>0</v>
+        <v>22.64</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
@@ -39499,7 +39344,7 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>一级产区</t>
+          <t>重要产区</t>
         </is>
       </c>
     </row>
@@ -39997,7 +39842,6 @@
           <t>雷波县</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr"/>
       <c r="F342" t="n">
         <v>103.57</v>
       </c>
@@ -40036,7 +39880,6 @@
           <t>盐源县</t>
         </is>
       </c>
-      <c r="E343" t="inlineStr"/>
       <c r="F343" t="n">
         <v>101.51</v>
       </c>
@@ -40075,7 +39918,6 @@
           <t>蒲江县</t>
         </is>
       </c>
-      <c r="E344" t="inlineStr"/>
       <c r="F344" t="n">
         <v>103.54</v>
       </c>
@@ -40114,7 +39956,6 @@
           <t>都江堰市</t>
         </is>
       </c>
-      <c r="E345" t="inlineStr"/>
       <c r="F345" t="n">
         <v>103.62</v>
       </c>
@@ -40153,7 +39994,6 @@
           <t>米易县</t>
         </is>
       </c>
-      <c r="E346" t="inlineStr"/>
       <c r="F346" t="n">
         <v>102.11</v>
       </c>
@@ -40192,7 +40032,6 @@
           <t>邻水县</t>
         </is>
       </c>
-      <c r="E347" t="inlineStr"/>
       <c r="F347" t="n">
         <v>106.93</v>
       </c>
@@ -40231,7 +40070,6 @@
           <t>石棉县</t>
         </is>
       </c>
-      <c r="E348" t="inlineStr"/>
       <c r="F348" t="n">
         <v>102.36</v>
       </c>
@@ -40270,7 +40108,6 @@
           <t>德昌县</t>
         </is>
       </c>
-      <c r="E349" t="inlineStr"/>
       <c r="F349" t="n">
         <v>102.18</v>
       </c>
@@ -40309,7 +40146,6 @@
           <t>江阳区</t>
         </is>
       </c>
-      <c r="E350" t="inlineStr"/>
       <c r="F350" t="n">
         <v>105.44</v>
       </c>
@@ -40348,7 +40184,6 @@
           <t>大邑县</t>
         </is>
       </c>
-      <c r="E351" t="inlineStr"/>
       <c r="F351" t="n">
         <v>103.52</v>
       </c>
@@ -40387,7 +40222,6 @@
           <t>从江县</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr"/>
       <c r="F352" t="n">
         <v>108.9</v>
       </c>
@@ -40426,7 +40260,6 @@
           <t>水城区</t>
         </is>
       </c>
-      <c r="E353" t="inlineStr"/>
       <c r="F353" t="n">
         <v>104.82</v>
       </c>
@@ -40465,7 +40298,6 @@
           <t>威宁彝族回族苗族自治县</t>
         </is>
       </c>
-      <c r="E354" t="inlineStr"/>
       <c r="F354" t="n">
         <v>104.28</v>
       </c>
@@ -40504,7 +40336,6 @@
           <t>开阳县</t>
         </is>
       </c>
-      <c r="E355" t="inlineStr"/>
       <c r="F355" t="n">
         <v>106.97</v>
       </c>
@@ -40543,7 +40374,6 @@
           <t>荔波县</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr"/>
       <c r="F356" t="n">
         <v>107.88</v>
       </c>
@@ -40582,7 +40412,6 @@
           <t>沿河土家族自治县</t>
         </is>
       </c>
-      <c r="E357" t="inlineStr"/>
       <c r="F357" t="n">
         <v>108.5</v>
       </c>
@@ -40621,7 +40450,6 @@
           <t>敦煌市</t>
         </is>
       </c>
-      <c r="E358" t="inlineStr"/>
       <c r="F358" t="n">
         <v>94.66</v>
       </c>
@@ -40660,7 +40488,6 @@
           <t>皋兰县</t>
         </is>
       </c>
-      <c r="E359" t="inlineStr"/>
       <c r="F359" t="n">
         <v>103.95</v>
       </c>
@@ -40699,7 +40526,6 @@
           <t>临泽县</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr"/>
       <c r="F360" t="n">
         <v>100.16</v>
       </c>
@@ -40738,7 +40564,6 @@
           <t>秦安县</t>
         </is>
       </c>
-      <c r="E361" t="inlineStr"/>
       <c r="F361" t="n">
         <v>105.67</v>
       </c>
@@ -40777,7 +40602,6 @@
           <t>金寨县</t>
         </is>
       </c>
-      <c r="E362" t="inlineStr"/>
       <c r="F362" t="n">
         <v>115.93</v>
       </c>
@@ -40816,7 +40640,6 @@
           <t>徽州区</t>
         </is>
       </c>
-      <c r="E363" t="inlineStr"/>
       <c r="F363" t="n">
         <v>118.34</v>
       </c>
@@ -40855,7 +40678,6 @@
           <t>黟县</t>
         </is>
       </c>
-      <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
         <v>117.94</v>
       </c>
@@ -40894,7 +40716,6 @@
           <t>万州区</t>
         </is>
       </c>
-      <c r="E365" t="inlineStr"/>
       <c r="F365" t="n">
         <v>108.41</v>
       </c>
@@ -40933,7 +40754,6 @@
           <t>万州区</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
         <v>108.41</v>
       </c>
@@ -40972,7 +40792,6 @@
           <t>开州区</t>
         </is>
       </c>
-      <c r="E367" t="inlineStr"/>
       <c r="F367" t="n">
         <v>108.42</v>
       </c>
@@ -41011,7 +40830,6 @@
           <t>黔江区</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr"/>
       <c r="F368" t="n">
         <v>108.77</v>
       </c>
@@ -41050,7 +40868,6 @@
           <t>璧山区</t>
         </is>
       </c>
-      <c r="E369" t="inlineStr"/>
       <c r="F369" t="n">
         <v>106.23</v>
       </c>
@@ -41089,7 +40906,6 @@
           <t>集安市</t>
         </is>
       </c>
-      <c r="E370" t="inlineStr"/>
       <c r="F370" t="n">
         <v>126.18</v>
       </c>
@@ -41128,7 +40944,6 @@
           <t>洮南市</t>
         </is>
       </c>
-      <c r="E371" t="inlineStr"/>
       <c r="F371" t="n">
         <v>122.78</v>
       </c>
@@ -41167,7 +40982,6 @@
           <t>勃利县</t>
         </is>
       </c>
-      <c r="E372" t="inlineStr"/>
       <c r="F372" t="n">
         <v>130.57</v>
       </c>
@@ -41206,7 +41020,6 @@
           <t>孙吴县</t>
         </is>
       </c>
-      <c r="E373" t="inlineStr"/>
       <c r="F373" t="n">
         <v>127.33</v>
       </c>
@@ -41245,7 +41058,6 @@
           <t>宁陵县</t>
         </is>
       </c>
-      <c r="E374" t="inlineStr"/>
       <c r="F374" t="n">
         <v>115.32</v>
       </c>
@@ -41284,7 +41096,6 @@
           <t>荥阳市</t>
         </is>
       </c>
-      <c r="E375" t="inlineStr"/>
       <c r="F375" t="n">
         <v>113.38</v>
       </c>
@@ -41323,7 +41134,6 @@
           <t>深州市</t>
         </is>
       </c>
-      <c r="E376" t="inlineStr"/>
       <c r="F376" t="n">
         <v>115.56</v>
       </c>
@@ -41362,7 +41172,6 @@
           <t>怀来县</t>
         </is>
       </c>
-      <c r="E377" t="inlineStr"/>
       <c r="F377" t="n">
         <v>115.52</v>
       </c>
@@ -41401,7 +41210,6 @@
           <t>黄骅市</t>
         </is>
       </c>
-      <c r="E378" t="inlineStr"/>
       <c r="F378" t="n">
         <v>117.35</v>
       </c>
@@ -41440,7 +41248,6 @@
           <t>赵县</t>
         </is>
       </c>
-      <c r="E379" t="inlineStr"/>
       <c r="F379" t="n">
         <v>114.78</v>
       </c>
@@ -41479,7 +41286,6 @@
           <t>襄汾县</t>
         </is>
       </c>
-      <c r="E380" t="inlineStr"/>
       <c r="F380" t="n">
         <v>111.44</v>
       </c>
@@ -41518,7 +41324,6 @@
           <t>平陆县</t>
         </is>
       </c>
-      <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
         <v>111.22</v>
       </c>
@@ -41557,7 +41362,6 @@
           <t>清徐县</t>
         </is>
       </c>
-      <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
         <v>112.35</v>
       </c>
@@ -41596,7 +41400,6 @@
           <t>惠山区</t>
         </is>
       </c>
-      <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
         <v>120.3</v>
       </c>
@@ -41635,7 +41438,6 @@
           <t>句容市</t>
         </is>
       </c>
-      <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
         <v>119.16</v>
       </c>
@@ -41674,7 +41476,6 @@
           <t>吴中区</t>
         </is>
       </c>
-      <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>120.4</v>
       </c>
@@ -41713,7 +41514,6 @@
           <t>丰县</t>
         </is>
       </c>
-      <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
         <v>116.6</v>
       </c>
@@ -41752,7 +41552,6 @@
           <t>凤凰县</t>
         </is>
       </c>
-      <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
         <v>109.6</v>
       </c>
@@ -41791,7 +41590,6 @@
           <t>道县</t>
         </is>
       </c>
-      <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
         <v>111.6</v>
       </c>
@@ -41830,7 +41628,6 @@
           <t>枣阳市</t>
         </is>
       </c>
-      <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>112.77</v>
       </c>
@@ -41869,7 +41666,6 @@
           <t>麻城市</t>
         </is>
       </c>
-      <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
         <v>115.03</v>
       </c>
@@ -41908,7 +41704,6 @@
           <t>蒙阴县</t>
         </is>
       </c>
-      <c r="E391" t="inlineStr"/>
       <c r="F391" t="n">
         <v>117.93</v>
       </c>
@@ -41947,7 +41742,6 @@
           <t>博山区</t>
         </is>
       </c>
-      <c r="E392" t="inlineStr"/>
       <c r="F392" t="n">
         <v>117.86</v>
       </c>
@@ -41986,7 +41780,6 @@
           <t>黄陵县</t>
         </is>
       </c>
-      <c r="E393" t="inlineStr"/>
       <c r="F393" t="n">
         <v>109.26</v>
       </c>
@@ -42025,7 +41818,6 @@
           <t>郁南县</t>
         </is>
       </c>
-      <c r="E394" t="inlineStr"/>
       <c r="F394" t="n">
         <v>111.54</v>
       </c>
@@ -42064,7 +41856,6 @@
           <t>德庆县</t>
         </is>
       </c>
-      <c r="E395" t="inlineStr"/>
       <c r="F395" t="n">
         <v>111.77</v>
       </c>
@@ -42103,7 +41894,6 @@
           <t>梅县区</t>
         </is>
       </c>
-      <c r="E396" t="inlineStr"/>
       <c r="F396" t="n">
         <v>116.1</v>
       </c>
@@ -42142,7 +41932,6 @@
           <t>连州市</t>
         </is>
       </c>
-      <c r="E397" t="inlineStr"/>
       <c r="F397" t="n">
         <v>112.38</v>
       </c>
@@ -42181,7 +41970,6 @@
           <t>容县</t>
         </is>
       </c>
-      <c r="E398" t="inlineStr"/>
       <c r="F398" t="n">
         <v>110.55</v>
       </c>
@@ -42220,7 +42008,6 @@
           <t>富川瑶族自治县</t>
         </is>
       </c>
-      <c r="E399" t="inlineStr"/>
       <c r="F399" t="n">
         <v>111.28</v>
       </c>
@@ -42259,7 +42046,6 @@
           <t>保城镇</t>
         </is>
       </c>
-      <c r="E400" t="inlineStr"/>
       <c r="F400" t="n">
         <v>109.7</v>
       </c>
@@ -42298,7 +42084,6 @@
           <t>天涯区</t>
         </is>
       </c>
-      <c r="E401" t="inlineStr"/>
       <c r="F401" t="n">
         <v>109.51</v>
       </c>
@@ -42337,7 +42122,6 @@
           <t>佛罗镇</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr"/>
       <c r="F402" t="n">
         <v>108.98</v>
       </c>
@@ -42376,7 +42160,6 @@
           <t>龙海区</t>
         </is>
       </c>
-      <c r="E403" t="inlineStr"/>
       <c r="F403" t="n">
         <v>117.8</v>
       </c>
@@ -42415,7 +42198,6 @@
           <t>仙游县</t>
         </is>
       </c>
-      <c r="E404" t="inlineStr"/>
       <c r="F404" t="n">
         <v>118.69</v>
       </c>
@@ -42454,7 +42236,6 @@
           <t>顺昌县</t>
         </is>
       </c>
-      <c r="E405" t="inlineStr"/>
       <c r="F405" t="n">
         <v>117.81</v>
       </c>
@@ -42493,7 +42274,6 @@
           <t>浦江县</t>
         </is>
       </c>
-      <c r="E406" t="inlineStr"/>
       <c r="F406" t="n">
         <v>119.89</v>
       </c>
@@ -42532,7 +42312,6 @@
           <t>玉环市</t>
         </is>
       </c>
-      <c r="E407" t="inlineStr"/>
       <c r="F407" t="n">
         <v>121.23</v>
       </c>
@@ -42571,7 +42350,6 @@
           <t>孟连傣族拉祜族佤族自治县</t>
         </is>
       </c>
-      <c r="E408" t="inlineStr"/>
       <c r="F408" t="n">
         <v>99.58</v>
       </c>
@@ -42610,7 +42388,6 @@
           <t>华宁县</t>
         </is>
       </c>
-      <c r="E409" t="inlineStr"/>
       <c r="F409" t="n">
         <v>102.93</v>
       </c>
@@ -42649,7 +42426,6 @@
           <t>高昌区</t>
         </is>
       </c>
-      <c r="E410" t="inlineStr"/>
       <c r="F410" t="n">
         <v>89.19</v>
       </c>
@@ -42688,7 +42464,6 @@
           <t>伊州区</t>
         </is>
       </c>
-      <c r="E411" t="inlineStr"/>
       <c r="F411" t="n">
         <v>93.51000000000001</v>
       </c>
@@ -42727,7 +42502,6 @@
           <t>伽师县</t>
         </is>
       </c>
-      <c r="E412" t="inlineStr"/>
       <c r="F412" t="n">
         <v>76.73</v>
       </c>
@@ -42766,7 +42540,6 @@
           <t>徐闻县</t>
         </is>
       </c>
-      <c r="E413" t="inlineStr"/>
       <c r="F413" t="n">
         <v>0</v>
       </c>
@@ -42805,7 +42578,6 @@
           <t>福山镇</t>
         </is>
       </c>
-      <c r="E414" t="inlineStr"/>
       <c r="F414" t="n">
         <v>0</v>
       </c>
@@ -42844,7 +42616,6 @@
           <t>元江哈尼族彝族傣族自治县</t>
         </is>
       </c>
-      <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
         <v>0</v>
       </c>
@@ -42883,7 +42654,6 @@
           <t>新宁县</t>
         </is>
       </c>
-      <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
         <v>0</v>
       </c>
@@ -42922,7 +42692,6 @@
           <t>吴中区</t>
         </is>
       </c>
-      <c r="E417" t="inlineStr"/>
       <c r="F417" t="n">
         <v>0</v>
       </c>
@@ -42961,7 +42730,6 @@
           <t>宾川县</t>
         </is>
       </c>
-      <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
         <v>0</v>
       </c>
@@ -43000,7 +42768,6 @@
           <t>荔城区</t>
         </is>
       </c>
-      <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
         <v>0</v>
       </c>
@@ -43039,7 +42806,6 @@
           <t>敖汉旗</t>
         </is>
       </c>
-      <c r="E420" t="inlineStr"/>
       <c r="F420" t="n">
         <v>0</v>
       </c>
@@ -43078,7 +42844,6 @@
           <t>扎兰屯市</t>
         </is>
       </c>
-      <c r="E421" t="inlineStr"/>
       <c r="F421" t="n">
         <v>0</v>
       </c>
@@ -43117,7 +42882,6 @@
           <t>攀枝花市</t>
         </is>
       </c>
-      <c r="E422" t="inlineStr"/>
       <c r="F422" t="n">
         <v>101.72</v>
       </c>
@@ -43605,6 +43369,196 @@
       <c r="I433" t="inlineStr">
         <is>
           <t>核心产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>000000000</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>新疆维吾尔自治区</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>阿克苏地区</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>阿克苏市</t>
+        </is>
+      </c>
+      <c r="F434" t="n">
+        <v>80.26000000000001</v>
+      </c>
+      <c r="G434" t="n">
+        <v>41.17</v>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>F489</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>一般产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>000000000</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>福建省</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>龙岩市</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>新罗区</t>
+        </is>
+      </c>
+      <c r="F435" t="n">
+        <v>117.02</v>
+      </c>
+      <c r="G435" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>F490</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>一般产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>000000000</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>河源市</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>源城区</t>
+        </is>
+      </c>
+      <c r="F436" t="n">
+        <v>114.7</v>
+      </c>
+      <c r="G436" t="n">
+        <v>23.73</v>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>F491</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>一般产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>000000000</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>海南省</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>海口市</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>琼山区</t>
+        </is>
+      </c>
+      <c r="F437" t="n">
+        <v>110.35</v>
+      </c>
+      <c r="G437" t="n">
+        <v>20</v>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>F492</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>一般产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>000000000</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>贵州省</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>黔南布依族苗族自治州</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>都匀市</t>
+        </is>
+      </c>
+      <c r="F438" t="n">
+        <v>107.52</v>
+      </c>
+      <c r="G438" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>F493</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>一般产区</t>
         </is>
       </c>
     </row>

--- a/fruit_data.xlsx
+++ b/fruit_data.xlsx
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="I197" t="n">
         <v>9</v>
@@ -20975,10 +20975,10 @@
         </is>
       </c>
       <c r="H363" t="n">
-        <v>106.93</v>
+        <v>11.5</v>
       </c>
       <c r="I363" t="n">
-        <v>30.33</v>
+        <v>1</v>
       </c>
       <c r="J363" t="n">
         <v>11</v>
@@ -22895,7 +22895,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>无锡水蜜桃</t>
+          <t>阳山水蜜桃</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -22919,10 +22919,10 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>120.3</v>
+        <v>6.9</v>
       </c>
       <c r="I399" t="n">
-        <v>31.58</v>
+        <v>9</v>
       </c>
       <c r="J399" t="n">
         <v>7</v>
@@ -23080,17 +23080,18 @@
           <t>丰县</t>
         </is>
       </c>
+      <c r="G402" t="inlineStr"/>
       <c r="H402" t="n">
-        <v>116.6</v>
+        <v>7.5</v>
       </c>
       <c r="I402" t="n">
-        <v>34.69</v>
+        <v>9</v>
       </c>
       <c r="J402" t="n">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="K402" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L402" t="inlineStr">
         <is>
@@ -23099,7 +23100,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>国家地理标志产品。黄河故道优质苹果产区，果大色艳、皮薄肉脆、酸甜适口。</t>
+          <t>国家地理标志产品。黄河故道优质苹果产区，果大色艳、皮薄肉脆、酸甜适口。大沙河青苹果（主要为青金帅品种）</t>
         </is>
       </c>
     </row>
@@ -23327,7 +23328,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>蒙阴蜜桃</t>
+          <t>黄金油桃</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -23351,16 +23352,16 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>117.93</v>
+        <v>5.9</v>
       </c>
       <c r="I407" t="n">
-        <v>35.71</v>
+        <v>10</v>
       </c>
       <c r="J407" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="K407" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="L407" t="inlineStr">
         <is>
@@ -23369,7 +23370,11 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>国家地理标志产品。中国蜜桃之都，果大形美、肉质细密、汁多甘甜。</t>
+          <t>国家地理标志产品。中国蜜桃之都，果大形美、肉质细密、汁多甘甜。‌
+大棚油桃‌：4月份就能上市，比露地提前两个多月。
+‌早熟露地油桃‌：5月下旬至6月中旬开始成熟。
+‌中熟油桃‌：6月下旬至8月上旬是主力上市期。
+‌晚熟油桃/油蟠桃‌：部分可延续到9月底甚至10月中下旬</t>
         </is>
       </c>
     </row>
@@ -41514,6 +41519,7 @@
           <t>丰县</t>
         </is>
       </c>
+      <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
         <v>116.6</v>
       </c>

--- a/fruit_data.xlsx
+++ b/fruit_data.xlsx
@@ -12892,7 +12892,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>柑橘类</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -12901,6 +12901,11 @@
         </is>
       </c>
       <c r="E219" t="inlineStr">
+        <is>
+          <t>文昌市</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
         <is>
           <t>文昌市</t>
         </is>
@@ -12929,7 +12934,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>海南文昌椰子之乡，全国最大椰子产地，地理标志产品</t>
+          <t>椰子的最佳食用季节通常是7月至8月, 海南文昌椰子之乡，全国最大椰子产地，地理标志产品</t>
         </is>
       </c>
     </row>
@@ -24411,7 +24416,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>伽师新梅</t>
+          <t>伽师西梅</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -24543,16 +24548,16 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I429" t="n">
-        <v>12</v>
+        <v>2.5</v>
       </c>
       <c r="J429" t="n">
-        <v>10</v>
+        <v>10.9</v>
       </c>
       <c r="K429" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="L429" t="inlineStr">
         <is>
@@ -31116,7 +31121,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>澄江市</t>
+          <t>玉溪市</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -31192,7 +31197,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>蒙自市</t>
+          <t>红河哈尼族彝族自治州</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -31420,7 +31425,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>开远市</t>
+          <t>红河哈尼族彝族自治州</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -31534,7 +31539,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>高州市</t>
+          <t>茂名市</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -31648,7 +31653,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>四会市</t>
+          <t>肇庆市</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -31762,7 +31767,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>荔浦市</t>
+          <t>桂林市</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -31990,7 +31995,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>北流市</t>
+          <t>玉林市</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -32522,7 +32527,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>省直辖</t>
+          <t>陵水黎族自治县</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -32560,7 +32565,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>省直辖</t>
+          <t>澄迈县</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -33643,7 +33648,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>浦东新区</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35515,7 +35520,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>嘉定区</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -35558,7 +35563,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>奉贤区</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -35753,7 +35758,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>蓟州区</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -35910,7 +35915,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>梁平区</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -35948,7 +35953,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>潼南区</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -38062,7 +38067,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>长寿区</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -38100,7 +38105,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>永川区</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -38275,7 +38280,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>密云区</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -38313,7 +38318,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>滨海新区</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -38351,7 +38356,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>嘉定区</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -38501,6 +38506,11 @@
           <t>文昌市</t>
         </is>
       </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>文昌市</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>东郊镇</t>
@@ -40862,7 +40872,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>万州区</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -40900,7 +40910,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>万州区</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -40938,7 +40948,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>开州区</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -40976,7 +40986,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>黔江区</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -41014,7 +41024,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>璧山区</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">

--- a/fruit_data.xlsx
+++ b/fruit_data.xlsx
@@ -26819,10 +26819,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>116.41</v>
+        <v>116.083482</v>
       </c>
       <c r="G14" t="n">
-        <v>24.28</v>
+        <v>24.267825</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -27851,10 +27851,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>122.99</v>
+        <v>122.949298</v>
       </c>
       <c r="G38" t="n">
-        <v>41.08</v>
+        <v>41.068909</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -29700,10 +29700,10 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>117.72</v>
+        <v>118.129902</v>
       </c>
       <c r="G81" t="n">
-        <v>37.9</v>
+        <v>37.698456</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -29786,10 +29786,10 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>114.3</v>
+        <v>114.437622</v>
       </c>
       <c r="G83" t="n">
-        <v>34.76</v>
+        <v>34.756476</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -35164,10 +35164,10 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>117.12</v>
+        <v>117.216657</v>
       </c>
       <c r="G219" t="n">
-        <v>37.44</v>
+        <v>37.729115</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -38980,10 +38980,10 @@
         </is>
       </c>
       <c r="F316" t="n">
-        <v>118.18319</v>
+        <v>118.110793</v>
       </c>
       <c r="G316" t="n">
-        <v>39.64381</v>
+        <v>39.56303</v>
       </c>
       <c r="H316" t="inlineStr">
         <is>
@@ -39023,10 +39023,10 @@
         </is>
       </c>
       <c r="F317" t="n">
-        <v>118.08187</v>
+        <v>118.150455</v>
       </c>
       <c r="G317" t="n">
-        <v>24.47979</v>
+        <v>24.729333</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
@@ -39453,10 +39453,10 @@
         </is>
       </c>
       <c r="F327" t="n">
-        <v>106.77</v>
+        <v>110.009423</v>
       </c>
       <c r="G327" t="n">
-        <v>22.09</v>
+        <v>25.796428</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
@@ -39496,10 +39496,10 @@
         </is>
       </c>
       <c r="F328" t="n">
-        <v>107.91</v>
+        <v>109.989208</v>
       </c>
       <c r="G328" t="n">
-        <v>22.64</v>
+        <v>24.986692</v>
       </c>
       <c r="H328" t="inlineStr">
         <is>
@@ -39926,10 +39926,10 @@
         </is>
       </c>
       <c r="F338" t="n">
-        <v>124.39472</v>
+        <v>124.784867</v>
       </c>
       <c r="G338" t="n">
-        <v>40.12917</v>
+        <v>40.730412</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
@@ -40425,10 +40425,10 @@
         </is>
       </c>
       <c r="F351" t="n">
-        <v>104.82</v>
+        <v>104.95685</v>
       </c>
       <c r="G351" t="n">
-        <v>26.58</v>
+        <v>26.540478</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
@@ -41565,10 +41565,10 @@
         </is>
       </c>
       <c r="F381" t="n">
-        <v>120.3</v>
+        <v>120.303543</v>
       </c>
       <c r="G381" t="n">
-        <v>31.58</v>
+        <v>31.681019</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
@@ -41983,10 +41983,10 @@
         </is>
       </c>
       <c r="F392" t="n">
-        <v>111.54</v>
+        <v>111.535921</v>
       </c>
       <c r="G392" t="n">
-        <v>23.23</v>
+        <v>23.237709</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
@@ -42249,10 +42249,10 @@
         </is>
       </c>
       <c r="F399" t="n">
-        <v>109.51</v>
+        <v>109.506357</v>
       </c>
       <c r="G399" t="n">
-        <v>18.25</v>
+        <v>18.24734</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
@@ -42781,10 +42781,10 @@
         </is>
       </c>
       <c r="F413" t="n">
-        <v>102.54222</v>
+        <v>101.999658</v>
       </c>
       <c r="G413" t="n">
-        <v>24.355</v>
+        <v>23.597618</v>
       </c>
       <c r="H413" t="inlineStr">
         <is>
@@ -42819,10 +42819,10 @@
         </is>
       </c>
       <c r="F414" t="n">
-        <v>111.46214</v>
+        <v>110.859115</v>
       </c>
       <c r="G414" t="n">
-        <v>27.23818</v>
+        <v>26.438912</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
@@ -42933,10 +42933,10 @@
         </is>
       </c>
       <c r="F417" t="n">
-        <v>119.01028</v>
+        <v>119.020047</v>
       </c>
       <c r="G417" t="n">
-        <v>25.43944</v>
+        <v>25.430047</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>

--- a/fruit_data.xlsx
+++ b/fruit_data.xlsx
@@ -6177,6 +6177,7 @@
           <t>丹棱县</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>11</v>
       </c>
@@ -6231,6 +6232,7 @@
           <t>丹棱县</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>10</v>
       </c>
@@ -6285,6 +6287,7 @@
           <t>苍溪县</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>8</v>
       </c>
@@ -6339,6 +6342,7 @@
           <t>金川县</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>8</v>
       </c>
@@ -6393,6 +6397,7 @@
           <t>龙泉驿区</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>4</v>
       </c>
@@ -6506,6 +6511,7 @@
           <t>会理市</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>7.9</v>
       </c>
@@ -6560,6 +6566,7 @@
           <t>双流区</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>12</v>
       </c>
@@ -6614,6 +6621,7 @@
           <t>新平县</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>1</v>
       </c>
@@ -6668,6 +6676,7 @@
           <t>新平县</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>10</v>
       </c>
@@ -6722,6 +6731,7 @@
           <t>弥勒市</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>12</v>
       </c>
@@ -6776,6 +6786,7 @@
           <t>宾川县</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>8</v>
       </c>
@@ -6830,6 +6841,7 @@
           <t>华坪县</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>6</v>
       </c>
@@ -6884,6 +6896,7 @@
           <t>丘北县</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>6</v>
       </c>
@@ -6938,6 +6951,7 @@
           <t>昭阳区</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>7</v>
       </c>
@@ -6992,6 +7006,7 @@
           <t>高州市</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>5</v>
       </c>
@@ -7046,6 +7061,7 @@
           <t>增城区</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>6</v>
       </c>
@@ -7100,6 +7116,7 @@
           <t>高州市</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>7</v>
       </c>
@@ -7154,6 +7171,7 @@
           <t>四会市</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>12</v>
       </c>
@@ -7267,6 +7285,7 @@
           <t>高州市</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>11</v>
       </c>
@@ -7321,6 +7340,7 @@
           <t>荔浦市</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>12</v>
       </c>
@@ -7375,6 +7395,7 @@
           <t>田东县</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>6</v>
       </c>
@@ -7429,6 +7450,7 @@
           <t>隆安县</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>5</v>
       </c>
@@ -7483,6 +7505,7 @@
           <t>北流市</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>7</v>
       </c>
@@ -7537,6 +7560,7 @@
           <t>八步区</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>5</v>
       </c>
@@ -7709,6 +7733,7 @@
           <t>麻江县</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>6</v>
       </c>
@@ -7763,6 +7788,7 @@
           <t>罗甸县</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>11</v>
       </c>
@@ -7817,6 +7843,7 @@
           <t>纳雍县</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>4</v>
       </c>
@@ -7871,6 +7898,7 @@
           <t>罗甸县</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>7</v>
       </c>
@@ -7925,6 +7953,7 @@
           <t>乐东黎族自治县</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>1</v>
       </c>
@@ -7979,6 +8008,7 @@
           <t>乐东县</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>9</v>
       </c>
@@ -8033,6 +8063,7 @@
           <t>万宁市</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>2</v>
       </c>
@@ -8087,6 +8118,7 @@
           <t>澄迈县</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>4</v>
       </c>
@@ -8141,6 +8173,7 @@
           <t>琼山区</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>12</v>
       </c>
@@ -8195,6 +8228,7 @@
           <t>乐东县</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
         <v>1</v>
       </c>
@@ -9724,6 +9758,7 @@
           <t>长阳土家族自治县</t>
         </is>
       </c>
+      <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
         <v>11</v>
       </c>
@@ -9896,6 +9931,7 @@
           <t>公安县</t>
         </is>
       </c>
+      <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
         <v>7</v>
       </c>
@@ -9950,6 +9986,7 @@
           <t>赤壁市</t>
         </is>
       </c>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
         <v>8</v>
       </c>
@@ -10004,6 +10041,7 @@
           <t>建始县</t>
         </is>
       </c>
+      <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
         <v>9</v>
       </c>
@@ -10117,6 +10155,7 @@
           <t>宜都市</t>
         </is>
       </c>
+      <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
         <v>10</v>
       </c>
@@ -10171,6 +10210,7 @@
           <t>罗田县</t>
         </is>
       </c>
+      <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
         <v>8</v>
       </c>
@@ -10225,6 +10265,7 @@
           <t>房县</t>
         </is>
       </c>
+      <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
         <v>4</v>
       </c>
@@ -10279,6 +10320,7 @@
           <t>老河口市</t>
         </is>
       </c>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
         <v>6</v>
       </c>
@@ -10333,6 +10375,7 @@
           <t>老河口市</t>
         </is>
       </c>
+      <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
         <v>7</v>
       </c>
@@ -10387,6 +10430,7 @@
           <t>兴山县</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
         <v>11</v>
       </c>
@@ -10441,6 +10485,7 @@
           <t>凉城县</t>
         </is>
       </c>
+      <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
         <v>8</v>
       </c>
@@ -10495,6 +10540,7 @@
           <t>宁城县</t>
         </is>
       </c>
+      <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
         <v>9</v>
       </c>
@@ -10544,6 +10590,8 @@
           <t>乌海市</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
         <v>7</v>
       </c>
@@ -10652,6 +10700,8 @@
           <t>白山市</t>
         </is>
       </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
         <v>7</v>
       </c>
@@ -10706,6 +10756,7 @@
           <t>柳河县</t>
         </is>
       </c>
+      <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
         <v>8</v>
       </c>
@@ -10760,6 +10811,7 @@
           <t>通化县</t>
         </is>
       </c>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
         <v>7</v>
       </c>
@@ -10809,6 +10861,8 @@
           <t>大兴安岭地区</t>
         </is>
       </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
         <v>7</v>
       </c>
@@ -10863,6 +10917,7 @@
           <t>尚志市</t>
         </is>
       </c>
+      <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
         <v>7</v>
       </c>
@@ -10917,6 +10972,7 @@
           <t>勃利县</t>
         </is>
       </c>
+      <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
         <v>6</v>
       </c>
@@ -10971,6 +11027,7 @@
           <t>穆棱市</t>
         </is>
       </c>
+      <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
         <v>9</v>
       </c>
@@ -11025,6 +11082,7 @@
           <t>友好区</t>
         </is>
       </c>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
         <v>7</v>
       </c>
@@ -11074,6 +11132,8 @@
           <t>海西蒙古族藏族自治州</t>
         </is>
       </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
         <v>7</v>
       </c>
@@ -11128,6 +11188,7 @@
           <t>乐都区</t>
         </is>
       </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
         <v>8</v>
       </c>
@@ -11182,6 +11243,7 @@
           <t>乐都区</t>
         </is>
       </c>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
         <v>6</v>
       </c>
@@ -11236,6 +11298,7 @@
           <t>巴宜区</t>
         </is>
       </c>
+      <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
         <v>9</v>
       </c>
@@ -11290,6 +11353,7 @@
           <t>芒康县</t>
         </is>
       </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
         <v>8</v>
       </c>
@@ -11344,6 +11408,7 @@
           <t>朗县</t>
         </is>
       </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
         <v>9</v>
       </c>
@@ -11457,6 +11522,7 @@
           <t>西峡县</t>
         </is>
       </c>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
         <v>8</v>
       </c>
@@ -11511,6 +11577,7 @@
           <t>肥城市</t>
         </is>
       </c>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
         <v>8</v>
       </c>
@@ -11565,6 +11632,7 @@
           <t>乐陵市</t>
         </is>
       </c>
+      <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
         <v>9</v>
       </c>
@@ -11619,6 +11687,7 @@
           <t>威远县</t>
         </is>
       </c>
+      <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
         <v>7</v>
       </c>
@@ -11673,6 +11742,7 @@
           <t>炎陵县</t>
         </is>
       </c>
+      <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
         <v>6.9</v>
       </c>
@@ -11727,6 +11797,7 @@
           <t>隰县</t>
         </is>
       </c>
+      <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
         <v>9</v>
       </c>
@@ -11776,6 +11847,8 @@
           <t>东方市</t>
         </is>
       </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
         <v>5</v>
       </c>
@@ -11830,6 +11903,7 @@
           <t>灵武市</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
         <v>9</v>
       </c>
@@ -11884,6 +11958,7 @@
           <t>集安市</t>
         </is>
       </c>
+      <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
         <v>8</v>
       </c>
@@ -11933,6 +12008,8 @@
           <t>龙岩市</t>
         </is>
       </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
         <v>7</v>
       </c>
@@ -11987,6 +12064,7 @@
           <t>青州市</t>
         </is>
       </c>
+      <c r="G202" t="inlineStr"/>
       <c r="H202" t="n">
         <v>9</v>
       </c>
@@ -12036,6 +12114,8 @@
           <t>威海市</t>
         </is>
       </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
       <c r="H203" t="n">
         <v>7</v>
       </c>
@@ -12208,6 +12288,7 @@
           <t>察隅县</t>
         </is>
       </c>
+      <c r="G206" t="inlineStr"/>
       <c r="H206" t="n">
         <v>9</v>
       </c>
@@ -12262,6 +12343,7 @@
           <t>中宁县</t>
         </is>
       </c>
+      <c r="G207" t="inlineStr"/>
       <c r="H207" t="n">
         <v>6</v>
       </c>
@@ -12316,6 +12398,7 @@
           <t>海原县</t>
         </is>
       </c>
+      <c r="G208" t="inlineStr"/>
       <c r="H208" t="n">
         <v>9</v>
       </c>
@@ -12429,6 +12512,7 @@
           <t>怀远县</t>
         </is>
       </c>
+      <c r="G210" t="inlineStr"/>
       <c r="H210" t="n">
         <v>9</v>
       </c>
@@ -12483,6 +12567,7 @@
           <t>萧县</t>
         </is>
       </c>
+      <c r="G211" t="inlineStr"/>
       <c r="H211" t="n">
         <v>7</v>
       </c>
@@ -12537,6 +12622,7 @@
           <t>广丰区</t>
         </is>
       </c>
+      <c r="G212" t="inlineStr"/>
       <c r="H212" t="n">
         <v>11</v>
       </c>
@@ -12591,6 +12677,7 @@
           <t>梁平区</t>
         </is>
       </c>
+      <c r="G213" t="inlineStr"/>
       <c r="H213" t="n">
         <v>10</v>
       </c>
@@ -12645,6 +12732,7 @@
           <t>潼南区</t>
         </is>
       </c>
+      <c r="G214" t="inlineStr"/>
       <c r="H214" t="n">
         <v>9</v>
       </c>
@@ -12699,6 +12787,7 @@
           <t>磴口县</t>
         </is>
       </c>
+      <c r="G215" t="inlineStr"/>
       <c r="H215" t="n">
         <v>7</v>
       </c>
@@ -12753,6 +12842,7 @@
           <t>鄂伦春自治旗</t>
         </is>
       </c>
+      <c r="G216" t="inlineStr"/>
       <c r="H216" t="n">
         <v>7</v>
       </c>
@@ -12807,6 +12897,7 @@
           <t>民和回族土族自治县</t>
         </is>
       </c>
+      <c r="G217" t="inlineStr"/>
       <c r="H217" t="n">
         <v>7</v>
       </c>
@@ -12856,6 +12947,8 @@
           <t>琼中黎族苗族自治县</t>
         </is>
       </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
       <c r="H218" t="n">
         <v>10</v>
       </c>
@@ -12969,6 +13062,7 @@
           <t>民勤县</t>
         </is>
       </c>
+      <c r="G220" t="inlineStr"/>
       <c r="H220" t="n">
         <v>7</v>
       </c>
@@ -13023,6 +13117,7 @@
           <t>西峰区</t>
         </is>
       </c>
+      <c r="G221" t="inlineStr"/>
       <c r="H221" t="n">
         <v>9</v>
       </c>
@@ -14555,6 +14650,7 @@
           <t>白水县</t>
         </is>
       </c>
+      <c r="G247" t="inlineStr"/>
       <c r="H247" t="n">
         <v>9</v>
       </c>
@@ -14609,6 +14705,7 @@
           <t>清涧县</t>
         </is>
       </c>
+      <c r="G248" t="inlineStr"/>
       <c r="H248" t="n">
         <v>9</v>
       </c>
@@ -14663,6 +14760,7 @@
           <t>城固县</t>
         </is>
       </c>
+      <c r="G249" t="inlineStr"/>
       <c r="H249" t="n">
         <v>10</v>
       </c>
@@ -14717,6 +14815,7 @@
           <t>彬州市</t>
         </is>
       </c>
+      <c r="G250" t="inlineStr"/>
       <c r="H250" t="n">
         <v>9</v>
       </c>
@@ -14766,6 +14865,8 @@
           <t>延安市</t>
         </is>
       </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr"/>
       <c r="H251" t="n">
         <v>10</v>
       </c>
@@ -14815,6 +14916,8 @@
           <t>西安市</t>
         </is>
       </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr"/>
       <c r="H252" t="n">
         <v>12</v>
       </c>
@@ -14869,6 +14972,7 @@
           <t>永春县</t>
         </is>
       </c>
+      <c r="G253" t="inlineStr"/>
       <c r="H253" t="n">
         <v>11</v>
       </c>
@@ -14918,6 +15022,8 @@
           <t>莆田市</t>
         </is>
       </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
       <c r="H254" t="n">
         <v>3</v>
       </c>
@@ -14972,6 +15078,7 @@
           <t>闽侯县</t>
         </is>
       </c>
+      <c r="G255" t="inlineStr"/>
       <c r="H255" t="n">
         <v>7</v>
       </c>
@@ -15026,6 +15133,7 @@
           <t>诏安县</t>
         </is>
       </c>
+      <c r="G256" t="inlineStr"/>
       <c r="H256" t="n">
         <v>4</v>
       </c>
@@ -15080,6 +15188,7 @@
           <t>建瓯市</t>
         </is>
       </c>
+      <c r="G257" t="inlineStr"/>
       <c r="H257" t="n">
         <v>9</v>
       </c>
@@ -15134,6 +15243,7 @@
           <t>福鼎市</t>
         </is>
       </c>
+      <c r="G258" t="inlineStr"/>
       <c r="H258" t="n">
         <v>10</v>
       </c>
@@ -15188,6 +15298,7 @@
           <t>长泰区</t>
         </is>
       </c>
+      <c r="G259" t="inlineStr"/>
       <c r="H259" t="n">
         <v>11</v>
       </c>
@@ -15242,6 +15353,7 @@
           <t>闽侯县</t>
         </is>
       </c>
+      <c r="G260" t="inlineStr"/>
       <c r="H260" t="n">
         <v>6</v>
       </c>
@@ -15355,6 +15467,7 @@
           <t>黄岩区</t>
         </is>
       </c>
+      <c r="G262" t="inlineStr"/>
       <c r="H262" t="n">
         <v>10</v>
       </c>
@@ -15409,6 +15522,7 @@
           <t>象山县</t>
         </is>
       </c>
+      <c r="G263" t="inlineStr"/>
       <c r="H263" t="n">
         <v>11</v>
       </c>
@@ -15463,6 +15577,7 @@
           <t>余姚市</t>
         </is>
       </c>
+      <c r="G264" t="inlineStr"/>
       <c r="H264" t="n">
         <v>6</v>
       </c>
@@ -15512,6 +15627,8 @@
           <t>衢州市</t>
         </is>
       </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr"/>
       <c r="H265" t="n">
         <v>11</v>
       </c>
@@ -15566,6 +15683,7 @@
           <t>常山县</t>
         </is>
       </c>
+      <c r="G266" t="inlineStr"/>
       <c r="H266" t="n">
         <v>11</v>
       </c>
@@ -15620,6 +15738,7 @@
           <t>桐乡市</t>
         </is>
       </c>
+      <c r="G267" t="inlineStr"/>
       <c r="H267" t="n">
         <v>6</v>
       </c>
@@ -15669,6 +15788,8 @@
           <t>大连市</t>
         </is>
       </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr"/>
       <c r="H268" t="n">
         <v>5</v>
       </c>
@@ -15718,6 +15839,8 @@
           <t>丹东市</t>
         </is>
       </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr"/>
       <c r="H269" t="n">
         <v>12</v>
       </c>
@@ -15772,6 +15895,7 @@
           <t>盖州市</t>
         </is>
       </c>
+      <c r="G270" t="inlineStr"/>
       <c r="H270" t="n">
         <v>8</v>
       </c>
@@ -15826,6 +15950,7 @@
           <t>绥中县</t>
         </is>
       </c>
+      <c r="G271" t="inlineStr"/>
       <c r="H271" t="n">
         <v>9</v>
       </c>
@@ -15880,6 +16005,7 @@
           <t>辽中区</t>
         </is>
       </c>
+      <c r="G272" t="inlineStr"/>
       <c r="H272" t="n">
         <v>10</v>
       </c>
@@ -15934,6 +16060,7 @@
           <t>庄河市</t>
         </is>
       </c>
+      <c r="G273" t="inlineStr"/>
       <c r="H273" t="n">
         <v>6</v>
       </c>
@@ -15983,6 +16110,8 @@
           <t>朝阳市</t>
         </is>
       </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr"/>
       <c r="H274" t="n">
         <v>9</v>
       </c>
@@ -16032,6 +16161,8 @@
           <t>苏州市</t>
         </is>
       </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
       <c r="H275" t="n">
         <v>6</v>
       </c>
@@ -16086,6 +16217,7 @@
           <t>句容市</t>
         </is>
       </c>
+      <c r="G276" t="inlineStr"/>
       <c r="H276" t="n">
         <v>7</v>
       </c>
@@ -16140,6 +16272,7 @@
           <t>吴中区</t>
         </is>
       </c>
+      <c r="G277" t="inlineStr"/>
       <c r="H277" t="n">
         <v>5</v>
       </c>
@@ -16194,6 +16327,7 @@
           <t>丰县</t>
         </is>
       </c>
+      <c r="G278" t="inlineStr"/>
       <c r="H278" t="n">
         <v>9</v>
       </c>
@@ -16248,6 +16382,7 @@
           <t>溧水区</t>
         </is>
       </c>
+      <c r="G279" t="inlineStr"/>
       <c r="H279" t="n">
         <v>12</v>
       </c>
@@ -16302,6 +16437,7 @@
           <t>江都区</t>
         </is>
       </c>
+      <c r="G280" t="inlineStr"/>
       <c r="H280" t="n">
         <v>9</v>
       </c>
@@ -16356,6 +16492,7 @@
           <t>句容市</t>
         </is>
       </c>
+      <c r="G281" t="inlineStr"/>
       <c r="H281" t="n">
         <v>7</v>
       </c>
@@ -16410,6 +16547,7 @@
           <t>秦州区</t>
         </is>
       </c>
+      <c r="G282" t="inlineStr"/>
       <c r="H282" t="n">
         <v>9</v>
       </c>
@@ -16459,6 +16597,8 @@
           <t>兰州市</t>
         </is>
       </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr"/>
       <c r="H283" t="n">
         <v>9</v>
       </c>
@@ -16513,6 +16653,7 @@
           <t>牡丹江市</t>
         </is>
       </c>
+      <c r="G284" t="inlineStr"/>
       <c r="H284" t="n">
         <v>9</v>
       </c>
@@ -16562,6 +16703,8 @@
           <t>通化市</t>
         </is>
       </c>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr"/>
       <c r="H285" t="n">
         <v>9</v>
       </c>
@@ -16611,6 +16754,8 @@
           <t>四平市</t>
         </is>
       </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr"/>
       <c r="H286" t="n">
         <v>9</v>
       </c>
@@ -16665,6 +16810,7 @@
           <t>临猗县</t>
         </is>
       </c>
+      <c r="G287" t="inlineStr"/>
       <c r="H287" t="n">
         <v>10</v>
       </c>
@@ -16714,6 +16860,8 @@
           <t>吕梁市</t>
         </is>
       </c>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr"/>
       <c r="H288" t="n">
         <v>9</v>
       </c>
@@ -16763,6 +16911,8 @@
           <t>晋中市</t>
         </is>
       </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr"/>
       <c r="H289" t="n">
         <v>8</v>
       </c>
@@ -16812,6 +16962,8 @@
           <t>晋城市</t>
         </is>
       </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr"/>
       <c r="H290" t="n">
         <v>9</v>
       </c>
@@ -16866,6 +17018,7 @@
           <t>万州区</t>
         </is>
       </c>
+      <c r="G291" t="inlineStr"/>
       <c r="H291" t="n">
         <v>10</v>
       </c>
@@ -16920,6 +17073,7 @@
           <t>长寿区</t>
         </is>
       </c>
+      <c r="G292" t="inlineStr"/>
       <c r="H292" t="n">
         <v>11</v>
       </c>
@@ -16974,6 +17128,7 @@
           <t>江津区</t>
         </is>
       </c>
+      <c r="G293" t="inlineStr"/>
       <c r="H293" t="n">
         <v>10</v>
       </c>
@@ -17028,6 +17183,7 @@
           <t>永川区</t>
         </is>
       </c>
+      <c r="G294" t="inlineStr"/>
       <c r="H294" t="n">
         <v>8</v>
       </c>
@@ -17082,6 +17238,7 @@
           <t>忠县</t>
         </is>
       </c>
+      <c r="G295" t="inlineStr"/>
       <c r="H295" t="n">
         <v>10</v>
       </c>
@@ -17131,6 +17288,8 @@
           <t>吴忠市</t>
         </is>
       </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr"/>
       <c r="H296" t="n">
         <v>8</v>
       </c>
@@ -17180,6 +17339,8 @@
           <t>海东市</t>
         </is>
       </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr"/>
       <c r="H297" t="n">
         <v>6</v>
       </c>
@@ -17229,6 +17390,8 @@
           <t>海南藏族自治州</t>
         </is>
       </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr"/>
       <c r="H298" t="n">
         <v>9</v>
       </c>
@@ -17283,6 +17446,7 @@
           <t>磴口县</t>
         </is>
       </c>
+      <c r="G299" t="inlineStr"/>
       <c r="H299" t="n">
         <v>7</v>
       </c>
@@ -17332,6 +17496,8 @@
           <t>赤峰市</t>
         </is>
       </c>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr"/>
       <c r="H300" t="n">
         <v>9</v>
       </c>
@@ -17386,6 +17552,7 @@
           <t>昌平区</t>
         </is>
       </c>
+      <c r="G301" t="inlineStr"/>
       <c r="H301" t="n">
         <v>12</v>
       </c>
@@ -17440,6 +17607,7 @@
           <t>密云区</t>
         </is>
       </c>
+      <c r="G302" t="inlineStr"/>
       <c r="H302" t="n">
         <v>5</v>
       </c>
@@ -17494,6 +17662,7 @@
           <t>蓟州区</t>
         </is>
       </c>
+      <c r="G303" t="inlineStr"/>
       <c r="H303" t="n">
         <v>10</v>
       </c>
@@ -17548,6 +17717,7 @@
           <t>滨海新区</t>
         </is>
       </c>
+      <c r="G304" t="inlineStr"/>
       <c r="H304" t="n">
         <v>8</v>
       </c>
@@ -17602,6 +17772,7 @@
           <t>武清区</t>
         </is>
       </c>
+      <c r="G305" t="inlineStr"/>
       <c r="H305" t="n">
         <v>6</v>
       </c>
@@ -17656,6 +17827,7 @@
           <t>崇明区</t>
         </is>
       </c>
+      <c r="G306" t="inlineStr"/>
       <c r="H306" t="n">
         <v>10</v>
       </c>
@@ -17710,6 +17882,7 @@
           <t>嘉定区</t>
         </is>
       </c>
+      <c r="G307" t="inlineStr"/>
       <c r="H307" t="n">
         <v>7</v>
       </c>
@@ -20655,6 +20828,7 @@
           <t>雷波县</t>
         </is>
       </c>
+      <c r="G357" t="inlineStr"/>
       <c r="H357" t="n">
         <v>10.9</v>
       </c>
@@ -20709,6 +20883,7 @@
           <t>盐源县</t>
         </is>
       </c>
+      <c r="G358" t="inlineStr"/>
       <c r="H358" t="n">
         <v>7.9</v>
       </c>
@@ -20763,6 +20938,7 @@
           <t>蒲江县</t>
         </is>
       </c>
+      <c r="G359" t="inlineStr"/>
       <c r="H359" t="n">
         <v>8.9</v>
       </c>
@@ -20817,6 +20993,7 @@
           <t>都江堰市</t>
         </is>
       </c>
+      <c r="G360" t="inlineStr"/>
       <c r="H360" t="n">
         <v>8</v>
       </c>
@@ -20871,6 +21048,7 @@
           <t>米易县</t>
         </is>
       </c>
+      <c r="G361" t="inlineStr"/>
       <c r="H361" t="n">
         <v>12</v>
       </c>
@@ -20925,6 +21103,7 @@
           <t>邻水县</t>
         </is>
       </c>
+      <c r="G362" t="inlineStr"/>
       <c r="H362" t="n">
         <v>11.5</v>
       </c>
@@ -20979,6 +21158,7 @@
           <t>石棉县</t>
         </is>
       </c>
+      <c r="G363" t="inlineStr"/>
       <c r="H363" t="n">
         <v>1</v>
       </c>
@@ -21033,6 +21213,7 @@
           <t>德昌县</t>
         </is>
       </c>
+      <c r="G364" t="inlineStr"/>
       <c r="H364" t="n">
         <v>3.5</v>
       </c>
@@ -21087,6 +21268,7 @@
           <t>江阳区</t>
         </is>
       </c>
+      <c r="G365" t="inlineStr"/>
       <c r="H365" t="n">
         <v>8</v>
       </c>
@@ -21141,6 +21323,7 @@
           <t>大邑县</t>
         </is>
       </c>
+      <c r="G366" t="inlineStr"/>
       <c r="H366" t="n">
         <v>4.5</v>
       </c>
@@ -21195,6 +21378,7 @@
           <t>从江县</t>
         </is>
       </c>
+      <c r="G367" t="inlineStr"/>
       <c r="H367" t="n">
         <v>10</v>
       </c>
@@ -21249,6 +21433,7 @@
           <t>水城区</t>
         </is>
       </c>
+      <c r="G368" t="inlineStr"/>
       <c r="H368" t="n">
         <v>8</v>
       </c>
@@ -21303,6 +21488,7 @@
           <t>威宁彝族回族苗族自治县</t>
         </is>
       </c>
+      <c r="G369" t="inlineStr"/>
       <c r="H369" t="n">
         <v>8</v>
       </c>
@@ -21357,6 +21543,7 @@
           <t>开阳县</t>
         </is>
       </c>
+      <c r="G370" t="inlineStr"/>
       <c r="H370" t="n">
         <v>4</v>
       </c>
@@ -21411,6 +21598,7 @@
           <t>荔波县</t>
         </is>
       </c>
+      <c r="G371" t="inlineStr"/>
       <c r="H371" t="n">
         <v>9</v>
       </c>
@@ -21465,6 +21653,7 @@
           <t>沿河土家族自治县</t>
         </is>
       </c>
+      <c r="G372" t="inlineStr"/>
       <c r="H372" t="n">
         <v>6</v>
       </c>
@@ -21519,6 +21708,7 @@
           <t>敦煌市</t>
         </is>
       </c>
+      <c r="G373" t="inlineStr"/>
       <c r="H373" t="n">
         <v>8</v>
       </c>
@@ -21573,6 +21763,7 @@
           <t>皋兰县</t>
         </is>
       </c>
+      <c r="G374" t="inlineStr"/>
       <c r="H374" t="n">
         <v>1</v>
       </c>
@@ -21627,6 +21818,7 @@
           <t>临泽县</t>
         </is>
       </c>
+      <c r="G375" t="inlineStr"/>
       <c r="H375" t="n">
         <v>8.9</v>
       </c>
@@ -21681,6 +21873,7 @@
           <t>秦安县</t>
         </is>
       </c>
+      <c r="G376" t="inlineStr"/>
       <c r="H376" t="n">
         <v>6</v>
       </c>
@@ -21735,6 +21928,7 @@
           <t>金寨县</t>
         </is>
       </c>
+      <c r="G377" t="inlineStr"/>
       <c r="H377" t="n">
         <v>8</v>
       </c>
@@ -21789,6 +21983,7 @@
           <t>徽州区</t>
         </is>
       </c>
+      <c r="G378" t="inlineStr"/>
       <c r="H378" t="n">
         <v>7</v>
       </c>
@@ -21843,6 +22038,7 @@
           <t>黟县</t>
         </is>
       </c>
+      <c r="G379" t="inlineStr"/>
       <c r="H379" t="n">
         <v>9</v>
       </c>
@@ -21897,6 +22093,7 @@
           <t>万州区</t>
         </is>
       </c>
+      <c r="G380" t="inlineStr"/>
       <c r="H380" t="n">
         <v>12</v>
       </c>
@@ -21951,6 +22148,7 @@
           <t>万州区</t>
         </is>
       </c>
+      <c r="G381" t="inlineStr"/>
       <c r="H381" t="n">
         <v>9</v>
       </c>
@@ -22005,6 +22203,7 @@
           <t>开州区</t>
         </is>
       </c>
+      <c r="G382" t="inlineStr"/>
       <c r="H382" t="n">
         <v>1</v>
       </c>
@@ -22059,6 +22258,7 @@
           <t>黔江区</t>
         </is>
       </c>
+      <c r="G383" t="inlineStr"/>
       <c r="H383" t="n">
         <v>8</v>
       </c>
@@ -22113,6 +22313,7 @@
           <t>璧山区</t>
         </is>
       </c>
+      <c r="G384" t="inlineStr"/>
       <c r="H384" t="n">
         <v>6</v>
       </c>
@@ -22167,6 +22368,7 @@
           <t>集安市</t>
         </is>
       </c>
+      <c r="G385" t="inlineStr"/>
       <c r="H385" t="n">
         <v>7</v>
       </c>
@@ -22221,6 +22423,7 @@
           <t>洮南市</t>
         </is>
       </c>
+      <c r="G386" t="inlineStr"/>
       <c r="H386" t="n">
         <v>6</v>
       </c>
@@ -22275,6 +22478,7 @@
           <t>勃利县</t>
         </is>
       </c>
+      <c r="G387" t="inlineStr"/>
       <c r="H387" t="n">
         <v>7</v>
       </c>
@@ -22329,6 +22533,7 @@
           <t>孙吴县</t>
         </is>
       </c>
+      <c r="G388" t="inlineStr"/>
       <c r="H388" t="n">
         <v>8</v>
       </c>
@@ -22383,6 +22588,7 @@
           <t>宁陵县</t>
         </is>
       </c>
+      <c r="G389" t="inlineStr"/>
       <c r="H389" t="n">
         <v>8</v>
       </c>
@@ -22437,6 +22643,7 @@
           <t>荥阳市</t>
         </is>
       </c>
+      <c r="G390" t="inlineStr"/>
       <c r="H390" t="n">
         <v>9</v>
       </c>
@@ -22491,6 +22698,7 @@
           <t>深州市</t>
         </is>
       </c>
+      <c r="G391" t="inlineStr"/>
       <c r="H391" t="n">
         <v>7</v>
       </c>
@@ -22545,6 +22753,7 @@
           <t>怀来县</t>
         </is>
       </c>
+      <c r="G392" t="inlineStr"/>
       <c r="H392" t="n">
         <v>7</v>
       </c>
@@ -22599,6 +22808,7 @@
           <t>黄骅市</t>
         </is>
       </c>
+      <c r="G393" t="inlineStr"/>
       <c r="H393" t="n">
         <v>9</v>
       </c>
@@ -22653,6 +22863,7 @@
           <t>赵县</t>
         </is>
       </c>
+      <c r="G394" t="inlineStr"/>
       <c r="H394" t="n">
         <v>8</v>
       </c>
@@ -22707,6 +22918,7 @@
           <t>襄汾县</t>
         </is>
       </c>
+      <c r="G395" t="inlineStr"/>
       <c r="H395" t="n">
         <v>8</v>
       </c>
@@ -22761,6 +22973,7 @@
           <t>平陆县</t>
         </is>
       </c>
+      <c r="G396" t="inlineStr"/>
       <c r="H396" t="n">
         <v>9</v>
       </c>
@@ -22815,6 +23028,7 @@
           <t>清徐县</t>
         </is>
       </c>
+      <c r="G397" t="inlineStr"/>
       <c r="H397" t="n">
         <v>7.5</v>
       </c>
@@ -22869,6 +23083,7 @@
           <t>惠山区</t>
         </is>
       </c>
+      <c r="G398" t="inlineStr"/>
       <c r="H398" t="n">
         <v>6.9</v>
       </c>
@@ -22923,6 +23138,7 @@
           <t>句容市</t>
         </is>
       </c>
+      <c r="G399" t="inlineStr"/>
       <c r="H399" t="n">
         <v>7</v>
       </c>
@@ -22977,6 +23193,7 @@
           <t>吴中区</t>
         </is>
       </c>
+      <c r="G400" t="inlineStr"/>
       <c r="H400" t="n">
         <v>4</v>
       </c>
@@ -23031,6 +23248,7 @@
           <t>丰县</t>
         </is>
       </c>
+      <c r="G401" t="inlineStr"/>
       <c r="H401" t="n">
         <v>7.5</v>
       </c>
@@ -23085,6 +23303,7 @@
           <t>凤凰县</t>
         </is>
       </c>
+      <c r="G402" t="inlineStr"/>
       <c r="H402" t="n">
         <v>8</v>
       </c>
@@ -23139,6 +23358,7 @@
           <t>道县</t>
         </is>
       </c>
+      <c r="G403" t="inlineStr"/>
       <c r="H403" t="n">
         <v>10</v>
       </c>
@@ -23193,6 +23413,7 @@
           <t>枣阳市</t>
         </is>
       </c>
+      <c r="G404" t="inlineStr"/>
       <c r="H404" t="n">
         <v>5</v>
       </c>
@@ -23247,6 +23468,7 @@
           <t>麻城市</t>
         </is>
       </c>
+      <c r="G405" t="inlineStr"/>
       <c r="H405" t="n">
         <v>9</v>
       </c>
@@ -23301,6 +23523,7 @@
           <t>蒙阴县</t>
         </is>
       </c>
+      <c r="G406" t="inlineStr"/>
       <c r="H406" t="n">
         <v>5.9</v>
       </c>
@@ -23359,6 +23582,7 @@
           <t>博山区</t>
         </is>
       </c>
+      <c r="G407" t="inlineStr"/>
       <c r="H407" t="n">
         <v>8</v>
       </c>
@@ -23413,6 +23637,7 @@
           <t>黄陵县</t>
         </is>
       </c>
+      <c r="G408" t="inlineStr"/>
       <c r="H408" t="n">
         <v>9</v>
       </c>
@@ -23467,6 +23692,7 @@
           <t>郁南县</t>
         </is>
       </c>
+      <c r="G409" t="inlineStr"/>
       <c r="H409" t="n">
         <v>6</v>
       </c>
@@ -23521,6 +23747,7 @@
           <t>德庆县</t>
         </is>
       </c>
+      <c r="G410" t="inlineStr"/>
       <c r="H410" t="n">
         <v>10</v>
       </c>
@@ -23575,6 +23802,7 @@
           <t>梅县区</t>
         </is>
       </c>
+      <c r="G411" t="inlineStr"/>
       <c r="H411" t="n">
         <v>9</v>
       </c>
@@ -23629,6 +23857,7 @@
           <t>连州市</t>
         </is>
       </c>
+      <c r="G412" t="inlineStr"/>
       <c r="H412" t="n">
         <v>6</v>
       </c>
@@ -23683,6 +23912,7 @@
           <t>容县</t>
         </is>
       </c>
+      <c r="G413" t="inlineStr"/>
       <c r="H413" t="n">
         <v>9</v>
       </c>
@@ -23737,6 +23967,7 @@
           <t>富川瑶族自治县</t>
         </is>
       </c>
+      <c r="G414" t="inlineStr"/>
       <c r="H414" t="n">
         <v>10.9</v>
       </c>
@@ -23791,6 +24022,7 @@
           <t>保城镇</t>
         </is>
       </c>
+      <c r="G415" t="inlineStr"/>
       <c r="H415" t="n">
         <v>5</v>
       </c>
@@ -23845,6 +24077,7 @@
           <t>天涯区</t>
         </is>
       </c>
+      <c r="G416" t="inlineStr"/>
       <c r="H416" t="n">
         <v>12</v>
       </c>
@@ -23899,6 +24132,7 @@
           <t>佛罗镇</t>
         </is>
       </c>
+      <c r="G417" t="inlineStr"/>
       <c r="H417" t="n">
         <v>12</v>
       </c>
@@ -23953,6 +24187,7 @@
           <t>龙海区</t>
         </is>
       </c>
+      <c r="G418" t="inlineStr"/>
       <c r="H418" t="n">
         <v>4</v>
       </c>
@@ -24007,6 +24242,7 @@
           <t>仙游县</t>
         </is>
       </c>
+      <c r="G419" t="inlineStr"/>
       <c r="H419" t="n">
         <v>9.5</v>
       </c>
@@ -24061,6 +24297,7 @@
           <t>顺昌县</t>
         </is>
       </c>
+      <c r="G420" t="inlineStr"/>
       <c r="H420" t="n">
         <v>10.9</v>
       </c>
@@ -24115,6 +24352,7 @@
           <t>浦江县</t>
         </is>
       </c>
+      <c r="G421" t="inlineStr"/>
       <c r="H421" t="n">
         <v>6</v>
       </c>
@@ -24169,6 +24407,7 @@
           <t>玉环市</t>
         </is>
       </c>
+      <c r="G422" t="inlineStr"/>
       <c r="H422" t="n">
         <v>9.5</v>
       </c>
@@ -24223,6 +24462,7 @@
           <t>孟连傣族拉祜族佤族自治县</t>
         </is>
       </c>
+      <c r="G423" t="inlineStr"/>
       <c r="H423" t="n">
         <v>8</v>
       </c>
@@ -24277,6 +24517,7 @@
           <t>华宁县</t>
         </is>
       </c>
+      <c r="G424" t="inlineStr"/>
       <c r="H424" t="n">
         <v>8</v>
       </c>
@@ -24331,6 +24572,7 @@
           <t>高昌区</t>
         </is>
       </c>
+      <c r="G425" t="inlineStr"/>
       <c r="H425" t="n">
         <v>7</v>
       </c>
@@ -24385,6 +24627,7 @@
           <t>伊州区</t>
         </is>
       </c>
+      <c r="G426" t="inlineStr"/>
       <c r="H426" t="n">
         <v>6</v>
       </c>
@@ -24439,6 +24682,7 @@
           <t>伽师县</t>
         </is>
       </c>
+      <c r="G427" t="inlineStr"/>
       <c r="H427" t="n">
         <v>8</v>
       </c>
@@ -24493,6 +24737,7 @@
           <t>徐闻县</t>
         </is>
       </c>
+      <c r="G428" t="inlineStr"/>
       <c r="H428" t="n">
         <v>1</v>
       </c>
@@ -24547,6 +24792,7 @@
           <t>福山镇</t>
         </is>
       </c>
+      <c r="G429" t="inlineStr"/>
       <c r="H429" t="n">
         <v>10</v>
       </c>
@@ -24601,6 +24847,7 @@
           <t>元江哈尼族彝族傣族自治县</t>
         </is>
       </c>
+      <c r="G430" t="inlineStr"/>
       <c r="H430" t="n">
         <v>1</v>
       </c>
@@ -24655,6 +24902,7 @@
           <t>新宁县</t>
         </is>
       </c>
+      <c r="G431" t="inlineStr"/>
       <c r="H431" t="n">
         <v>1</v>
       </c>
@@ -24709,6 +24957,7 @@
           <t>吴中区</t>
         </is>
       </c>
+      <c r="G432" t="inlineStr"/>
       <c r="H432" t="n">
         <v>1</v>
       </c>
@@ -24763,6 +25012,7 @@
           <t>宾川县</t>
         </is>
       </c>
+      <c r="G433" t="inlineStr"/>
       <c r="H433" t="n">
         <v>1</v>
       </c>
@@ -24817,6 +25067,7 @@
           <t>荔城区</t>
         </is>
       </c>
+      <c r="G434" t="inlineStr"/>
       <c r="H434" t="n">
         <v>1</v>
       </c>
@@ -24871,6 +25122,7 @@
           <t>敖汉旗</t>
         </is>
       </c>
+      <c r="G435" t="inlineStr"/>
       <c r="H435" t="n">
         <v>1</v>
       </c>
@@ -24925,6 +25177,7 @@
           <t>扎兰屯市</t>
         </is>
       </c>
+      <c r="G436" t="inlineStr"/>
       <c r="H436" t="n">
         <v>1</v>
       </c>
@@ -24979,6 +25232,7 @@
           <t>攀枝花市</t>
         </is>
       </c>
+      <c r="G437" t="inlineStr"/>
       <c r="H437" t="n">
         <v>6.5</v>
       </c>
@@ -24996,6 +25250,7 @@
           <t>冬季巅峰型</t>
         </is>
       </c>
+      <c r="M437" t="inlineStr"/>
     </row>
     <row r="438" hidden="1">
       <c r="A438" t="inlineStr">
@@ -25677,6 +25932,7 @@
           <t>阿克苏市</t>
         </is>
       </c>
+      <c r="G449" t="inlineStr"/>
       <c r="H449" t="n">
         <v>7</v>
       </c>
@@ -25731,6 +25987,7 @@
           <t>新罗区</t>
         </is>
       </c>
+      <c r="G450" t="inlineStr"/>
       <c r="H450" t="n">
         <v>7</v>
       </c>
@@ -25785,6 +26042,7 @@
           <t>源城区</t>
         </is>
       </c>
+      <c r="G451" t="inlineStr"/>
       <c r="H451" t="n">
         <v>6</v>
       </c>
@@ -25839,6 +26097,7 @@
           <t>琼山区</t>
         </is>
       </c>
+      <c r="G452" t="inlineStr"/>
       <c r="H452" t="n">
         <v>5</v>
       </c>
@@ -25893,6 +26152,7 @@
           <t>都匀市</t>
         </is>
       </c>
+      <c r="G453" t="inlineStr"/>
       <c r="H453" t="n">
         <v>7</v>
       </c>
@@ -25947,6 +26207,7 @@
           <t>莎车县</t>
         </is>
       </c>
+      <c r="G454" t="inlineStr"/>
       <c r="H454" t="n">
         <v>8</v>
       </c>
@@ -26001,6 +26262,7 @@
           <t>库车市</t>
         </is>
       </c>
+      <c r="G455" t="inlineStr"/>
       <c r="H455" t="n">
         <v>8</v>
       </c>
@@ -26173,6 +26435,7 @@
           <t>波莲镇</t>
         </is>
       </c>
+      <c r="G458" t="inlineStr"/>
       <c r="H458" t="n">
         <v>7</v>
       </c>
@@ -30554,6 +30817,7 @@
           <t>丹棱县</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="n">
         <v>103.53</v>
       </c>
@@ -30592,6 +30856,7 @@
           <t>东坡区</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="n">
         <v>103.83</v>
       </c>
@@ -30630,6 +30895,7 @@
           <t>蒲江县</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="n">
         <v>103.51</v>
       </c>
@@ -30668,6 +30934,7 @@
           <t>金堂县</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="n">
         <v>104.41</v>
       </c>
@@ -30706,6 +30973,7 @@
           <t>名山区</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="n">
         <v>103.11</v>
       </c>
@@ -30744,6 +31012,7 @@
           <t>苍溪县</t>
         </is>
       </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="n">
         <v>105.93</v>
       </c>
@@ -30782,6 +31051,7 @@
           <t>金川县</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="n">
         <v>102.06</v>
       </c>
@@ -30820,6 +31090,7 @@
           <t>龙泉驿区</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="n">
         <v>104.27</v>
       </c>
@@ -30858,6 +31129,7 @@
           <t>双流区</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
         <v>103.92</v>
       </c>
@@ -30939,6 +31211,7 @@
           <t>会理市</t>
         </is>
       </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="n">
         <v>102.25</v>
       </c>
@@ -30977,6 +31250,7 @@
           <t>新平县</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="n">
         <v>101.99</v>
       </c>
@@ -31015,6 +31289,7 @@
           <t>华宁县</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="n">
         <v>102.93</v>
       </c>
@@ -31053,6 +31328,7 @@
           <t>弥勒市</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="n">
         <v>103.41</v>
       </c>
@@ -31091,6 +31367,7 @@
           <t>沾益区</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="n">
         <v>103.82</v>
       </c>
@@ -31129,6 +31406,7 @@
           <t>澄江市</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="n">
         <v>102.91</v>
       </c>
@@ -31167,6 +31445,7 @@
           <t>大理州</t>
         </is>
       </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
         <v>100.23</v>
       </c>
@@ -31205,6 +31484,7 @@
           <t>蒙自市</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
         <v>103.36</v>
       </c>
@@ -31243,6 +31523,7 @@
           <t>永仁县</t>
         </is>
       </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
         <v>101.67</v>
       </c>
@@ -31281,6 +31562,7 @@
           <t>华坪县</t>
         </is>
       </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
         <v>101.27</v>
       </c>
@@ -31319,6 +31601,7 @@
           <t>元阳县</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
         <v>102.83</v>
       </c>
@@ -31357,6 +31640,7 @@
           <t>永德县</t>
         </is>
       </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
         <v>99.26000000000001</v>
       </c>
@@ -31395,6 +31679,7 @@
           <t>丘北县</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
         <v>104.19</v>
       </c>
@@ -31433,6 +31718,7 @@
           <t>开远市</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
         <v>103.27</v>
       </c>
@@ -31471,6 +31757,7 @@
           <t>富民县</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="n">
         <v>102.5</v>
       </c>
@@ -31509,6 +31796,7 @@
           <t>昭阳区</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
         <v>103.71</v>
       </c>
@@ -31547,6 +31835,7 @@
           <t>高州市</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
         <v>110.85</v>
       </c>
@@ -31585,6 +31874,7 @@
           <t>增城区</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="n">
         <v>113.81</v>
       </c>
@@ -31623,6 +31913,7 @@
           <t>阳东区</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="n">
         <v>112.01</v>
       </c>
@@ -31661,6 +31952,7 @@
           <t>四会市</t>
         </is>
       </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="n">
         <v>112.73</v>
       </c>
@@ -31699,6 +31991,7 @@
           <t>清远市</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="n">
         <v>113.06</v>
       </c>
@@ -31737,6 +32030,7 @@
           <t>徐闻县</t>
         </is>
       </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="n">
         <v>110.18</v>
       </c>
@@ -31775,6 +32069,7 @@
           <t>荔浦市</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="n">
         <v>110.39</v>
       </c>
@@ -31813,6 +32108,7 @@
           <t>蒙山县</t>
         </is>
       </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="n">
         <v>110.52</v>
       </c>
@@ -31851,6 +32147,7 @@
           <t>象州县</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="n">
         <v>109.68</v>
       </c>
@@ -31889,6 +32186,7 @@
           <t>田东县</t>
         </is>
       </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="n">
         <v>107.12</v>
       </c>
@@ -31927,6 +32225,7 @@
           <t>隆安县</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="n">
         <v>107.7</v>
       </c>
@@ -31965,6 +32264,7 @@
           <t>扶绥县</t>
         </is>
       </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="n">
         <v>107.9</v>
       </c>
@@ -32003,6 +32303,7 @@
           <t>北流市</t>
         </is>
       </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="n">
         <v>110.35</v>
       </c>
@@ -32041,6 +32342,7 @@
           <t>钦州市</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="n">
         <v>108.65</v>
       </c>
@@ -32079,6 +32381,7 @@
           <t>崇左市</t>
         </is>
       </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="n">
         <v>107.35</v>
       </c>
@@ -32117,6 +32420,7 @@
           <t>八步区</t>
         </is>
       </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
         <v>111.55</v>
       </c>
@@ -32155,6 +32459,7 @@
           <t>浦北县</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
         <v>109.56</v>
       </c>
@@ -32193,6 +32498,7 @@
           <t>天峨县</t>
         </is>
       </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
         <v>107.17</v>
       </c>
@@ -32231,6 +32537,7 @@
           <t>紫云县</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
         <v>106.08</v>
       </c>
@@ -32269,6 +32576,7 @@
           <t>麻江县</t>
         </is>
       </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
         <v>107.59</v>
       </c>
@@ -32307,6 +32615,7 @@
           <t>龙里县</t>
         </is>
       </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="n">
         <v>106.98</v>
       </c>
@@ -32345,6 +32654,7 @@
           <t>罗甸县</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="n">
         <v>106.75</v>
       </c>
@@ -32383,6 +32693,7 @@
           <t>纳雍县</t>
         </is>
       </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="n">
         <v>105.38</v>
       </c>
@@ -32421,6 +32732,7 @@
           <t>六盘水市</t>
         </is>
       </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="n">
         <v>104.83</v>
       </c>
@@ -32459,6 +32771,7 @@
           <t>贞丰县</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="n">
         <v>105.65</v>
       </c>
@@ -32497,6 +32810,7 @@
           <t>三亚市</t>
         </is>
       </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="n">
         <v>109.51</v>
       </c>
@@ -32535,6 +32849,7 @@
           <t>陵水县</t>
         </is>
       </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="n">
         <v>110.04</v>
       </c>
@@ -32573,6 +32888,7 @@
           <t>澄迈县</t>
         </is>
       </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="n">
         <v>110</v>
       </c>
@@ -32611,6 +32927,7 @@
           <t>琼海市</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="n">
         <v>110.47</v>
       </c>
@@ -32649,6 +32966,7 @@
           <t>万宁市</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
         <v>110.39</v>
       </c>
@@ -32687,6 +33005,7 @@
           <t>海口市</t>
         </is>
       </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
         <v>110.2</v>
       </c>
@@ -32725,6 +33044,7 @@
           <t>琼山区</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>110.35</v>
       </c>
@@ -32763,6 +33083,7 @@
           <t>文昌市</t>
         </is>
       </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
         <v>110.8</v>
       </c>
@@ -32801,6 +33122,7 @@
           <t>石棉县</t>
         </is>
       </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
         <v>102.36</v>
       </c>
@@ -33914,6 +34236,7 @@
           <t>长阳土家族自治县</t>
         </is>
       </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
         <v>111.20105</v>
       </c>
@@ -34038,6 +34361,7 @@
           <t>公安县</t>
         </is>
       </c>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="n">
         <v>112.23242</v>
       </c>
@@ -34076,6 +34400,7 @@
           <t>赤壁市</t>
         </is>
       </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="n">
         <v>113.90039</v>
       </c>
@@ -34114,6 +34439,7 @@
           <t>建始县</t>
         </is>
       </c>
+      <c r="E191" t="inlineStr"/>
       <c r="F191" t="n">
         <v>109.7182</v>
       </c>
@@ -34195,6 +34521,7 @@
           <t>宜都市</t>
         </is>
       </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="n">
         <v>111.45025</v>
       </c>
@@ -34233,6 +34560,7 @@
           <t>罗田县</t>
         </is>
       </c>
+      <c r="E194" t="inlineStr"/>
       <c r="F194" t="n">
         <v>115.39056</v>
       </c>
@@ -34271,6 +34599,7 @@
           <t>房县</t>
         </is>
       </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="n">
         <v>110.73333</v>
       </c>
@@ -34309,6 +34638,7 @@
           <t>老河口市</t>
         </is>
       </c>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="n">
         <v>111.66944</v>
       </c>
@@ -34347,6 +34677,7 @@
           <t>老河口市</t>
         </is>
       </c>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="n">
         <v>111.66944</v>
       </c>
@@ -34385,6 +34716,7 @@
           <t>兴山县</t>
         </is>
       </c>
+      <c r="E198" t="inlineStr"/>
       <c r="F198" t="n">
         <v>110.74951</v>
       </c>
@@ -34423,6 +34755,7 @@
           <t>凉城县</t>
         </is>
       </c>
+      <c r="E199" t="inlineStr"/>
       <c r="F199" t="n">
         <v>112.5</v>
       </c>
@@ -34461,6 +34794,7 @@
           <t>宁城县</t>
         </is>
       </c>
+      <c r="E200" t="inlineStr"/>
       <c r="F200" t="n">
         <v>119.33333</v>
       </c>
@@ -34494,6 +34828,8 @@
           <t>乌海市</t>
         </is>
       </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="n">
         <v>106.8</v>
       </c>
@@ -34532,6 +34868,7 @@
           <t>延吉市</t>
         </is>
       </c>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="n">
         <v>129.5</v>
       </c>
@@ -34565,6 +34902,8 @@
           <t>白山市</t>
         </is>
       </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="n">
         <v>126.41667</v>
       </c>
@@ -34603,6 +34942,7 @@
           <t>柳河县</t>
         </is>
       </c>
+      <c r="E204" t="inlineStr"/>
       <c r="F204" t="n">
         <v>125.74475</v>
       </c>
@@ -34641,6 +34981,7 @@
           <t>通化县</t>
         </is>
       </c>
+      <c r="E205" t="inlineStr"/>
       <c r="F205" t="n">
         <v>125.75936</v>
       </c>
@@ -34674,6 +35015,8 @@
           <t>大兴安岭地区</t>
         </is>
       </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
       <c r="F206" t="n">
         <v>124.11667</v>
       </c>
@@ -34712,6 +35055,7 @@
           <t>尚志市</t>
         </is>
       </c>
+      <c r="E207" t="inlineStr"/>
       <c r="F207" t="n">
         <v>127.96194</v>
       </c>
@@ -34750,6 +35094,7 @@
           <t>勃利县</t>
         </is>
       </c>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="n">
         <v>130.56806</v>
       </c>
@@ -34788,6 +35133,7 @@
           <t>穆棱市</t>
         </is>
       </c>
+      <c r="E209" t="inlineStr"/>
       <c r="F209" t="n">
         <v>130.51667</v>
       </c>
@@ -34821,6 +35167,8 @@
           <t>伊春市</t>
         </is>
       </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
       <c r="F210" t="n">
         <v>128.84</v>
       </c>
@@ -34854,6 +35202,8 @@
           <t>海西蒙古族藏族自治州</t>
         </is>
       </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
       <c r="F211" t="n">
         <v>97.36667</v>
       </c>
@@ -34892,6 +35242,7 @@
           <t>乐都区</t>
         </is>
       </c>
+      <c r="E212" t="inlineStr"/>
       <c r="F212" t="n">
         <v>102.4</v>
       </c>
@@ -34930,6 +35281,7 @@
           <t>乐都区</t>
         </is>
       </c>
+      <c r="E213" t="inlineStr"/>
       <c r="F213" t="n">
         <v>102.4</v>
       </c>
@@ -34968,6 +35320,7 @@
           <t>芒康县</t>
         </is>
       </c>
+      <c r="E214" t="inlineStr"/>
       <c r="F214" t="n">
         <v>98.59999999999999</v>
       </c>
@@ -35006,6 +35359,7 @@
           <t>朗县</t>
         </is>
       </c>
+      <c r="E215" t="inlineStr"/>
       <c r="F215" t="n">
         <v>93.06667</v>
       </c>
@@ -35087,6 +35441,7 @@
           <t>西峡县</t>
         </is>
       </c>
+      <c r="E217" t="inlineStr"/>
       <c r="F217" t="n">
         <v>111.47917</v>
       </c>
@@ -35125,6 +35480,7 @@
           <t>肥城市</t>
         </is>
       </c>
+      <c r="E218" t="inlineStr"/>
       <c r="F218" t="n">
         <v>116.65</v>
       </c>
@@ -35163,6 +35519,7 @@
           <t>乐陵市</t>
         </is>
       </c>
+      <c r="E219" t="inlineStr"/>
       <c r="F219" t="n">
         <v>117.216657</v>
       </c>
@@ -35201,6 +35558,7 @@
           <t>威远县</t>
         </is>
       </c>
+      <c r="E220" t="inlineStr"/>
       <c r="F220" t="n">
         <v>104.66667</v>
       </c>
@@ -35239,6 +35597,7 @@
           <t>炎陵县</t>
         </is>
       </c>
+      <c r="E221" t="inlineStr"/>
       <c r="F221" t="n">
         <v>113.76667</v>
       </c>
@@ -35277,6 +35636,7 @@
           <t>隰县</t>
         </is>
       </c>
+      <c r="E222" t="inlineStr"/>
       <c r="F222" t="n">
         <v>110.93333</v>
       </c>
@@ -35310,6 +35670,8 @@
           <t>东方市</t>
         </is>
       </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
       <c r="F223" t="n">
         <v>108.63333</v>
       </c>
@@ -35348,6 +35710,7 @@
           <t>灵武市</t>
         </is>
       </c>
+      <c r="E224" t="inlineStr"/>
       <c r="F224" t="n">
         <v>106.33333</v>
       </c>
@@ -35386,6 +35749,7 @@
           <t>集安市</t>
         </is>
       </c>
+      <c r="E225" t="inlineStr"/>
       <c r="F225" t="n">
         <v>126.18829</v>
       </c>
@@ -35419,6 +35783,8 @@
           <t>龙岩市</t>
         </is>
       </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
       <c r="F226" t="n">
         <v>117.01667</v>
       </c>
@@ -35457,6 +35823,7 @@
           <t>青州市</t>
         </is>
       </c>
+      <c r="E227" t="inlineStr"/>
       <c r="F227" t="n">
         <v>118.46667</v>
       </c>
@@ -35490,6 +35857,8 @@
           <t>威海市</t>
         </is>
       </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
       <c r="F228" t="n">
         <v>122.11667</v>
       </c>
@@ -35614,6 +35983,7 @@
           <t>巴宜区</t>
         </is>
       </c>
+      <c r="E231" t="inlineStr"/>
       <c r="F231" t="n">
         <v>94.361</v>
       </c>
@@ -35652,6 +36022,7 @@
           <t>察隅县</t>
         </is>
       </c>
+      <c r="E232" t="inlineStr"/>
       <c r="F232" t="n">
         <v>97.465</v>
       </c>
@@ -35690,6 +36061,7 @@
           <t>中宁县</t>
         </is>
       </c>
+      <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
         <v>105.685</v>
       </c>
@@ -35728,6 +36100,7 @@
           <t>海原县</t>
         </is>
       </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
         <v>105.643</v>
       </c>
@@ -35809,6 +36182,7 @@
           <t>怀远县</t>
         </is>
       </c>
+      <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
         <v>117.205</v>
       </c>
@@ -35847,6 +36221,7 @@
           <t>萧县</t>
         </is>
       </c>
+      <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
         <v>116.947</v>
       </c>
@@ -35885,6 +36260,7 @@
           <t>广丰区</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
         <v>118.191</v>
       </c>
@@ -35923,6 +36299,7 @@
           <t>梁平区</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
         <v>107.802</v>
       </c>
@@ -35961,6 +36338,7 @@
           <t>潼南区</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
         <v>105.84</v>
       </c>
@@ -35999,6 +36377,7 @@
           <t>磴口县</t>
         </is>
       </c>
+      <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>107.008</v>
       </c>
@@ -36037,6 +36416,7 @@
           <t>鄂伦春自治旗</t>
         </is>
       </c>
+      <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
         <v>123.726</v>
       </c>
@@ -36075,6 +36455,7 @@
           <t>民和回族土族自治县</t>
         </is>
       </c>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
         <v>102.83</v>
       </c>
@@ -36113,6 +36494,7 @@
           <t>尚志市</t>
         </is>
       </c>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
         <v>127.961</v>
       </c>
@@ -36151,6 +36533,7 @@
           <t>友好区</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr"/>
       <c r="F245" t="n">
         <v>128.841</v>
       </c>
@@ -36189,6 +36572,7 @@
           <t>天涯区</t>
         </is>
       </c>
+      <c r="E246" t="inlineStr"/>
       <c r="F246" t="n">
         <v>109.506</v>
       </c>
@@ -36222,6 +36606,8 @@
           <t>琼中黎族苗族自治县</t>
         </is>
       </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr"/>
       <c r="F247" t="n">
         <v>109.838</v>
       </c>
@@ -36255,6 +36641,7 @@
           <t>文昌市</t>
         </is>
       </c>
+      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>东郊镇</t>
@@ -36298,6 +36685,7 @@
           <t>西峰区</t>
         </is>
       </c>
+      <c r="E249" t="inlineStr"/>
       <c r="F249" t="n">
         <v>107.651</v>
       </c>
@@ -37368,6 +37756,7 @@
           <t>白水县</t>
         </is>
       </c>
+      <c r="E274" t="inlineStr"/>
       <c r="F274" t="n">
         <v>109.59</v>
       </c>
@@ -37406,6 +37795,7 @@
           <t>彬州市</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr"/>
       <c r="F275" t="n">
         <v>108.08</v>
       </c>
@@ -37444,6 +37834,7 @@
           <t>永春县</t>
         </is>
       </c>
+      <c r="E276" t="inlineStr"/>
       <c r="F276" t="n">
         <v>118.29</v>
       </c>
@@ -37482,6 +37873,7 @@
           <t>诏安县</t>
         </is>
       </c>
+      <c r="E277" t="inlineStr"/>
       <c r="F277" t="n">
         <v>117.18</v>
       </c>
@@ -37563,6 +37955,7 @@
           <t>黄岩区</t>
         </is>
       </c>
+      <c r="E279" t="inlineStr"/>
       <c r="F279" t="n">
         <v>121.26</v>
       </c>
@@ -37601,6 +37994,7 @@
           <t>余姚市</t>
         </is>
       </c>
+      <c r="E280" t="inlineStr"/>
       <c r="F280" t="n">
         <v>121.16</v>
       </c>
@@ -37639,6 +38033,7 @@
           <t>常山县</t>
         </is>
       </c>
+      <c r="E281" t="inlineStr"/>
       <c r="F281" t="n">
         <v>118.51</v>
       </c>
@@ -37672,6 +38067,8 @@
           <t>大连市</t>
         </is>
       </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr"/>
       <c r="F282" t="n">
         <v>121.61</v>
       </c>
@@ -37710,6 +38107,7 @@
           <t>盖州市</t>
         </is>
       </c>
+      <c r="E283" t="inlineStr"/>
       <c r="F283" t="n">
         <v>122.35</v>
       </c>
@@ -37748,6 +38146,7 @@
           <t>辽中区</t>
         </is>
       </c>
+      <c r="E284" t="inlineStr"/>
       <c r="F284" t="n">
         <v>122.73</v>
       </c>
@@ -37781,6 +38180,8 @@
           <t>苏州市</t>
         </is>
       </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr"/>
       <c r="F285" t="n">
         <v>120.63</v>
       </c>
@@ -37819,6 +38220,7 @@
           <t>句容市</t>
         </is>
       </c>
+      <c r="E286" t="inlineStr"/>
       <c r="F286" t="n">
         <v>119.16</v>
       </c>
@@ -37857,6 +38259,7 @@
           <t>吴中区</t>
         </is>
       </c>
+      <c r="E287" t="inlineStr"/>
       <c r="F287" t="n">
         <v>120.63</v>
       </c>
@@ -37895,6 +38298,7 @@
           <t>江都区</t>
         </is>
       </c>
+      <c r="E288" t="inlineStr"/>
       <c r="F288" t="n">
         <v>119.57</v>
       </c>
@@ -37933,6 +38337,7 @@
           <t>牡丹江市</t>
         </is>
       </c>
+      <c r="E289" t="inlineStr"/>
       <c r="F289" t="n">
         <v>129.63</v>
       </c>
@@ -37966,6 +38371,8 @@
           <t>通化市</t>
         </is>
       </c>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr"/>
       <c r="F290" t="n">
         <v>125.94</v>
       </c>
@@ -38004,6 +38411,7 @@
           <t>临猗县</t>
         </is>
       </c>
+      <c r="E291" t="inlineStr"/>
       <c r="F291" t="n">
         <v>110.77</v>
       </c>
@@ -38037,6 +38445,8 @@
           <t>晋城市</t>
         </is>
       </c>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr"/>
       <c r="F292" t="n">
         <v>112.85</v>
       </c>
@@ -38075,6 +38485,7 @@
           <t>长寿区</t>
         </is>
       </c>
+      <c r="E293" t="inlineStr"/>
       <c r="F293" t="n">
         <v>107.08</v>
       </c>
@@ -38113,6 +38524,7 @@
           <t>永川区</t>
         </is>
       </c>
+      <c r="E294" t="inlineStr"/>
       <c r="F294" t="n">
         <v>105.89</v>
       </c>
@@ -38146,6 +38558,8 @@
           <t>吴忠市</t>
         </is>
       </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr"/>
       <c r="F295" t="n">
         <v>106.2</v>
       </c>
@@ -38179,6 +38593,8 @@
           <t>海东市</t>
         </is>
       </c>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr"/>
       <c r="F296" t="n">
         <v>102.1</v>
       </c>
@@ -38217,6 +38633,7 @@
           <t>磴口县</t>
         </is>
       </c>
+      <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
         <v>107.01</v>
       </c>
@@ -38250,6 +38667,8 @@
           <t>赤峰市</t>
         </is>
       </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
         <v>118.89</v>
       </c>
@@ -38288,6 +38707,7 @@
           <t>密云区</t>
         </is>
       </c>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
         <v>116.84</v>
       </c>
@@ -38326,6 +38746,7 @@
           <t>滨海新区</t>
         </is>
       </c>
+      <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>117.65</v>
       </c>
@@ -38364,6 +38785,7 @@
           <t>嘉定区</t>
         </is>
       </c>
+      <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
         <v>121.27</v>
       </c>
@@ -38402,6 +38824,7 @@
           <t>民和回族土族自治县</t>
         </is>
       </c>
+      <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>102.83</v>
       </c>
@@ -38440,6 +38863,7 @@
           <t>友好区</t>
         </is>
       </c>
+      <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
         <v>128.84</v>
       </c>
@@ -38473,6 +38897,8 @@
           <t>琼中黎族苗族自治县</t>
         </is>
       </c>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
         <v>109.84</v>
       </c>
@@ -38554,6 +38980,7 @@
           <t>民勤县</t>
         </is>
       </c>
+      <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
         <v>103.1</v>
       </c>
@@ -38592,6 +39019,7 @@
           <t>西峰区</t>
         </is>
       </c>
+      <c r="E307" t="inlineStr"/>
       <c r="F307" t="n">
         <v>107.65</v>
       </c>
@@ -40006,6 +40434,7 @@
           <t>雷波县</t>
         </is>
       </c>
+      <c r="E340" t="inlineStr"/>
       <c r="F340" t="n">
         <v>103.57</v>
       </c>
@@ -40044,6 +40473,7 @@
           <t>盐源县</t>
         </is>
       </c>
+      <c r="E341" t="inlineStr"/>
       <c r="F341" t="n">
         <v>101.51</v>
       </c>
@@ -40082,6 +40512,7 @@
           <t>蒲江县</t>
         </is>
       </c>
+      <c r="E342" t="inlineStr"/>
       <c r="F342" t="n">
         <v>103.54</v>
       </c>
@@ -40120,6 +40551,7 @@
           <t>都江堰市</t>
         </is>
       </c>
+      <c r="E343" t="inlineStr"/>
       <c r="F343" t="n">
         <v>103.62</v>
       </c>
@@ -40158,6 +40590,7 @@
           <t>米易县</t>
         </is>
       </c>
+      <c r="E344" t="inlineStr"/>
       <c r="F344" t="n">
         <v>102.11</v>
       </c>
@@ -40196,6 +40629,7 @@
           <t>邻水县</t>
         </is>
       </c>
+      <c r="E345" t="inlineStr"/>
       <c r="F345" t="n">
         <v>106.93</v>
       </c>
@@ -40234,6 +40668,7 @@
           <t>石棉县</t>
         </is>
       </c>
+      <c r="E346" t="inlineStr"/>
       <c r="F346" t="n">
         <v>102.36</v>
       </c>
@@ -40272,6 +40707,7 @@
           <t>德昌县</t>
         </is>
       </c>
+      <c r="E347" t="inlineStr"/>
       <c r="F347" t="n">
         <v>102.18</v>
       </c>
@@ -40310,6 +40746,7 @@
           <t>江阳区</t>
         </is>
       </c>
+      <c r="E348" t="inlineStr"/>
       <c r="F348" t="n">
         <v>105.44</v>
       </c>
@@ -40348,6 +40785,7 @@
           <t>大邑县</t>
         </is>
       </c>
+      <c r="E349" t="inlineStr"/>
       <c r="F349" t="n">
         <v>103.52</v>
       </c>
@@ -40386,6 +40824,7 @@
           <t>从江县</t>
         </is>
       </c>
+      <c r="E350" t="inlineStr"/>
       <c r="F350" t="n">
         <v>108.9</v>
       </c>
@@ -40424,6 +40863,7 @@
           <t>水城区</t>
         </is>
       </c>
+      <c r="E351" t="inlineStr"/>
       <c r="F351" t="n">
         <v>104.95685</v>
       </c>
@@ -40462,6 +40902,7 @@
           <t>威宁彝族回族苗族自治县</t>
         </is>
       </c>
+      <c r="E352" t="inlineStr"/>
       <c r="F352" t="n">
         <v>104.28</v>
       </c>
@@ -40500,6 +40941,7 @@
           <t>开阳县</t>
         </is>
       </c>
+      <c r="E353" t="inlineStr"/>
       <c r="F353" t="n">
         <v>106.97</v>
       </c>
@@ -40538,6 +40980,7 @@
           <t>荔波县</t>
         </is>
       </c>
+      <c r="E354" t="inlineStr"/>
       <c r="F354" t="n">
         <v>107.88</v>
       </c>
@@ -40576,6 +41019,7 @@
           <t>沿河土家族自治县</t>
         </is>
       </c>
+      <c r="E355" t="inlineStr"/>
       <c r="F355" t="n">
         <v>108.5</v>
       </c>
@@ -40614,6 +41058,7 @@
           <t>敦煌市</t>
         </is>
       </c>
+      <c r="E356" t="inlineStr"/>
       <c r="F356" t="n">
         <v>94.66</v>
       </c>
@@ -40652,6 +41097,7 @@
           <t>皋兰县</t>
         </is>
       </c>
+      <c r="E357" t="inlineStr"/>
       <c r="F357" t="n">
         <v>103.95</v>
       </c>
@@ -40690,6 +41136,7 @@
           <t>临泽县</t>
         </is>
       </c>
+      <c r="E358" t="inlineStr"/>
       <c r="F358" t="n">
         <v>100.16</v>
       </c>
@@ -40728,6 +41175,7 @@
           <t>秦安县</t>
         </is>
       </c>
+      <c r="E359" t="inlineStr"/>
       <c r="F359" t="n">
         <v>105.67</v>
       </c>
@@ -40766,6 +41214,7 @@
           <t>金寨县</t>
         </is>
       </c>
+      <c r="E360" t="inlineStr"/>
       <c r="F360" t="n">
         <v>115.93</v>
       </c>
@@ -40804,6 +41253,7 @@
           <t>徽州区</t>
         </is>
       </c>
+      <c r="E361" t="inlineStr"/>
       <c r="F361" t="n">
         <v>118.34</v>
       </c>
@@ -40842,6 +41292,7 @@
           <t>黟县</t>
         </is>
       </c>
+      <c r="E362" t="inlineStr"/>
       <c r="F362" t="n">
         <v>117.94</v>
       </c>
@@ -40880,6 +41331,7 @@
           <t>万州区</t>
         </is>
       </c>
+      <c r="E363" t="inlineStr"/>
       <c r="F363" t="n">
         <v>108.41</v>
       </c>
@@ -40918,6 +41370,7 @@
           <t>万州区</t>
         </is>
       </c>
+      <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
         <v>108.41</v>
       </c>
@@ -40956,6 +41409,7 @@
           <t>开州区</t>
         </is>
       </c>
+      <c r="E365" t="inlineStr"/>
       <c r="F365" t="n">
         <v>108.42</v>
       </c>
@@ -40994,6 +41448,7 @@
           <t>黔江区</t>
         </is>
       </c>
+      <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
         <v>108.77</v>
       </c>
@@ -41032,6 +41487,7 @@
           <t>璧山区</t>
         </is>
       </c>
+      <c r="E367" t="inlineStr"/>
       <c r="F367" t="n">
         <v>106.23</v>
       </c>
@@ -41070,6 +41526,7 @@
           <t>集安市</t>
         </is>
       </c>
+      <c r="E368" t="inlineStr"/>
       <c r="F368" t="n">
         <v>126.18</v>
       </c>
@@ -41108,6 +41565,7 @@
           <t>洮南市</t>
         </is>
       </c>
+      <c r="E369" t="inlineStr"/>
       <c r="F369" t="n">
         <v>122.78</v>
       </c>
@@ -41146,6 +41604,7 @@
           <t>勃利县</t>
         </is>
       </c>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="n">
         <v>130.57</v>
       </c>
@@ -41184,6 +41643,7 @@
           <t>孙吴县</t>
         </is>
       </c>
+      <c r="E371" t="inlineStr"/>
       <c r="F371" t="n">
         <v>127.33</v>
       </c>
@@ -41222,6 +41682,7 @@
           <t>宁陵县</t>
         </is>
       </c>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="n">
         <v>115.32</v>
       </c>
@@ -41260,6 +41721,7 @@
           <t>荥阳市</t>
         </is>
       </c>
+      <c r="E373" t="inlineStr"/>
       <c r="F373" t="n">
         <v>113.38</v>
       </c>
@@ -41298,6 +41760,7 @@
           <t>深州市</t>
         </is>
       </c>
+      <c r="E374" t="inlineStr"/>
       <c r="F374" t="n">
         <v>115.56</v>
       </c>
@@ -41336,6 +41799,7 @@
           <t>怀来县</t>
         </is>
       </c>
+      <c r="E375" t="inlineStr"/>
       <c r="F375" t="n">
         <v>115.52</v>
       </c>
@@ -41374,6 +41838,7 @@
           <t>黄骅市</t>
         </is>
       </c>
+      <c r="E376" t="inlineStr"/>
       <c r="F376" t="n">
         <v>117.35</v>
       </c>
@@ -41412,6 +41877,7 @@
           <t>赵县</t>
         </is>
       </c>
+      <c r="E377" t="inlineStr"/>
       <c r="F377" t="n">
         <v>114.78</v>
       </c>
@@ -41450,6 +41916,7 @@
           <t>襄汾县</t>
         </is>
       </c>
+      <c r="E378" t="inlineStr"/>
       <c r="F378" t="n">
         <v>111.44</v>
       </c>
@@ -41488,6 +41955,7 @@
           <t>平陆县</t>
         </is>
       </c>
+      <c r="E379" t="inlineStr"/>
       <c r="F379" t="n">
         <v>111.22</v>
       </c>
@@ -41526,6 +41994,7 @@
           <t>清徐县</t>
         </is>
       </c>
+      <c r="E380" t="inlineStr"/>
       <c r="F380" t="n">
         <v>112.35</v>
       </c>
@@ -41564,6 +42033,7 @@
           <t>惠山区</t>
         </is>
       </c>
+      <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
         <v>120.303543</v>
       </c>
@@ -41602,6 +42072,7 @@
           <t>句容市</t>
         </is>
       </c>
+      <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
         <v>119.16</v>
       </c>
@@ -41640,6 +42111,7 @@
           <t>吴中区</t>
         </is>
       </c>
+      <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
         <v>120.4</v>
       </c>
@@ -41678,6 +42150,7 @@
           <t>丰县</t>
         </is>
       </c>
+      <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
         <v>116.6</v>
       </c>
@@ -41716,6 +42189,7 @@
           <t>凤凰县</t>
         </is>
       </c>
+      <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>109.6</v>
       </c>
@@ -41754,6 +42228,7 @@
           <t>道县</t>
         </is>
       </c>
+      <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
         <v>111.6</v>
       </c>
@@ -41792,6 +42267,7 @@
           <t>枣阳市</t>
         </is>
       </c>
+      <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
         <v>112.77</v>
       </c>
@@ -41830,6 +42306,7 @@
           <t>麻城市</t>
         </is>
       </c>
+      <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
         <v>115.03</v>
       </c>
@@ -41868,6 +42345,7 @@
           <t>蒙阴县</t>
         </is>
       </c>
+      <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>117.93</v>
       </c>
@@ -41906,6 +42384,7 @@
           <t>博山区</t>
         </is>
       </c>
+      <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
         <v>117.86</v>
       </c>
@@ -41944,6 +42423,7 @@
           <t>黄陵县</t>
         </is>
       </c>
+      <c r="E391" t="inlineStr"/>
       <c r="F391" t="n">
         <v>109.26</v>
       </c>
@@ -41982,6 +42462,7 @@
           <t>郁南县</t>
         </is>
       </c>
+      <c r="E392" t="inlineStr"/>
       <c r="F392" t="n">
         <v>111.535921</v>
       </c>
@@ -42020,6 +42501,7 @@
           <t>德庆县</t>
         </is>
       </c>
+      <c r="E393" t="inlineStr"/>
       <c r="F393" t="n">
         <v>111.77</v>
       </c>
@@ -42058,6 +42540,7 @@
           <t>梅县区</t>
         </is>
       </c>
+      <c r="E394" t="inlineStr"/>
       <c r="F394" t="n">
         <v>116.1</v>
       </c>
@@ -42096,6 +42579,7 @@
           <t>连州市</t>
         </is>
       </c>
+      <c r="E395" t="inlineStr"/>
       <c r="F395" t="n">
         <v>112.38</v>
       </c>
@@ -42134,6 +42618,7 @@
           <t>容县</t>
         </is>
       </c>
+      <c r="E396" t="inlineStr"/>
       <c r="F396" t="n">
         <v>110.55</v>
       </c>
@@ -42172,6 +42657,7 @@
           <t>富川瑶族自治县</t>
         </is>
       </c>
+      <c r="E397" t="inlineStr"/>
       <c r="F397" t="n">
         <v>111.28</v>
       </c>
@@ -42210,6 +42696,7 @@
           <t>保城镇</t>
         </is>
       </c>
+      <c r="E398" t="inlineStr"/>
       <c r="F398" t="n">
         <v>109.7</v>
       </c>
@@ -42248,6 +42735,7 @@
           <t>天涯区</t>
         </is>
       </c>
+      <c r="E399" t="inlineStr"/>
       <c r="F399" t="n">
         <v>109.506357</v>
       </c>
@@ -42286,6 +42774,7 @@
           <t>佛罗镇</t>
         </is>
       </c>
+      <c r="E400" t="inlineStr"/>
       <c r="F400" t="n">
         <v>108.98</v>
       </c>
@@ -42324,6 +42813,7 @@
           <t>龙海区</t>
         </is>
       </c>
+      <c r="E401" t="inlineStr"/>
       <c r="F401" t="n">
         <v>117.8</v>
       </c>
@@ -42362,6 +42852,7 @@
           <t>仙游县</t>
         </is>
       </c>
+      <c r="E402" t="inlineStr"/>
       <c r="F402" t="n">
         <v>118.69</v>
       </c>
@@ -42400,6 +42891,7 @@
           <t>顺昌县</t>
         </is>
       </c>
+      <c r="E403" t="inlineStr"/>
       <c r="F403" t="n">
         <v>117.81</v>
       </c>
@@ -42438,6 +42930,7 @@
           <t>浦江县</t>
         </is>
       </c>
+      <c r="E404" t="inlineStr"/>
       <c r="F404" t="n">
         <v>119.89</v>
       </c>
@@ -42476,6 +42969,7 @@
           <t>玉环市</t>
         </is>
       </c>
+      <c r="E405" t="inlineStr"/>
       <c r="F405" t="n">
         <v>121.23</v>
       </c>
@@ -42514,6 +43008,7 @@
           <t>孟连傣族拉祜族佤族自治县</t>
         </is>
       </c>
+      <c r="E406" t="inlineStr"/>
       <c r="F406" t="n">
         <v>99.58</v>
       </c>
@@ -42552,6 +43047,7 @@
           <t>华宁县</t>
         </is>
       </c>
+      <c r="E407" t="inlineStr"/>
       <c r="F407" t="n">
         <v>102.93</v>
       </c>
@@ -42590,6 +43086,7 @@
           <t>高昌区</t>
         </is>
       </c>
+      <c r="E408" t="inlineStr"/>
       <c r="F408" t="n">
         <v>89.19</v>
       </c>
@@ -42628,6 +43125,7 @@
           <t>伊州区</t>
         </is>
       </c>
+      <c r="E409" t="inlineStr"/>
       <c r="F409" t="n">
         <v>93.51000000000001</v>
       </c>
@@ -42666,6 +43164,7 @@
           <t>伽师县</t>
         </is>
       </c>
+      <c r="E410" t="inlineStr"/>
       <c r="F410" t="n">
         <v>76.73</v>
       </c>
@@ -42704,6 +43203,7 @@
           <t>徐闻县</t>
         </is>
       </c>
+      <c r="E411" t="inlineStr"/>
       <c r="F411" t="n">
         <v>110.17</v>
       </c>
@@ -42742,6 +43242,7 @@
           <t>福山镇</t>
         </is>
       </c>
+      <c r="E412" t="inlineStr"/>
       <c r="F412" t="n">
         <v>109.93</v>
       </c>
@@ -42780,6 +43281,7 @@
           <t>元江哈尼族彝族傣族自治县</t>
         </is>
       </c>
+      <c r="E413" t="inlineStr"/>
       <c r="F413" t="n">
         <v>101.999658</v>
       </c>
@@ -42818,6 +43320,7 @@
           <t>新宁县</t>
         </is>
       </c>
+      <c r="E414" t="inlineStr"/>
       <c r="F414" t="n">
         <v>110.859115</v>
       </c>
@@ -42856,6 +43359,7 @@
           <t>吴中区</t>
         </is>
       </c>
+      <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
         <v>120.63</v>
       </c>
@@ -42894,6 +43398,7 @@
           <t>宾川县</t>
         </is>
       </c>
+      <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
         <v>100.58</v>
       </c>
@@ -42932,6 +43437,7 @@
           <t>荔城区</t>
         </is>
       </c>
+      <c r="E417" t="inlineStr"/>
       <c r="F417" t="n">
         <v>119.020047</v>
       </c>
@@ -42970,6 +43476,7 @@
           <t>敖汉旗</t>
         </is>
       </c>
+      <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
         <v>119.92</v>
       </c>
@@ -43008,6 +43515,7 @@
           <t>扎兰屯市</t>
         </is>
       </c>
+      <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
         <v>122.74</v>
       </c>
@@ -43046,6 +43554,7 @@
           <t>攀枝花市</t>
         </is>
       </c>
+      <c r="E420" t="inlineStr"/>
       <c r="F420" t="n">
         <v>101.72</v>
       </c>
@@ -43557,6 +44066,7 @@
           <t>阿克苏市</t>
         </is>
       </c>
+      <c r="E432" t="inlineStr"/>
       <c r="F432" t="n">
         <v>80.26000000000001</v>
       </c>
@@ -43595,6 +44105,7 @@
           <t>新罗区</t>
         </is>
       </c>
+      <c r="E433" t="inlineStr"/>
       <c r="F433" t="n">
         <v>117.02</v>
       </c>
@@ -43633,6 +44144,7 @@
           <t>源城区</t>
         </is>
       </c>
+      <c r="E434" t="inlineStr"/>
       <c r="F434" t="n">
         <v>114.7</v>
       </c>
@@ -43671,6 +44183,7 @@
           <t>都匀市</t>
         </is>
       </c>
+      <c r="E435" t="inlineStr"/>
       <c r="F435" t="n">
         <v>107.52</v>
       </c>
@@ -43709,6 +44222,7 @@
           <t>莎车县</t>
         </is>
       </c>
+      <c r="E436" t="inlineStr"/>
       <c r="F436" t="n">
         <v>76.97595</v>
       </c>
@@ -43747,6 +44261,7 @@
           <t>库车市</t>
         </is>
       </c>
+      <c r="E437" t="inlineStr"/>
       <c r="F437" t="n">
         <v>82.97</v>
       </c>
@@ -43871,6 +44386,7 @@
           <t>波莲镇</t>
         </is>
       </c>
+      <c r="E440" t="inlineStr"/>
       <c r="F440" t="n">
         <v>109.7</v>
       </c>

--- a/fruit_data.xlsx
+++ b/fruit_data.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M458"/>
+  <dimension ref="A1:M464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>莱阳梨</t>
+          <t>秋月梨</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>中国四大名梨之一，国家地理标志产品。果肉细嫩清脆、汁多味甜，明清时期即为贡品。</t>
+          <t>莱阳秋月梨中国四大名梨之一，国家地理标志产品。果肉细嫩清脆、汁多味甜，明清时期即为贡品。</t>
         </is>
       </c>
     </row>
@@ -6177,7 +6177,6 @@
           <t>丹棱县</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>11</v>
       </c>
@@ -6232,7 +6231,6 @@
           <t>丹棱县</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>10</v>
       </c>
@@ -6287,7 +6285,6 @@
           <t>苍溪县</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>8</v>
       </c>
@@ -6342,7 +6339,6 @@
           <t>金川县</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>8</v>
       </c>
@@ -6397,7 +6393,6 @@
           <t>龙泉驿区</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>4</v>
       </c>
@@ -6511,7 +6506,6 @@
           <t>会理市</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>7.9</v>
       </c>
@@ -6566,7 +6560,6 @@
           <t>双流区</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>12</v>
       </c>
@@ -6621,7 +6614,6 @@
           <t>新平县</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>1</v>
       </c>
@@ -6676,7 +6668,6 @@
           <t>新平县</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>10</v>
       </c>
@@ -6731,7 +6722,6 @@
           <t>弥勒市</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>12</v>
       </c>
@@ -6786,7 +6776,6 @@
           <t>宾川县</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>8</v>
       </c>
@@ -6841,7 +6830,6 @@
           <t>华坪县</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>6</v>
       </c>
@@ -6896,7 +6884,6 @@
           <t>丘北县</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>6</v>
       </c>
@@ -6951,7 +6938,6 @@
           <t>昭阳区</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>7</v>
       </c>
@@ -7006,7 +6992,6 @@
           <t>高州市</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>5</v>
       </c>
@@ -7061,7 +7046,6 @@
           <t>增城区</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>6</v>
       </c>
@@ -7116,7 +7100,6 @@
           <t>高州市</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>7</v>
       </c>
@@ -7171,7 +7154,6 @@
           <t>四会市</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>12</v>
       </c>
@@ -7285,7 +7267,6 @@
           <t>高州市</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>11</v>
       </c>
@@ -7340,7 +7321,6 @@
           <t>荔浦市</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>12</v>
       </c>
@@ -7395,7 +7375,6 @@
           <t>田东县</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>6</v>
       </c>
@@ -7450,7 +7429,6 @@
           <t>隆安县</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>5</v>
       </c>
@@ -7505,7 +7483,6 @@
           <t>北流市</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>7</v>
       </c>
@@ -7560,7 +7537,6 @@
           <t>八步区</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>5</v>
       </c>
@@ -7733,7 +7709,6 @@
           <t>麻江县</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>6</v>
       </c>
@@ -7788,7 +7763,6 @@
           <t>罗甸县</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>11</v>
       </c>
@@ -7843,7 +7817,6 @@
           <t>纳雍县</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>4</v>
       </c>
@@ -7898,7 +7871,6 @@
           <t>罗甸县</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>7</v>
       </c>
@@ -7953,7 +7925,6 @@
           <t>乐东黎族自治县</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>1</v>
       </c>
@@ -8008,7 +7979,6 @@
           <t>乐东县</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>9</v>
       </c>
@@ -8063,7 +8033,6 @@
           <t>万宁市</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>2</v>
       </c>
@@ -8118,7 +8087,6 @@
           <t>澄迈县</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>4</v>
       </c>
@@ -8173,7 +8141,6 @@
           <t>琼山区</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>12</v>
       </c>
@@ -8228,7 +8195,6 @@
           <t>乐东县</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
         <v>1</v>
       </c>
@@ -9758,7 +9724,6 @@
           <t>长阳土家族自治县</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
         <v>11</v>
       </c>
@@ -9931,7 +9896,6 @@
           <t>公安县</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
         <v>7</v>
       </c>
@@ -9986,7 +9950,6 @@
           <t>赤壁市</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
         <v>8</v>
       </c>
@@ -10041,7 +10004,6 @@
           <t>建始县</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
         <v>9</v>
       </c>
@@ -10155,7 +10117,6 @@
           <t>宜都市</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
         <v>10</v>
       </c>
@@ -10210,7 +10171,6 @@
           <t>罗田县</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
         <v>8</v>
       </c>
@@ -10265,7 +10225,6 @@
           <t>房县</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
         <v>4</v>
       </c>
@@ -10320,7 +10279,6 @@
           <t>老河口市</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
         <v>6</v>
       </c>
@@ -10375,7 +10333,6 @@
           <t>老河口市</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
         <v>7</v>
       </c>
@@ -10430,7 +10387,6 @@
           <t>兴山县</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
         <v>11</v>
       </c>
@@ -10485,7 +10441,6 @@
           <t>凉城县</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
         <v>8</v>
       </c>
@@ -10540,7 +10495,6 @@
           <t>宁城县</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
         <v>9</v>
       </c>
@@ -10590,8 +10544,6 @@
           <t>乌海市</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
         <v>7</v>
       </c>
@@ -10700,8 +10652,6 @@
           <t>白山市</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
         <v>7</v>
       </c>
@@ -10756,7 +10706,6 @@
           <t>柳河县</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
         <v>8</v>
       </c>
@@ -10811,7 +10760,6 @@
           <t>通化县</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
         <v>7</v>
       </c>
@@ -10861,8 +10809,6 @@
           <t>大兴安岭地区</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
         <v>7</v>
       </c>
@@ -10917,7 +10863,6 @@
           <t>尚志市</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
         <v>7</v>
       </c>
@@ -10972,7 +10917,6 @@
           <t>勃利县</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
         <v>6</v>
       </c>
@@ -11027,7 +10971,6 @@
           <t>穆棱市</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
         <v>9</v>
       </c>
@@ -11082,7 +11025,6 @@
           <t>友好区</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
         <v>7</v>
       </c>
@@ -11132,8 +11074,6 @@
           <t>海西蒙古族藏族自治州</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
         <v>7</v>
       </c>
@@ -11188,7 +11128,6 @@
           <t>乐都区</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
         <v>8</v>
       </c>
@@ -11243,7 +11182,6 @@
           <t>乐都区</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
         <v>6</v>
       </c>
@@ -11298,7 +11236,6 @@
           <t>巴宜区</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
         <v>9</v>
       </c>
@@ -11353,7 +11290,6 @@
           <t>芒康县</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
         <v>8</v>
       </c>
@@ -11408,7 +11344,6 @@
           <t>朗县</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
         <v>9</v>
       </c>
@@ -11522,7 +11457,6 @@
           <t>西峡县</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
         <v>8</v>
       </c>
@@ -11577,7 +11511,6 @@
           <t>肥城市</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
         <v>8</v>
       </c>
@@ -11632,7 +11565,6 @@
           <t>乐陵市</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
         <v>9</v>
       </c>
@@ -11687,7 +11619,6 @@
           <t>威远县</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
         <v>7</v>
       </c>
@@ -11742,7 +11673,6 @@
           <t>炎陵县</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
         <v>6.9</v>
       </c>
@@ -11797,7 +11727,6 @@
           <t>隰县</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
         <v>9</v>
       </c>
@@ -11847,8 +11776,6 @@
           <t>东方市</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
         <v>5</v>
       </c>
@@ -11903,7 +11830,6 @@
           <t>灵武市</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
         <v>9</v>
       </c>
@@ -11958,7 +11884,6 @@
           <t>集安市</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
         <v>8</v>
       </c>
@@ -12008,8 +11933,6 @@
           <t>龙岩市</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
         <v>7</v>
       </c>
@@ -12064,7 +11987,6 @@
           <t>青州市</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr"/>
       <c r="H202" t="n">
         <v>9</v>
       </c>
@@ -12114,8 +12036,6 @@
           <t>威海市</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
       <c r="H203" t="n">
         <v>7</v>
       </c>
@@ -12288,7 +12208,6 @@
           <t>察隅县</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr"/>
       <c r="H206" t="n">
         <v>9</v>
       </c>
@@ -12343,7 +12262,6 @@
           <t>中宁县</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr"/>
       <c r="H207" t="n">
         <v>6</v>
       </c>
@@ -12398,7 +12316,6 @@
           <t>海原县</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr"/>
       <c r="H208" t="n">
         <v>9</v>
       </c>
@@ -12512,7 +12429,6 @@
           <t>怀远县</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr"/>
       <c r="H210" t="n">
         <v>9</v>
       </c>
@@ -12567,7 +12483,6 @@
           <t>萧县</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr"/>
       <c r="H211" t="n">
         <v>7</v>
       </c>
@@ -12622,7 +12537,6 @@
           <t>广丰区</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr"/>
       <c r="H212" t="n">
         <v>11</v>
       </c>
@@ -12677,7 +12591,6 @@
           <t>梁平区</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
       <c r="H213" t="n">
         <v>10</v>
       </c>
@@ -12732,7 +12645,6 @@
           <t>潼南区</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
       <c r="H214" t="n">
         <v>9</v>
       </c>
@@ -12787,7 +12699,6 @@
           <t>磴口县</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr"/>
       <c r="H215" t="n">
         <v>7</v>
       </c>
@@ -12842,7 +12753,6 @@
           <t>鄂伦春自治旗</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
       <c r="H216" t="n">
         <v>7</v>
       </c>
@@ -12897,7 +12807,6 @@
           <t>民和回族土族自治县</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
       <c r="H217" t="n">
         <v>7</v>
       </c>
@@ -12947,8 +12856,6 @@
           <t>琼中黎族苗族自治县</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr"/>
       <c r="H218" t="n">
         <v>10</v>
       </c>
@@ -13062,7 +12969,6 @@
           <t>民勤县</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr"/>
       <c r="H220" t="n">
         <v>7</v>
       </c>
@@ -13117,7 +13023,6 @@
           <t>西峰区</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr"/>
       <c r="H221" t="n">
         <v>9</v>
       </c>
@@ -14650,7 +14555,6 @@
           <t>白水县</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr"/>
       <c r="H247" t="n">
         <v>9</v>
       </c>
@@ -14705,7 +14609,6 @@
           <t>清涧县</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr"/>
       <c r="H248" t="n">
         <v>9</v>
       </c>
@@ -14760,7 +14663,6 @@
           <t>城固县</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr"/>
       <c r="H249" t="n">
         <v>10</v>
       </c>
@@ -14815,7 +14717,6 @@
           <t>彬州市</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr"/>
       <c r="H250" t="n">
         <v>9</v>
       </c>
@@ -14865,8 +14766,6 @@
           <t>延安市</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr"/>
-      <c r="G251" t="inlineStr"/>
       <c r="H251" t="n">
         <v>10</v>
       </c>
@@ -14916,8 +14815,6 @@
           <t>西安市</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
       <c r="H252" t="n">
         <v>12</v>
       </c>
@@ -14972,7 +14869,6 @@
           <t>永春县</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr"/>
       <c r="H253" t="n">
         <v>11</v>
       </c>
@@ -15022,8 +14918,6 @@
           <t>莆田市</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr"/>
-      <c r="G254" t="inlineStr"/>
       <c r="H254" t="n">
         <v>3</v>
       </c>
@@ -15078,7 +14972,6 @@
           <t>闽侯县</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr"/>
       <c r="H255" t="n">
         <v>7</v>
       </c>
@@ -15133,7 +15026,6 @@
           <t>诏安县</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr"/>
       <c r="H256" t="n">
         <v>4</v>
       </c>
@@ -15188,7 +15080,6 @@
           <t>建瓯市</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr"/>
       <c r="H257" t="n">
         <v>9</v>
       </c>
@@ -15243,7 +15134,6 @@
           <t>福鼎市</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr"/>
       <c r="H258" t="n">
         <v>10</v>
       </c>
@@ -15298,7 +15188,6 @@
           <t>长泰区</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr"/>
       <c r="H259" t="n">
         <v>11</v>
       </c>
@@ -15353,7 +15242,6 @@
           <t>闽侯县</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr"/>
       <c r="H260" t="n">
         <v>6</v>
       </c>
@@ -15467,7 +15355,6 @@
           <t>黄岩区</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr"/>
       <c r="H262" t="n">
         <v>10</v>
       </c>
@@ -15522,7 +15409,6 @@
           <t>象山县</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr"/>
       <c r="H263" t="n">
         <v>11</v>
       </c>
@@ -15577,7 +15463,6 @@
           <t>余姚市</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr"/>
       <c r="H264" t="n">
         <v>6</v>
       </c>
@@ -15627,8 +15512,6 @@
           <t>衢州市</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr"/>
       <c r="H265" t="n">
         <v>11</v>
       </c>
@@ -15683,7 +15566,6 @@
           <t>常山县</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr"/>
       <c r="H266" t="n">
         <v>11</v>
       </c>
@@ -15738,7 +15620,6 @@
           <t>桐乡市</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr"/>
       <c r="H267" t="n">
         <v>6</v>
       </c>
@@ -15788,8 +15669,6 @@
           <t>大连市</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr"/>
-      <c r="G268" t="inlineStr"/>
       <c r="H268" t="n">
         <v>5</v>
       </c>
@@ -15839,8 +15718,6 @@
           <t>丹东市</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr"/>
-      <c r="G269" t="inlineStr"/>
       <c r="H269" t="n">
         <v>12</v>
       </c>
@@ -15895,7 +15772,6 @@
           <t>盖州市</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr"/>
       <c r="H270" t="n">
         <v>8</v>
       </c>
@@ -15950,7 +15826,6 @@
           <t>绥中县</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr"/>
       <c r="H271" t="n">
         <v>9</v>
       </c>
@@ -16005,7 +15880,6 @@
           <t>辽中区</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr"/>
       <c r="H272" t="n">
         <v>10</v>
       </c>
@@ -16060,7 +15934,6 @@
           <t>庄河市</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr"/>
       <c r="H273" t="n">
         <v>6</v>
       </c>
@@ -16110,8 +15983,6 @@
           <t>朝阳市</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr"/>
       <c r="H274" t="n">
         <v>9</v>
       </c>
@@ -16161,8 +16032,6 @@
           <t>苏州市</t>
         </is>
       </c>
-      <c r="F275" t="inlineStr"/>
-      <c r="G275" t="inlineStr"/>
       <c r="H275" t="n">
         <v>6</v>
       </c>
@@ -16217,7 +16086,6 @@
           <t>句容市</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr"/>
       <c r="H276" t="n">
         <v>7</v>
       </c>
@@ -16272,7 +16140,6 @@
           <t>吴中区</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr"/>
       <c r="H277" t="n">
         <v>5</v>
       </c>
@@ -16327,7 +16194,6 @@
           <t>丰县</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr"/>
       <c r="H278" t="n">
         <v>9</v>
       </c>
@@ -16382,7 +16248,6 @@
           <t>溧水区</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr"/>
       <c r="H279" t="n">
         <v>12</v>
       </c>
@@ -16437,7 +16302,6 @@
           <t>江都区</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr"/>
       <c r="H280" t="n">
         <v>9</v>
       </c>
@@ -16492,7 +16356,6 @@
           <t>句容市</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr"/>
       <c r="H281" t="n">
         <v>7</v>
       </c>
@@ -16547,7 +16410,6 @@
           <t>秦州区</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr"/>
       <c r="H282" t="n">
         <v>9</v>
       </c>
@@ -16597,8 +16459,6 @@
           <t>兰州市</t>
         </is>
       </c>
-      <c r="F283" t="inlineStr"/>
-      <c r="G283" t="inlineStr"/>
       <c r="H283" t="n">
         <v>9</v>
       </c>
@@ -16653,7 +16513,6 @@
           <t>牡丹江市</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr"/>
       <c r="H284" t="n">
         <v>9</v>
       </c>
@@ -16703,8 +16562,6 @@
           <t>通化市</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr"/>
-      <c r="G285" t="inlineStr"/>
       <c r="H285" t="n">
         <v>9</v>
       </c>
@@ -16754,8 +16611,6 @@
           <t>四平市</t>
         </is>
       </c>
-      <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr"/>
       <c r="H286" t="n">
         <v>9</v>
       </c>
@@ -16810,7 +16665,6 @@
           <t>临猗县</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr"/>
       <c r="H287" t="n">
         <v>10</v>
       </c>
@@ -16860,8 +16714,6 @@
           <t>吕梁市</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr"/>
-      <c r="G288" t="inlineStr"/>
       <c r="H288" t="n">
         <v>9</v>
       </c>
@@ -16911,8 +16763,6 @@
           <t>晋中市</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr"/>
-      <c r="G289" t="inlineStr"/>
       <c r="H289" t="n">
         <v>8</v>
       </c>
@@ -16962,8 +16812,6 @@
           <t>晋城市</t>
         </is>
       </c>
-      <c r="F290" t="inlineStr"/>
-      <c r="G290" t="inlineStr"/>
       <c r="H290" t="n">
         <v>9</v>
       </c>
@@ -17018,7 +16866,6 @@
           <t>万州区</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr"/>
       <c r="H291" t="n">
         <v>10</v>
       </c>
@@ -17073,7 +16920,6 @@
           <t>长寿区</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr"/>
       <c r="H292" t="n">
         <v>11</v>
       </c>
@@ -17128,7 +16974,6 @@
           <t>江津区</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr"/>
       <c r="H293" t="n">
         <v>10</v>
       </c>
@@ -17183,7 +17028,6 @@
           <t>永川区</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr"/>
       <c r="H294" t="n">
         <v>8</v>
       </c>
@@ -17238,7 +17082,6 @@
           <t>忠县</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr"/>
       <c r="H295" t="n">
         <v>10</v>
       </c>
@@ -17288,8 +17131,6 @@
           <t>吴忠市</t>
         </is>
       </c>
-      <c r="F296" t="inlineStr"/>
-      <c r="G296" t="inlineStr"/>
       <c r="H296" t="n">
         <v>8</v>
       </c>
@@ -17339,8 +17180,6 @@
           <t>海东市</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr"/>
-      <c r="G297" t="inlineStr"/>
       <c r="H297" t="n">
         <v>6</v>
       </c>
@@ -17390,8 +17229,6 @@
           <t>海南藏族自治州</t>
         </is>
       </c>
-      <c r="F298" t="inlineStr"/>
-      <c r="G298" t="inlineStr"/>
       <c r="H298" t="n">
         <v>9</v>
       </c>
@@ -17446,7 +17283,6 @@
           <t>磴口县</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr"/>
       <c r="H299" t="n">
         <v>7</v>
       </c>
@@ -17496,8 +17332,6 @@
           <t>赤峰市</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr"/>
-      <c r="G300" t="inlineStr"/>
       <c r="H300" t="n">
         <v>9</v>
       </c>
@@ -17552,7 +17386,6 @@
           <t>昌平区</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr"/>
       <c r="H301" t="n">
         <v>12</v>
       </c>
@@ -17607,7 +17440,6 @@
           <t>密云区</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr"/>
       <c r="H302" t="n">
         <v>5</v>
       </c>
@@ -17662,7 +17494,6 @@
           <t>蓟州区</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr"/>
       <c r="H303" t="n">
         <v>10</v>
       </c>
@@ -17717,7 +17548,6 @@
           <t>滨海新区</t>
         </is>
       </c>
-      <c r="G304" t="inlineStr"/>
       <c r="H304" t="n">
         <v>8</v>
       </c>
@@ -17772,7 +17602,6 @@
           <t>武清区</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr"/>
       <c r="H305" t="n">
         <v>6</v>
       </c>
@@ -17827,7 +17656,6 @@
           <t>崇明区</t>
         </is>
       </c>
-      <c r="G306" t="inlineStr"/>
       <c r="H306" t="n">
         <v>10</v>
       </c>
@@ -17882,7 +17710,6 @@
           <t>嘉定区</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr"/>
       <c r="H307" t="n">
         <v>7</v>
       </c>
@@ -20828,7 +20655,6 @@
           <t>雷波县</t>
         </is>
       </c>
-      <c r="G357" t="inlineStr"/>
       <c r="H357" t="n">
         <v>10.9</v>
       </c>
@@ -20883,7 +20709,6 @@
           <t>盐源县</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr"/>
       <c r="H358" t="n">
         <v>7.9</v>
       </c>
@@ -20938,7 +20763,6 @@
           <t>蒲江县</t>
         </is>
       </c>
-      <c r="G359" t="inlineStr"/>
       <c r="H359" t="n">
         <v>8.9</v>
       </c>
@@ -20993,7 +20817,6 @@
           <t>都江堰市</t>
         </is>
       </c>
-      <c r="G360" t="inlineStr"/>
       <c r="H360" t="n">
         <v>8</v>
       </c>
@@ -21048,7 +20871,6 @@
           <t>米易县</t>
         </is>
       </c>
-      <c r="G361" t="inlineStr"/>
       <c r="H361" t="n">
         <v>12</v>
       </c>
@@ -21103,7 +20925,6 @@
           <t>邻水县</t>
         </is>
       </c>
-      <c r="G362" t="inlineStr"/>
       <c r="H362" t="n">
         <v>11.5</v>
       </c>
@@ -21158,7 +20979,6 @@
           <t>石棉县</t>
         </is>
       </c>
-      <c r="G363" t="inlineStr"/>
       <c r="H363" t="n">
         <v>1</v>
       </c>
@@ -21213,7 +21033,6 @@
           <t>德昌县</t>
         </is>
       </c>
-      <c r="G364" t="inlineStr"/>
       <c r="H364" t="n">
         <v>3.5</v>
       </c>
@@ -21268,7 +21087,6 @@
           <t>江阳区</t>
         </is>
       </c>
-      <c r="G365" t="inlineStr"/>
       <c r="H365" t="n">
         <v>8</v>
       </c>
@@ -21323,7 +21141,6 @@
           <t>大邑县</t>
         </is>
       </c>
-      <c r="G366" t="inlineStr"/>
       <c r="H366" t="n">
         <v>4.5</v>
       </c>
@@ -21378,7 +21195,6 @@
           <t>从江县</t>
         </is>
       </c>
-      <c r="G367" t="inlineStr"/>
       <c r="H367" t="n">
         <v>10</v>
       </c>
@@ -21433,7 +21249,6 @@
           <t>水城区</t>
         </is>
       </c>
-      <c r="G368" t="inlineStr"/>
       <c r="H368" t="n">
         <v>8</v>
       </c>
@@ -21488,7 +21303,6 @@
           <t>威宁彝族回族苗族自治县</t>
         </is>
       </c>
-      <c r="G369" t="inlineStr"/>
       <c r="H369" t="n">
         <v>8</v>
       </c>
@@ -21543,7 +21357,6 @@
           <t>开阳县</t>
         </is>
       </c>
-      <c r="G370" t="inlineStr"/>
       <c r="H370" t="n">
         <v>4</v>
       </c>
@@ -21598,7 +21411,6 @@
           <t>荔波县</t>
         </is>
       </c>
-      <c r="G371" t="inlineStr"/>
       <c r="H371" t="n">
         <v>9</v>
       </c>
@@ -21653,7 +21465,6 @@
           <t>沿河土家族自治县</t>
         </is>
       </c>
-      <c r="G372" t="inlineStr"/>
       <c r="H372" t="n">
         <v>6</v>
       </c>
@@ -21708,7 +21519,6 @@
           <t>敦煌市</t>
         </is>
       </c>
-      <c r="G373" t="inlineStr"/>
       <c r="H373" t="n">
         <v>8</v>
       </c>
@@ -21763,7 +21573,6 @@
           <t>皋兰县</t>
         </is>
       </c>
-      <c r="G374" t="inlineStr"/>
       <c r="H374" t="n">
         <v>1</v>
       </c>
@@ -21818,7 +21627,6 @@
           <t>临泽县</t>
         </is>
       </c>
-      <c r="G375" t="inlineStr"/>
       <c r="H375" t="n">
         <v>8.9</v>
       </c>
@@ -21873,7 +21681,6 @@
           <t>秦安县</t>
         </is>
       </c>
-      <c r="G376" t="inlineStr"/>
       <c r="H376" t="n">
         <v>6</v>
       </c>
@@ -21928,7 +21735,6 @@
           <t>金寨县</t>
         </is>
       </c>
-      <c r="G377" t="inlineStr"/>
       <c r="H377" t="n">
         <v>8</v>
       </c>
@@ -21983,7 +21789,6 @@
           <t>徽州区</t>
         </is>
       </c>
-      <c r="G378" t="inlineStr"/>
       <c r="H378" t="n">
         <v>7</v>
       </c>
@@ -22038,7 +21843,6 @@
           <t>黟县</t>
         </is>
       </c>
-      <c r="G379" t="inlineStr"/>
       <c r="H379" t="n">
         <v>9</v>
       </c>
@@ -22093,7 +21897,6 @@
           <t>万州区</t>
         </is>
       </c>
-      <c r="G380" t="inlineStr"/>
       <c r="H380" t="n">
         <v>12</v>
       </c>
@@ -22148,7 +21951,6 @@
           <t>万州区</t>
         </is>
       </c>
-      <c r="G381" t="inlineStr"/>
       <c r="H381" t="n">
         <v>9</v>
       </c>
@@ -22203,7 +22005,6 @@
           <t>开州区</t>
         </is>
       </c>
-      <c r="G382" t="inlineStr"/>
       <c r="H382" t="n">
         <v>1</v>
       </c>
@@ -22258,7 +22059,6 @@
           <t>黔江区</t>
         </is>
       </c>
-      <c r="G383" t="inlineStr"/>
       <c r="H383" t="n">
         <v>8</v>
       </c>
@@ -22313,7 +22113,6 @@
           <t>璧山区</t>
         </is>
       </c>
-      <c r="G384" t="inlineStr"/>
       <c r="H384" t="n">
         <v>6</v>
       </c>
@@ -22368,7 +22167,6 @@
           <t>集安市</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr"/>
       <c r="H385" t="n">
         <v>7</v>
       </c>
@@ -22423,7 +22221,6 @@
           <t>洮南市</t>
         </is>
       </c>
-      <c r="G386" t="inlineStr"/>
       <c r="H386" t="n">
         <v>6</v>
       </c>
@@ -22478,7 +22275,6 @@
           <t>勃利县</t>
         </is>
       </c>
-      <c r="G387" t="inlineStr"/>
       <c r="H387" t="n">
         <v>7</v>
       </c>
@@ -22533,7 +22329,6 @@
           <t>孙吴县</t>
         </is>
       </c>
-      <c r="G388" t="inlineStr"/>
       <c r="H388" t="n">
         <v>8</v>
       </c>
@@ -22588,7 +22383,6 @@
           <t>宁陵县</t>
         </is>
       </c>
-      <c r="G389" t="inlineStr"/>
       <c r="H389" t="n">
         <v>8</v>
       </c>
@@ -22643,7 +22437,6 @@
           <t>荥阳市</t>
         </is>
       </c>
-      <c r="G390" t="inlineStr"/>
       <c r="H390" t="n">
         <v>9</v>
       </c>
@@ -22698,7 +22491,6 @@
           <t>深州市</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr"/>
       <c r="H391" t="n">
         <v>7</v>
       </c>
@@ -22753,7 +22545,6 @@
           <t>怀来县</t>
         </is>
       </c>
-      <c r="G392" t="inlineStr"/>
       <c r="H392" t="n">
         <v>7</v>
       </c>
@@ -22808,7 +22599,6 @@
           <t>黄骅市</t>
         </is>
       </c>
-      <c r="G393" t="inlineStr"/>
       <c r="H393" t="n">
         <v>9</v>
       </c>
@@ -22863,7 +22653,6 @@
           <t>赵县</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr"/>
       <c r="H394" t="n">
         <v>8</v>
       </c>
@@ -22918,7 +22707,6 @@
           <t>襄汾县</t>
         </is>
       </c>
-      <c r="G395" t="inlineStr"/>
       <c r="H395" t="n">
         <v>8</v>
       </c>
@@ -22973,7 +22761,6 @@
           <t>平陆县</t>
         </is>
       </c>
-      <c r="G396" t="inlineStr"/>
       <c r="H396" t="n">
         <v>9</v>
       </c>
@@ -23028,7 +22815,6 @@
           <t>清徐县</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr"/>
       <c r="H397" t="n">
         <v>7.5</v>
       </c>
@@ -23083,7 +22869,6 @@
           <t>惠山区</t>
         </is>
       </c>
-      <c r="G398" t="inlineStr"/>
       <c r="H398" t="n">
         <v>6.9</v>
       </c>
@@ -23138,7 +22923,6 @@
           <t>句容市</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr"/>
       <c r="H399" t="n">
         <v>7</v>
       </c>
@@ -23193,7 +22977,6 @@
           <t>吴中区</t>
         </is>
       </c>
-      <c r="G400" t="inlineStr"/>
       <c r="H400" t="n">
         <v>4</v>
       </c>
@@ -23248,7 +23031,6 @@
           <t>丰县</t>
         </is>
       </c>
-      <c r="G401" t="inlineStr"/>
       <c r="H401" t="n">
         <v>7.5</v>
       </c>
@@ -23303,7 +23085,6 @@
           <t>凤凰县</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr"/>
       <c r="H402" t="n">
         <v>8</v>
       </c>
@@ -23358,7 +23139,6 @@
           <t>道县</t>
         </is>
       </c>
-      <c r="G403" t="inlineStr"/>
       <c r="H403" t="n">
         <v>10</v>
       </c>
@@ -23413,7 +23193,6 @@
           <t>枣阳市</t>
         </is>
       </c>
-      <c r="G404" t="inlineStr"/>
       <c r="H404" t="n">
         <v>5</v>
       </c>
@@ -23468,7 +23247,6 @@
           <t>麻城市</t>
         </is>
       </c>
-      <c r="G405" t="inlineStr"/>
       <c r="H405" t="n">
         <v>9</v>
       </c>
@@ -23523,7 +23301,6 @@
           <t>蒙阴县</t>
         </is>
       </c>
-      <c r="G406" t="inlineStr"/>
       <c r="H406" t="n">
         <v>5.9</v>
       </c>
@@ -23582,7 +23359,6 @@
           <t>博山区</t>
         </is>
       </c>
-      <c r="G407" t="inlineStr"/>
       <c r="H407" t="n">
         <v>8</v>
       </c>
@@ -23637,7 +23413,6 @@
           <t>黄陵县</t>
         </is>
       </c>
-      <c r="G408" t="inlineStr"/>
       <c r="H408" t="n">
         <v>9</v>
       </c>
@@ -23692,7 +23467,6 @@
           <t>郁南县</t>
         </is>
       </c>
-      <c r="G409" t="inlineStr"/>
       <c r="H409" t="n">
         <v>6</v>
       </c>
@@ -23747,7 +23521,6 @@
           <t>德庆县</t>
         </is>
       </c>
-      <c r="G410" t="inlineStr"/>
       <c r="H410" t="n">
         <v>10</v>
       </c>
@@ -23802,7 +23575,6 @@
           <t>梅县区</t>
         </is>
       </c>
-      <c r="G411" t="inlineStr"/>
       <c r="H411" t="n">
         <v>9</v>
       </c>
@@ -23857,7 +23629,6 @@
           <t>连州市</t>
         </is>
       </c>
-      <c r="G412" t="inlineStr"/>
       <c r="H412" t="n">
         <v>6</v>
       </c>
@@ -23912,7 +23683,6 @@
           <t>容县</t>
         </is>
       </c>
-      <c r="G413" t="inlineStr"/>
       <c r="H413" t="n">
         <v>9</v>
       </c>
@@ -23967,7 +23737,6 @@
           <t>富川瑶族自治县</t>
         </is>
       </c>
-      <c r="G414" t="inlineStr"/>
       <c r="H414" t="n">
         <v>10.9</v>
       </c>
@@ -24022,7 +23791,6 @@
           <t>保城镇</t>
         </is>
       </c>
-      <c r="G415" t="inlineStr"/>
       <c r="H415" t="n">
         <v>5</v>
       </c>
@@ -24077,7 +23845,6 @@
           <t>天涯区</t>
         </is>
       </c>
-      <c r="G416" t="inlineStr"/>
       <c r="H416" t="n">
         <v>12</v>
       </c>
@@ -24132,7 +23899,6 @@
           <t>佛罗镇</t>
         </is>
       </c>
-      <c r="G417" t="inlineStr"/>
       <c r="H417" t="n">
         <v>12</v>
       </c>
@@ -24187,7 +23953,6 @@
           <t>龙海区</t>
         </is>
       </c>
-      <c r="G418" t="inlineStr"/>
       <c r="H418" t="n">
         <v>4</v>
       </c>
@@ -24242,7 +24007,6 @@
           <t>仙游县</t>
         </is>
       </c>
-      <c r="G419" t="inlineStr"/>
       <c r="H419" t="n">
         <v>9.5</v>
       </c>
@@ -24297,7 +24061,6 @@
           <t>顺昌县</t>
         </is>
       </c>
-      <c r="G420" t="inlineStr"/>
       <c r="H420" t="n">
         <v>10.9</v>
       </c>
@@ -24352,7 +24115,6 @@
           <t>浦江县</t>
         </is>
       </c>
-      <c r="G421" t="inlineStr"/>
       <c r="H421" t="n">
         <v>6</v>
       </c>
@@ -24407,7 +24169,6 @@
           <t>玉环市</t>
         </is>
       </c>
-      <c r="G422" t="inlineStr"/>
       <c r="H422" t="n">
         <v>9.5</v>
       </c>
@@ -24462,7 +24223,6 @@
           <t>孟连傣族拉祜族佤族自治县</t>
         </is>
       </c>
-      <c r="G423" t="inlineStr"/>
       <c r="H423" t="n">
         <v>8</v>
       </c>
@@ -24517,7 +24277,6 @@
           <t>华宁县</t>
         </is>
       </c>
-      <c r="G424" t="inlineStr"/>
       <c r="H424" t="n">
         <v>8</v>
       </c>
@@ -24572,7 +24331,6 @@
           <t>高昌区</t>
         </is>
       </c>
-      <c r="G425" t="inlineStr"/>
       <c r="H425" t="n">
         <v>7</v>
       </c>
@@ -24627,7 +24385,6 @@
           <t>伊州区</t>
         </is>
       </c>
-      <c r="G426" t="inlineStr"/>
       <c r="H426" t="n">
         <v>6</v>
       </c>
@@ -24682,7 +24439,6 @@
           <t>伽师县</t>
         </is>
       </c>
-      <c r="G427" t="inlineStr"/>
       <c r="H427" t="n">
         <v>8</v>
       </c>
@@ -24737,7 +24493,6 @@
           <t>徐闻县</t>
         </is>
       </c>
-      <c r="G428" t="inlineStr"/>
       <c r="H428" t="n">
         <v>1</v>
       </c>
@@ -24792,7 +24547,6 @@
           <t>福山镇</t>
         </is>
       </c>
-      <c r="G429" t="inlineStr"/>
       <c r="H429" t="n">
         <v>10</v>
       </c>
@@ -24847,7 +24601,6 @@
           <t>元江哈尼族彝族傣族自治县</t>
         </is>
       </c>
-      <c r="G430" t="inlineStr"/>
       <c r="H430" t="n">
         <v>1</v>
       </c>
@@ -24902,7 +24655,6 @@
           <t>新宁县</t>
         </is>
       </c>
-      <c r="G431" t="inlineStr"/>
       <c r="H431" t="n">
         <v>1</v>
       </c>
@@ -24957,7 +24709,6 @@
           <t>吴中区</t>
         </is>
       </c>
-      <c r="G432" t="inlineStr"/>
       <c r="H432" t="n">
         <v>1</v>
       </c>
@@ -25012,7 +24763,6 @@
           <t>宾川县</t>
         </is>
       </c>
-      <c r="G433" t="inlineStr"/>
       <c r="H433" t="n">
         <v>1</v>
       </c>
@@ -25067,7 +24817,6 @@
           <t>荔城区</t>
         </is>
       </c>
-      <c r="G434" t="inlineStr"/>
       <c r="H434" t="n">
         <v>1</v>
       </c>
@@ -25122,7 +24871,6 @@
           <t>敖汉旗</t>
         </is>
       </c>
-      <c r="G435" t="inlineStr"/>
       <c r="H435" t="n">
         <v>1</v>
       </c>
@@ -25177,7 +24925,6 @@
           <t>扎兰屯市</t>
         </is>
       </c>
-      <c r="G436" t="inlineStr"/>
       <c r="H436" t="n">
         <v>1</v>
       </c>
@@ -25232,7 +24979,6 @@
           <t>攀枝花市</t>
         </is>
       </c>
-      <c r="G437" t="inlineStr"/>
       <c r="H437" t="n">
         <v>6.5</v>
       </c>
@@ -25250,7 +24996,6 @@
           <t>冬季巅峰型</t>
         </is>
       </c>
-      <c r="M437" t="inlineStr"/>
     </row>
     <row r="438" hidden="1">
       <c r="A438" t="inlineStr">
@@ -25932,7 +25677,6 @@
           <t>阿克苏市</t>
         </is>
       </c>
-      <c r="G449" t="inlineStr"/>
       <c r="H449" t="n">
         <v>7</v>
       </c>
@@ -25987,7 +25731,6 @@
           <t>新罗区</t>
         </is>
       </c>
-      <c r="G450" t="inlineStr"/>
       <c r="H450" t="n">
         <v>7</v>
       </c>
@@ -26042,7 +25785,6 @@
           <t>源城区</t>
         </is>
       </c>
-      <c r="G451" t="inlineStr"/>
       <c r="H451" t="n">
         <v>6</v>
       </c>
@@ -26097,7 +25839,6 @@
           <t>琼山区</t>
         </is>
       </c>
-      <c r="G452" t="inlineStr"/>
       <c r="H452" t="n">
         <v>5</v>
       </c>
@@ -26152,7 +25893,6 @@
           <t>都匀市</t>
         </is>
       </c>
-      <c r="G453" t="inlineStr"/>
       <c r="H453" t="n">
         <v>7</v>
       </c>
@@ -26207,7 +25947,6 @@
           <t>莎车县</t>
         </is>
       </c>
-      <c r="G454" t="inlineStr"/>
       <c r="H454" t="n">
         <v>8</v>
       </c>
@@ -26262,7 +26001,6 @@
           <t>库车市</t>
         </is>
       </c>
-      <c r="G455" t="inlineStr"/>
       <c r="H455" t="n">
         <v>8</v>
       </c>
@@ -26435,7 +26173,6 @@
           <t>波莲镇</t>
         </is>
       </c>
-      <c r="G458" t="inlineStr"/>
       <c r="H458" t="n">
         <v>7</v>
       </c>
@@ -26456,6 +26193,355 @@
       <c r="M458" t="inlineStr">
         <is>
           <t>海南临高红心蜜柚，全国名特优新农产品，全国最早熟蜜柚，7月上市，果大皮薄无籽汁多清甜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>F499</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>秋月梨</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>仁果类</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>青岛市</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>莱西市</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>日庄镇</t>
+        </is>
+      </c>
+      <c r="H459" t="n">
+        <v>8</v>
+      </c>
+      <c r="I459" t="n">
+        <v>11</v>
+      </c>
+      <c r="J459" t="n">
+        <v>9</v>
+      </c>
+      <c r="K459" t="n">
+        <v>10</v>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>秋季巅峰型</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>胶东秋月梨核心产区，日庄镇种植两万余亩、年产量约六万吨，果肉细脆、汁多味甜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>F500</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>秋月梨</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>仁果类</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>威海市</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>乳山市</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>崖子镇</t>
+        </is>
+      </c>
+      <c r="H460" t="n">
+        <v>8</v>
+      </c>
+      <c r="I460" t="n">
+        <v>11</v>
+      </c>
+      <c r="J460" t="n">
+        <v>9</v>
+      </c>
+      <c r="K460" t="n">
+        <v>10</v>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>秋季巅峰型</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>胶东产区，崖子镇沟东村2015年自日本引种，昼夜温差大，果品脆甜、糖分充足。</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>F501</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>秋月梨</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>仁果类</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>河北省</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>邢台市</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>巨鹿县</t>
+        </is>
+      </c>
+      <c r="H461" t="n">
+        <v>9</v>
+      </c>
+      <c r="I461" t="n">
+        <v>11</v>
+      </c>
+      <c r="J461" t="n">
+        <v>9</v>
+      </c>
+      <c r="K461" t="n">
+        <v>10</v>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>秋季巅峰型</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>河北主产区，全县种植1.2万余亩、产量超两万吨，果个大、耐储运。</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>F502</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>秋月梨</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>仁果类</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>河北省</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>石家庄市</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>辛集市</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>田家庄乡</t>
+        </is>
+      </c>
+      <c r="H462" t="n">
+        <v>9</v>
+      </c>
+      <c r="I462" t="n">
+        <v>11</v>
+      </c>
+      <c r="J462" t="n">
+        <v>9</v>
+      </c>
+      <c r="K462" t="n">
+        <v>10</v>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>秋季巅峰型</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>河北传统梨区，田家庄乡东张口村引进黄冠、秋月等优新品种，果品优质。</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>F503</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>秋月梨</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>仁果类</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>河南省</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>商丘市</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>宁陵县</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>刘楼乡</t>
+        </is>
+      </c>
+      <c r="H463" t="n">
+        <v>9</v>
+      </c>
+      <c r="I463" t="n">
+        <v>11</v>
+      </c>
+      <c r="J463" t="n">
+        <v>9</v>
+      </c>
+      <c r="K463" t="n">
+        <v>10</v>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>秋季巅峰型</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>黄河故道梨区，刘楼乡陈庄村发展有机秋月梨种植，果肉细脆、风味清甜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>F504</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>秋月梨</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>仁果类</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>河南省</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>商丘市</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>民权县</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>野岗镇</t>
+        </is>
+      </c>
+      <c r="H464" t="n">
+        <v>9</v>
+      </c>
+      <c r="I464" t="n">
+        <v>11</v>
+      </c>
+      <c r="J464" t="n">
+        <v>9</v>
+      </c>
+      <c r="K464" t="n">
+        <v>10</v>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>秋季巅峰型</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>黄河故道特殊地理，野岗镇优质梨种植稳定两万亩，9月初即可采摘上市。</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I440"/>
+  <dimension ref="A1:I446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="13.7265625" customWidth="1" min="1" max="1"/>
@@ -30817,7 +30903,6 @@
           <t>丹棱县</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="n">
         <v>103.53</v>
       </c>
@@ -30856,7 +30941,6 @@
           <t>东坡区</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="n">
         <v>103.83</v>
       </c>
@@ -30895,7 +30979,6 @@
           <t>蒲江县</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="n">
         <v>103.51</v>
       </c>
@@ -30934,7 +31017,6 @@
           <t>金堂县</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="n">
         <v>104.41</v>
       </c>
@@ -30973,7 +31055,6 @@
           <t>名山区</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="n">
         <v>103.11</v>
       </c>
@@ -31012,7 +31093,6 @@
           <t>苍溪县</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="n">
         <v>105.93</v>
       </c>
@@ -31051,7 +31131,6 @@
           <t>金川县</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="n">
         <v>102.06</v>
       </c>
@@ -31090,7 +31169,6 @@
           <t>龙泉驿区</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="n">
         <v>104.27</v>
       </c>
@@ -31129,7 +31207,6 @@
           <t>双流区</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
         <v>103.92</v>
       </c>
@@ -31211,7 +31288,6 @@
           <t>会理市</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="n">
         <v>102.25</v>
       </c>
@@ -31250,7 +31326,6 @@
           <t>新平县</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
       <c r="F112" t="n">
         <v>101.99</v>
       </c>
@@ -31289,7 +31364,6 @@
           <t>华宁县</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="n">
         <v>102.93</v>
       </c>
@@ -31328,7 +31402,6 @@
           <t>弥勒市</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="n">
         <v>103.41</v>
       </c>
@@ -31367,7 +31440,6 @@
           <t>沾益区</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="n">
         <v>103.82</v>
       </c>
@@ -31406,7 +31478,6 @@
           <t>澄江市</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="n">
         <v>102.91</v>
       </c>
@@ -31445,7 +31516,6 @@
           <t>大理州</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
         <v>100.23</v>
       </c>
@@ -31484,7 +31554,6 @@
           <t>蒙自市</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
         <v>103.36</v>
       </c>
@@ -31523,7 +31592,6 @@
           <t>永仁县</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
         <v>101.67</v>
       </c>
@@ -31562,7 +31630,6 @@
           <t>华坪县</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
         <v>101.27</v>
       </c>
@@ -31601,7 +31668,6 @@
           <t>元阳县</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
         <v>102.83</v>
       </c>
@@ -31640,7 +31706,6 @@
           <t>永德县</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
         <v>99.26000000000001</v>
       </c>
@@ -31679,7 +31744,6 @@
           <t>丘北县</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
         <v>104.19</v>
       </c>
@@ -31718,7 +31782,6 @@
           <t>开远市</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
         <v>103.27</v>
       </c>
@@ -31757,7 +31820,6 @@
           <t>富民县</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="n">
         <v>102.5</v>
       </c>
@@ -31796,7 +31858,6 @@
           <t>昭阳区</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
         <v>103.71</v>
       </c>
@@ -31835,7 +31896,6 @@
           <t>高州市</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
         <v>110.85</v>
       </c>
@@ -31874,7 +31934,6 @@
           <t>增城区</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="n">
         <v>113.81</v>
       </c>
@@ -31913,7 +31972,6 @@
           <t>阳东区</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="n">
         <v>112.01</v>
       </c>
@@ -31952,7 +32010,6 @@
           <t>四会市</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
       <c r="F130" t="n">
         <v>112.73</v>
       </c>
@@ -31991,7 +32048,6 @@
           <t>清远市</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
       <c r="F131" t="n">
         <v>113.06</v>
       </c>
@@ -32030,7 +32086,6 @@
           <t>徐闻县</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
       <c r="F132" t="n">
         <v>110.18</v>
       </c>
@@ -32069,7 +32124,6 @@
           <t>荔浦市</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="n">
         <v>110.39</v>
       </c>
@@ -32108,7 +32162,6 @@
           <t>蒙山县</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="n">
         <v>110.52</v>
       </c>
@@ -32147,7 +32200,6 @@
           <t>象州县</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="n">
         <v>109.68</v>
       </c>
@@ -32186,7 +32238,6 @@
           <t>田东县</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
       <c r="F136" t="n">
         <v>107.12</v>
       </c>
@@ -32225,7 +32276,6 @@
           <t>隆安县</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
       <c r="F137" t="n">
         <v>107.7</v>
       </c>
@@ -32264,7 +32314,6 @@
           <t>扶绥县</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
       <c r="F138" t="n">
         <v>107.9</v>
       </c>
@@ -32303,7 +32352,6 @@
           <t>北流市</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" t="n">
         <v>110.35</v>
       </c>
@@ -32342,7 +32390,6 @@
           <t>钦州市</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
       <c r="F140" t="n">
         <v>108.65</v>
       </c>
@@ -32381,7 +32428,6 @@
           <t>崇左市</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
       <c r="F141" t="n">
         <v>107.35</v>
       </c>
@@ -32420,7 +32466,6 @@
           <t>八步区</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
         <v>111.55</v>
       </c>
@@ -32459,7 +32504,6 @@
           <t>浦北县</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
         <v>109.56</v>
       </c>
@@ -32498,7 +32542,6 @@
           <t>天峨县</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
         <v>107.17</v>
       </c>
@@ -32537,7 +32580,6 @@
           <t>紫云县</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
         <v>106.08</v>
       </c>
@@ -32576,7 +32618,6 @@
           <t>麻江县</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
         <v>107.59</v>
       </c>
@@ -32615,7 +32656,6 @@
           <t>龙里县</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
       <c r="F147" t="n">
         <v>106.98</v>
       </c>
@@ -32654,7 +32694,6 @@
           <t>罗甸县</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
       <c r="F148" t="n">
         <v>106.75</v>
       </c>
@@ -32693,7 +32732,6 @@
           <t>纳雍县</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
       <c r="F149" t="n">
         <v>105.38</v>
       </c>
@@ -32732,7 +32770,6 @@
           <t>六盘水市</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
       <c r="F150" t="n">
         <v>104.83</v>
       </c>
@@ -32771,7 +32808,6 @@
           <t>贞丰县</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
       <c r="F151" t="n">
         <v>105.65</v>
       </c>
@@ -32810,7 +32846,6 @@
           <t>三亚市</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
       <c r="F152" t="n">
         <v>109.51</v>
       </c>
@@ -32849,7 +32884,6 @@
           <t>陵水县</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
       <c r="F153" t="n">
         <v>110.04</v>
       </c>
@@ -32888,7 +32922,6 @@
           <t>澄迈县</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
       <c r="F154" t="n">
         <v>110</v>
       </c>
@@ -32927,7 +32960,6 @@
           <t>琼海市</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr"/>
       <c r="F155" t="n">
         <v>110.47</v>
       </c>
@@ -32966,7 +32998,6 @@
           <t>万宁市</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
         <v>110.39</v>
       </c>
@@ -33005,7 +33036,6 @@
           <t>海口市</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
         <v>110.2</v>
       </c>
@@ -33044,7 +33074,6 @@
           <t>琼山区</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>110.35</v>
       </c>
@@ -33083,7 +33112,6 @@
           <t>文昌市</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
         <v>110.8</v>
       </c>
@@ -33122,7 +33150,6 @@
           <t>石棉县</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
         <v>102.36</v>
       </c>
@@ -34236,7 +34263,6 @@
           <t>长阳土家族自治县</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
         <v>111.20105</v>
       </c>
@@ -34361,7 +34387,6 @@
           <t>公安县</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr"/>
       <c r="F189" t="n">
         <v>112.23242</v>
       </c>
@@ -34400,7 +34425,6 @@
           <t>赤壁市</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr"/>
       <c r="F190" t="n">
         <v>113.90039</v>
       </c>
@@ -34439,7 +34463,6 @@
           <t>建始县</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr"/>
       <c r="F191" t="n">
         <v>109.7182</v>
       </c>
@@ -34521,7 +34544,6 @@
           <t>宜都市</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr"/>
       <c r="F193" t="n">
         <v>111.45025</v>
       </c>
@@ -34560,7 +34582,6 @@
           <t>罗田县</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr"/>
       <c r="F194" t="n">
         <v>115.39056</v>
       </c>
@@ -34599,7 +34620,6 @@
           <t>房县</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr"/>
       <c r="F195" t="n">
         <v>110.73333</v>
       </c>
@@ -34638,7 +34658,6 @@
           <t>老河口市</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
       <c r="F196" t="n">
         <v>111.66944</v>
       </c>
@@ -34677,7 +34696,6 @@
           <t>老河口市</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr"/>
       <c r="F197" t="n">
         <v>111.66944</v>
       </c>
@@ -34716,7 +34734,6 @@
           <t>兴山县</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr"/>
       <c r="F198" t="n">
         <v>110.74951</v>
       </c>
@@ -34755,7 +34772,6 @@
           <t>凉城县</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr"/>
       <c r="F199" t="n">
         <v>112.5</v>
       </c>
@@ -34794,7 +34810,6 @@
           <t>宁城县</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr"/>
       <c r="F200" t="n">
         <v>119.33333</v>
       </c>
@@ -34828,8 +34843,6 @@
           <t>乌海市</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr"/>
       <c r="F201" t="n">
         <v>106.8</v>
       </c>
@@ -34868,7 +34881,6 @@
           <t>延吉市</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr"/>
       <c r="F202" t="n">
         <v>129.5</v>
       </c>
@@ -34902,8 +34914,6 @@
           <t>白山市</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr"/>
       <c r="F203" t="n">
         <v>126.41667</v>
       </c>
@@ -34942,7 +34952,6 @@
           <t>柳河县</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr"/>
       <c r="F204" t="n">
         <v>125.74475</v>
       </c>
@@ -34981,7 +34990,6 @@
           <t>通化县</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr"/>
       <c r="F205" t="n">
         <v>125.75936</v>
       </c>
@@ -35015,8 +35023,6 @@
           <t>大兴安岭地区</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
       <c r="F206" t="n">
         <v>124.11667</v>
       </c>
@@ -35055,7 +35061,6 @@
           <t>尚志市</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr"/>
       <c r="F207" t="n">
         <v>127.96194</v>
       </c>
@@ -35094,7 +35099,6 @@
           <t>勃利县</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
       <c r="F208" t="n">
         <v>130.56806</v>
       </c>
@@ -35133,7 +35137,6 @@
           <t>穆棱市</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr"/>
       <c r="F209" t="n">
         <v>130.51667</v>
       </c>
@@ -35167,8 +35170,6 @@
           <t>伊春市</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
       <c r="F210" t="n">
         <v>128.84</v>
       </c>
@@ -35202,8 +35203,6 @@
           <t>海西蒙古族藏族自治州</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr"/>
       <c r="F211" t="n">
         <v>97.36667</v>
       </c>
@@ -35242,7 +35241,6 @@
           <t>乐都区</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr"/>
       <c r="F212" t="n">
         <v>102.4</v>
       </c>
@@ -35281,7 +35279,6 @@
           <t>乐都区</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr"/>
       <c r="F213" t="n">
         <v>102.4</v>
       </c>
@@ -35320,7 +35317,6 @@
           <t>芒康县</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr"/>
       <c r="F214" t="n">
         <v>98.59999999999999</v>
       </c>
@@ -35359,7 +35355,6 @@
           <t>朗县</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr"/>
       <c r="F215" t="n">
         <v>93.06667</v>
       </c>
@@ -35441,7 +35436,6 @@
           <t>西峡县</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr"/>
       <c r="F217" t="n">
         <v>111.47917</v>
       </c>
@@ -35480,7 +35474,6 @@
           <t>肥城市</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr"/>
       <c r="F218" t="n">
         <v>116.65</v>
       </c>
@@ -35519,7 +35512,6 @@
           <t>乐陵市</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr"/>
       <c r="F219" t="n">
         <v>117.216657</v>
       </c>
@@ -35558,7 +35550,6 @@
           <t>威远县</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
       <c r="F220" t="n">
         <v>104.66667</v>
       </c>
@@ -35597,7 +35588,6 @@
           <t>炎陵县</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr"/>
       <c r="F221" t="n">
         <v>113.76667</v>
       </c>
@@ -35636,7 +35626,6 @@
           <t>隰县</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr"/>
       <c r="F222" t="n">
         <v>110.93333</v>
       </c>
@@ -35670,8 +35659,6 @@
           <t>东方市</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr"/>
       <c r="F223" t="n">
         <v>108.63333</v>
       </c>
@@ -35710,7 +35697,6 @@
           <t>灵武市</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr"/>
       <c r="F224" t="n">
         <v>106.33333</v>
       </c>
@@ -35749,7 +35735,6 @@
           <t>集安市</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr"/>
       <c r="F225" t="n">
         <v>126.18829</v>
       </c>
@@ -35783,8 +35768,6 @@
           <t>龙岩市</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr"/>
       <c r="F226" t="n">
         <v>117.01667</v>
       </c>
@@ -35823,7 +35806,6 @@
           <t>青州市</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr"/>
       <c r="F227" t="n">
         <v>118.46667</v>
       </c>
@@ -35857,8 +35839,6 @@
           <t>威海市</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr"/>
       <c r="F228" t="n">
         <v>122.11667</v>
       </c>
@@ -35983,7 +35963,6 @@
           <t>巴宜区</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr"/>
       <c r="F231" t="n">
         <v>94.361</v>
       </c>
@@ -36022,7 +36001,6 @@
           <t>察隅县</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
       <c r="F232" t="n">
         <v>97.465</v>
       </c>
@@ -36061,7 +36039,6 @@
           <t>中宁县</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
         <v>105.685</v>
       </c>
@@ -36100,7 +36077,6 @@
           <t>海原县</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
         <v>105.643</v>
       </c>
@@ -36182,7 +36158,6 @@
           <t>怀远县</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
         <v>117.205</v>
       </c>
@@ -36221,7 +36196,6 @@
           <t>萧县</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
         <v>116.947</v>
       </c>
@@ -36260,7 +36234,6 @@
           <t>广丰区</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
         <v>118.191</v>
       </c>
@@ -36299,7 +36272,6 @@
           <t>梁平区</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
         <v>107.802</v>
       </c>
@@ -36338,7 +36310,6 @@
           <t>潼南区</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
         <v>105.84</v>
       </c>
@@ -36377,7 +36348,6 @@
           <t>磴口县</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>107.008</v>
       </c>
@@ -36416,7 +36386,6 @@
           <t>鄂伦春自治旗</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
         <v>123.726</v>
       </c>
@@ -36455,7 +36424,6 @@
           <t>民和回族土族自治县</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
         <v>102.83</v>
       </c>
@@ -36494,7 +36462,6 @@
           <t>尚志市</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
         <v>127.961</v>
       </c>
@@ -36533,7 +36500,6 @@
           <t>友好区</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr"/>
       <c r="F245" t="n">
         <v>128.841</v>
       </c>
@@ -36572,7 +36538,6 @@
           <t>天涯区</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr"/>
       <c r="F246" t="n">
         <v>109.506</v>
       </c>
@@ -36606,8 +36571,6 @@
           <t>琼中黎族苗族自治县</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
-      <c r="E247" t="inlineStr"/>
       <c r="F247" t="n">
         <v>109.838</v>
       </c>
@@ -36641,7 +36604,6 @@
           <t>文昌市</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>东郊镇</t>
@@ -36685,7 +36647,6 @@
           <t>西峰区</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr"/>
       <c r="F249" t="n">
         <v>107.651</v>
       </c>
@@ -37756,7 +37717,6 @@
           <t>白水县</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr"/>
       <c r="F274" t="n">
         <v>109.59</v>
       </c>
@@ -37795,7 +37755,6 @@
           <t>彬州市</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr"/>
       <c r="F275" t="n">
         <v>108.08</v>
       </c>
@@ -37834,7 +37793,6 @@
           <t>永春县</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr"/>
       <c r="F276" t="n">
         <v>118.29</v>
       </c>
@@ -37873,7 +37831,6 @@
           <t>诏安县</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr"/>
       <c r="F277" t="n">
         <v>117.18</v>
       </c>
@@ -37955,7 +37912,6 @@
           <t>黄岩区</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr"/>
       <c r="F279" t="n">
         <v>121.26</v>
       </c>
@@ -37994,7 +37950,6 @@
           <t>余姚市</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr"/>
       <c r="F280" t="n">
         <v>121.16</v>
       </c>
@@ -38033,7 +37988,6 @@
           <t>常山县</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr"/>
       <c r="F281" t="n">
         <v>118.51</v>
       </c>
@@ -38067,8 +38021,6 @@
           <t>大连市</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
-      <c r="E282" t="inlineStr"/>
       <c r="F282" t="n">
         <v>121.61</v>
       </c>
@@ -38107,7 +38059,6 @@
           <t>盖州市</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr"/>
       <c r="F283" t="n">
         <v>122.35</v>
       </c>
@@ -38146,7 +38097,6 @@
           <t>辽中区</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr"/>
       <c r="F284" t="n">
         <v>122.73</v>
       </c>
@@ -38180,8 +38130,6 @@
           <t>苏州市</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
-      <c r="E285" t="inlineStr"/>
       <c r="F285" t="n">
         <v>120.63</v>
       </c>
@@ -38220,7 +38168,6 @@
           <t>句容市</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr"/>
       <c r="F286" t="n">
         <v>119.16</v>
       </c>
@@ -38259,7 +38206,6 @@
           <t>吴中区</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr"/>
       <c r="F287" t="n">
         <v>120.63</v>
       </c>
@@ -38298,7 +38244,6 @@
           <t>江都区</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr"/>
       <c r="F288" t="n">
         <v>119.57</v>
       </c>
@@ -38337,7 +38282,6 @@
           <t>牡丹江市</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr"/>
       <c r="F289" t="n">
         <v>129.63</v>
       </c>
@@ -38371,8 +38315,6 @@
           <t>通化市</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr"/>
       <c r="F290" t="n">
         <v>125.94</v>
       </c>
@@ -38411,7 +38353,6 @@
           <t>临猗县</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr"/>
       <c r="F291" t="n">
         <v>110.77</v>
       </c>
@@ -38445,8 +38386,6 @@
           <t>晋城市</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr"/>
       <c r="F292" t="n">
         <v>112.85</v>
       </c>
@@ -38485,7 +38424,6 @@
           <t>长寿区</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr"/>
       <c r="F293" t="n">
         <v>107.08</v>
       </c>
@@ -38524,7 +38462,6 @@
           <t>永川区</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr"/>
       <c r="F294" t="n">
         <v>105.89</v>
       </c>
@@ -38558,8 +38495,6 @@
           <t>吴忠市</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr"/>
       <c r="F295" t="n">
         <v>106.2</v>
       </c>
@@ -38593,8 +38528,6 @@
           <t>海东市</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
-      <c r="E296" t="inlineStr"/>
       <c r="F296" t="n">
         <v>102.1</v>
       </c>
@@ -38633,7 +38566,6 @@
           <t>磴口县</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
         <v>107.01</v>
       </c>
@@ -38667,8 +38599,6 @@
           <t>赤峰市</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
-      <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
         <v>118.89</v>
       </c>
@@ -38707,7 +38637,6 @@
           <t>密云区</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
         <v>116.84</v>
       </c>
@@ -38746,7 +38675,6 @@
           <t>滨海新区</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>117.65</v>
       </c>
@@ -38785,7 +38713,6 @@
           <t>嘉定区</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
         <v>121.27</v>
       </c>
@@ -38824,7 +38751,6 @@
           <t>民和回族土族自治县</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>102.83</v>
       </c>
@@ -38863,7 +38789,6 @@
           <t>友好区</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
         <v>128.84</v>
       </c>
@@ -38897,8 +38822,6 @@
           <t>琼中黎族苗族自治县</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
-      <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
         <v>109.84</v>
       </c>
@@ -38980,7 +38903,6 @@
           <t>民勤县</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
         <v>103.1</v>
       </c>
@@ -39019,7 +38941,6 @@
           <t>西峰区</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr"/>
       <c r="F307" t="n">
         <v>107.65</v>
       </c>
@@ -40434,7 +40355,6 @@
           <t>雷波县</t>
         </is>
       </c>
-      <c r="E340" t="inlineStr"/>
       <c r="F340" t="n">
         <v>103.57</v>
       </c>
@@ -40473,7 +40393,6 @@
           <t>盐源县</t>
         </is>
       </c>
-      <c r="E341" t="inlineStr"/>
       <c r="F341" t="n">
         <v>101.51</v>
       </c>
@@ -40512,7 +40431,6 @@
           <t>蒲江县</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr"/>
       <c r="F342" t="n">
         <v>103.54</v>
       </c>
@@ -40551,7 +40469,6 @@
           <t>都江堰市</t>
         </is>
       </c>
-      <c r="E343" t="inlineStr"/>
       <c r="F343" t="n">
         <v>103.62</v>
       </c>
@@ -40590,7 +40507,6 @@
           <t>米易县</t>
         </is>
       </c>
-      <c r="E344" t="inlineStr"/>
       <c r="F344" t="n">
         <v>102.11</v>
       </c>
@@ -40629,7 +40545,6 @@
           <t>邻水县</t>
         </is>
       </c>
-      <c r="E345" t="inlineStr"/>
       <c r="F345" t="n">
         <v>106.93</v>
       </c>
@@ -40668,7 +40583,6 @@
           <t>石棉县</t>
         </is>
       </c>
-      <c r="E346" t="inlineStr"/>
       <c r="F346" t="n">
         <v>102.36</v>
       </c>
@@ -40707,7 +40621,6 @@
           <t>德昌县</t>
         </is>
       </c>
-      <c r="E347" t="inlineStr"/>
       <c r="F347" t="n">
         <v>102.18</v>
       </c>
@@ -40746,7 +40659,6 @@
           <t>江阳区</t>
         </is>
       </c>
-      <c r="E348" t="inlineStr"/>
       <c r="F348" t="n">
         <v>105.44</v>
       </c>
@@ -40785,7 +40697,6 @@
           <t>大邑县</t>
         </is>
       </c>
-      <c r="E349" t="inlineStr"/>
       <c r="F349" t="n">
         <v>103.52</v>
       </c>
@@ -40824,7 +40735,6 @@
           <t>从江县</t>
         </is>
       </c>
-      <c r="E350" t="inlineStr"/>
       <c r="F350" t="n">
         <v>108.9</v>
       </c>
@@ -40863,7 +40773,6 @@
           <t>水城区</t>
         </is>
       </c>
-      <c r="E351" t="inlineStr"/>
       <c r="F351" t="n">
         <v>104.95685</v>
       </c>
@@ -40902,7 +40811,6 @@
           <t>威宁彝族回族苗族自治县</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr"/>
       <c r="F352" t="n">
         <v>104.28</v>
       </c>
@@ -40941,7 +40849,6 @@
           <t>开阳县</t>
         </is>
       </c>
-      <c r="E353" t="inlineStr"/>
       <c r="F353" t="n">
         <v>106.97</v>
       </c>
@@ -40980,7 +40887,6 @@
           <t>荔波县</t>
         </is>
       </c>
-      <c r="E354" t="inlineStr"/>
       <c r="F354" t="n">
         <v>107.88</v>
       </c>
@@ -41019,7 +40925,6 @@
           <t>沿河土家族自治县</t>
         </is>
       </c>
-      <c r="E355" t="inlineStr"/>
       <c r="F355" t="n">
         <v>108.5</v>
       </c>
@@ -41058,7 +40963,6 @@
           <t>敦煌市</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr"/>
       <c r="F356" t="n">
         <v>94.66</v>
       </c>
@@ -41097,7 +41001,6 @@
           <t>皋兰县</t>
         </is>
       </c>
-      <c r="E357" t="inlineStr"/>
       <c r="F357" t="n">
         <v>103.95</v>
       </c>
@@ -41136,7 +41039,6 @@
           <t>临泽县</t>
         </is>
       </c>
-      <c r="E358" t="inlineStr"/>
       <c r="F358" t="n">
         <v>100.16</v>
       </c>
@@ -41175,7 +41077,6 @@
           <t>秦安县</t>
         </is>
       </c>
-      <c r="E359" t="inlineStr"/>
       <c r="F359" t="n">
         <v>105.67</v>
       </c>
@@ -41214,7 +41115,6 @@
           <t>金寨县</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr"/>
       <c r="F360" t="n">
         <v>115.93</v>
       </c>
@@ -41253,7 +41153,6 @@
           <t>徽州区</t>
         </is>
       </c>
-      <c r="E361" t="inlineStr"/>
       <c r="F361" t="n">
         <v>118.34</v>
       </c>
@@ -41292,7 +41191,6 @@
           <t>黟县</t>
         </is>
       </c>
-      <c r="E362" t="inlineStr"/>
       <c r="F362" t="n">
         <v>117.94</v>
       </c>
@@ -41331,7 +41229,6 @@
           <t>万州区</t>
         </is>
       </c>
-      <c r="E363" t="inlineStr"/>
       <c r="F363" t="n">
         <v>108.41</v>
       </c>
@@ -41370,7 +41267,6 @@
           <t>万州区</t>
         </is>
       </c>
-      <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
         <v>108.41</v>
       </c>
@@ -41409,7 +41305,6 @@
           <t>开州区</t>
         </is>
       </c>
-      <c r="E365" t="inlineStr"/>
       <c r="F365" t="n">
         <v>108.42</v>
       </c>
@@ -41448,7 +41343,6 @@
           <t>黔江区</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
         <v>108.77</v>
       </c>
@@ -41487,7 +41381,6 @@
           <t>璧山区</t>
         </is>
       </c>
-      <c r="E367" t="inlineStr"/>
       <c r="F367" t="n">
         <v>106.23</v>
       </c>
@@ -41526,7 +41419,6 @@
           <t>集安市</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr"/>
       <c r="F368" t="n">
         <v>126.18</v>
       </c>
@@ -41565,7 +41457,6 @@
           <t>洮南市</t>
         </is>
       </c>
-      <c r="E369" t="inlineStr"/>
       <c r="F369" t="n">
         <v>122.78</v>
       </c>
@@ -41604,7 +41495,6 @@
           <t>勃利县</t>
         </is>
       </c>
-      <c r="E370" t="inlineStr"/>
       <c r="F370" t="n">
         <v>130.57</v>
       </c>
@@ -41643,7 +41533,6 @@
           <t>孙吴县</t>
         </is>
       </c>
-      <c r="E371" t="inlineStr"/>
       <c r="F371" t="n">
         <v>127.33</v>
       </c>
@@ -41682,7 +41571,6 @@
           <t>宁陵县</t>
         </is>
       </c>
-      <c r="E372" t="inlineStr"/>
       <c r="F372" t="n">
         <v>115.32</v>
       </c>
@@ -41721,7 +41609,6 @@
           <t>荥阳市</t>
         </is>
       </c>
-      <c r="E373" t="inlineStr"/>
       <c r="F373" t="n">
         <v>113.38</v>
       </c>
@@ -41760,7 +41647,6 @@
           <t>深州市</t>
         </is>
       </c>
-      <c r="E374" t="inlineStr"/>
       <c r="F374" t="n">
         <v>115.56</v>
       </c>
@@ -41799,7 +41685,6 @@
           <t>怀来县</t>
         </is>
       </c>
-      <c r="E375" t="inlineStr"/>
       <c r="F375" t="n">
         <v>115.52</v>
       </c>
@@ -41838,7 +41723,6 @@
           <t>黄骅市</t>
         </is>
       </c>
-      <c r="E376" t="inlineStr"/>
       <c r="F376" t="n">
         <v>117.35</v>
       </c>
@@ -41877,7 +41761,6 @@
           <t>赵县</t>
         </is>
       </c>
-      <c r="E377" t="inlineStr"/>
       <c r="F377" t="n">
         <v>114.78</v>
       </c>
@@ -41916,7 +41799,6 @@
           <t>襄汾县</t>
         </is>
       </c>
-      <c r="E378" t="inlineStr"/>
       <c r="F378" t="n">
         <v>111.44</v>
       </c>
@@ -41955,7 +41837,6 @@
           <t>平陆县</t>
         </is>
       </c>
-      <c r="E379" t="inlineStr"/>
       <c r="F379" t="n">
         <v>111.22</v>
       </c>
@@ -41994,7 +41875,6 @@
           <t>清徐县</t>
         </is>
       </c>
-      <c r="E380" t="inlineStr"/>
       <c r="F380" t="n">
         <v>112.35</v>
       </c>
@@ -42033,7 +41913,6 @@
           <t>惠山区</t>
         </is>
       </c>
-      <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
         <v>120.303543</v>
       </c>
@@ -42072,7 +41951,6 @@
           <t>句容市</t>
         </is>
       </c>
-      <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
         <v>119.16</v>
       </c>
@@ -42111,7 +41989,6 @@
           <t>吴中区</t>
         </is>
       </c>
-      <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
         <v>120.4</v>
       </c>
@@ -42150,7 +42027,6 @@
           <t>丰县</t>
         </is>
       </c>
-      <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
         <v>116.6</v>
       </c>
@@ -42189,7 +42065,6 @@
           <t>凤凰县</t>
         </is>
       </c>
-      <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>109.6</v>
       </c>
@@ -42228,7 +42103,6 @@
           <t>道县</t>
         </is>
       </c>
-      <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
         <v>111.6</v>
       </c>
@@ -42267,7 +42141,6 @@
           <t>枣阳市</t>
         </is>
       </c>
-      <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
         <v>112.77</v>
       </c>
@@ -42306,7 +42179,6 @@
           <t>麻城市</t>
         </is>
       </c>
-      <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
         <v>115.03</v>
       </c>
@@ -42345,7 +42217,6 @@
           <t>蒙阴县</t>
         </is>
       </c>
-      <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>117.93</v>
       </c>
@@ -42384,7 +42255,6 @@
           <t>博山区</t>
         </is>
       </c>
-      <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
         <v>117.86</v>
       </c>
@@ -42423,7 +42293,6 @@
           <t>黄陵县</t>
         </is>
       </c>
-      <c r="E391" t="inlineStr"/>
       <c r="F391" t="n">
         <v>109.26</v>
       </c>
@@ -42462,7 +42331,6 @@
           <t>郁南县</t>
         </is>
       </c>
-      <c r="E392" t="inlineStr"/>
       <c r="F392" t="n">
         <v>111.535921</v>
       </c>
@@ -42501,7 +42369,6 @@
           <t>德庆县</t>
         </is>
       </c>
-      <c r="E393" t="inlineStr"/>
       <c r="F393" t="n">
         <v>111.77</v>
       </c>
@@ -42540,7 +42407,6 @@
           <t>梅县区</t>
         </is>
       </c>
-      <c r="E394" t="inlineStr"/>
       <c r="F394" t="n">
         <v>116.1</v>
       </c>
@@ -42579,7 +42445,6 @@
           <t>连州市</t>
         </is>
       </c>
-      <c r="E395" t="inlineStr"/>
       <c r="F395" t="n">
         <v>112.38</v>
       </c>
@@ -42618,7 +42483,6 @@
           <t>容县</t>
         </is>
       </c>
-      <c r="E396" t="inlineStr"/>
       <c r="F396" t="n">
         <v>110.55</v>
       </c>
@@ -42657,7 +42521,6 @@
           <t>富川瑶族自治县</t>
         </is>
       </c>
-      <c r="E397" t="inlineStr"/>
       <c r="F397" t="n">
         <v>111.28</v>
       </c>
@@ -42696,7 +42559,6 @@
           <t>保城镇</t>
         </is>
       </c>
-      <c r="E398" t="inlineStr"/>
       <c r="F398" t="n">
         <v>109.7</v>
       </c>
@@ -42735,7 +42597,6 @@
           <t>天涯区</t>
         </is>
       </c>
-      <c r="E399" t="inlineStr"/>
       <c r="F399" t="n">
         <v>109.506357</v>
       </c>
@@ -42774,7 +42635,6 @@
           <t>佛罗镇</t>
         </is>
       </c>
-      <c r="E400" t="inlineStr"/>
       <c r="F400" t="n">
         <v>108.98</v>
       </c>
@@ -42813,7 +42673,6 @@
           <t>龙海区</t>
         </is>
       </c>
-      <c r="E401" t="inlineStr"/>
       <c r="F401" t="n">
         <v>117.8</v>
       </c>
@@ -42852,7 +42711,6 @@
           <t>仙游县</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr"/>
       <c r="F402" t="n">
         <v>118.69</v>
       </c>
@@ -42891,7 +42749,6 @@
           <t>顺昌县</t>
         </is>
       </c>
-      <c r="E403" t="inlineStr"/>
       <c r="F403" t="n">
         <v>117.81</v>
       </c>
@@ -42930,7 +42787,6 @@
           <t>浦江县</t>
         </is>
       </c>
-      <c r="E404" t="inlineStr"/>
       <c r="F404" t="n">
         <v>119.89</v>
       </c>
@@ -42969,7 +42825,6 @@
           <t>玉环市</t>
         </is>
       </c>
-      <c r="E405" t="inlineStr"/>
       <c r="F405" t="n">
         <v>121.23</v>
       </c>
@@ -43008,7 +42863,6 @@
           <t>孟连傣族拉祜族佤族自治县</t>
         </is>
       </c>
-      <c r="E406" t="inlineStr"/>
       <c r="F406" t="n">
         <v>99.58</v>
       </c>
@@ -43047,7 +42901,6 @@
           <t>华宁县</t>
         </is>
       </c>
-      <c r="E407" t="inlineStr"/>
       <c r="F407" t="n">
         <v>102.93</v>
       </c>
@@ -43086,7 +42939,6 @@
           <t>高昌区</t>
         </is>
       </c>
-      <c r="E408" t="inlineStr"/>
       <c r="F408" t="n">
         <v>89.19</v>
       </c>
@@ -43125,7 +42977,6 @@
           <t>伊州区</t>
         </is>
       </c>
-      <c r="E409" t="inlineStr"/>
       <c r="F409" t="n">
         <v>93.51000000000001</v>
       </c>
@@ -43164,7 +43015,6 @@
           <t>伽师县</t>
         </is>
       </c>
-      <c r="E410" t="inlineStr"/>
       <c r="F410" t="n">
         <v>76.73</v>
       </c>
@@ -43203,7 +43053,6 @@
           <t>徐闻县</t>
         </is>
       </c>
-      <c r="E411" t="inlineStr"/>
       <c r="F411" t="n">
         <v>110.17</v>
       </c>
@@ -43242,7 +43091,6 @@
           <t>福山镇</t>
         </is>
       </c>
-      <c r="E412" t="inlineStr"/>
       <c r="F412" t="n">
         <v>109.93</v>
       </c>
@@ -43281,7 +43129,6 @@
           <t>元江哈尼族彝族傣族自治县</t>
         </is>
       </c>
-      <c r="E413" t="inlineStr"/>
       <c r="F413" t="n">
         <v>101.999658</v>
       </c>
@@ -43320,7 +43167,6 @@
           <t>新宁县</t>
         </is>
       </c>
-      <c r="E414" t="inlineStr"/>
       <c r="F414" t="n">
         <v>110.859115</v>
       </c>
@@ -43359,7 +43205,6 @@
           <t>吴中区</t>
         </is>
       </c>
-      <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
         <v>120.63</v>
       </c>
@@ -43398,7 +43243,6 @@
           <t>宾川县</t>
         </is>
       </c>
-      <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
         <v>100.58</v>
       </c>
@@ -43437,7 +43281,6 @@
           <t>荔城区</t>
         </is>
       </c>
-      <c r="E417" t="inlineStr"/>
       <c r="F417" t="n">
         <v>119.020047</v>
       </c>
@@ -43476,7 +43319,6 @@
           <t>敖汉旗</t>
         </is>
       </c>
-      <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
         <v>119.92</v>
       </c>
@@ -43515,7 +43357,6 @@
           <t>扎兰屯市</t>
         </is>
       </c>
-      <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
         <v>122.74</v>
       </c>
@@ -43554,7 +43395,6 @@
           <t>攀枝花市</t>
         </is>
       </c>
-      <c r="E420" t="inlineStr"/>
       <c r="F420" t="n">
         <v>101.72</v>
       </c>
@@ -44066,7 +43906,6 @@
           <t>阿克苏市</t>
         </is>
       </c>
-      <c r="E432" t="inlineStr"/>
       <c r="F432" t="n">
         <v>80.26000000000001</v>
       </c>
@@ -44105,7 +43944,6 @@
           <t>新罗区</t>
         </is>
       </c>
-      <c r="E433" t="inlineStr"/>
       <c r="F433" t="n">
         <v>117.02</v>
       </c>
@@ -44144,7 +43982,6 @@
           <t>源城区</t>
         </is>
       </c>
-      <c r="E434" t="inlineStr"/>
       <c r="F434" t="n">
         <v>114.7</v>
       </c>
@@ -44183,7 +44020,6 @@
           <t>都匀市</t>
         </is>
       </c>
-      <c r="E435" t="inlineStr"/>
       <c r="F435" t="n">
         <v>107.52</v>
       </c>
@@ -44222,7 +44058,6 @@
           <t>莎车县</t>
         </is>
       </c>
-      <c r="E436" t="inlineStr"/>
       <c r="F436" t="n">
         <v>76.97595</v>
       </c>
@@ -44261,7 +44096,6 @@
           <t>库车市</t>
         </is>
       </c>
-      <c r="E437" t="inlineStr"/>
       <c r="F437" t="n">
         <v>82.97</v>
       </c>
@@ -44386,7 +44220,6 @@
           <t>波莲镇</t>
         </is>
       </c>
-      <c r="E440" t="inlineStr"/>
       <c r="F440" t="n">
         <v>109.7</v>
       </c>
@@ -44399,6 +44232,259 @@
         </is>
       </c>
       <c r="I440" t="inlineStr">
+        <is>
+          <t>核心产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>370285105</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>青岛市</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>莱西市</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>日庄镇</t>
+        </is>
+      </c>
+      <c r="F441" t="n">
+        <v>120.376</v>
+      </c>
+      <c r="G441" t="n">
+        <v>36.949</v>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>F499</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>核心产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>371083110</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>威海市</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>乳山市</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>崖子镇</t>
+        </is>
+      </c>
+      <c r="F442" t="n">
+        <v>121.303</v>
+      </c>
+      <c r="G442" t="n">
+        <v>37.08</v>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>F500</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>核心产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>130529000</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>河北省</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>邢台市</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>巨鹿县</t>
+        </is>
+      </c>
+      <c r="F443" t="n">
+        <v>115.031</v>
+      </c>
+      <c r="G443" t="n">
+        <v>37.221</v>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>F501</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>核心产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>130181204</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>河北省</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>石家庄市</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>辛集市</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>田家庄乡</t>
+        </is>
+      </c>
+      <c r="F444" t="n">
+        <v>115.19</v>
+      </c>
+      <c r="G444" t="n">
+        <v>37.881</v>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>F502</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>核心产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>411423203</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>河南省</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>商丘市</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>宁陵县</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>刘楼乡</t>
+        </is>
+      </c>
+      <c r="F445" t="n">
+        <v>115.251</v>
+      </c>
+      <c r="G445" t="n">
+        <v>34.376</v>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>F503</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>核心产区</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>411421204</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>河南省</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>商丘市</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>民权县</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>野岗镇</t>
+        </is>
+      </c>
+      <c r="F446" t="n">
+        <v>115.053</v>
+      </c>
+      <c r="G446" t="n">
+        <v>34.69</v>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>F504</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
         <is>
           <t>核心产区</t>
         </is>

--- a/fruit_data.xlsx
+++ b/fruit_data.xlsx
@@ -4561,7 +4561,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>新疆哈密瓜</t>
+          <t>哈密瓜</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>海南金钻凤梨</t>
+          <t>金钻凤梨</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5478,13 +5478,13 @@
         <v>2</v>
       </c>
       <c r="I85" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J85" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="K85" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -7980,16 +7980,16 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I130" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J130" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K130" t="n">
-        <v>10</v>
+        <v>2.9</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -9556,13 +9556,13 @@
         <v>6</v>
       </c>
       <c r="I157" t="n">
-        <v>11</v>
+        <v>12.9</v>
       </c>
       <c r="J157" t="n">
         <v>7</v>
       </c>
       <c r="K157" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -30465,12 +30465,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
+          <t>省直辖</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
           <t>琼海市</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>嘉积镇</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -32914,12 +32914,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>澄迈县</t>
+          <t>乐东黎族自治县</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>澄迈县</t>
+          <t>乐东县</t>
         </is>
       </c>
       <c r="F154" t="n">
